--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G24" t="n">

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G28" t="n">

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,16 +2727,16 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.3</v>
+        <v>3.5</v>
       </c>
       <c r="M20" t="n">
-        <v>5.7</v>
+        <v>3.75</v>
       </c>
       <c r="N20" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,16 +2846,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G25" t="n">

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="M16" t="n">
-        <v>5.5</v>
+        <v>3.2</v>
       </c>
       <c r="N16" t="n">
-        <v>12</v>
+        <v>2.3</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,16 +2608,16 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.3</v>
+        <v>3.5</v>
       </c>
       <c r="M19" t="n">
-        <v>5.7</v>
+        <v>3.75</v>
       </c>
       <c r="N19" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,16 +2727,16 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G24" t="n">

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.3</v>
+        <v>3.5</v>
       </c>
       <c r="M18" t="n">
-        <v>5.7</v>
+        <v>3.75</v>
       </c>
       <c r="N18" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,16 +2608,16 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.5</v>
+        <v>1.3</v>
       </c>
       <c r="M19" t="n">
-        <v>3.75</v>
+        <v>5.7</v>
       </c>
       <c r="N19" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,16 +2727,16 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G25" t="n">

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="M5" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="N5" t="n">
-        <v>6.3</v>
+        <v>2.2</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,7 +1061,7 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AB5" t="n">
         <v>1.75</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="M13" t="n">
-        <v>5.5</v>
+        <v>3.2</v>
       </c>
       <c r="N13" t="n">
-        <v>12</v>
+        <v>2.3</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.5</v>
+        <v>1.3</v>
       </c>
       <c r="M18" t="n">
-        <v>3.75</v>
+        <v>5.7</v>
       </c>
       <c r="N18" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,16 +2608,16 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.3</v>
+        <v>3.5</v>
       </c>
       <c r="M19" t="n">
-        <v>5.7</v>
+        <v>3.75</v>
       </c>
       <c r="N19" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,16 +2727,16 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G25" t="n">

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="M12" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="N12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.3</v>
+        <v>1.65</v>
       </c>
       <c r="M18" t="n">
-        <v>5.7</v>
+        <v>3.75</v>
       </c>
       <c r="N18" t="n">
-        <v>9</v>
+        <v>4.8</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,16 +2608,16 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.65</v>
+        <v>1.3</v>
       </c>
       <c r="M20" t="n">
-        <v>3.75</v>
+        <v>5.7</v>
       </c>
       <c r="N20" t="n">
-        <v>4.8</v>
+        <v>9</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,16 +2846,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.8</v>
+        <v>2.75</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G25" t="n">

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.1</v>
+        <v>1.61</v>
       </c>
       <c r="M5" t="n">
-        <v>3.25</v>
+        <v>3.41</v>
       </c>
       <c r="N5" t="n">
-        <v>2.2</v>
+        <v>4.8</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,7 +1061,7 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AB5" t="n">
         <v>1.75</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="M7" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="N7" t="n">
-        <v>6.3</v>
+        <v>2.2</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,7 +1299,7 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AB7" t="n">
         <v>1.75</v>
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>8</v>
+        <v>1.25</v>
       </c>
       <c r="M14" t="n">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="N14" t="n">
-        <v>1.4</v>
+        <v>14</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="AB14" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="M19" t="n">
-        <v>3.75</v>
+        <v>3.39</v>
       </c>
       <c r="N19" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="M26" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="N26" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G28" t="n">

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.41</v>
+        <v>2</v>
       </c>
       <c r="M8" t="n">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="N8" t="n">
-        <v>2.6</v>
+        <v>3.88</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>2.36</v>
       </c>
       <c r="M9" t="n">
-        <v>3.38</v>
+        <v>3.65</v>
       </c>
       <c r="N9" t="n">
-        <v>3.88</v>
+        <v>2.37</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,16 +1537,16 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,55 +2563,55 @@
         </is>
       </c>
       <c r="L18" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
         <v>1.65</v>
       </c>
-      <c r="M18" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N18" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AB18" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.05</v>
+        <v>1.65</v>
       </c>
       <c r="M19" t="n">
-        <v>3.39</v>
+        <v>3.75</v>
       </c>
       <c r="N19" t="n">
-        <v>2.01</v>
+        <v>4.8</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="M20" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="N20" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2852,10 +2852,10 @@
         <v>2.75</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G24" t="n">

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.05</v>
+        <v>1.65</v>
       </c>
       <c r="M18" t="n">
-        <v>3.39</v>
+        <v>3.75</v>
       </c>
       <c r="N18" t="n">
-        <v>2.01</v>
+        <v>4.8</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,55 +2682,55 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
         <v>1.65</v>
       </c>
-      <c r="M19" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AB19" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G25" t="n">

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI30"/>
+  <dimension ref="A1:AI29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>2.36</v>
       </c>
       <c r="M8" t="n">
-        <v>3.38</v>
+        <v>3.65</v>
       </c>
       <c r="N8" t="n">
-        <v>3.88</v>
+        <v>2.37</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,16 +1418,16 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.36</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>3.65</v>
+        <v>3.38</v>
       </c>
       <c r="N9" t="n">
-        <v>2.37</v>
+        <v>3.88</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,16 +1537,16 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>8</v>
+        <v>1.25</v>
       </c>
       <c r="M14" t="n">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="N14" t="n">
-        <v>1.4</v>
+        <v>14</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="AB14" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3942,125 +3942,6 @@
       </c>
       <c r="AI29" s="3" t="n">
         <v>45992.71875</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
-        <v>45992</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Chile Primera División</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Universidad Chile</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Coquimbo Unido</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI30" s="3" t="n">
-        <v>45992.83333333334</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.25</v>
+        <v>2.79</v>
       </c>
       <c r="M14" t="n">
-        <v>5.8</v>
+        <v>3.23</v>
       </c>
       <c r="N14" t="n">
-        <v>14</v>
+        <v>2.21</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.63</v>
+        <v>2.08</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.65</v>
+        <v>1.21</v>
       </c>
       <c r="M18" t="n">
-        <v>3.75</v>
+        <v>5.6</v>
       </c>
       <c r="N18" t="n">
-        <v>4.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,16 +2608,16 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.8</v>
+        <v>2.75</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.05</v>
+        <v>1.65</v>
       </c>
       <c r="M19" t="n">
-        <v>3.39</v>
+        <v>3.75</v>
       </c>
       <c r="N19" t="n">
-        <v>2.01</v>
+        <v>4.8</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.21</v>
+        <v>3.05</v>
       </c>
       <c r="M20" t="n">
-        <v>5.6</v>
+        <v>3.39</v>
       </c>
       <c r="N20" t="n">
-        <v>8.800000000000001</v>
+        <v>2.01</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,16 +2846,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G25" t="n">

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.1</v>
+        <v>1.61</v>
       </c>
       <c r="M6" t="n">
-        <v>3.25</v>
+        <v>3.41</v>
       </c>
       <c r="N6" t="n">
-        <v>2.2</v>
+        <v>4.8</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,7 +1180,7 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AB6" t="n">
         <v>1.75</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.79</v>
+        <v>1.25</v>
       </c>
       <c r="M14" t="n">
-        <v>3.23</v>
+        <v>5.8</v>
       </c>
       <c r="N14" t="n">
-        <v>2.21</v>
+        <v>14</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.08</v>
+        <v>1.63</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.21</v>
+        <v>3.05</v>
       </c>
       <c r="M18" t="n">
-        <v>5.6</v>
+        <v>3.39</v>
       </c>
       <c r="N18" t="n">
-        <v>8.800000000000001</v>
+        <v>2.01</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,16 +2608,16 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.05</v>
+        <v>1.21</v>
       </c>
       <c r="M20" t="n">
-        <v>3.39</v>
+        <v>5.6</v>
       </c>
       <c r="N20" t="n">
-        <v>2.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,16 +2846,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G28" t="n">

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.36</v>
+        <v>2</v>
       </c>
       <c r="M8" t="n">
-        <v>3.65</v>
+        <v>3.38</v>
       </c>
       <c r="N8" t="n">
-        <v>2.37</v>
+        <v>3.88</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,16 +1418,16 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>2.36</v>
       </c>
       <c r="M9" t="n">
-        <v>3.38</v>
+        <v>3.65</v>
       </c>
       <c r="N9" t="n">
-        <v>3.88</v>
+        <v>2.37</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,16 +1537,16 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>8</v>
+        <v>2.79</v>
       </c>
       <c r="M12" t="n">
-        <v>4.6</v>
+        <v>3.23</v>
       </c>
       <c r="N12" t="n">
-        <v>1.4</v>
+        <v>2.21</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.8</v>
+        <v>2.08</v>
       </c>
       <c r="AB12" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.05</v>
+        <v>1.21</v>
       </c>
       <c r="M18" t="n">
-        <v>3.39</v>
+        <v>5.6</v>
       </c>
       <c r="N18" t="n">
-        <v>2.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,16 +2608,16 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,55 +2682,55 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
         <v>1.65</v>
       </c>
-      <c r="M19" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AB19" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.21</v>
+        <v>1.65</v>
       </c>
       <c r="M20" t="n">
-        <v>5.6</v>
+        <v>3.75</v>
       </c>
       <c r="N20" t="n">
-        <v>8.800000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,16 +2846,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.61</v>
+        <v>3.1</v>
       </c>
       <c r="M6" t="n">
-        <v>3.41</v>
+        <v>3.25</v>
       </c>
       <c r="N6" t="n">
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,7 +1180,7 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AB6" t="n">
         <v>1.75</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.1</v>
+        <v>1.61</v>
       </c>
       <c r="M7" t="n">
-        <v>3.25</v>
+        <v>3.41</v>
       </c>
       <c r="N7" t="n">
-        <v>2.2</v>
+        <v>4.8</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,7 +1299,7 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AB7" t="n">
         <v>1.75</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>2.36</v>
       </c>
       <c r="M8" t="n">
-        <v>3.38</v>
+        <v>3.65</v>
       </c>
       <c r="N8" t="n">
-        <v>3.88</v>
+        <v>2.37</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,16 +1418,16 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.36</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>3.65</v>
+        <v>3.38</v>
       </c>
       <c r="N9" t="n">
-        <v>2.37</v>
+        <v>3.88</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,16 +1537,16 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.05</v>
+        <v>1.65</v>
       </c>
       <c r="M19" t="n">
-        <v>3.39</v>
+        <v>3.75</v>
       </c>
       <c r="N19" t="n">
-        <v>2.01</v>
+        <v>4.8</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,55 +2801,55 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
         <v>1.65</v>
       </c>
-      <c r="M20" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N20" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AB20" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.36</v>
+        <v>2</v>
       </c>
       <c r="M8" t="n">
-        <v>3.65</v>
+        <v>3.38</v>
       </c>
       <c r="N8" t="n">
-        <v>2.37</v>
+        <v>3.88</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,16 +1418,16 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>2.36</v>
       </c>
       <c r="M9" t="n">
-        <v>3.38</v>
+        <v>3.65</v>
       </c>
       <c r="N9" t="n">
-        <v>3.88</v>
+        <v>2.37</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,16 +1537,16 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.25</v>
+        <v>8</v>
       </c>
       <c r="M13" t="n">
-        <v>5.8</v>
+        <v>4.6</v>
       </c>
       <c r="N13" t="n">
-        <v>14</v>
+        <v>1.4</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G25" t="n">

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.1</v>
+        <v>1.61</v>
       </c>
       <c r="M6" t="n">
-        <v>3.25</v>
+        <v>3.41</v>
       </c>
       <c r="N6" t="n">
-        <v>2.2</v>
+        <v>4.8</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,7 +1180,7 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AB6" t="n">
         <v>1.75</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>2.36</v>
       </c>
       <c r="M8" t="n">
-        <v>3.38</v>
+        <v>3.65</v>
       </c>
       <c r="N8" t="n">
-        <v>3.88</v>
+        <v>2.37</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,16 +1418,16 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.36</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>3.65</v>
+        <v>3.38</v>
       </c>
       <c r="N9" t="n">
-        <v>2.37</v>
+        <v>3.88</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,16 +1537,16 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.79</v>
+        <v>1.25</v>
       </c>
       <c r="M16" t="n">
-        <v>3.23</v>
+        <v>5.8</v>
       </c>
       <c r="N16" t="n">
-        <v>2.21</v>
+        <v>14</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.08</v>
+        <v>1.63</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.21</v>
+        <v>3.05</v>
       </c>
       <c r="M18" t="n">
-        <v>5.6</v>
+        <v>3.39</v>
       </c>
       <c r="N18" t="n">
-        <v>8.800000000000001</v>
+        <v>2.01</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,16 +2608,16 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.65</v>
+        <v>1.21</v>
       </c>
       <c r="M19" t="n">
-        <v>3.75</v>
+        <v>5.6</v>
       </c>
       <c r="N19" t="n">
-        <v>4.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,16 +2727,16 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.8</v>
+        <v>2.75</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.05</v>
+        <v>1.65</v>
       </c>
       <c r="M20" t="n">
-        <v>3.39</v>
+        <v>3.75</v>
       </c>
       <c r="N20" t="n">
-        <v>2.01</v>
+        <v>4.8</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.1</v>
+        <v>1.61</v>
       </c>
       <c r="M5" t="n">
-        <v>3.25</v>
+        <v>3.41</v>
       </c>
       <c r="N5" t="n">
-        <v>2.2</v>
+        <v>4.8</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.61</v>
+        <v>3.1</v>
       </c>
       <c r="M6" t="n">
-        <v>3.41</v>
+        <v>3.25</v>
       </c>
       <c r="N6" t="n">
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,7 +1180,7 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AB6" t="n">
         <v>1.75</v>
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="M9" t="n">
-        <v>3.38</v>
+        <v>3.65</v>
       </c>
       <c r="N9" t="n">
-        <v>3.88</v>
+        <v>4.9</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.31</v>
+        <v>1.97</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>8</v>
+        <v>1.25</v>
       </c>
       <c r="M17" t="n">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="N17" t="n">
-        <v>1.4</v>
+        <v>14</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="AB17" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.05</v>
+        <v>1.65</v>
       </c>
       <c r="M18" t="n">
-        <v>3.39</v>
+        <v>3.75</v>
       </c>
       <c r="N18" t="n">
-        <v>2.01</v>
+        <v>4.8</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.21</v>
+        <v>3.05</v>
       </c>
       <c r="M19" t="n">
-        <v>5.6</v>
+        <v>3.39</v>
       </c>
       <c r="N19" t="n">
-        <v>8.800000000000001</v>
+        <v>2.01</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,16 +2727,16 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.65</v>
+        <v>1.21</v>
       </c>
       <c r="M20" t="n">
-        <v>3.75</v>
+        <v>5.6</v>
       </c>
       <c r="N20" t="n">
-        <v>4.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,16 +2846,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.8</v>
+        <v>2.75</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.61</v>
+        <v>3.1</v>
       </c>
       <c r="M5" t="n">
-        <v>3.41</v>
+        <v>3.25</v>
       </c>
       <c r="N5" t="n">
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.36</v>
+        <v>1.65</v>
       </c>
       <c r="M8" t="n">
         <v>3.65</v>
       </c>
       <c r="N8" t="n">
-        <v>2.37</v>
+        <v>4.9</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,16 +1418,16 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.65</v>
+        <v>2.36</v>
       </c>
       <c r="M9" t="n">
         <v>3.65</v>
       </c>
       <c r="N9" t="n">
-        <v>4.9</v>
+        <v>2.37</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,16 +1537,16 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>8</v>
+        <v>1.25</v>
       </c>
       <c r="M12" t="n">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="N12" t="n">
-        <v>1.4</v>
+        <v>14</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="AB12" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,55 +2563,55 @@
         </is>
       </c>
       <c r="L18" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
         <v>1.65</v>
       </c>
-      <c r="M18" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N18" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AB18" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.05</v>
+        <v>1.65</v>
       </c>
       <c r="M19" t="n">
-        <v>3.39</v>
+        <v>3.75</v>
       </c>
       <c r="N19" t="n">
-        <v>2.01</v>
+        <v>4.8</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.7</v>
+        <v>1.97</v>
       </c>
       <c r="M23" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="N23" t="n">
-        <v>2.44</v>
+        <v>3.75</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3280,10 +3280,10 @@
         <v>2.7</v>
       </c>
       <c r="M24" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="N24" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.97</v>
+        <v>2.7</v>
       </c>
       <c r="M25" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="N25" t="n">
-        <v>3.75</v>
+        <v>2.48</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.1</v>
+        <v>1.61</v>
       </c>
       <c r="M5" t="n">
-        <v>3.25</v>
+        <v>3.41</v>
       </c>
       <c r="N5" t="n">
-        <v>2.2</v>
+        <v>4.8</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.61</v>
+        <v>3.1</v>
       </c>
       <c r="M7" t="n">
-        <v>3.41</v>
+        <v>3.25</v>
       </c>
       <c r="N7" t="n">
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.65</v>
+        <v>2.36</v>
       </c>
       <c r="M8" t="n">
         <v>3.65</v>
       </c>
       <c r="N8" t="n">
-        <v>4.9</v>
+        <v>2.37</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,16 +1418,16 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.36</v>
+        <v>1.65</v>
       </c>
       <c r="M9" t="n">
         <v>3.65</v>
       </c>
       <c r="N9" t="n">
-        <v>2.37</v>
+        <v>4.9</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,16 +1537,16 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.05</v>
+        <v>1.21</v>
       </c>
       <c r="M18" t="n">
-        <v>3.39</v>
+        <v>5.6</v>
       </c>
       <c r="N18" t="n">
-        <v>2.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,16 +2608,16 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,55 +2682,55 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
         <v>1.65</v>
       </c>
-      <c r="M19" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AB19" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.21</v>
+        <v>1.65</v>
       </c>
       <c r="M20" t="n">
-        <v>5.6</v>
+        <v>3.75</v>
       </c>
       <c r="N20" t="n">
-        <v>8.800000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,16 +2846,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3280,10 +3280,10 @@
         <v>2.7</v>
       </c>
       <c r="M24" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="N24" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3399,10 +3399,10 @@
         <v>2.7</v>
       </c>
       <c r="M25" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="N25" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.25</v>
+        <v>2.79</v>
       </c>
       <c r="M12" t="n">
-        <v>5.8</v>
+        <v>3.23</v>
       </c>
       <c r="N12" t="n">
-        <v>14</v>
+        <v>2.21</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.63</v>
+        <v>1.93</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.25</v>
+        <v>1.77</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.25</v>
+        <v>2.79</v>
       </c>
       <c r="M13" t="n">
-        <v>5.8</v>
+        <v>3.23</v>
       </c>
       <c r="N13" t="n">
-        <v>14</v>
+        <v>2.21</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.63</v>
+        <v>1.93</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.25</v>
+        <v>1.77</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.97</v>
+        <v>3.6</v>
       </c>
       <c r="M23" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="N23" t="n">
-        <v>3.75</v>
+        <v>2.07</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.7</v>
+        <v>1.97</v>
       </c>
       <c r="M24" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="N24" t="n">
-        <v>2.48</v>
+        <v>3.75</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="M25" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N25" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3435,10 +3435,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.25</v>
+        <v>8</v>
       </c>
       <c r="M11" t="n">
-        <v>5.8</v>
+        <v>4.6</v>
       </c>
       <c r="N11" t="n">
-        <v>14</v>
+        <v>1.4</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.79</v>
+        <v>1.25</v>
       </c>
       <c r="M13" t="n">
-        <v>3.23</v>
+        <v>5.8</v>
       </c>
       <c r="N13" t="n">
-        <v>2.21</v>
+        <v>14</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.93</v>
+        <v>1.63</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.77</v>
+        <v>2.25</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>8</v>
+        <v>2.79</v>
       </c>
       <c r="M16" t="n">
-        <v>4.6</v>
+        <v>3.23</v>
       </c>
       <c r="N16" t="n">
-        <v>1.4</v>
+        <v>2.21</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AB16" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.21</v>
+        <v>1.65</v>
       </c>
       <c r="M18" t="n">
-        <v>5.6</v>
+        <v>3.75</v>
       </c>
       <c r="N18" t="n">
-        <v>8.800000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,16 +2608,16 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.65</v>
+        <v>1.21</v>
       </c>
       <c r="M20" t="n">
-        <v>3.75</v>
+        <v>5.6</v>
       </c>
       <c r="N20" t="n">
-        <v>4.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,16 +2846,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.8</v>
+        <v>2.75</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>8</v>
+        <v>1.25</v>
       </c>
       <c r="M11" t="n">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="N11" t="n">
-        <v>1.4</v>
+        <v>14</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="AB11" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.25</v>
+        <v>2.79</v>
       </c>
       <c r="M13" t="n">
-        <v>5.8</v>
+        <v>3.23</v>
       </c>
       <c r="N13" t="n">
-        <v>14</v>
+        <v>2.21</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.63</v>
+        <v>1.93</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.25</v>
+        <v>1.77</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.79</v>
+        <v>8</v>
       </c>
       <c r="M16" t="n">
-        <v>3.23</v>
+        <v>4.6</v>
       </c>
       <c r="N16" t="n">
-        <v>2.21</v>
+        <v>1.4</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.65</v>
+        <v>1.21</v>
       </c>
       <c r="M18" t="n">
-        <v>3.75</v>
+        <v>5.6</v>
       </c>
       <c r="N18" t="n">
-        <v>4.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,16 +2608,16 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.8</v>
+        <v>2.75</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.21</v>
+        <v>1.65</v>
       </c>
       <c r="M20" t="n">
-        <v>5.6</v>
+        <v>3.75</v>
       </c>
       <c r="N20" t="n">
-        <v>8.800000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,16 +2846,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.36</v>
+        <v>1.65</v>
       </c>
       <c r="M8" t="n">
         <v>3.65</v>
       </c>
       <c r="N8" t="n">
-        <v>2.37</v>
+        <v>4.9</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,16 +1418,16 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.65</v>
+        <v>2.36</v>
       </c>
       <c r="M9" t="n">
         <v>3.65</v>
       </c>
       <c r="N9" t="n">
-        <v>4.9</v>
+        <v>2.37</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,16 +1537,16 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.21</v>
+        <v>1.65</v>
       </c>
       <c r="M18" t="n">
-        <v>5.6</v>
+        <v>3.75</v>
       </c>
       <c r="N18" t="n">
-        <v>8.800000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,16 +2608,16 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.65</v>
+        <v>1.21</v>
       </c>
       <c r="M20" t="n">
-        <v>3.75</v>
+        <v>5.6</v>
       </c>
       <c r="N20" t="n">
-        <v>4.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,16 +2846,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.8</v>
+        <v>2.75</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.1</v>
+        <v>1.61</v>
       </c>
       <c r="M5" t="n">
-        <v>3.25</v>
+        <v>3.41</v>
       </c>
       <c r="N5" t="n">
-        <v>2.2</v>
+        <v>4.8</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.61</v>
+        <v>3.1</v>
       </c>
       <c r="M7" t="n">
-        <v>3.41</v>
+        <v>3.25</v>
       </c>
       <c r="N7" t="n">
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.65</v>
+        <v>2.36</v>
       </c>
       <c r="M8" t="n">
         <v>3.65</v>
       </c>
       <c r="N8" t="n">
-        <v>4.9</v>
+        <v>2.37</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,16 +1418,16 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.36</v>
+        <v>1.65</v>
       </c>
       <c r="M9" t="n">
         <v>3.65</v>
       </c>
       <c r="N9" t="n">
-        <v>2.37</v>
+        <v>4.9</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,16 +1537,16 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,55 +2563,55 @@
         </is>
       </c>
       <c r="L18" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
         <v>1.65</v>
       </c>
-      <c r="M18" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N18" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AB18" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.05</v>
+        <v>1.21</v>
       </c>
       <c r="M19" t="n">
-        <v>3.39</v>
+        <v>5.6</v>
       </c>
       <c r="N19" t="n">
-        <v>2.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,16 +2727,16 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.21</v>
+        <v>1.65</v>
       </c>
       <c r="M20" t="n">
-        <v>5.6</v>
+        <v>3.75</v>
       </c>
       <c r="N20" t="n">
-        <v>8.800000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,16 +2846,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.6</v>
+        <v>1.97</v>
       </c>
       <c r="M23" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="N23" t="n">
-        <v>2.07</v>
+        <v>3.75</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.97</v>
+        <v>3.6</v>
       </c>
       <c r="M24" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="N24" t="n">
-        <v>3.75</v>
+        <v>2.07</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.36</v>
+        <v>1.65</v>
       </c>
       <c r="M8" t="n">
         <v>3.65</v>
       </c>
       <c r="N8" t="n">
-        <v>2.37</v>
+        <v>4.9</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,16 +1418,16 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.65</v>
+        <v>2.36</v>
       </c>
       <c r="M9" t="n">
         <v>3.65</v>
       </c>
       <c r="N9" t="n">
-        <v>4.9</v>
+        <v>2.37</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,16 +1537,16 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.21</v>
+        <v>1.65</v>
       </c>
       <c r="M19" t="n">
-        <v>5.6</v>
+        <v>3.75</v>
       </c>
       <c r="N19" t="n">
-        <v>8.800000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,16 +2727,16 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.65</v>
+        <v>1.21</v>
       </c>
       <c r="M20" t="n">
-        <v>3.75</v>
+        <v>5.6</v>
       </c>
       <c r="N20" t="n">
-        <v>4.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,16 +2846,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.8</v>
+        <v>2.75</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="M24" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N24" t="n">
-        <v>2.07</v>
+        <v>2.4</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3316,16 +3316,16 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="M25" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N25" t="n">
-        <v>2.4</v>
+        <v>2.07</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3435,16 +3435,16 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
         <v>2.35</v>
       </c>
-      <c r="AA25" t="n">
-        <v>0</v>
-      </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.1</v>
+        <v>1.61</v>
       </c>
       <c r="M7" t="n">
-        <v>3.25</v>
+        <v>3.41</v>
       </c>
       <c r="N7" t="n">
-        <v>2.2</v>
+        <v>4.8</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.79</v>
+        <v>8</v>
       </c>
       <c r="M16" t="n">
-        <v>3.23</v>
+        <v>4.6</v>
       </c>
       <c r="N16" t="n">
-        <v>2.21</v>
+        <v>1.4</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.05</v>
+        <v>1.65</v>
       </c>
       <c r="M18" t="n">
-        <v>3.39</v>
+        <v>3.75</v>
       </c>
       <c r="N18" t="n">
-        <v>2.01</v>
+        <v>4.8</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.65</v>
+        <v>1.21</v>
       </c>
       <c r="M19" t="n">
-        <v>3.75</v>
+        <v>5.6</v>
       </c>
       <c r="N19" t="n">
-        <v>4.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,16 +2727,16 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.8</v>
+        <v>2.75</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.21</v>
+        <v>3.05</v>
       </c>
       <c r="M20" t="n">
-        <v>5.6</v>
+        <v>3.39</v>
       </c>
       <c r="N20" t="n">
-        <v>8.800000000000001</v>
+        <v>2.01</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,16 +2846,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.97</v>
+        <v>3.6</v>
       </c>
       <c r="M23" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="N23" t="n">
-        <v>3.75</v>
+        <v>2.07</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.6</v>
+        <v>1.97</v>
       </c>
       <c r="M25" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="N25" t="n">
-        <v>2.07</v>
+        <v>3.75</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.65</v>
+        <v>2.36</v>
       </c>
       <c r="M8" t="n">
         <v>3.65</v>
       </c>
       <c r="N8" t="n">
-        <v>4.9</v>
+        <v>2.37</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,16 +1418,16 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.36</v>
+        <v>1.65</v>
       </c>
       <c r="M9" t="n">
         <v>3.65</v>
       </c>
       <c r="N9" t="n">
-        <v>2.37</v>
+        <v>4.9</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,16 +1537,16 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.65</v>
+        <v>1.21</v>
       </c>
       <c r="M18" t="n">
-        <v>3.75</v>
+        <v>5.6</v>
       </c>
       <c r="N18" t="n">
-        <v>4.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,16 +2608,16 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.8</v>
+        <v>2.75</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.21</v>
+        <v>1.65</v>
       </c>
       <c r="M19" t="n">
-        <v>5.6</v>
+        <v>3.75</v>
       </c>
       <c r="N19" t="n">
-        <v>8.800000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,16 +2727,16 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="M23" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N23" t="n">
-        <v>2.07</v>
+        <v>2.4</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3197,16 +3197,16 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.8</v>
+        <v>1.97</v>
       </c>
       <c r="M24" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="N24" t="n">
-        <v>2.4</v>
+        <v>3.75</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3316,16 +3316,16 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.97</v>
+        <v>3.6</v>
       </c>
       <c r="M25" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="N25" t="n">
-        <v>3.75</v>
+        <v>2.07</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.36</v>
+        <v>1.65</v>
       </c>
       <c r="M8" t="n">
         <v>3.65</v>
       </c>
       <c r="N8" t="n">
-        <v>2.37</v>
+        <v>4.9</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,16 +1418,16 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.65</v>
+        <v>2.36</v>
       </c>
       <c r="M9" t="n">
         <v>3.65</v>
       </c>
       <c r="N9" t="n">
-        <v>4.9</v>
+        <v>2.37</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,16 +1537,16 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.21</v>
+        <v>3.05</v>
       </c>
       <c r="M18" t="n">
-        <v>5.6</v>
+        <v>3.39</v>
       </c>
       <c r="N18" t="n">
-        <v>8.800000000000001</v>
+        <v>2.01</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,16 +2608,16 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.05</v>
+        <v>1.21</v>
       </c>
       <c r="M20" t="n">
-        <v>3.39</v>
+        <v>5.6</v>
       </c>
       <c r="N20" t="n">
-        <v>2.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,16 +2846,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.8</v>
+        <v>1.97</v>
       </c>
       <c r="M23" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="N23" t="n">
-        <v>2.4</v>
+        <v>3.75</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3197,16 +3197,16 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.97</v>
+        <v>3.6</v>
       </c>
       <c r="M24" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="N24" t="n">
-        <v>3.75</v>
+        <v>2.07</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="M25" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N25" t="n">
-        <v>2.07</v>
+        <v>2.4</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3435,16 +3435,16 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.61</v>
+        <v>3.1</v>
       </c>
       <c r="M7" t="n">
-        <v>3.41</v>
+        <v>3.25</v>
       </c>
       <c r="N7" t="n">
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.65</v>
+        <v>2.36</v>
       </c>
       <c r="M8" t="n">
         <v>3.65</v>
       </c>
       <c r="N8" t="n">
-        <v>4.9</v>
+        <v>2.37</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,16 +1418,16 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.36</v>
+        <v>1.65</v>
       </c>
       <c r="M9" t="n">
         <v>3.65</v>
       </c>
       <c r="N9" t="n">
-        <v>2.37</v>
+        <v>4.9</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,16 +1537,16 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.05</v>
+        <v>1.65</v>
       </c>
       <c r="M18" t="n">
-        <v>3.39</v>
+        <v>3.75</v>
       </c>
       <c r="N18" t="n">
-        <v>2.01</v>
+        <v>4.8</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,55 +2682,55 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
         <v>1.65</v>
       </c>
-      <c r="M19" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AB19" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -936,10 +936,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.61</v>
+        <v>3.1</v>
       </c>
       <c r="M5" t="n">
-        <v>3.41</v>
+        <v>3.25</v>
       </c>
       <c r="N5" t="n">
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.25</v>
+        <v>8</v>
       </c>
       <c r="M16" t="n">
-        <v>5.8</v>
+        <v>4.6</v>
       </c>
       <c r="N16" t="n">
-        <v>14</v>
+        <v>1.4</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.05</v>
+        <v>1.21</v>
       </c>
       <c r="M19" t="n">
-        <v>3.39</v>
+        <v>5.6</v>
       </c>
       <c r="N19" t="n">
-        <v>2.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,16 +2727,16 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.21</v>
+        <v>3.05</v>
       </c>
       <c r="M20" t="n">
-        <v>5.6</v>
+        <v>3.39</v>
       </c>
       <c r="N20" t="n">
-        <v>8.800000000000001</v>
+        <v>2.01</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,16 +2846,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="M24" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N24" t="n">
-        <v>2.07</v>
+        <v>2.4</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3316,16 +3316,16 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="M25" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N25" t="n">
-        <v>2.4</v>
+        <v>2.07</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3435,16 +3435,16 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
         <v>2.35</v>
       </c>
-      <c r="AA25" t="n">
-        <v>0</v>
-      </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -1025,64 +1025,64 @@
         <v>2.2</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45992.45833333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.79</v>
+        <v>1.25</v>
       </c>
       <c r="M13" t="n">
-        <v>3.23</v>
+        <v>5.8</v>
       </c>
       <c r="N13" t="n">
-        <v>2.21</v>
+        <v>14</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>7.24</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.93</v>
+        <v>1.63</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.77</v>
+        <v>2.25</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.65</v>
+        <v>1.21</v>
       </c>
       <c r="M18" t="n">
-        <v>3.75</v>
+        <v>5.6</v>
       </c>
       <c r="N18" t="n">
-        <v>4.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,16 +2608,16 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.8</v>
+        <v>2.75</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.21</v>
+        <v>3.05</v>
       </c>
       <c r="M19" t="n">
-        <v>5.6</v>
+        <v>3.39</v>
       </c>
       <c r="N19" t="n">
-        <v>8.800000000000001</v>
+        <v>2.01</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,16 +2727,16 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.05</v>
+        <v>1.65</v>
       </c>
       <c r="M20" t="n">
-        <v>3.39</v>
+        <v>3.75</v>
       </c>
       <c r="N20" t="n">
-        <v>2.01</v>
+        <v>4.8</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="M24" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N24" t="n">
-        <v>2.4</v>
+        <v>2.07</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3316,16 +3316,16 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
         <v>2.35</v>
       </c>
-      <c r="AA24" t="n">
-        <v>0</v>
-      </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="M25" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N25" t="n">
-        <v>2.07</v>
+        <v>2.4</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3435,16 +3435,16 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="N5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>6</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="T5" t="n">
         <v>3.1</v>
       </c>
-      <c r="M5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="O5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.9</v>
-      </c>
       <c r="U5" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="V5" t="n">
-        <v>7.5</v>
+        <v>8.4</v>
       </c>
       <c r="W5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.97</v>
+        <v>2.14</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.47</v>
+        <v>3.78</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AF5" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.36</v>
+        <v>2.3</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45992.45833333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.61</v>
+        <v>3.1</v>
       </c>
       <c r="M7" t="n">
-        <v>3.41</v>
+        <v>3.25</v>
       </c>
       <c r="N7" t="n">
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45992.45833333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.36</v>
+        <v>1.65</v>
       </c>
       <c r="M8" t="n">
         <v>3.65</v>
       </c>
       <c r="N8" t="n">
-        <v>2.37</v>
+        <v>4.9</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.94</v>
+        <v>3.88</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.76</v>
+        <v>1.2</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45992.54166666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.65</v>
+        <v>2.36</v>
       </c>
       <c r="M9" t="n">
         <v>3.65</v>
       </c>
       <c r="N9" t="n">
-        <v>4.9</v>
+        <v>2.37</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.97</v>
+        <v>1.44</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.73</v>
+        <v>2.68</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45992.54166666666</v>
@@ -1620,34 +1620,34 @@
         <v>3.05</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y10" t="n">
         <v>1.58</v>
@@ -1656,28 +1656,28 @@
         <v>2.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45992.5625</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>7.24</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45992.58333333334</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45992.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.25</v>
+        <v>2.2</v>
       </c>
       <c r="M13" t="n">
-        <v>5.8</v>
+        <v>3.7</v>
       </c>
       <c r="N13" t="n">
-        <v>14</v>
+        <v>3.2</v>
       </c>
       <c r="O13" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V13" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH13" t="n">
         <v>1.62</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>7.24</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V13" t="n">
-        <v>5</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>3.8</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>8</v>
+        <v>6.25</v>
       </c>
       <c r="M14" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="N14" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="O14" t="n">
-        <v>8.6</v>
+        <v>6.5</v>
       </c>
       <c r="P14" t="n">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.73</v>
+        <v>1.89</v>
       </c>
       <c r="R14" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V14" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD14" t="n">
         <v>1.36</v>
       </c>
-      <c r="S14" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V14" t="n">
-        <v>6</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AE14" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.19</v>
+        <v>2.63</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,22 +2444,22 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.79</v>
+        <v>5.8</v>
       </c>
       <c r="M17" t="n">
-        <v>3.23</v>
+        <v>4.2</v>
       </c>
       <c r="N17" t="n">
-        <v>2.21</v>
+        <v>1.49</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2468,10 +2468,10 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -2483,34 +2483,34 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.93</v>
+        <v>1.64</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.77</v>
+        <v>2.08</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.21</v>
+        <v>3.05</v>
       </c>
       <c r="M18" t="n">
-        <v>5.6</v>
+        <v>3.39</v>
       </c>
       <c r="N18" t="n">
-        <v>8.800000000000001</v>
+        <v>2.01</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.91</v>
+        <v>2.7</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.79</v>
+        <v>1.39</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45992.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.05</v>
+        <v>1.65</v>
       </c>
       <c r="M19" t="n">
-        <v>3.39</v>
+        <v>3.75</v>
       </c>
       <c r="N19" t="n">
-        <v>2.01</v>
+        <v>4.8</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.65</v>
+        <v>1.21</v>
       </c>
       <c r="M20" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="N20" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>7</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AH20" t="n">
         <v>3.75</v>
-      </c>
-      <c r="N20" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45992.625</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.97</v>
+        <v>3.6</v>
       </c>
       <c r="M23" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="N23" t="n">
-        <v>3.75</v>
+        <v>2.07</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.6</v>
+        <v>1.97</v>
       </c>
       <c r="M24" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="N24" t="n">
-        <v>2.07</v>
+        <v>3.75</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -1272,16 +1272,16 @@
         <v>2.8</v>
       </c>
       <c r="R7" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="S7" t="n">
         <v>2.9</v>
       </c>
       <c r="T7" t="n">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="U7" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="V7" t="n">
         <v>7.5</v>
@@ -1293,16 +1293,16 @@
         <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z7" t="n">
         <v>3.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AC7" t="n">
         <v>3.47</v>
@@ -1314,10 +1314,10 @@
         <v>1.7</v>
       </c>
       <c r="AF7" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
         <v>1.36</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.65</v>
+        <v>2.36</v>
       </c>
       <c r="M8" t="n">
         <v>3.65</v>
       </c>
       <c r="N8" t="n">
-        <v>4.9</v>
+        <v>2.37</v>
       </c>
       <c r="O8" t="n">
-        <v>2.15</v>
+        <v>2.8</v>
       </c>
       <c r="P8" t="n">
-        <v>2.07</v>
+        <v>2.38</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.4</v>
+        <v>2.75</v>
       </c>
       <c r="R8" t="n">
-        <v>1.42</v>
+        <v>1.2</v>
       </c>
       <c r="S8" t="n">
-        <v>2.62</v>
+        <v>4</v>
       </c>
       <c r="T8" t="n">
-        <v>3.05</v>
+        <v>2.09</v>
       </c>
       <c r="U8" t="n">
-        <v>1.32</v>
+        <v>1.7</v>
       </c>
       <c r="V8" t="n">
-        <v>7.8</v>
+        <v>4.33</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="X8" t="n">
         <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.32</v>
+        <v>1.13</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.88</v>
+        <v>5.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.97</v>
+        <v>1.44</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.73</v>
+        <v>2.68</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.88</v>
+        <v>1.94</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.2</v>
+        <v>1.76</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.66</v>
+        <v>2.8</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.29</v>
+        <v>1.5</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45992.54166666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.36</v>
+        <v>1.65</v>
       </c>
       <c r="M9" t="n">
         <v>3.65</v>
       </c>
       <c r="N9" t="n">
-        <v>2.37</v>
+        <v>4.9</v>
       </c>
       <c r="O9" t="n">
-        <v>2.8</v>
+        <v>2.15</v>
       </c>
       <c r="P9" t="n">
-        <v>2.38</v>
+        <v>2.07</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.75</v>
+        <v>5.4</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2</v>
+        <v>1.42</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>2.62</v>
       </c>
       <c r="T9" t="n">
-        <v>2.09</v>
+        <v>3.05</v>
       </c>
       <c r="U9" t="n">
-        <v>1.7</v>
+        <v>1.32</v>
       </c>
       <c r="V9" t="n">
-        <v>4.33</v>
+        <v>7.8</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2</v>
+        <v>1.02</v>
       </c>
       <c r="X9" t="n">
         <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.13</v>
+        <v>1.32</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.5</v>
+        <v>2.88</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.44</v>
+        <v>1.97</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.68</v>
+        <v>1.73</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.94</v>
+        <v>3.88</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.76</v>
+        <v>1.2</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.8</v>
+        <v>1.66</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.5</v>
+        <v>2.29</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45992.54166666666</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.25</v>
+        <v>2.79</v>
       </c>
       <c r="M11" t="n">
-        <v>5.8</v>
+        <v>3.23</v>
       </c>
       <c r="N11" t="n">
-        <v>14</v>
+        <v>2.21</v>
       </c>
       <c r="O11" t="n">
-        <v>1.62</v>
+        <v>3.64</v>
       </c>
       <c r="P11" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>7.24</v>
+        <v>2.63</v>
       </c>
       <c r="R11" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="S11" t="n">
-        <v>3.7</v>
+        <v>2.77</v>
       </c>
       <c r="T11" t="n">
-        <v>2.25</v>
+        <v>2.73</v>
       </c>
       <c r="U11" t="n">
-        <v>1.57</v>
+        <v>1.39</v>
       </c>
       <c r="V11" t="n">
-        <v>5</v>
+        <v>6.45</v>
       </c>
       <c r="W11" t="n">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.63</v>
+        <v>1.93</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.25</v>
+        <v>1.77</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.4</v>
+        <v>3.08</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AE11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF11" t="n">
         <v>2.05</v>
       </c>
-      <c r="AF11" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AG11" t="n">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.8</v>
+        <v>1.34</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45992.58333333334</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="M12" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q12" t="n">
         <v>3.5</v>
       </c>
-      <c r="N12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O12" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>4.6</v>
-      </c>
       <c r="R12" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="S12" t="n">
-        <v>2.77</v>
+        <v>3.1</v>
       </c>
       <c r="T12" t="n">
-        <v>2.9</v>
+        <v>2.44</v>
       </c>
       <c r="U12" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="V12" t="n">
-        <v>7</v>
+        <v>5.4</v>
       </c>
       <c r="W12" t="n">
         <v>1.09</v>
       </c>
       <c r="X12" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG12" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AH12" t="n">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45992.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.2</v>
+        <v>1.25</v>
       </c>
       <c r="M13" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="N13" t="n">
+        <v>14</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S13" t="n">
         <v>3.7</v>
       </c>
-      <c r="N13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O13" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.1</v>
-      </c>
       <c r="T13" t="n">
-        <v>2.44</v>
+        <v>2.25</v>
       </c>
       <c r="U13" t="n">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="V13" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="X13" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.51</v>
+        <v>2.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.53</v>
+        <v>2.05</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.62</v>
+        <v>3.8</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>8</v>
+        <v>5.8</v>
       </c>
       <c r="M15" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="N15" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="O15" t="n">
-        <v>8.6</v>
+        <v>5.4</v>
       </c>
       <c r="P15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
         <v>2.23</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="U15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE15" t="n">
         <v>1.73</v>
       </c>
-      <c r="R15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V15" t="n">
-        <v>6</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AF15" t="n">
-        <v>1.62</v>
+        <v>1.88</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.79</v>
+        <v>1.85</v>
       </c>
       <c r="M16" t="n">
-        <v>3.23</v>
+        <v>3.5</v>
       </c>
       <c r="N16" t="n">
-        <v>2.21</v>
+        <v>4.3</v>
       </c>
       <c r="O16" t="n">
-        <v>3.64</v>
+        <v>2.35</v>
       </c>
       <c r="P16" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.63</v>
+        <v>4.6</v>
       </c>
       <c r="R16" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="S16" t="n">
         <v>2.77</v>
       </c>
       <c r="T16" t="n">
-        <v>2.73</v>
+        <v>2.9</v>
       </c>
       <c r="U16" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="V16" t="n">
-        <v>6.45</v>
+        <v>7</v>
       </c>
       <c r="W16" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y16" t="n">
         <v>1.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.08</v>
+        <v>3.18</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.34</v>
+        <v>1.91</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>5.8</v>
+        <v>8</v>
       </c>
       <c r="M17" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="N17" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="O17" t="n">
-        <v>5.4</v>
+        <v>8.6</v>
       </c>
       <c r="P17" t="n">
-        <v>2.5</v>
+        <v>2.23</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T17" t="n">
-        <v>2.23</v>
+        <v>2.66</v>
       </c>
       <c r="U17" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG17" t="n">
         <v>1.19</v>
       </c>
-      <c r="Z17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AH17" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.05</v>
+        <v>1.65</v>
       </c>
       <c r="M18" t="n">
-        <v>3.39</v>
+        <v>3.75</v>
       </c>
       <c r="N18" t="n">
-        <v>2.01</v>
+        <v>4.8</v>
       </c>
       <c r="O18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V18" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC18" t="n">
         <v>3.5</v>
       </c>
-      <c r="P18" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V18" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.7</v>
-      </c>
       <c r="AD18" t="n">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.56</v>
+        <v>1.85</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.24</v>
+        <v>1.81</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.29</v>
+        <v>2</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45992.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="O19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V19" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AA19" t="n">
         <v>1.65</v>
       </c>
-      <c r="M19" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AB19" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45992.625</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.6</v>
+        <v>1.97</v>
       </c>
       <c r="M23" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="N23" t="n">
-        <v>2.07</v>
+        <v>3.75</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.97</v>
+        <v>3.6</v>
       </c>
       <c r="M24" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="N24" t="n">
-        <v>3.75</v>
+        <v>2.07</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>2.35</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="M28" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="N28" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>5.22</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45992.70833333334</v>

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45992.45833333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45992.45833333334</v>
@@ -1501,13 +1501,13 @@
         <v>4.9</v>
       </c>
       <c r="O9" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="P9" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.4</v>
+        <v>6.35</v>
       </c>
       <c r="R9" t="n">
         <v>1.42</v>
@@ -1546,7 +1546,7 @@
         <v>3.88</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AE9" t="n">
         <v>2.1</v>
@@ -1555,10 +1555,10 @@
         <v>1.66</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45992.54166666666</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.79</v>
+        <v>2.2</v>
       </c>
       <c r="M11" t="n">
-        <v>3.23</v>
+        <v>3.7</v>
       </c>
       <c r="N11" t="n">
-        <v>2.21</v>
+        <v>3.2</v>
       </c>
       <c r="O11" t="n">
-        <v>3.64</v>
+        <v>2.74</v>
       </c>
       <c r="P11" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.63</v>
+        <v>3.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>2.77</v>
+        <v>3.1</v>
       </c>
       <c r="T11" t="n">
-        <v>2.73</v>
+        <v>2.44</v>
       </c>
       <c r="U11" t="n">
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
       <c r="V11" t="n">
-        <v>6.45</v>
+        <v>5.4</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG11" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AH11" t="n">
-        <v>1.34</v>
+        <v>1.62</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45992.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.2</v>
+        <v>6.25</v>
       </c>
       <c r="M12" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="N12" t="n">
-        <v>3.2</v>
+        <v>1.44</v>
       </c>
       <c r="O12" t="n">
-        <v>2.74</v>
+        <v>6.5</v>
       </c>
       <c r="P12" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.5</v>
+        <v>1.89</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S12" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="T12" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="U12" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="V12" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="W12" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X12" t="n">
         <v>1.04</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.2</v>
+        <v>3.78</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.51</v>
+        <v>2.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.3</v>
+        <v>2.63</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.62</v>
+        <v>1.08</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45992.58333333334</v>
@@ -1980,28 +1980,28 @@
         <v>1.62</v>
       </c>
       <c r="P13" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="Q13" t="n">
-        <v>7.24</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="R13" t="n">
         <v>1.28</v>
       </c>
       <c r="S13" t="n">
-        <v>3.7</v>
+        <v>3.28</v>
       </c>
       <c r="T13" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="U13" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="V13" t="n">
         <v>5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="X13" t="n">
         <v>1.03</v>
@@ -2010,7 +2010,7 @@
         <v>1.17</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="AA13" t="n">
         <v>1.63</v>
@@ -2022,19 +2022,19 @@
         <v>2.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,61 +2087,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>6.25</v>
+        <v>1.85</v>
       </c>
       <c r="M14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N14" t="n">
         <v>4.3</v>
       </c>
-      <c r="N14" t="n">
-        <v>1.44</v>
-      </c>
       <c r="O14" t="n">
-        <v>6.5</v>
+        <v>2.35</v>
       </c>
       <c r="P14" t="n">
-        <v>2.28</v>
+        <v>2.33</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.89</v>
+        <v>4.6</v>
       </c>
       <c r="R14" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>3.05</v>
+        <v>2.77</v>
       </c>
       <c r="T14" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="U14" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="V14" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="W14" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X14" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.78</v>
+        <v>3.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.74</v>
+        <v>1.98</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.06</v>
+        <v>1.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.8</v>
+        <v>3.18</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AE14" t="n">
         <v>1.85</v>
@@ -2150,10 +2150,10 @@
         <v>1.85</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.63</v>
+        <v>1.31</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.08</v>
+        <v>1.91</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5.8</v>
+        <v>2.79</v>
       </c>
       <c r="M15" t="n">
-        <v>4.2</v>
+        <v>3.23</v>
       </c>
       <c r="N15" t="n">
-        <v>1.49</v>
+        <v>2.21</v>
       </c>
       <c r="O15" t="n">
-        <v>5.4</v>
+        <v>3.64</v>
       </c>
       <c r="P15" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.91</v>
+        <v>2.63</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T15" t="n">
-        <v>2.23</v>
+        <v>2.73</v>
       </c>
       <c r="U15" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.64</v>
+        <v>1.93</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.08</v>
+        <v>1.77</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.63</v>
+        <v>3.08</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.88</v>
+        <v>2.05</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.08</v>
+        <v>1.34</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.85</v>
+        <v>5.8</v>
       </c>
       <c r="M16" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="N16" t="n">
-        <v>4.3</v>
+        <v>1.49</v>
       </c>
       <c r="O16" t="n">
-        <v>2.35</v>
+        <v>5.4</v>
       </c>
       <c r="P16" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.6</v>
+        <v>1.91</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.9</v>
+        <v>2.23</v>
       </c>
       <c r="U16" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.98</v>
+        <v>1.64</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.8</v>
+        <v>2.08</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.18</v>
+        <v>2.63</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.31</v>
+        <v>1.15</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.91</v>
+        <v>1.08</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2456,28 +2456,28 @@
         <v>8.6</v>
       </c>
       <c r="P17" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="Q17" t="n">
         <v>1.73</v>
       </c>
       <c r="R17" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S17" t="n">
-        <v>2.77</v>
+        <v>3.02</v>
       </c>
       <c r="T17" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="U17" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="V17" t="n">
         <v>6</v>
       </c>
       <c r="W17" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X17" t="n">
         <v>1.05</v>
@@ -2495,22 +2495,22 @@
         <v>2</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.65</v>
+        <v>1.21</v>
       </c>
       <c r="M18" t="n">
-        <v>3.75</v>
+        <v>5.6</v>
       </c>
       <c r="N18" t="n">
-        <v>4.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>2.38</v>
+        <v>1.58</v>
       </c>
       <c r="P18" t="n">
-        <v>2.04</v>
+        <v>2.81</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.16</v>
+        <v>7</v>
       </c>
       <c r="R18" t="n">
-        <v>1.41</v>
+        <v>1.19</v>
       </c>
       <c r="S18" t="n">
-        <v>2.8</v>
+        <v>3.92</v>
       </c>
       <c r="T18" t="n">
-        <v>2.9</v>
+        <v>1.94</v>
       </c>
       <c r="U18" t="n">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="V18" t="n">
-        <v>7.2</v>
+        <v>4.1</v>
       </c>
       <c r="W18" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.33</v>
+        <v>1.11</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.25</v>
+        <v>6</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.8</v>
+        <v>2.75</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.5</v>
+        <v>1.91</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.24</v>
+        <v>1.79</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.81</v>
+        <v>1.97</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.3</v>
+        <v>1.06</v>
       </c>
       <c r="AH18" t="n">
-        <v>2</v>
+        <v>3.75</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45992.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.05</v>
+        <v>1.65</v>
       </c>
       <c r="M19" t="n">
-        <v>3.39</v>
+        <v>3.75</v>
       </c>
       <c r="N19" t="n">
-        <v>2.01</v>
+        <v>4.8</v>
       </c>
       <c r="O19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC19" t="n">
         <v>3.5</v>
       </c>
-      <c r="P19" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V19" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.7</v>
-      </c>
       <c r="AD19" t="n">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.56</v>
+        <v>1.85</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.24</v>
+        <v>1.81</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.29</v>
+        <v>2</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45992.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.21</v>
+        <v>3.05</v>
       </c>
       <c r="M20" t="n">
-        <v>5.6</v>
+        <v>3.39</v>
       </c>
       <c r="N20" t="n">
-        <v>8.800000000000001</v>
+        <v>2.01</v>
       </c>
       <c r="O20" t="n">
-        <v>1.58</v>
+        <v>3.5</v>
       </c>
       <c r="P20" t="n">
-        <v>2.81</v>
+        <v>2.39</v>
       </c>
       <c r="Q20" t="n">
-        <v>7</v>
+        <v>2.65</v>
       </c>
       <c r="R20" t="n">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="S20" t="n">
-        <v>3.92</v>
+        <v>3.1</v>
       </c>
       <c r="T20" t="n">
-        <v>1.94</v>
+        <v>2.5</v>
       </c>
       <c r="U20" t="n">
-        <v>1.75</v>
+        <v>1.46</v>
       </c>
       <c r="V20" t="n">
-        <v>4.1</v>
+        <v>5.95</v>
       </c>
       <c r="W20" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="Z20" t="n">
-        <v>6</v>
+        <v>4.35</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.91</v>
+        <v>2.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.79</v>
+        <v>1.39</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.73</v>
+        <v>1.56</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.97</v>
+        <v>2.24</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.06</v>
+        <v>1.23</v>
       </c>
       <c r="AH20" t="n">
-        <v>3.75</v>
+        <v>1.29</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45992.625</v>
@@ -3167,40 +3167,40 @@
         <v>3.75</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA23" t="n">
         <v>2.2</v>
@@ -3209,22 +3209,22 @@
         <v>1.6</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45992.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="M24" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N24" t="n">
-        <v>2.07</v>
+        <v>2.4</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3316,16 +3316,16 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.35</v>
+        <v>2.62</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="M25" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N25" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="O25" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S25" t="n">
         <v>2.4</v>
       </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="Z25" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AA25" t="n">
         <v>2.35</v>
       </c>
-      <c r="AA25" t="n">
-        <v>2.62</v>
-      </c>
       <c r="AB25" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45992.6875</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>5.22</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>45992.70833333334</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>5.22</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45992.70833333334</v>
@@ -3881,40 +3881,40 @@
         <v>1.6</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA29" t="n">
         <v>1.63</v>
@@ -3923,22 +3923,22 @@
         <v>2.25</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>45992.71875</v>

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.61</v>
+        <v>3.1</v>
       </c>
       <c r="M6" t="n">
-        <v>3.72</v>
+        <v>3.25</v>
       </c>
       <c r="N6" t="n">
-        <v>5.4</v>
+        <v>2.2</v>
       </c>
       <c r="O6" t="n">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="P6" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="R6" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U6" t="n">
         <v>1.42</v>
       </c>
-      <c r="S6" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z6" t="n">
         <v>3.1</v>
       </c>
-      <c r="U6" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V6" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y6" t="n">
+      <c r="AA6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH6" t="n">
         <v>1.36</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>2.3</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45992.45833333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>6</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="T7" t="n">
         <v>3.1</v>
       </c>
-      <c r="M7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="O7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.65</v>
-      </c>
       <c r="U7" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="V7" t="n">
-        <v>7.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.47</v>
+        <v>3.74</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.95</v>
+        <v>1.64</v>
       </c>
       <c r="AG7" t="n">
         <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.36</v>
+        <v>2.3</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45992.45833333334</v>
@@ -1385,10 +1385,10 @@
         <v>2.8</v>
       </c>
       <c r="P8" t="n">
-        <v>2.38</v>
+        <v>2.57</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="R8" t="n">
         <v>1.2</v>
@@ -1397,10 +1397,10 @@
         <v>4</v>
       </c>
       <c r="T8" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="U8" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="V8" t="n">
         <v>4.33</v>
@@ -1412,16 +1412,16 @@
         <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.5</v>
+        <v>5.55</v>
       </c>
       <c r="AA8" t="n">
         <v>1.44</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="AC8" t="n">
         <v>1.94</v>
@@ -1620,16 +1620,16 @@
         <v>3.05</v>
       </c>
       <c r="O10" t="n">
-        <v>3.46</v>
+        <v>3.92</v>
       </c>
       <c r="P10" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.43</v>
+        <v>3.4</v>
       </c>
       <c r="R10" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="S10" t="n">
         <v>2.27</v>
@@ -1656,10 +1656,10 @@
         <v>2.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AC10" t="n">
         <v>5.3</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,61 +1849,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>6.25</v>
+        <v>1.85</v>
       </c>
       <c r="M12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N12" t="n">
         <v>4.3</v>
       </c>
-      <c r="N12" t="n">
-        <v>1.44</v>
-      </c>
       <c r="O12" t="n">
-        <v>6.5</v>
+        <v>2.35</v>
       </c>
       <c r="P12" t="n">
-        <v>2.28</v>
+        <v>2.33</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.89</v>
+        <v>4.6</v>
       </c>
       <c r="R12" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>3.05</v>
+        <v>2.77</v>
       </c>
       <c r="T12" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="U12" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="V12" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="W12" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X12" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.78</v>
+        <v>3.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.74</v>
+        <v>1.98</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.06</v>
+        <v>1.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.8</v>
+        <v>3.18</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AE12" t="n">
         <v>1.85</v>
@@ -1912,10 +1912,10 @@
         <v>1.85</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.63</v>
+        <v>1.31</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.08</v>
+        <v>1.91</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45992.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.25</v>
+        <v>6.25</v>
       </c>
       <c r="M13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="O13" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V13" t="n">
         <v>5.8</v>
       </c>
-      <c r="N13" t="n">
-        <v>14</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V13" t="n">
-        <v>5</v>
-      </c>
       <c r="W13" t="n">
-        <v>1.19</v>
+        <v>1.07</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.3</v>
+        <v>3.78</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.63</v>
+        <v>1.74</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.08</v>
+        <v>1.85</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.11</v>
+        <v>2.63</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.9</v>
+        <v>1.08</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.85</v>
+        <v>8</v>
       </c>
       <c r="M14" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="N14" t="n">
-        <v>4.3</v>
+        <v>1.4</v>
       </c>
       <c r="O14" t="n">
-        <v>2.35</v>
+        <v>8.6</v>
       </c>
       <c r="P14" t="n">
-        <v>2.33</v>
+        <v>2.24</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.6</v>
+        <v>1.73</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="S14" t="n">
-        <v>2.77</v>
+        <v>3.02</v>
       </c>
       <c r="T14" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W14" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X14" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.18</v>
+        <v>2.92</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.31</v>
+        <v>1.11</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.91</v>
+        <v>1.01</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.79</v>
+        <v>1.25</v>
       </c>
       <c r="M15" t="n">
-        <v>3.23</v>
+        <v>5.8</v>
       </c>
       <c r="N15" t="n">
-        <v>2.21</v>
+        <v>14</v>
       </c>
       <c r="O15" t="n">
-        <v>3.64</v>
+        <v>1.62</v>
       </c>
       <c r="P15" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.63</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="R15" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="S15" t="n">
-        <v>2.77</v>
+        <v>3.28</v>
       </c>
       <c r="T15" t="n">
-        <v>2.73</v>
+        <v>2.28</v>
       </c>
       <c r="U15" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="V15" t="n">
-        <v>6.45</v>
+        <v>5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.05</v>
+        <v>1.19</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.93</v>
+        <v>1.63</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.77</v>
+        <v>2.25</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.08</v>
+        <v>2.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.7</v>
+        <v>2.08</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.29</v>
+        <v>1.11</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.34</v>
+        <v>3.9</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>8</v>
+        <v>2.79</v>
       </c>
       <c r="M17" t="n">
-        <v>4.6</v>
+        <v>3.23</v>
       </c>
       <c r="N17" t="n">
-        <v>1.4</v>
+        <v>2.21</v>
       </c>
       <c r="O17" t="n">
-        <v>8.6</v>
+        <v>3.64</v>
       </c>
       <c r="P17" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.73</v>
+        <v>2.57</v>
       </c>
       <c r="R17" t="n">
         <v>1.35</v>
       </c>
       <c r="S17" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="T17" t="n">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="U17" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="V17" t="n">
-        <v>6</v>
+        <v>6.45</v>
       </c>
       <c r="W17" t="n">
         <v>1.1</v>
       </c>
       <c r="X17" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AB17" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.92</v>
+        <v>3.21</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.04</v>
+        <v>1.7</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.61</v>
+        <v>2.01</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.21</v>
+        <v>1.65</v>
       </c>
       <c r="M18" t="n">
-        <v>5.6</v>
+        <v>3.75</v>
       </c>
       <c r="N18" t="n">
-        <v>8.800000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="O18" t="n">
-        <v>1.58</v>
+        <v>2.38</v>
       </c>
       <c r="P18" t="n">
-        <v>2.81</v>
+        <v>2.04</v>
       </c>
       <c r="Q18" t="n">
-        <v>7</v>
+        <v>4.16</v>
       </c>
       <c r="R18" t="n">
-        <v>1.19</v>
+        <v>1.41</v>
       </c>
       <c r="S18" t="n">
-        <v>3.92</v>
+        <v>2.8</v>
       </c>
       <c r="T18" t="n">
-        <v>1.94</v>
+        <v>2.9</v>
       </c>
       <c r="U18" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="V18" t="n">
-        <v>4.1</v>
+        <v>7.2</v>
       </c>
       <c r="W18" t="n">
-        <v>1.18</v>
+        <v>1.03</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="Z18" t="n">
-        <v>6</v>
+        <v>3.25</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.91</v>
+        <v>3.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.79</v>
+        <v>1.24</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.97</v>
+        <v>1.81</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.06</v>
+        <v>1.3</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.75</v>
+        <v>2</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45992.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="O19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V19" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA19" t="n">
         <v>1.65</v>
       </c>
-      <c r="M19" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O19" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U19" t="n">
+      <c r="AB19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD19" t="n">
         <v>1.4</v>
       </c>
-      <c r="V19" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y19" t="n">
+      <c r="AE19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH19" t="n">
         <v>1.33</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>2</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45992.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.05</v>
+        <v>1.21</v>
       </c>
       <c r="M20" t="n">
-        <v>3.39</v>
+        <v>5.6</v>
       </c>
       <c r="N20" t="n">
-        <v>2.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>3.5</v>
+        <v>1.58</v>
       </c>
       <c r="P20" t="n">
-        <v>2.39</v>
+        <v>2.81</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.65</v>
+        <v>7</v>
       </c>
       <c r="R20" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="S20" t="n">
-        <v>3.1</v>
+        <v>3.92</v>
       </c>
       <c r="T20" t="n">
-        <v>2.5</v>
+        <v>1.94</v>
       </c>
       <c r="U20" t="n">
-        <v>1.46</v>
+        <v>1.75</v>
       </c>
       <c r="V20" t="n">
-        <v>5.95</v>
+        <v>4.1</v>
       </c>
       <c r="W20" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="X20" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.35</v>
+        <v>6</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.7</v>
+        <v>1.91</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.39</v>
+        <v>1.79</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.24</v>
+        <v>1.97</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.23</v>
+        <v>1.06</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.29</v>
+        <v>3.75</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45992.625</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.97</v>
+        <v>3.6</v>
       </c>
       <c r="M23" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="N23" t="n">
-        <v>3.75</v>
+        <v>2.07</v>
       </c>
       <c r="O23" t="n">
-        <v>2.65</v>
+        <v>4.9</v>
       </c>
       <c r="P23" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.25</v>
+        <v>2.62</v>
       </c>
       <c r="R23" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="S23" t="n">
-        <v>2.64</v>
+        <v>2.4</v>
       </c>
       <c r="T23" t="n">
-        <v>3.07</v>
+        <v>3.5</v>
       </c>
       <c r="U23" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="V23" t="n">
-        <v>7.8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W23" t="n">
         <v>1.02</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.88</v>
+        <v>2.42</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.58</v>
+        <v>4.85</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.84</v>
+        <v>2.13</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.83</v>
+        <v>1.61</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.22</v>
+        <v>1.72</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.66</v>
+        <v>1.16</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45992.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.8</v>
+        <v>1.97</v>
       </c>
       <c r="M24" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="N24" t="n">
-        <v>2.4</v>
+        <v>3.75</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.52</v>
+        <v>1.32</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.35</v>
+        <v>2.88</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45992.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="M25" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N25" t="n">
-        <v>2.07</v>
+        <v>2.4</v>
       </c>
       <c r="O25" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA25" t="n">
         <v>2.62</v>
       </c>
-      <c r="R25" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V25" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y25" t="n">
+      <c r="AB25" t="n">
         <v>1.44</v>
       </c>
-      <c r="Z25" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AC25" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45992.6875</v>
@@ -3524,40 +3524,40 @@
         <v>7.2</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AA26" t="n">
         <v>1.97</v>
@@ -3566,22 +3566,22 @@
         <v>1.83</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>45992.69791666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>5.22</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>45992.70833333334</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>5.22</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45992.70833333334</v>

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.1</v>
+        <v>1.61</v>
       </c>
       <c r="M6" t="n">
-        <v>3.25</v>
+        <v>3.41</v>
       </c>
       <c r="N6" t="n">
-        <v>2.2</v>
+        <v>4.8</v>
       </c>
       <c r="O6" t="n">
-        <v>3.5</v>
+        <v>2.17</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="R6" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="S6" t="n">
-        <v>2.9</v>
+        <v>2.56</v>
       </c>
       <c r="T6" t="n">
-        <v>2.65</v>
+        <v>3.15</v>
       </c>
       <c r="U6" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="V6" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.47</v>
+        <v>3.72</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.36</v>
+        <v>2.27</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45992.45833333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.61</v>
+        <v>3.1</v>
       </c>
       <c r="M7" t="n">
-        <v>3.41</v>
+        <v>3.25</v>
       </c>
       <c r="N7" t="n">
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="O7" t="n">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="P7" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="R7" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="S7" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="T7" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V7" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z7" t="n">
         <v>3.1</v>
       </c>
-      <c r="U7" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V7" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y7" t="n">
+      <c r="AA7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH7" t="n">
         <v>1.36</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>2.3</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45992.45833333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.36</v>
+        <v>1.65</v>
       </c>
       <c r="M8" t="n">
         <v>3.65</v>
       </c>
       <c r="N8" t="n">
-        <v>2.37</v>
+        <v>4.9</v>
       </c>
       <c r="O8" t="n">
-        <v>2.8</v>
+        <v>2.12</v>
       </c>
       <c r="P8" t="n">
-        <v>2.57</v>
+        <v>2.09</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.95</v>
+        <v>6.2</v>
       </c>
       <c r="R8" t="n">
-        <v>1.2</v>
+        <v>1.42</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>2.62</v>
       </c>
       <c r="T8" t="n">
-        <v>2.04</v>
+        <v>3.19</v>
       </c>
       <c r="U8" t="n">
-        <v>1.69</v>
+        <v>1.32</v>
       </c>
       <c r="V8" t="n">
-        <v>4.33</v>
+        <v>7.8</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
         <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.08</v>
+        <v>1.32</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.55</v>
+        <v>2.88</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.44</v>
+        <v>1.97</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.62</v>
+        <v>1.73</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.94</v>
+        <v>3.88</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.76</v>
+        <v>1.2</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.8</v>
+        <v>1.66</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.5</v>
+        <v>2.32</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45992.54166666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.65</v>
+        <v>2.36</v>
       </c>
       <c r="M9" t="n">
         <v>3.65</v>
       </c>
       <c r="N9" t="n">
-        <v>4.9</v>
+        <v>2.37</v>
       </c>
       <c r="O9" t="n">
-        <v>2.12</v>
+        <v>2.8</v>
       </c>
       <c r="P9" t="n">
-        <v>2.09</v>
+        <v>2.57</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.35</v>
+        <v>2.95</v>
       </c>
       <c r="R9" t="n">
-        <v>1.42</v>
+        <v>1.2</v>
       </c>
       <c r="S9" t="n">
-        <v>2.62</v>
+        <v>4</v>
       </c>
       <c r="T9" t="n">
-        <v>3.05</v>
+        <v>2.04</v>
       </c>
       <c r="U9" t="n">
-        <v>1.32</v>
+        <v>1.69</v>
       </c>
       <c r="V9" t="n">
-        <v>7.8</v>
+        <v>4.33</v>
       </c>
       <c r="W9" t="n">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="X9" t="n">
         <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.32</v>
+        <v>1.08</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.88</v>
+        <v>5.55</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.97</v>
+        <v>1.44</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.73</v>
+        <v>2.62</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.88</v>
+        <v>1.94</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.23</v>
+        <v>1.76</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.66</v>
+        <v>2.8</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.32</v>
+        <v>1.5</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45992.54166666666</v>
@@ -1656,10 +1656,10 @@
         <v>2.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AC10" t="n">
         <v>5.3</v>
@@ -1668,13 +1668,13 @@
         <v>1.09</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="AH10" t="n">
         <v>1.42</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="P11" t="n">
         <v>2.2</v>
       </c>
-      <c r="M11" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="N11" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O11" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.3</v>
-      </c>
       <c r="Q11" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V11" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z11" t="n">
         <v>3.5</v>
       </c>
-      <c r="R11" t="n">
+      <c r="AA11" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AD11" t="n">
         <v>1.3</v>
       </c>
-      <c r="S11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V11" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AE11" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.3</v>
+        <v>2.01</v>
       </c>
       <c r="AG11" t="n">
         <v>1.3</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.62</v>
+        <v>1.34</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45992.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.85</v>
+        <v>5.8</v>
       </c>
       <c r="M12" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="N12" t="n">
-        <v>4.3</v>
+        <v>1.49</v>
       </c>
       <c r="O12" t="n">
-        <v>2.35</v>
+        <v>5.4</v>
       </c>
       <c r="P12" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.6</v>
+        <v>1.91</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.9</v>
+        <v>2.23</v>
       </c>
       <c r="U12" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.98</v>
+        <v>1.64</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.8</v>
+        <v>2.08</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.18</v>
+        <v>2.63</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.31</v>
+        <v>1.15</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.91</v>
+        <v>1.08</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45992.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>6.25</v>
+        <v>2.2</v>
       </c>
       <c r="M13" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="N13" t="n">
-        <v>1.44</v>
+        <v>3.2</v>
       </c>
       <c r="O13" t="n">
-        <v>6.5</v>
+        <v>2.74</v>
       </c>
       <c r="P13" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.89</v>
+        <v>3.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S13" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T13" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="U13" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="V13" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="W13" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X13" t="n">
         <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.78</v>
+        <v>4.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.8</v>
+        <v>2.51</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.63</v>
+        <v>1.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.08</v>
+        <v>1.62</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>8</v>
+        <v>6.25</v>
       </c>
       <c r="M14" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="N14" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="O14" t="n">
-        <v>8.6</v>
+        <v>6.5</v>
       </c>
       <c r="P14" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.73</v>
+        <v>1.89</v>
       </c>
       <c r="R14" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="S14" t="n">
-        <v>3.02</v>
+        <v>3.05</v>
       </c>
       <c r="T14" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="U14" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="V14" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X14" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.34</v>
+        <v>3.78</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AB14" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.04</v>
+        <v>1.85</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.11</v>
+        <v>2.63</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>8</v>
+      </c>
+      <c r="M15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="O15" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V15" t="n">
+        <v>6</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y15" t="n">
         <v>1.25</v>
       </c>
-      <c r="M15" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="N15" t="n">
-        <v>14</v>
-      </c>
-      <c r="O15" t="n">
+      <c r="Z15" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF15" t="n">
         <v>1.62</v>
       </c>
-      <c r="P15" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V15" t="n">
-        <v>5</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AG15" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AH15" t="n">
-        <v>3.9</v>
+        <v>1.06</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>5.8</v>
+        <v>1.85</v>
       </c>
       <c r="M16" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="N16" t="n">
-        <v>1.49</v>
+        <v>4.3</v>
       </c>
       <c r="O16" t="n">
-        <v>5.4</v>
+        <v>2.35</v>
       </c>
       <c r="P16" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="Q16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V16" t="n">
+        <v>7</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH16" t="n">
         <v>1.91</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.08</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.79</v>
+        <v>1.25</v>
       </c>
       <c r="M17" t="n">
-        <v>3.23</v>
+        <v>5.8</v>
       </c>
       <c r="N17" t="n">
-        <v>2.21</v>
+        <v>14</v>
       </c>
       <c r="O17" t="n">
-        <v>3.64</v>
+        <v>1.62</v>
       </c>
       <c r="P17" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.57</v>
+        <v>9</v>
       </c>
       <c r="R17" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>3.28</v>
       </c>
       <c r="T17" t="n">
-        <v>2.73</v>
+        <v>2.29</v>
       </c>
       <c r="U17" t="n">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="V17" t="n">
-        <v>6.45</v>
+        <v>4.4</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.5</v>
+        <v>5.13</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.93</v>
+        <v>1.63</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.77</v>
+        <v>2.25</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.21</v>
+        <v>2.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AE17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF17" t="n">
         <v>1.7</v>
       </c>
-      <c r="AF17" t="n">
-        <v>2.01</v>
-      </c>
       <c r="AG17" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.34</v>
+        <v>3.9</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.65</v>
+        <v>1.21</v>
       </c>
       <c r="M18" t="n">
-        <v>3.75</v>
+        <v>5.6</v>
       </c>
       <c r="N18" t="n">
-        <v>4.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>2.38</v>
+        <v>1.67</v>
       </c>
       <c r="P18" t="n">
-        <v>2.04</v>
+        <v>2.75</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.16</v>
+        <v>7</v>
       </c>
       <c r="R18" t="n">
-        <v>1.41</v>
+        <v>1.18</v>
       </c>
       <c r="S18" t="n">
-        <v>2.8</v>
+        <v>3.92</v>
       </c>
       <c r="T18" t="n">
-        <v>2.9</v>
+        <v>2.02</v>
       </c>
       <c r="U18" t="n">
-        <v>1.4</v>
+        <v>1.74</v>
       </c>
       <c r="V18" t="n">
-        <v>7.2</v>
+        <v>4.4</v>
       </c>
       <c r="W18" t="n">
-        <v>1.03</v>
+        <v>1.21</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.25</v>
+        <v>6</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.8</v>
+        <v>2.75</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.5</v>
+        <v>1.91</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.24</v>
+        <v>1.79</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.81</v>
+        <v>2.1</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.3</v>
+        <v>1.08</v>
       </c>
       <c r="AH18" t="n">
-        <v>2</v>
+        <v>3.33</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45992.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.05</v>
+        <v>1.65</v>
       </c>
       <c r="M19" t="n">
-        <v>3.39</v>
+        <v>3.75</v>
       </c>
       <c r="N19" t="n">
-        <v>2.01</v>
+        <v>4.8</v>
       </c>
       <c r="O19" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V19" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC19" t="n">
         <v>3.5</v>
       </c>
-      <c r="P19" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V19" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.7</v>
-      </c>
       <c r="AD19" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.28</v>
+        <v>1.85</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.33</v>
+        <v>1.95</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45992.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V20" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y20" t="n">
         <v>1.21</v>
       </c>
-      <c r="M20" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="N20" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>7</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V20" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.11</v>
-      </c>
       <c r="Z20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AA20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD20" t="n">
         <v>1.4</v>
       </c>
-      <c r="AB20" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.79</v>
-      </c>
       <c r="AE20" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.97</v>
+        <v>2.3</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.06</v>
+        <v>1.3</v>
       </c>
       <c r="AH20" t="n">
-        <v>3.75</v>
+        <v>1.33</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45992.625</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="M23" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N23" t="n">
-        <v>2.07</v>
+        <v>2.4</v>
       </c>
       <c r="O23" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA23" t="n">
         <v>2.62</v>
       </c>
-      <c r="R23" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V23" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y23" t="n">
+      <c r="AB23" t="n">
         <v>1.44</v>
       </c>
-      <c r="Z23" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AC23" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45992.6875</v>
@@ -3292,19 +3292,19 @@
         <v>1.97</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.25</v>
+        <v>4.45</v>
       </c>
       <c r="R24" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S24" t="n">
-        <v>2.64</v>
+        <v>2.53</v>
       </c>
       <c r="T24" t="n">
-        <v>3.07</v>
+        <v>2.97</v>
       </c>
       <c r="U24" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="V24" t="n">
         <v>7.8</v>
@@ -3316,7 +3316,7 @@
         <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="Z24" t="n">
         <v>2.88</v>
@@ -3340,7 +3340,7 @@
         <v>1.83</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AH24" t="n">
         <v>1.66</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="M25" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N25" t="n">
-        <v>2.4</v>
+        <v>2.07</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="Z25" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AA25" t="n">
         <v>2.35</v>
       </c>
-      <c r="AA25" t="n">
-        <v>2.62</v>
-      </c>
       <c r="AB25" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45992.6875</v>
@@ -3527,22 +3527,22 @@
         <v>1.93</v>
       </c>
       <c r="P26" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="Q26" t="n">
         <v>6.5</v>
       </c>
       <c r="R26" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S26" t="n">
-        <v>2.79</v>
+        <v>2.87</v>
       </c>
       <c r="T26" t="n">
         <v>2.8</v>
       </c>
       <c r="U26" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="V26" t="n">
         <v>7.5</v>
@@ -3551,13 +3551,13 @@
         <v>1.05</v>
       </c>
       <c r="X26" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
         <v>1.35</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.16</v>
+        <v>3.12</v>
       </c>
       <c r="AA26" t="n">
         <v>1.97</v>
@@ -3566,7 +3566,7 @@
         <v>1.83</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.44</v>
+        <v>3.55</v>
       </c>
       <c r="AD26" t="n">
         <v>1.25</v>
@@ -3575,10 +3575,10 @@
         <v>2.2</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="AH26" t="n">
         <v>2.77</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>5.22</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>45992.70833333334</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>5.22</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45992.70833333334</v>
@@ -3884,7 +3884,7 @@
         <v>5.75</v>
       </c>
       <c r="P29" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q29" t="n">
         <v>2.1</v>
@@ -3896,10 +3896,10 @@
         <v>2.94</v>
       </c>
       <c r="T29" t="n">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="U29" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="V29" t="n">
         <v>6.5</v>
@@ -3926,19 +3926,19 @@
         <v>2.98</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.18</v>
+        <v>2.5</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>45992.71875</v>

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.65</v>
+        <v>2.36</v>
       </c>
       <c r="M8" t="n">
         <v>3.65</v>
       </c>
       <c r="N8" t="n">
-        <v>4.9</v>
+        <v>2.37</v>
       </c>
       <c r="O8" t="n">
-        <v>2.12</v>
+        <v>2.8</v>
       </c>
       <c r="P8" t="n">
-        <v>2.09</v>
+        <v>2.57</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.2</v>
+        <v>2.95</v>
       </c>
       <c r="R8" t="n">
-        <v>1.42</v>
+        <v>1.2</v>
       </c>
       <c r="S8" t="n">
-        <v>2.62</v>
+        <v>4</v>
       </c>
       <c r="T8" t="n">
-        <v>3.19</v>
+        <v>2.04</v>
       </c>
       <c r="U8" t="n">
-        <v>1.32</v>
+        <v>1.69</v>
       </c>
       <c r="V8" t="n">
-        <v>7.8</v>
+        <v>4.33</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="X8" t="n">
         <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.32</v>
+        <v>1.08</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.88</v>
+        <v>5.55</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.97</v>
+        <v>1.44</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.73</v>
+        <v>2.62</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.88</v>
+        <v>1.94</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.2</v>
+        <v>1.76</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.66</v>
+        <v>2.8</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.32</v>
+        <v>1.5</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45992.54166666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.36</v>
+        <v>1.65</v>
       </c>
       <c r="M9" t="n">
         <v>3.65</v>
       </c>
       <c r="N9" t="n">
-        <v>2.37</v>
+        <v>4.9</v>
       </c>
       <c r="O9" t="n">
-        <v>2.8</v>
+        <v>2.15</v>
       </c>
       <c r="P9" t="n">
-        <v>2.57</v>
+        <v>2.09</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.95</v>
+        <v>6.35</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2</v>
+        <v>1.43</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>2.72</v>
       </c>
       <c r="T9" t="n">
-        <v>2.04</v>
+        <v>3.19</v>
       </c>
       <c r="U9" t="n">
-        <v>1.69</v>
+        <v>1.33</v>
       </c>
       <c r="V9" t="n">
-        <v>4.33</v>
+        <v>7.8</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2</v>
+        <v>1.02</v>
       </c>
       <c r="X9" t="n">
         <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.08</v>
+        <v>1.32</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.55</v>
+        <v>2.88</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.44</v>
+        <v>1.97</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.62</v>
+        <v>1.73</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.94</v>
+        <v>3.72</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.76</v>
+        <v>1.23</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.8</v>
+        <v>1.63</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.5</v>
+        <v>2.29</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45992.54166666666</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.79</v>
+        <v>5.8</v>
       </c>
       <c r="M11" t="n">
-        <v>3.23</v>
+        <v>4.2</v>
       </c>
       <c r="N11" t="n">
-        <v>2.21</v>
+        <v>1.49</v>
       </c>
       <c r="O11" t="n">
-        <v>3.55</v>
+        <v>5.4</v>
       </c>
       <c r="P11" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.83</v>
+        <v>1.91</v>
       </c>
       <c r="R11" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.73</v>
+        <v>2.23</v>
       </c>
       <c r="U11" t="n">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="V11" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.93</v>
+        <v>1.64</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.77</v>
+        <v>2.08</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.35</v>
+        <v>2.63</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.01</v>
+        <v>1.88</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.34</v>
+        <v>1.08</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45992.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>5.8</v>
+        <v>1.81</v>
       </c>
       <c r="M12" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="N12" t="n">
-        <v>1.49</v>
+        <v>4.46</v>
       </c>
       <c r="O12" t="n">
-        <v>5.4</v>
+        <v>2.35</v>
       </c>
       <c r="P12" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="Q12" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V12" t="n">
+        <v>7</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH12" t="n">
         <v>1.91</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.08</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45992.58333333334</v>
@@ -1968,22 +1968,22 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="M13" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="N13" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="O13" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="P13" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.5</v>
+        <v>3.64</v>
       </c>
       <c r="R13" t="n">
         <v>1.3</v>
@@ -2010,13 +2010,13 @@
         <v>1.2</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.2</v>
+        <v>3.98</v>
       </c>
       <c r="AA13" t="n">
         <v>1.68</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AC13" t="n">
         <v>2.51</v>
@@ -2028,7 +2028,7 @@
         <v>1.53</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AG13" t="n">
         <v>1.3</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>6.25</v>
+        <v>2.79</v>
       </c>
       <c r="M14" t="n">
-        <v>4.3</v>
+        <v>3.23</v>
       </c>
       <c r="N14" t="n">
-        <v>1.44</v>
+        <v>2.21</v>
       </c>
       <c r="O14" t="n">
-        <v>6.5</v>
+        <v>3.55</v>
       </c>
       <c r="P14" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.89</v>
+        <v>2.83</v>
       </c>
       <c r="R14" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="S14" t="n">
-        <v>3.05</v>
+        <v>2.73</v>
       </c>
       <c r="T14" t="n">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="U14" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="V14" t="n">
-        <v>5.8</v>
+        <v>6.45</v>
       </c>
       <c r="W14" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.74</v>
+        <v>1.93</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.06</v>
+        <v>1.77</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.8</v>
+        <v>3.35</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.63</v>
+        <v>1.3</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.08</v>
+        <v>1.34</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2218,22 +2218,22 @@
         <v>8.6</v>
       </c>
       <c r="P15" t="n">
-        <v>2.5</v>
+        <v>2.24</v>
       </c>
       <c r="Q15" t="n">
         <v>1.73</v>
       </c>
       <c r="R15" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="S15" t="n">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="T15" t="n">
-        <v>2.66</v>
+        <v>2.83</v>
       </c>
       <c r="U15" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V15" t="n">
         <v>6</v>
@@ -2248,7 +2248,7 @@
         <v>1.25</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.34</v>
+        <v>3.47</v>
       </c>
       <c r="AA15" t="n">
         <v>1.8</v>
@@ -2257,22 +2257,22 @@
         <v>2</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.13</v>
+        <v>3.16</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.85</v>
+        <v>1.25</v>
       </c>
       <c r="M16" t="n">
-        <v>3.5</v>
+        <v>5.8</v>
       </c>
       <c r="N16" t="n">
-        <v>4.3</v>
+        <v>14</v>
       </c>
       <c r="O16" t="n">
-        <v>2.35</v>
+        <v>1.62</v>
       </c>
       <c r="P16" t="n">
-        <v>2.33</v>
+        <v>2.57</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.6</v>
+        <v>9</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="S16" t="n">
-        <v>2.77</v>
+        <v>3.28</v>
       </c>
       <c r="T16" t="n">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="U16" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="V16" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.09</v>
+        <v>1.19</v>
       </c>
       <c r="X16" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.98</v>
+        <v>1.63</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.18</v>
+        <v>2.38</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.29</v>
+        <v>1.53</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.31</v>
+        <v>1.11</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.91</v>
+        <v>4</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.25</v>
+        <v>6.5</v>
       </c>
       <c r="M17" t="n">
-        <v>5.8</v>
+        <v>4</v>
       </c>
       <c r="N17" t="n">
-        <v>14</v>
+        <v>1.38</v>
       </c>
       <c r="O17" t="n">
-        <v>1.62</v>
+        <v>5.75</v>
       </c>
       <c r="P17" t="n">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="Q17" t="n">
-        <v>9</v>
+        <v>1.85</v>
       </c>
       <c r="R17" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="S17" t="n">
-        <v>3.28</v>
+        <v>3.05</v>
       </c>
       <c r="T17" t="n">
-        <v>2.29</v>
+        <v>2.47</v>
       </c>
       <c r="U17" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="V17" t="n">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="W17" t="n">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.13</v>
+        <v>3.84</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.4</v>
+        <v>2.66</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AH17" t="n">
-        <v>3.9</v>
+        <v>1.1</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.21</v>
+        <v>1.65</v>
       </c>
       <c r="M18" t="n">
-        <v>5.6</v>
+        <v>3.75</v>
       </c>
       <c r="N18" t="n">
-        <v>8.800000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="O18" t="n">
-        <v>1.67</v>
+        <v>2.39</v>
       </c>
       <c r="P18" t="n">
-        <v>2.75</v>
+        <v>2.04</v>
       </c>
       <c r="Q18" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.18</v>
+        <v>1.42</v>
       </c>
       <c r="S18" t="n">
-        <v>3.92</v>
+        <v>2.62</v>
       </c>
       <c r="T18" t="n">
-        <v>2.02</v>
+        <v>2.9</v>
       </c>
       <c r="U18" t="n">
-        <v>1.74</v>
+        <v>1.35</v>
       </c>
       <c r="V18" t="n">
-        <v>4.4</v>
+        <v>7.3</v>
       </c>
       <c r="W18" t="n">
-        <v>1.21</v>
+        <v>1.03</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="Z18" t="n">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.91</v>
+        <v>3.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.79</v>
+        <v>1.25</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.08</v>
+        <v>1.3</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.33</v>
+        <v>1.95</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45992.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="O19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V19" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA19" t="n">
         <v>1.65</v>
       </c>
-      <c r="M19" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O19" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V19" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AB19" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="AG19" t="n">
         <v>1.3</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.95</v>
+        <v>1.33</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45992.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.05</v>
+        <v>1.21</v>
       </c>
       <c r="M20" t="n">
-        <v>3.39</v>
+        <v>5.6</v>
       </c>
       <c r="N20" t="n">
-        <v>2.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>3.5</v>
+        <v>1.67</v>
       </c>
       <c r="P20" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.48</v>
+        <v>7</v>
       </c>
       <c r="R20" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="S20" t="n">
-        <v>3.05</v>
+        <v>3.92</v>
       </c>
       <c r="T20" t="n">
-        <v>2.5</v>
+        <v>2.02</v>
       </c>
       <c r="U20" t="n">
-        <v>1.47</v>
+        <v>1.74</v>
       </c>
       <c r="V20" t="n">
-        <v>5.95</v>
+        <v>4.4</v>
       </c>
       <c r="W20" t="n">
-        <v>1.07</v>
+        <v>1.21</v>
       </c>
       <c r="X20" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="Z20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.6</v>
+        <v>1.91</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.4</v>
+        <v>1.79</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.3</v>
+        <v>1.08</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.33</v>
+        <v>3.33</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45992.625</v>
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45992.66666666666</v>
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45992.66666666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.8</v>
+        <v>1.97</v>
       </c>
       <c r="M23" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="N23" t="n">
-        <v>2.4</v>
+        <v>3.75</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.35</v>
+        <v>3.01</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45992.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.97</v>
+        <v>3.6</v>
       </c>
       <c r="M24" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="N24" t="n">
-        <v>3.75</v>
+        <v>2.07</v>
       </c>
       <c r="O24" t="n">
-        <v>2.65</v>
+        <v>4.55</v>
       </c>
       <c r="P24" t="n">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.45</v>
+        <v>2.93</v>
       </c>
       <c r="R24" t="n">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="S24" t="n">
-        <v>2.53</v>
+        <v>2.24</v>
       </c>
       <c r="T24" t="n">
-        <v>2.97</v>
+        <v>3.58</v>
       </c>
       <c r="U24" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="V24" t="n">
-        <v>7.8</v>
+        <v>9.5</v>
       </c>
       <c r="W24" t="n">
         <v>1.02</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.58</v>
+        <v>4.9</v>
       </c>
       <c r="AD24" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AH24" t="n">
         <v>1.21</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.66</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45992.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="M25" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N25" t="n">
-        <v>2.07</v>
+        <v>2.4</v>
       </c>
       <c r="O25" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.51</v>
+        <v>2.35</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.35</v>
+        <v>2.62</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AC25" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45992.6875</v>
@@ -3533,10 +3533,10 @@
         <v>6.5</v>
       </c>
       <c r="R26" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S26" t="n">
-        <v>2.87</v>
+        <v>2.79</v>
       </c>
       <c r="T26" t="n">
         <v>2.8</v>
@@ -3551,13 +3551,13 @@
         <v>1.05</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y26" t="n">
         <v>1.35</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="AA26" t="n">
         <v>1.97</v>
@@ -3581,7 +3581,7 @@
         <v>1.1</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.77</v>
+        <v>2.63</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>45992.69791666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="M27" t="n">
-        <v>3.65</v>
+        <v>3.36</v>
       </c>
       <c r="N27" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="O27" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="P27" t="n">
-        <v>2.03</v>
+        <v>2.14</v>
       </c>
       <c r="Q27" t="n">
-        <v>5.22</v>
+        <v>4.6</v>
       </c>
       <c r="R27" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="S27" t="n">
-        <v>2.86</v>
+        <v>2.64</v>
       </c>
       <c r="T27" t="n">
-        <v>2.9</v>
+        <v>3.12</v>
       </c>
       <c r="U27" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="V27" t="n">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="W27" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="AA27" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE27" t="n">
         <v>1.85</v>
       </c>
-      <c r="AB27" t="n">
+      <c r="AF27" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH27" t="n">
         <v>1.85</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.95</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>45992.70833333334</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>5.22</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45992.70833333334</v>
@@ -3881,7 +3881,7 @@
         <v>1.6</v>
       </c>
       <c r="O29" t="n">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="P29" t="n">
         <v>2.4</v>
@@ -3890,19 +3890,19 @@
         <v>2.1</v>
       </c>
       <c r="R29" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S29" t="n">
         <v>2.94</v>
       </c>
       <c r="T29" t="n">
-        <v>2.48</v>
+        <v>2.65</v>
       </c>
       <c r="U29" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="V29" t="n">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="W29" t="n">
         <v>1.05</v>
@@ -3914,7 +3914,7 @@
         <v>1.25</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AA29" t="n">
         <v>1.63</v>
@@ -3926,19 +3926,19 @@
         <v>2.98</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.5</v>
+        <v>1.25</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>45992.71875</v>

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45992.45833333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45992.45833333334</v>
@@ -1269,22 +1269,22 @@
         <v>2</v>
       </c>
       <c r="Q7" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S7" t="n">
         <v>2.8</v>
       </c>
-      <c r="R7" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.7</v>
-      </c>
       <c r="T7" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="U7" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="V7" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="W7" t="n">
         <v>1.03</v>
@@ -1293,16 +1293,16 @@
         <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z7" t="n">
         <v>3.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AC7" t="n">
         <v>3.47</v>
@@ -1311,13 +1311,13 @@
         <v>1.25</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AF7" t="n">
         <v>1.95</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="AH7" t="n">
         <v>1.36</v>
@@ -1388,40 +1388,40 @@
         <v>2.57</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="R8" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
       </c>
       <c r="T8" t="n">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="U8" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="V8" t="n">
         <v>4.33</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X8" t="n">
         <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z8" t="n">
         <v>5.55</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="AC8" t="n">
         <v>1.94</v>
@@ -1430,16 +1430,16 @@
         <v>1.76</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45992.54166666666</v>
@@ -1623,10 +1623,10 @@
         <v>3.92</v>
       </c>
       <c r="P10" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="R10" t="n">
         <v>1.63</v>
@@ -1647,7 +1647,7 @@
         <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="Y10" t="n">
         <v>1.58</v>
@@ -1656,10 +1656,10 @@
         <v>2.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="AC10" t="n">
         <v>5.3</v>
@@ -1668,10 +1668,10 @@
         <v>1.09</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AG10" t="n">
         <v>1.34</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>5.8</v>
+        <v>2.79</v>
       </c>
       <c r="M11" t="n">
-        <v>4.2</v>
+        <v>3.23</v>
       </c>
       <c r="N11" t="n">
-        <v>1.49</v>
+        <v>2.21</v>
       </c>
       <c r="O11" t="n">
-        <v>5.4</v>
+        <v>3.55</v>
       </c>
       <c r="P11" t="n">
-        <v>2.5</v>
+        <v>2.07</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.91</v>
+        <v>2.83</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="T11" t="n">
-        <v>2.23</v>
+        <v>2.73</v>
       </c>
       <c r="U11" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.64</v>
+        <v>1.93</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.08</v>
+        <v>1.77</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.63</v>
+        <v>3.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.88</v>
+        <v>2.01</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.15</v>
+        <v>1.6</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.08</v>
+        <v>1.34</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.79</v>
+        <v>5.8</v>
       </c>
       <c r="M14" t="n">
-        <v>3.23</v>
+        <v>4.2</v>
       </c>
       <c r="N14" t="n">
-        <v>2.21</v>
+        <v>1.49</v>
       </c>
       <c r="O14" t="n">
-        <v>3.55</v>
+        <v>5.4</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.83</v>
+        <v>1.91</v>
       </c>
       <c r="R14" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.73</v>
+        <v>2.23</v>
       </c>
       <c r="U14" t="n">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="V14" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.93</v>
+        <v>1.64</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.77</v>
+        <v>2.08</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.35</v>
+        <v>2.63</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.01</v>
+        <v>1.88</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.34</v>
+        <v>1.08</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>8</v>
+        <v>1.25</v>
       </c>
       <c r="M15" t="n">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="N15" t="n">
-        <v>1.4</v>
+        <v>14</v>
       </c>
       <c r="O15" t="n">
-        <v>8.6</v>
+        <v>1.62</v>
       </c>
       <c r="P15" t="n">
-        <v>2.24</v>
+        <v>2.57</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.73</v>
+        <v>9</v>
       </c>
       <c r="R15" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="S15" t="n">
-        <v>2.75</v>
+        <v>3.28</v>
       </c>
       <c r="T15" t="n">
-        <v>2.83</v>
+        <v>2.25</v>
       </c>
       <c r="U15" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="V15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="X15" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.47</v>
+        <v>4.8</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="AB15" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.16</v>
+        <v>2.38</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AG15" t="n">
         <v>1.11</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>8</v>
+      </c>
+      <c r="M16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="O16" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V16" t="n">
+        <v>6</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y16" t="n">
         <v>1.25</v>
       </c>
-      <c r="M16" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="N16" t="n">
-        <v>14</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>9</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V16" t="n">
-        <v>5</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.17</v>
-      </c>
       <c r="Z16" t="n">
-        <v>4.8</v>
+        <v>3.47</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.38</v>
+        <v>3.16</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AG16" t="n">
         <v>1.11</v>
       </c>
       <c r="AH16" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="M18" t="n">
-        <v>3.75</v>
+        <v>3.56</v>
       </c>
       <c r="N18" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="O18" t="n">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="P18" t="n">
         <v>2.04</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="R18" t="n">
         <v>1.42</v>
       </c>
       <c r="S18" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="T18" t="n">
         <v>2.9</v>
       </c>
       <c r="U18" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="V18" t="n">
         <v>7.3</v>
       </c>
       <c r="W18" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="AB18" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE18" t="n">
         <v>1.8</v>
       </c>
-      <c r="AC18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD18" t="n">
+      <c r="AF18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG18" t="n">
         <v>1.25</v>
       </c>
-      <c r="AE18" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH18" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45992.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.05</v>
+        <v>1.21</v>
       </c>
       <c r="M19" t="n">
-        <v>3.39</v>
+        <v>5.6</v>
       </c>
       <c r="N19" t="n">
-        <v>2.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>3.5</v>
+        <v>1.67</v>
       </c>
       <c r="P19" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.48</v>
+        <v>6.09</v>
       </c>
       <c r="R19" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="S19" t="n">
-        <v>3.05</v>
+        <v>3.92</v>
       </c>
       <c r="T19" t="n">
-        <v>2.5</v>
+        <v>2.09</v>
       </c>
       <c r="U19" t="n">
-        <v>1.47</v>
+        <v>1.74</v>
       </c>
       <c r="V19" t="n">
-        <v>5.95</v>
+        <v>4</v>
       </c>
       <c r="W19" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="X19" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="Z19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.6</v>
+        <v>1.91</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.4</v>
+        <v>1.79</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.33</v>
+        <v>3.75</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45992.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V20" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y20" t="n">
         <v>1.21</v>
       </c>
-      <c r="M20" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="N20" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>7</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="V20" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.08</v>
-      </c>
       <c r="Z20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AA20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD20" t="n">
         <v>1.4</v>
       </c>
-      <c r="AB20" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.79</v>
-      </c>
       <c r="AE20" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.08</v>
+        <v>1.3</v>
       </c>
       <c r="AH20" t="n">
-        <v>3.33</v>
+        <v>1.33</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45992.625</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.97</v>
+        <v>2.8</v>
       </c>
       <c r="M23" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="N23" t="n">
-        <v>3.75</v>
+        <v>2.4</v>
       </c>
       <c r="O23" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.35</v>
+        <v>1.52</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.01</v>
+        <v>2.35</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45992.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.6</v>
+        <v>1.97</v>
       </c>
       <c r="M24" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="N24" t="n">
-        <v>2.07</v>
+        <v>3.75</v>
       </c>
       <c r="O24" t="n">
-        <v>4.55</v>
+        <v>2.65</v>
       </c>
       <c r="P24" t="n">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.93</v>
+        <v>4.25</v>
       </c>
       <c r="R24" t="n">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
       <c r="S24" t="n">
-        <v>2.24</v>
+        <v>2.53</v>
       </c>
       <c r="T24" t="n">
-        <v>3.58</v>
+        <v>2.97</v>
       </c>
       <c r="U24" t="n">
-        <v>1.21</v>
+        <v>1.34</v>
       </c>
       <c r="V24" t="n">
-        <v>9.5</v>
+        <v>7.8</v>
       </c>
       <c r="W24" t="n">
         <v>1.02</v>
       </c>
       <c r="X24" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.38</v>
+        <v>3.01</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.9</v>
+        <v>3.58</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.09</v>
+        <v>1.83</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.63</v>
+        <v>1.81</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.59</v>
+        <v>1.26</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.21</v>
+        <v>1.66</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45992.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="M25" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N25" t="n">
-        <v>2.4</v>
+        <v>2.07</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="Z25" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AA25" t="n">
         <v>2.35</v>
       </c>
-      <c r="AA25" t="n">
-        <v>2.62</v>
-      </c>
       <c r="AB25" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45992.6875</v>
@@ -3771,10 +3771,10 @@
         <v>5.22</v>
       </c>
       <c r="R28" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="S28" t="n">
-        <v>2.86</v>
+        <v>2.62</v>
       </c>
       <c r="T28" t="n">
         <v>2.9</v>
@@ -3789,13 +3789,13 @@
         <v>1.02</v>
       </c>
       <c r="X28" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="AA28" t="n">
         <v>1.85</v>
@@ -3804,7 +3804,7 @@
         <v>1.85</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.52</v>
+        <v>3.54</v>
       </c>
       <c r="AD28" t="n">
         <v>1.28</v>
@@ -3819,7 +3819,7 @@
         <v>1.29</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45992.70833333334</v>

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -1016,58 +1016,58 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="M5" t="n">
-        <v>3.41</v>
+        <v>3.72</v>
       </c>
       <c r="N5" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="O5" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="P5" t="n">
         <v>2.03</v>
       </c>
       <c r="Q5" t="n">
-        <v>6</v>
+        <v>6.74</v>
       </c>
       <c r="R5" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S5" t="n">
         <v>2.71</v>
       </c>
       <c r="T5" t="n">
-        <v>3.19</v>
+        <v>3</v>
       </c>
       <c r="U5" t="n">
         <v>1.32</v>
       </c>
       <c r="V5" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="W5" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.93</v>
+        <v>2.16</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.77</v>
+        <v>1.56</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.78</v>
+        <v>3.91</v>
       </c>
       <c r="AD5" t="n">
         <v>1.22</v>
@@ -1079,7 +1079,7 @@
         <v>1.67</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AH5" t="n">
         <v>2.17</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.36</v>
+        <v>2</v>
       </c>
       <c r="M8" t="n">
-        <v>3.65</v>
+        <v>3.38</v>
       </c>
       <c r="N8" t="n">
-        <v>2.37</v>
+        <v>5.73</v>
       </c>
       <c r="O8" t="n">
-        <v>2.8</v>
+        <v>2.12</v>
       </c>
       <c r="P8" t="n">
-        <v>2.57</v>
+        <v>2.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.9</v>
+        <v>6.2</v>
       </c>
       <c r="R8" t="n">
-        <v>1.22</v>
+        <v>1.43</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>2.72</v>
       </c>
       <c r="T8" t="n">
-        <v>1.95</v>
+        <v>3.19</v>
       </c>
       <c r="U8" t="n">
-        <v>1.67</v>
+        <v>1.32</v>
       </c>
       <c r="V8" t="n">
-        <v>4.33</v>
+        <v>7.8</v>
       </c>
       <c r="W8" t="n">
-        <v>1.19</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
         <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.11</v>
+        <v>1.32</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.55</v>
+        <v>3.02</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.43</v>
+        <v>2.16</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.6</v>
+        <v>1.68</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.94</v>
+        <v>3.72</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.76</v>
+        <v>1.2</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.35</v>
+        <v>2.1</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.75</v>
+        <v>1.66</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.55</v>
+        <v>2.32</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45992.54166666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.65</v>
+        <v>2.3</v>
       </c>
       <c r="M9" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="N9" t="n">
-        <v>4.9</v>
+        <v>2.5</v>
       </c>
       <c r="O9" t="n">
-        <v>2.15</v>
+        <v>2.8</v>
       </c>
       <c r="P9" t="n">
-        <v>2.09</v>
+        <v>2.35</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.35</v>
+        <v>2.76</v>
       </c>
       <c r="R9" t="n">
-        <v>1.43</v>
+        <v>1.22</v>
       </c>
       <c r="S9" t="n">
-        <v>2.72</v>
+        <v>3.7</v>
       </c>
       <c r="T9" t="n">
-        <v>3.19</v>
+        <v>1.95</v>
       </c>
       <c r="U9" t="n">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="V9" t="n">
-        <v>7.8</v>
+        <v>4.2</v>
       </c>
       <c r="W9" t="n">
-        <v>1.02</v>
+        <v>1.19</v>
       </c>
       <c r="X9" t="n">
         <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.32</v>
+        <v>1.08</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.88</v>
+        <v>5.25</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.97</v>
+        <v>1.43</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.73</v>
+        <v>2.62</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.72</v>
+        <v>2.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.23</v>
+        <v>1.7</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.2</v>
+        <v>1.38</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.63</v>
+        <v>2.9</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.29</v>
+        <v>1.46</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45992.54166666666</v>
@@ -1611,22 +1611,22 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="M10" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>3.05</v>
+        <v>2.49</v>
       </c>
       <c r="O10" t="n">
         <v>3.92</v>
       </c>
       <c r="P10" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="R10" t="n">
         <v>1.63</v>
@@ -1647,19 +1647,19 @@
         <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="AC10" t="n">
         <v>5.3</v>
@@ -1668,13 +1668,13 @@
         <v>1.09</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="AF10" t="n">
         <v>1.63</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="AH10" t="n">
         <v>1.42</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.79</v>
+        <v>1.84</v>
       </c>
       <c r="M11" t="n">
-        <v>3.23</v>
+        <v>3.46</v>
       </c>
       <c r="N11" t="n">
-        <v>2.21</v>
+        <v>4</v>
       </c>
       <c r="O11" t="n">
-        <v>3.55</v>
+        <v>2.35</v>
       </c>
       <c r="P11" t="n">
-        <v>2.07</v>
+        <v>2.33</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.83</v>
+        <v>4.45</v>
       </c>
       <c r="R11" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S11" t="n">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="T11" t="n">
-        <v>2.73</v>
+        <v>2.81</v>
       </c>
       <c r="U11" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="V11" t="n">
         <v>7</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.6</v>
+        <v>1.22</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.34</v>
+        <v>1.91</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45992.58333333334</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.81</v>
+        <v>2.21</v>
       </c>
       <c r="M12" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="N12" t="n">
-        <v>4.46</v>
+        <v>3.28</v>
       </c>
       <c r="O12" t="n">
-        <v>2.35</v>
+        <v>2.75</v>
       </c>
       <c r="P12" t="n">
-        <v>2.33</v>
+        <v>2.24</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.83</v>
+        <v>3.62</v>
       </c>
       <c r="R12" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="S12" t="n">
-        <v>2.77</v>
+        <v>3.1</v>
       </c>
       <c r="T12" t="n">
-        <v>2.81</v>
+        <v>2.44</v>
       </c>
       <c r="U12" t="n">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="V12" t="n">
-        <v>7</v>
+        <v>5.25</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.98</v>
+        <v>1.68</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.18</v>
+        <v>2.51</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.85</v>
+        <v>1.54</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.85</v>
+        <v>2.28</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.91</v>
+        <v>1.58</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45992.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.21</v>
+        <v>3</v>
       </c>
       <c r="M13" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="N13" t="n">
-        <v>3.28</v>
+        <v>2.13</v>
       </c>
       <c r="O13" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="P13" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.64</v>
+        <v>2.83</v>
       </c>
       <c r="R13" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V13" t="n">
+        <v>7</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AD13" t="n">
         <v>1.3</v>
       </c>
-      <c r="S13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V13" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AE13" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.62</v>
+        <v>1.35</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="M14" t="n">
         <v>5.8</v>
       </c>
-      <c r="M14" t="n">
-        <v>4.2</v>
-      </c>
       <c r="N14" t="n">
-        <v>1.49</v>
+        <v>10</v>
       </c>
       <c r="O14" t="n">
-        <v>5.4</v>
+        <v>1.62</v>
       </c>
       <c r="P14" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.91</v>
+        <v>8.5</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="T14" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="U14" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA14" t="n">
         <v>1.5</v>
       </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.64</v>
-      </c>
       <c r="AB14" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.88</v>
+        <v>1.6</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.08</v>
+        <v>2.9</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.25</v>
+        <v>5.8</v>
       </c>
       <c r="M15" t="n">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="N15" t="n">
-        <v>14</v>
+        <v>1.49</v>
       </c>
       <c r="O15" t="n">
-        <v>1.62</v>
+        <v>5.4</v>
       </c>
       <c r="P15" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>9</v>
+        <v>1.91</v>
       </c>
       <c r="R15" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="U15" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="V15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
         <v>1.19</v>
       </c>
-      <c r="X15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.17</v>
-      </c>
       <c r="Z15" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.7</v>
+        <v>1.88</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AH15" t="n">
-        <v>4</v>
+        <v>1.08</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="M16" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="O16" t="n">
-        <v>8.6</v>
+        <v>6.25</v>
       </c>
       <c r="P16" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="R16" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="S16" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="T16" t="n">
-        <v>2.83</v>
+        <v>2.47</v>
       </c>
       <c r="U16" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="V16" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="W16" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X16" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.47</v>
+        <v>3.7</v>
       </c>
       <c r="AA16" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE16" t="n">
         <v>1.8</v>
       </c>
-      <c r="AB16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>2.07</v>
-      </c>
       <c r="AF16" t="n">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="M17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="O17" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V17" t="n">
         <v>6.5</v>
       </c>
-      <c r="M17" t="n">
-        <v>4</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="O17" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q17" t="n">
+      <c r="W17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AA17" t="n">
         <v>1.85</v>
       </c>
-      <c r="R17" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V17" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AB17" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.66</v>
+        <v>3.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.75</v>
+        <v>3.14</v>
       </c>
       <c r="M18" t="n">
-        <v>3.56</v>
+        <v>3.6</v>
       </c>
       <c r="N18" t="n">
-        <v>4.1</v>
+        <v>2.21</v>
       </c>
       <c r="O18" t="n">
-        <v>2.45</v>
+        <v>3.5</v>
       </c>
       <c r="P18" t="n">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.1</v>
+        <v>2.48</v>
       </c>
       <c r="R18" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="S18" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="T18" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="U18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V18" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD18" t="n">
         <v>1.4</v>
       </c>
-      <c r="V18" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AE18" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.25</v>
+        <v>1.64</v>
       </c>
       <c r="AH18" t="n">
-        <v>2</v>
+        <v>1.27</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45992.625</v>
@@ -2682,37 +2682,37 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="M19" t="n">
-        <v>5.6</v>
+        <v>6.25</v>
       </c>
       <c r="N19" t="n">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="O19" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="P19" t="n">
         <v>2.75</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.09</v>
+        <v>7</v>
       </c>
       <c r="R19" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="S19" t="n">
-        <v>3.92</v>
+        <v>3.75</v>
       </c>
       <c r="T19" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="U19" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="V19" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="W19" t="n">
         <v>1.18</v>
@@ -2721,34 +2721,34 @@
         <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z19" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.75</v>
+        <v>3.33</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45992.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.05</v>
+        <v>1.75</v>
       </c>
       <c r="M20" t="n">
-        <v>3.39</v>
+        <v>3.56</v>
       </c>
       <c r="N20" t="n">
-        <v>2.01</v>
+        <v>4.1</v>
       </c>
       <c r="O20" t="n">
-        <v>3.5</v>
+        <v>2.45</v>
       </c>
       <c r="P20" t="n">
-        <v>2.38</v>
+        <v>2.04</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.48</v>
+        <v>4.1</v>
       </c>
       <c r="R20" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="S20" t="n">
-        <v>3.05</v>
+        <v>2.75</v>
       </c>
       <c r="T20" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="U20" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="V20" t="n">
-        <v>5.95</v>
+        <v>7.3</v>
       </c>
       <c r="W20" t="n">
         <v>1.07</v>
       </c>
       <c r="X20" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="Z20" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.65</v>
+        <v>2.04</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.2</v>
+        <v>1.72</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.6</v>
+        <v>3.34</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45992.625</v>
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.02</v>
+        <v>2.9</v>
       </c>
       <c r="M21" t="n">
         <v>3.75</v>
       </c>
       <c r="N21" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="O21" t="n">
         <v>3.3</v>
@@ -2935,58 +2935,58 @@
         <v>2.51</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="R21" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="S21" t="n">
-        <v>4.4</v>
+        <v>4.75</v>
       </c>
       <c r="T21" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="U21" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="V21" t="n">
         <v>3.7</v>
       </c>
       <c r="W21" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="Z21" t="n">
-        <v>7.3</v>
+        <v>6.38</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AB21" t="n">
-        <v>3.22</v>
+        <v>3.37</v>
       </c>
       <c r="AC21" t="n">
         <v>1.78</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AF21" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.64</v>
+        <v>1.21</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45992.66666666666</v>
@@ -3039,10 +3039,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="M22" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="N22" t="n">
         <v>2.2</v>
@@ -3051,52 +3051,52 @@
         <v>3.1</v>
       </c>
       <c r="P22" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="R22" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>3.44</v>
+        <v>3.7</v>
       </c>
       <c r="T22" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="U22" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="V22" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X22" t="n">
         <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.75</v>
+        <v>4.97</v>
       </c>
       <c r="AA22" t="n">
         <v>1.56</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.35</v>
+        <v>2.43</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AF22" t="n">
         <v>2.5</v>
@@ -3105,7 +3105,7 @@
         <v>1.24</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45992.66666666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.8</v>
+        <v>1.95</v>
       </c>
       <c r="M23" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N23" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.52</v>
+        <v>1.32</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.35</v>
+        <v>2.88</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.62</v>
+        <v>2.07</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.44</v>
+        <v>1.66</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45992.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.97</v>
+        <v>3.5</v>
       </c>
       <c r="M24" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="N24" t="n">
-        <v>3.75</v>
+        <v>2.15</v>
       </c>
       <c r="O24" t="n">
-        <v>2.65</v>
+        <v>4.25</v>
       </c>
       <c r="P24" t="n">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.25</v>
+        <v>3</v>
       </c>
       <c r="R24" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="S24" t="n">
-        <v>2.53</v>
+        <v>2.24</v>
       </c>
       <c r="T24" t="n">
-        <v>2.97</v>
+        <v>3.58</v>
       </c>
       <c r="U24" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="V24" t="n">
-        <v>7.8</v>
+        <v>8.5</v>
       </c>
       <c r="W24" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.01</v>
+        <v>2.41</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.58</v>
+        <v>4.9</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.83</v>
+        <v>2.06</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.81</v>
+        <v>1.65</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.66</v>
+        <v>1.24</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45992.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.6</v>
+        <v>3.42</v>
       </c>
       <c r="M25" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="N25" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="O25" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.35</v>
+        <v>2.62</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AC25" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45992.6875</v>
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="M26" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="N26" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="O26" t="n">
         <v>1.93</v>
@@ -3530,16 +3530,16 @@
         <v>2.21</v>
       </c>
       <c r="Q26" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="R26" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="S26" t="n">
         <v>2.79</v>
       </c>
       <c r="T26" t="n">
-        <v>2.8</v>
+        <v>3.13</v>
       </c>
       <c r="U26" t="n">
         <v>1.38</v>
@@ -3551,37 +3551,37 @@
         <v>1.05</v>
       </c>
       <c r="X26" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AC26" t="n">
         <v>3.55</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.63</v>
+        <v>2.85</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>45992.69791666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="M27" t="n">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="N27" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O27" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="P27" t="n">
-        <v>2.14</v>
+        <v>2.03</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.6</v>
+        <v>5.22</v>
       </c>
       <c r="R27" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="S27" t="n">
-        <v>2.64</v>
+        <v>2.86</v>
       </c>
       <c r="T27" t="n">
-        <v>3.12</v>
+        <v>2.95</v>
       </c>
       <c r="U27" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="V27" t="n">
-        <v>7.7</v>
+        <v>7</v>
       </c>
       <c r="W27" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AB27" t="n">
         <v>1.75</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.7</v>
+        <v>3.52</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>45992.70833333334</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="M28" t="n">
-        <v>3.65</v>
+        <v>3.34</v>
       </c>
       <c r="N28" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="O28" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="P28" t="n">
-        <v>2.03</v>
+        <v>2.14</v>
       </c>
       <c r="Q28" t="n">
-        <v>5.22</v>
+        <v>4.6</v>
       </c>
       <c r="R28" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="S28" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="T28" t="n">
         <v>2.9</v>
       </c>
       <c r="U28" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="V28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W28" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X28" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AA28" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH28" t="n">
         <v>1.85</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.94</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45992.70833333334</v>
@@ -3872,19 +3872,19 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="M29" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="N29" t="n">
-        <v>1.6</v>
+        <v>1.49</v>
       </c>
       <c r="O29" t="n">
-        <v>5.25</v>
+        <v>4.84</v>
       </c>
       <c r="P29" t="n">
-        <v>2.4</v>
+        <v>2.21</v>
       </c>
       <c r="Q29" t="n">
         <v>2.1</v>
@@ -3893,7 +3893,7 @@
         <v>1.34</v>
       </c>
       <c r="S29" t="n">
-        <v>2.94</v>
+        <v>3.21</v>
       </c>
       <c r="T29" t="n">
         <v>2.65</v>
@@ -3902,25 +3902,25 @@
         <v>1.42</v>
       </c>
       <c r="V29" t="n">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="W29" t="n">
         <v>1.05</v>
       </c>
       <c r="X29" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z29" t="n">
         <v>3.7</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="AC29" t="n">
         <v>2.98</v>
@@ -3929,10 +3929,10 @@
         <v>1.33</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AG29" t="n">
         <v>1.25</v>

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -1299,10 +1299,10 @@
         <v>3.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AC7" t="n">
         <v>3.47</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>2.36</v>
       </c>
       <c r="M8" t="n">
-        <v>3.38</v>
+        <v>3.85</v>
       </c>
       <c r="N8" t="n">
-        <v>5.73</v>
+        <v>2.5</v>
       </c>
       <c r="O8" t="n">
-        <v>2.12</v>
+        <v>2.8</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.2</v>
+        <v>2.76</v>
       </c>
       <c r="R8" t="n">
-        <v>1.43</v>
+        <v>1.2</v>
       </c>
       <c r="S8" t="n">
-        <v>2.72</v>
+        <v>3.7</v>
       </c>
       <c r="T8" t="n">
-        <v>3.19</v>
+        <v>2.04</v>
       </c>
       <c r="U8" t="n">
-        <v>1.32</v>
+        <v>1.69</v>
       </c>
       <c r="V8" t="n">
-        <v>7.8</v>
+        <v>4.2</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="X8" t="n">
         <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.32</v>
+        <v>1.08</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.02</v>
+        <v>5.67</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.16</v>
+        <v>1.43</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.68</v>
+        <v>2.62</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.72</v>
+        <v>2.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.2</v>
+        <v>1.67</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.1</v>
+        <v>1.38</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.66</v>
+        <v>2.7</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.32</v>
+        <v>1.46</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45992.54166666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>3.7</v>
+        <v>3.38</v>
       </c>
       <c r="N9" t="n">
-        <v>2.5</v>
+        <v>5.73</v>
       </c>
       <c r="O9" t="n">
-        <v>2.8</v>
+        <v>2.12</v>
       </c>
       <c r="P9" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.76</v>
+        <v>6.2</v>
       </c>
       <c r="R9" t="n">
-        <v>1.22</v>
+        <v>1.43</v>
       </c>
       <c r="S9" t="n">
-        <v>3.7</v>
+        <v>2.72</v>
       </c>
       <c r="T9" t="n">
-        <v>1.95</v>
+        <v>3.19</v>
       </c>
       <c r="U9" t="n">
-        <v>1.67</v>
+        <v>1.32</v>
       </c>
       <c r="V9" t="n">
-        <v>4.2</v>
+        <v>7.8</v>
       </c>
       <c r="W9" t="n">
-        <v>1.19</v>
+        <v>1.02</v>
       </c>
       <c r="X9" t="n">
         <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.08</v>
+        <v>1.32</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.25</v>
+        <v>3.02</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.43</v>
+        <v>2.16</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.62</v>
+        <v>1.68</v>
       </c>
       <c r="AC9" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE9" t="n">
         <v>2.1</v>
       </c>
-      <c r="AD9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AF9" t="n">
-        <v>2.9</v>
+        <v>1.66</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.46</v>
+        <v>2.32</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45992.54166666666</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.84</v>
+        <v>3</v>
       </c>
       <c r="M11" t="n">
-        <v>3.46</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>4</v>
+        <v>2.13</v>
       </c>
       <c r="O11" t="n">
-        <v>2.35</v>
+        <v>3.4</v>
       </c>
       <c r="P11" t="n">
-        <v>2.33</v>
+        <v>2.24</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.45</v>
+        <v>2.83</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S11" t="n">
-        <v>2.77</v>
+        <v>3.04</v>
       </c>
       <c r="T11" t="n">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="U11" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="V11" t="n">
         <v>7</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.18</v>
+        <v>3.35</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.22</v>
+        <v>1.6</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.91</v>
+        <v>1.35</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45992.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3</v>
+        <v>1.84</v>
       </c>
       <c r="M13" t="n">
-        <v>3.25</v>
+        <v>3.46</v>
       </c>
       <c r="N13" t="n">
-        <v>2.13</v>
+        <v>4</v>
       </c>
       <c r="O13" t="n">
-        <v>3.4</v>
+        <v>2.35</v>
       </c>
       <c r="P13" t="n">
-        <v>2.24</v>
+        <v>2.33</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.83</v>
+        <v>4.45</v>
       </c>
       <c r="R13" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>3.04</v>
+        <v>2.77</v>
       </c>
       <c r="T13" t="n">
-        <v>2.73</v>
+        <v>2.81</v>
       </c>
       <c r="U13" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="V13" t="n">
         <v>7</v>
       </c>
       <c r="W13" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AD13" t="n">
         <v>1.32</v>
       </c>
-      <c r="Z13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AE13" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AF13" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.6</v>
+        <v>1.22</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.35</v>
+        <v>1.91</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="M15" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="N15" t="n">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="O15" t="n">
-        <v>5.4</v>
+        <v>6.25</v>
       </c>
       <c r="P15" t="n">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T15" t="n">
-        <v>2.23</v>
+        <v>2.47</v>
       </c>
       <c r="U15" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="M16" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="N16" t="n">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="O16" t="n">
-        <v>6.25</v>
+        <v>5.4</v>
       </c>
       <c r="P16" t="n">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="R16" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.47</v>
+        <v>2.23</v>
       </c>
       <c r="U16" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="V16" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AH16" t="n">
         <v>1.08</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.06</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.14</v>
+        <v>1.65</v>
       </c>
       <c r="M18" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="N18" t="n">
-        <v>2.21</v>
+        <v>4.8</v>
       </c>
       <c r="O18" t="n">
-        <v>3.5</v>
+        <v>2.45</v>
       </c>
       <c r="P18" t="n">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.48</v>
+        <v>4.1</v>
       </c>
       <c r="R18" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="S18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V18" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z18" t="n">
         <v>3.1</v>
       </c>
-      <c r="T18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V18" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>4.05</v>
-      </c>
       <c r="AA18" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.7</v>
+        <v>3.34</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.64</v>
+        <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.27</v>
+        <v>2</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45992.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.29</v>
+        <v>3.1</v>
       </c>
       <c r="M19" t="n">
-        <v>6.25</v>
+        <v>3.6</v>
       </c>
       <c r="N19" t="n">
-        <v>8.5</v>
+        <v>2.26</v>
       </c>
       <c r="O19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V19" t="n">
+        <v>6</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE19" t="n">
         <v>1.62</v>
       </c>
-      <c r="P19" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>7</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V19" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AF19" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.12</v>
+        <v>1.64</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.33</v>
+        <v>1.27</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45992.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.75</v>
+        <v>1.29</v>
       </c>
       <c r="M20" t="n">
-        <v>3.56</v>
+        <v>6.25</v>
       </c>
       <c r="N20" t="n">
-        <v>4.1</v>
+        <v>8.5</v>
       </c>
       <c r="O20" t="n">
-        <v>2.45</v>
+        <v>1.62</v>
       </c>
       <c r="P20" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>7</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T20" t="n">
         <v>2.04</v>
       </c>
-      <c r="Q20" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.9</v>
-      </c>
       <c r="U20" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="V20" t="n">
-        <v>7.3</v>
+        <v>4.4</v>
       </c>
       <c r="W20" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="X20" t="n">
         <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.3</v>
+        <v>1.08</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.1</v>
+        <v>6.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.04</v>
+        <v>1.38</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.72</v>
+        <v>2.95</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.34</v>
+        <v>1.99</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.24</v>
+        <v>1.78</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AH20" t="n">
-        <v>2</v>
+        <v>3.33</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45992.625</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M21" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="N21" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="O21" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P21" t="n">
-        <v>2.51</v>
+        <v>2.25</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="R21" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="S21" t="n">
-        <v>4.75</v>
+        <v>3.7</v>
       </c>
       <c r="T21" t="n">
-        <v>1.85</v>
+        <v>2.23</v>
       </c>
       <c r="U21" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="V21" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="W21" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="Z21" t="n">
-        <v>6.38</v>
+        <v>4.97</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.31</v>
+        <v>1.56</v>
       </c>
       <c r="AB21" t="n">
-        <v>3.37</v>
+        <v>2.43</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.78</v>
+        <v>2.29</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.05</v>
+        <v>1.56</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="AF21" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45992.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="M22" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="N22" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="O22" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P22" t="n">
-        <v>2.25</v>
+        <v>2.51</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="R22" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S22" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V22" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="W22" t="n">
         <v>1.25</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V22" t="n">
-        <v>5</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.15</v>
       </c>
       <c r="X22" t="n">
         <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.97</v>
+        <v>6.38</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.56</v>
+        <v>1.31</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.43</v>
+        <v>3.37</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.29</v>
+        <v>1.78</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.56</v>
+        <v>2.05</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45992.66666666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.95</v>
+        <v>3.42</v>
       </c>
       <c r="M23" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="N23" t="n">
-        <v>3.3</v>
+        <v>2.15</v>
       </c>
       <c r="O23" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.32</v>
+        <v>1.52</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.88</v>
+        <v>2.35</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.07</v>
+        <v>2.62</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.66</v>
+        <v>1.44</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45992.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.42</v>
+        <v>1.95</v>
       </c>
       <c r="M25" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="N25" t="n">
-        <v>2.15</v>
+        <v>3.3</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.52</v>
+        <v>1.32</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.35</v>
+        <v>2.88</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.62</v>
+        <v>2.07</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.44</v>
+        <v>1.66</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45992.6875</v>

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.55</v>
+        <v>3.1</v>
       </c>
       <c r="M5" t="n">
-        <v>3.72</v>
+        <v>3.25</v>
       </c>
       <c r="N5" t="n">
-        <v>5.5</v>
+        <v>2.2</v>
       </c>
       <c r="O5" t="n">
-        <v>2.16</v>
+        <v>3.5</v>
       </c>
       <c r="P5" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.74</v>
+        <v>2.88</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S5" t="n">
-        <v>2.71</v>
+        <v>2.8</v>
       </c>
       <c r="T5" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U5" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="V5" t="n">
-        <v>8.5</v>
+        <v>7.7</v>
       </c>
       <c r="W5" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.16</v>
+        <v>1.95</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.91</v>
+        <v>3.47</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.17</v>
+        <v>1.36</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45992.45833333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.1</v>
+        <v>1.55</v>
       </c>
       <c r="M7" t="n">
-        <v>3.25</v>
+        <v>3.72</v>
       </c>
       <c r="N7" t="n">
-        <v>2.2</v>
+        <v>5.5</v>
       </c>
       <c r="O7" t="n">
-        <v>3.5</v>
+        <v>2.16</v>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.88</v>
+        <v>6.74</v>
       </c>
       <c r="R7" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S7" t="n">
-        <v>2.8</v>
+        <v>2.71</v>
       </c>
       <c r="T7" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U7" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="V7" t="n">
-        <v>7.7</v>
+        <v>8.5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.95</v>
+        <v>2.16</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.47</v>
+        <v>3.91</v>
       </c>
       <c r="AD7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG7" t="n">
         <v>1.25</v>
       </c>
-      <c r="AE7" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AH7" t="n">
-        <v>1.36</v>
+        <v>2.17</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45992.45833333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.21</v>
+        <v>1.15</v>
       </c>
       <c r="M12" t="n">
-        <v>3.7</v>
+        <v>5.8</v>
       </c>
       <c r="N12" t="n">
+        <v>10</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S12" t="n">
         <v>3.28</v>
       </c>
-      <c r="O12" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.1</v>
-      </c>
       <c r="T12" t="n">
-        <v>2.44</v>
+        <v>2.29</v>
       </c>
       <c r="U12" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="V12" t="n">
-        <v>5.25</v>
+        <v>4.4</v>
       </c>
       <c r="W12" t="n">
-        <v>1.09</v>
+        <v>1.19</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.51</v>
+        <v>2.38</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.54</v>
+        <v>2.1</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.28</v>
+        <v>1.6</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.58</v>
+        <v>2.9</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45992.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.84</v>
+        <v>6.5</v>
       </c>
       <c r="M13" t="n">
-        <v>3.46</v>
+        <v>4</v>
       </c>
       <c r="N13" t="n">
-        <v>4</v>
+        <v>1.37</v>
       </c>
       <c r="O13" t="n">
-        <v>2.35</v>
+        <v>6.25</v>
       </c>
       <c r="P13" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.45</v>
+        <v>1.85</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="S13" t="n">
-        <v>2.77</v>
+        <v>3.1</v>
       </c>
       <c r="T13" t="n">
-        <v>2.81</v>
+        <v>2.47</v>
       </c>
       <c r="U13" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V13" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD13" t="n">
         <v>1.38</v>
       </c>
-      <c r="V13" t="n">
-        <v>7</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AE13" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.99</v>
+        <v>1.85</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.91</v>
+        <v>1.06</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.15</v>
+        <v>1.84</v>
       </c>
       <c r="M14" t="n">
-        <v>5.8</v>
+        <v>3.46</v>
       </c>
       <c r="N14" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="O14" t="n">
-        <v>1.62</v>
+        <v>2.35</v>
       </c>
       <c r="P14" t="n">
-        <v>2.7</v>
+        <v>2.33</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.5</v>
+        <v>4.45</v>
       </c>
       <c r="R14" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>3.28</v>
+        <v>2.77</v>
       </c>
       <c r="T14" t="n">
-        <v>2.29</v>
+        <v>2.81</v>
       </c>
       <c r="U14" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="V14" t="n">
-        <v>4.4</v>
+        <v>7</v>
       </c>
       <c r="W14" t="n">
-        <v>1.19</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.33</v>
+        <v>3.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.5</v>
+        <v>1.91</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.04</v>
+        <v>1.86</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.38</v>
+        <v>3.18</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.6</v>
+        <v>1.99</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.9</v>
+        <v>1.91</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="M15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="O15" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V15" t="n">
         <v>6.5</v>
       </c>
-      <c r="M15" t="n">
-        <v>4</v>
-      </c>
-      <c r="N15" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="O15" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Q15" t="n">
+      <c r="W15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AA15" t="n">
         <v>1.85</v>
       </c>
-      <c r="R15" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S15" t="n">
+      <c r="AB15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC15" t="n">
         <v>3.1</v>
       </c>
-      <c r="T15" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V15" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.6</v>
-      </c>
       <c r="AD15" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.8</v>
+        <v>2.07</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>5.8</v>
+        <v>2.21</v>
       </c>
       <c r="M16" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V16" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z16" t="n">
         <v>4.2</v>
       </c>
-      <c r="N16" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="O16" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AA16" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="AD16" t="n">
         <v>1.42</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.73</v>
+        <v>1.54</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.88</v>
+        <v>2.28</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.08</v>
+        <v>1.58</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>8.300000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="M17" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="N17" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="O17" t="n">
-        <v>6.57</v>
+        <v>5.4</v>
       </c>
       <c r="P17" t="n">
-        <v>2.24</v>
+        <v>2.5</v>
       </c>
       <c r="Q17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE17" t="n">
         <v>1.73</v>
       </c>
-      <c r="R17" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>2.07</v>
-      </c>
       <c r="AF17" t="n">
-        <v>1.58</v>
+        <v>1.88</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.65</v>
+        <v>1.29</v>
       </c>
       <c r="M18" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="N18" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>7</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S18" t="n">
         <v>3.75</v>
       </c>
-      <c r="N18" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O18" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="P18" t="n">
+      <c r="T18" t="n">
         <v>2.04</v>
       </c>
-      <c r="Q18" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.9</v>
-      </c>
       <c r="U18" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="V18" t="n">
-        <v>7.3</v>
+        <v>4.4</v>
       </c>
       <c r="W18" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.3</v>
+        <v>1.08</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.1</v>
+        <v>6.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.9</v>
+        <v>1.38</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.8</v>
+        <v>2.95</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.34</v>
+        <v>1.99</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.24</v>
+        <v>1.78</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AH18" t="n">
-        <v>2</v>
+        <v>3.33</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45992.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.29</v>
+        <v>1.65</v>
       </c>
       <c r="M20" t="n">
-        <v>6.25</v>
+        <v>3.75</v>
       </c>
       <c r="N20" t="n">
-        <v>8.5</v>
+        <v>4.8</v>
       </c>
       <c r="O20" t="n">
-        <v>1.62</v>
+        <v>2.45</v>
       </c>
       <c r="P20" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S20" t="n">
         <v>2.75</v>
       </c>
-      <c r="Q20" t="n">
-        <v>7</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.75</v>
-      </c>
       <c r="T20" t="n">
-        <v>2.04</v>
+        <v>2.9</v>
       </c>
       <c r="U20" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="V20" t="n">
-        <v>4.4</v>
+        <v>7.3</v>
       </c>
       <c r="W20" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="X20" t="n">
         <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.08</v>
+        <v>1.3</v>
       </c>
       <c r="Z20" t="n">
-        <v>6.5</v>
+        <v>3.1</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.38</v>
+        <v>1.9</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.95</v>
+        <v>1.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.99</v>
+        <v>3.34</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.78</v>
+        <v>1.24</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AF20" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH20" t="n">
         <v>2</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>3.33</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45992.625</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="M23" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="N23" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="Z23" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AA23" t="n">
         <v>2.35</v>
       </c>
-      <c r="AA23" t="n">
-        <v>2.62</v>
-      </c>
       <c r="AB23" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45992.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.5</v>
+        <v>1.95</v>
       </c>
       <c r="M24" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="N24" t="n">
-        <v>2.15</v>
+        <v>3.3</v>
       </c>
       <c r="O24" t="n">
-        <v>4.25</v>
+        <v>2.58</v>
       </c>
       <c r="P24" t="n">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="Q24" t="n">
-        <v>3</v>
+        <v>4.45</v>
       </c>
       <c r="R24" t="n">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="S24" t="n">
-        <v>2.24</v>
+        <v>2.65</v>
       </c>
       <c r="T24" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V24" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC24" t="n">
         <v>3.58</v>
       </c>
-      <c r="U24" t="n">
+      <c r="AD24" t="n">
         <v>1.21</v>
       </c>
-      <c r="V24" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AE24" t="n">
-        <v>2.06</v>
+        <v>1.83</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.65</v>
+        <v>1.81</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.24</v>
+        <v>1.66</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45992.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.95</v>
+        <v>2.8</v>
       </c>
       <c r="M25" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N25" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="O25" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.32</v>
+        <v>1.52</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.88</v>
+        <v>2.35</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.07</v>
+        <v>2.62</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.66</v>
+        <v>1.44</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45992.6875</v>
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="M26" t="n">
         <v>3.9</v>
@@ -3524,10 +3524,10 @@
         <v>8</v>
       </c>
       <c r="O26" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="P26" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="Q26" t="n">
         <v>7</v>
@@ -3539,7 +3539,7 @@
         <v>2.79</v>
       </c>
       <c r="T26" t="n">
-        <v>3.13</v>
+        <v>3.09</v>
       </c>
       <c r="U26" t="n">
         <v>1.38</v>
@@ -3554,16 +3554,16 @@
         <v>1.04</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.12</v>
+        <v>3.16</v>
       </c>
       <c r="AA26" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AC26" t="n">
         <v>3.55</v>
@@ -3572,16 +3572,16 @@
         <v>1.3</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.85</v>
+        <v>2.63</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>45992.69791666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="M27" t="n">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="N27" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O27" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="P27" t="n">
-        <v>2.03</v>
+        <v>2.14</v>
       </c>
       <c r="Q27" t="n">
-        <v>5.22</v>
+        <v>4.6</v>
       </c>
       <c r="R27" t="n">
         <v>1.4</v>
       </c>
       <c r="S27" t="n">
-        <v>2.86</v>
+        <v>2.6</v>
       </c>
       <c r="T27" t="n">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="U27" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="V27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W27" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="AB27" t="n">
         <v>1.75</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.52</v>
+        <v>3.56</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>45992.70833333334</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="M28" t="n">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="N28" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="O28" t="n">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="P28" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.6</v>
+        <v>5.53</v>
       </c>
       <c r="R28" t="n">
         <v>1.4</v>
       </c>
       <c r="S28" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="T28" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U28" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W28" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X28" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="AB28" t="n">
         <v>1.74</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45992.70833333334</v>
@@ -3875,25 +3875,25 @@
         <v>6</v>
       </c>
       <c r="M29" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="N29" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="O29" t="n">
-        <v>4.84</v>
+        <v>5.5</v>
       </c>
       <c r="P29" t="n">
-        <v>2.21</v>
+        <v>2.4</v>
       </c>
       <c r="Q29" t="n">
         <v>2.1</v>
       </c>
       <c r="R29" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S29" t="n">
-        <v>3.21</v>
+        <v>3.1</v>
       </c>
       <c r="T29" t="n">
         <v>2.65</v>
@@ -3908,7 +3908,7 @@
         <v>1.05</v>
       </c>
       <c r="X29" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y29" t="n">
         <v>1.23</v>
@@ -3920,7 +3920,7 @@
         <v>1.83</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AC29" t="n">
         <v>2.98</v>

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>6.27</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45992.45833333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.74</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45992.45833333334</v>
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="M9" t="n">
-        <v>3.38</v>
+        <v>3.65</v>
       </c>
       <c r="N9" t="n">
-        <v>5.73</v>
+        <v>4.9</v>
       </c>
       <c r="O9" t="n">
         <v>2.12</v>
@@ -1507,7 +1507,7 @@
         <v>2.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="R9" t="n">
         <v>1.43</v>
@@ -1519,7 +1519,7 @@
         <v>3.19</v>
       </c>
       <c r="U9" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V9" t="n">
         <v>7.8</v>
@@ -1534,16 +1534,16 @@
         <v>1.32</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.02</v>
+        <v>2.88</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.16</v>
+        <v>1.97</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.72</v>
+        <v>3.88</v>
       </c>
       <c r="AD9" t="n">
         <v>1.2</v>
@@ -1555,10 +1555,10 @@
         <v>1.66</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.32</v>
+        <v>2.13</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45992.54166666666</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3</v>
+        <v>6.5</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="N11" t="n">
-        <v>2.13</v>
+        <v>1.37</v>
       </c>
       <c r="O11" t="n">
-        <v>3.4</v>
+        <v>6.25</v>
       </c>
       <c r="P11" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.83</v>
+        <v>1.85</v>
       </c>
       <c r="R11" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="S11" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="T11" t="n">
-        <v>2.73</v>
+        <v>2.47</v>
       </c>
       <c r="U11" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="V11" t="n">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.35</v>
+        <v>2.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AF11" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.6</v>
+        <v>1.13</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.35</v>
+        <v>1.06</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45992.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.15</v>
+        <v>2.21</v>
       </c>
       <c r="M12" t="n">
-        <v>5.8</v>
+        <v>3.7</v>
       </c>
       <c r="N12" t="n">
-        <v>10</v>
+        <v>3.28</v>
       </c>
       <c r="O12" t="n">
-        <v>1.62</v>
+        <v>2.75</v>
       </c>
       <c r="P12" t="n">
-        <v>2.7</v>
+        <v>2.24</v>
       </c>
       <c r="Q12" t="n">
-        <v>8.5</v>
+        <v>3.62</v>
       </c>
       <c r="R12" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="S12" t="n">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="T12" t="n">
-        <v>2.29</v>
+        <v>2.44</v>
       </c>
       <c r="U12" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="V12" t="n">
-        <v>4.4</v>
+        <v>5.25</v>
       </c>
       <c r="W12" t="n">
-        <v>1.19</v>
+        <v>1.09</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.38</v>
+        <v>2.51</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.1</v>
+        <v>1.54</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.6</v>
+        <v>2.28</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.9</v>
+        <v>1.58</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45992.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="M13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="O13" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V13" t="n">
         <v>6.5</v>
       </c>
-      <c r="M13" t="n">
-        <v>4</v>
-      </c>
-      <c r="N13" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="O13" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Q13" t="n">
+      <c r="W13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AA13" t="n">
         <v>1.85</v>
       </c>
-      <c r="R13" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S13" t="n">
+      <c r="AB13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC13" t="n">
         <v>3.1</v>
       </c>
-      <c r="T13" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V13" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.6</v>
-      </c>
       <c r="AD13" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.8</v>
+        <v>2.07</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.84</v>
+        <v>5.8</v>
       </c>
       <c r="M14" t="n">
-        <v>3.46</v>
+        <v>4.2</v>
       </c>
       <c r="N14" t="n">
-        <v>4</v>
+        <v>1.49</v>
       </c>
       <c r="O14" t="n">
-        <v>2.35</v>
+        <v>5.4</v>
       </c>
       <c r="P14" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.45</v>
+        <v>1.91</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.81</v>
+        <v>2.23</v>
       </c>
       <c r="U14" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="V14" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.91</v>
+        <v>1.64</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.86</v>
+        <v>2.08</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.18</v>
+        <v>2.63</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.99</v>
+        <v>1.88</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.91</v>
+        <v>1.08</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>8.300000000000001</v>
+        <v>1.84</v>
       </c>
       <c r="M15" t="n">
-        <v>4.6</v>
+        <v>3.46</v>
       </c>
       <c r="N15" t="n">
-        <v>1.36</v>
+        <v>4</v>
       </c>
       <c r="O15" t="n">
-        <v>6.57</v>
+        <v>2.35</v>
       </c>
       <c r="P15" t="n">
-        <v>2.24</v>
+        <v>2.33</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.73</v>
+        <v>4.45</v>
       </c>
       <c r="R15" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>3.01</v>
+        <v>2.77</v>
       </c>
       <c r="T15" t="n">
-        <v>2.69</v>
+        <v>2.81</v>
       </c>
       <c r="U15" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="V15" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="W15" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.07</v>
+        <v>1.82</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.58</v>
+        <v>1.99</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.21</v>
+        <v>1.15</v>
       </c>
       <c r="M16" t="n">
-        <v>3.7</v>
+        <v>5.8</v>
       </c>
       <c r="N16" t="n">
+        <v>10</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S16" t="n">
         <v>3.28</v>
       </c>
-      <c r="O16" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.1</v>
-      </c>
       <c r="T16" t="n">
-        <v>2.44</v>
+        <v>2.29</v>
       </c>
       <c r="U16" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="V16" t="n">
-        <v>5.25</v>
+        <v>4.4</v>
       </c>
       <c r="W16" t="n">
-        <v>1.09</v>
+        <v>1.19</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.51</v>
+        <v>2.38</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.54</v>
+        <v>2.1</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.28</v>
+        <v>1.6</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.58</v>
+        <v>2.9</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>5.8</v>
+        <v>2.79</v>
       </c>
       <c r="M17" t="n">
-        <v>4.2</v>
+        <v>3.23</v>
       </c>
       <c r="N17" t="n">
-        <v>1.49</v>
+        <v>2.21</v>
       </c>
       <c r="O17" t="n">
-        <v>5.4</v>
+        <v>3.4</v>
       </c>
       <c r="P17" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.91</v>
+        <v>2.89</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T17" t="n">
-        <v>2.23</v>
+        <v>2.9</v>
       </c>
       <c r="U17" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.64</v>
+        <v>1.93</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.08</v>
+        <v>1.77</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.63</v>
+        <v>3.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.15</v>
+        <v>1.6</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.08</v>
+        <v>1.34</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.29</v>
+        <v>1.65</v>
       </c>
       <c r="M18" t="n">
-        <v>6.25</v>
+        <v>3.75</v>
       </c>
       <c r="N18" t="n">
-        <v>8.5</v>
+        <v>4.8</v>
       </c>
       <c r="O18" t="n">
-        <v>1.62</v>
+        <v>2.45</v>
       </c>
       <c r="P18" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S18" t="n">
         <v>2.75</v>
       </c>
-      <c r="Q18" t="n">
-        <v>7</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.75</v>
-      </c>
       <c r="T18" t="n">
-        <v>2.04</v>
+        <v>2.9</v>
       </c>
       <c r="U18" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="V18" t="n">
-        <v>4.4</v>
+        <v>7.3</v>
       </c>
       <c r="W18" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.08</v>
+        <v>1.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>6.5</v>
+        <v>3.1</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.38</v>
+        <v>1.9</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.95</v>
+        <v>1.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.99</v>
+        <v>3.34</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.78</v>
+        <v>1.24</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AF18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH18" t="n">
         <v>2</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>3.33</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45992.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.1</v>
+        <v>1.29</v>
       </c>
       <c r="M19" t="n">
-        <v>3.6</v>
+        <v>6.25</v>
       </c>
       <c r="N19" t="n">
-        <v>2.26</v>
+        <v>8.5</v>
       </c>
       <c r="O19" t="n">
-        <v>3.5</v>
+        <v>1.62</v>
       </c>
       <c r="P19" t="n">
-        <v>2.15</v>
+        <v>2.75</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.48</v>
+        <v>7</v>
       </c>
       <c r="R19" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="S19" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="T19" t="n">
-        <v>2.5</v>
+        <v>2.04</v>
       </c>
       <c r="U19" t="n">
-        <v>1.46</v>
+        <v>1.73</v>
       </c>
       <c r="V19" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="W19" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="X19" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="Z19" t="n">
-        <v>4</v>
+        <v>6.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.7</v>
+        <v>1.38</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.02</v>
+        <v>2.95</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.7</v>
+        <v>1.99</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.4</v>
+        <v>1.78</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.64</v>
+        <v>1.12</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.27</v>
+        <v>3.33</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45992.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V20" t="n">
+        <v>6</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA20" t="n">
         <v>1.65</v>
       </c>
-      <c r="M20" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N20" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O20" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U20" t="n">
+      <c r="AB20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD20" t="n">
         <v>1.4</v>
       </c>
-      <c r="V20" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AE20" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>1.64</v>
       </c>
       <c r="AH20" t="n">
-        <v>2</v>
+        <v>1.27</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45992.625</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.95</v>
+        <v>2.8</v>
       </c>
       <c r="M24" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N24" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="O24" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.32</v>
+        <v>1.52</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.88</v>
+        <v>2.35</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.07</v>
+        <v>2.62</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.66</v>
+        <v>1.44</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45992.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.8</v>
+        <v>1.95</v>
       </c>
       <c r="M25" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N25" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.52</v>
+        <v>1.32</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.35</v>
+        <v>2.88</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.62</v>
+        <v>2.07</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.44</v>
+        <v>1.66</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45992.6875</v>
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="M26" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="N26" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="O26" t="n">
         <v>1.91</v>
@@ -3560,10 +3560,10 @@
         <v>3.16</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.03</v>
+        <v>1.97</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AC26" t="n">
         <v>3.55</v>
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="M29" t="n">
         <v>4.1</v>
       </c>
       <c r="N29" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="O29" t="n">
         <v>5.5</v>
@@ -3917,10 +3917,10 @@
         <v>3.7</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.83</v>
+        <v>1.63</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AC29" t="n">
         <v>2.98</v>

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -900,10 +900,10 @@
         <v>2.15</v>
       </c>
       <c r="M4" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="N4" t="n">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.1</v>
+        <v>1.61</v>
       </c>
       <c r="M5" t="n">
-        <v>3.25</v>
+        <v>3.41</v>
       </c>
       <c r="N5" t="n">
-        <v>2.2</v>
+        <v>4.8</v>
       </c>
       <c r="O5" t="n">
-        <v>3.5</v>
+        <v>2.25</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.88</v>
+        <v>6.37</v>
       </c>
       <c r="R5" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V5" t="n">
+        <v>9</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y5" t="n">
         <v>1.36</v>
       </c>
-      <c r="S5" t="n">
+      <c r="Z5" t="n">
         <v>2.8</v>
       </c>
-      <c r="T5" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V5" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3.1</v>
-      </c>
       <c r="AA5" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.47</v>
+        <v>4.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.75</v>
+        <v>2.16</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.36</v>
+        <v>2.16</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45992.45833333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.27</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45992.45833333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45992.45833333334</v>
@@ -1376,31 +1376,31 @@
         <v>2.36</v>
       </c>
       <c r="M8" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="N8" t="n">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="O8" t="n">
         <v>2.8</v>
       </c>
       <c r="P8" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="R8" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S8" t="n">
         <v>3.7</v>
       </c>
       <c r="T8" t="n">
-        <v>2.04</v>
+        <v>2.09</v>
       </c>
       <c r="U8" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="V8" t="n">
         <v>4.2</v>
@@ -1412,7 +1412,7 @@
         <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="Z8" t="n">
         <v>5.67</v>
@@ -1421,25 +1421,25 @@
         <v>1.43</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45992.54166666666</v>
@@ -1504,16 +1504,16 @@
         <v>2.12</v>
       </c>
       <c r="P9" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.4</v>
+        <v>5.22</v>
       </c>
       <c r="R9" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S9" t="n">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="T9" t="n">
         <v>3.19</v>
@@ -1543,7 +1543,7 @@
         <v>1.73</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.88</v>
+        <v>3.72</v>
       </c>
       <c r="AD9" t="n">
         <v>1.2</v>
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="N10" t="n">
-        <v>2.49</v>
+        <v>3.05</v>
       </c>
       <c r="O10" t="n">
         <v>3.92</v>
@@ -1650,16 +1650,16 @@
         <v>1.09</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="AC10" t="n">
         <v>5.3</v>
@@ -1668,7 +1668,7 @@
         <v>1.09</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
       <c r="AF10" t="n">
         <v>1.63</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>6.5</v>
+        <v>2.79</v>
       </c>
       <c r="M11" t="n">
-        <v>4</v>
+        <v>3.23</v>
       </c>
       <c r="N11" t="n">
-        <v>1.37</v>
+        <v>2.21</v>
       </c>
       <c r="O11" t="n">
-        <v>6.25</v>
+        <v>3.4</v>
       </c>
       <c r="P11" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.85</v>
+        <v>2.89</v>
       </c>
       <c r="R11" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="S11" t="n">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="T11" t="n">
-        <v>2.47</v>
+        <v>2.9</v>
       </c>
       <c r="U11" t="n">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="V11" t="n">
-        <v>5.7</v>
+        <v>6.9</v>
       </c>
       <c r="W11" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.72</v>
+        <v>1.93</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.1</v>
+        <v>1.77</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.6</v>
+        <v>3.34</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.06</v>
+        <v>1.34</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45992.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.21</v>
+        <v>8</v>
       </c>
       <c r="M12" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="N12" t="n">
-        <v>3.28</v>
+        <v>1.4</v>
       </c>
       <c r="O12" t="n">
-        <v>2.75</v>
+        <v>8.6</v>
       </c>
       <c r="P12" t="n">
         <v>2.24</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.62</v>
+        <v>1.73</v>
       </c>
       <c r="R12" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD12" t="n">
         <v>1.33</v>
       </c>
-      <c r="S12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V12" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y12" t="n">
+      <c r="AE12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG12" t="n">
         <v>1.2</v>
       </c>
-      <c r="Z12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH12" t="n">
-        <v>1.58</v>
+        <v>1.06</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45992.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>8.300000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="M13" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="N13" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="O13" t="n">
-        <v>6.57</v>
+        <v>5.4</v>
       </c>
       <c r="P13" t="n">
-        <v>2.24</v>
+        <v>2.5</v>
       </c>
       <c r="Q13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE13" t="n">
         <v>1.73</v>
       </c>
-      <c r="R13" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V13" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>2.07</v>
-      </c>
       <c r="AF13" t="n">
-        <v>1.58</v>
+        <v>1.88</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>5.8</v>
+        <v>2.21</v>
       </c>
       <c r="M14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V14" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z14" t="n">
         <v>4.2</v>
       </c>
-      <c r="N14" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="O14" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AA14" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="AD14" t="n">
         <v>1.42</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.73</v>
+        <v>1.54</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.88</v>
+        <v>2.28</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.08</v>
+        <v>1.58</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.84</v>
+        <v>1.25</v>
       </c>
       <c r="M15" t="n">
-        <v>3.46</v>
+        <v>5.8</v>
       </c>
       <c r="N15" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="O15" t="n">
-        <v>2.35</v>
+        <v>1.62</v>
       </c>
       <c r="P15" t="n">
-        <v>2.33</v>
+        <v>2.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.45</v>
+        <v>8.5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="S15" t="n">
-        <v>2.77</v>
+        <v>3.28</v>
       </c>
       <c r="T15" t="n">
-        <v>2.81</v>
+        <v>2.21</v>
       </c>
       <c r="U15" t="n">
-        <v>1.38</v>
+        <v>1.59</v>
       </c>
       <c r="V15" t="n">
-        <v>7</v>
+        <v>4.4</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.19</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.91</v>
+        <v>1.63</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.86</v>
+        <v>2.25</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.18</v>
+        <v>2.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.32</v>
+        <v>1.53</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.99</v>
+        <v>1.7</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.91</v>
+        <v>3.9</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.15</v>
+        <v>1.84</v>
       </c>
       <c r="M16" t="n">
-        <v>5.8</v>
+        <v>3.46</v>
       </c>
       <c r="N16" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="O16" t="n">
-        <v>1.62</v>
+        <v>2.35</v>
       </c>
       <c r="P16" t="n">
-        <v>2.7</v>
+        <v>2.33</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.5</v>
+        <v>4.45</v>
       </c>
       <c r="R16" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="S16" t="n">
-        <v>3.28</v>
+        <v>2.77</v>
       </c>
       <c r="T16" t="n">
-        <v>2.29</v>
+        <v>2.81</v>
       </c>
       <c r="U16" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="V16" t="n">
-        <v>4.4</v>
+        <v>7</v>
       </c>
       <c r="W16" t="n">
-        <v>1.19</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.33</v>
+        <v>3.3</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.5</v>
+        <v>1.91</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.04</v>
+        <v>1.86</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.38</v>
+        <v>3.18</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.6</v>
+        <v>1.99</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.9</v>
+        <v>1.91</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.79</v>
+        <v>6.5</v>
       </c>
       <c r="M17" t="n">
-        <v>3.23</v>
+        <v>4</v>
       </c>
       <c r="N17" t="n">
-        <v>2.21</v>
+        <v>1.37</v>
       </c>
       <c r="O17" t="n">
-        <v>3.4</v>
+        <v>6.25</v>
       </c>
       <c r="P17" t="n">
-        <v>2.14</v>
+        <v>2.32</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.89</v>
+        <v>1.85</v>
       </c>
       <c r="R17" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="S17" t="n">
-        <v>2.81</v>
+        <v>3.1</v>
       </c>
       <c r="T17" t="n">
-        <v>2.9</v>
+        <v>2.47</v>
       </c>
       <c r="U17" t="n">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="V17" t="n">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="W17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X17" t="n">
         <v>1.04</v>
       </c>
-      <c r="X17" t="n">
-        <v>1.02</v>
-      </c>
       <c r="Y17" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.93</v>
+        <v>1.72</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.6</v>
+        <v>1.13</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.34</v>
+        <v>1.06</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.65</v>
+        <v>3.05</v>
       </c>
       <c r="M18" t="n">
-        <v>3.75</v>
+        <v>3.39</v>
       </c>
       <c r="N18" t="n">
-        <v>4.8</v>
+        <v>2.01</v>
       </c>
       <c r="O18" t="n">
-        <v>2.45</v>
+        <v>3.78</v>
       </c>
       <c r="P18" t="n">
-        <v>2.04</v>
+        <v>2.38</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.1</v>
+        <v>2.48</v>
       </c>
       <c r="R18" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="S18" t="n">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="T18" t="n">
-        <v>2.9</v>
+        <v>2.35</v>
       </c>
       <c r="U18" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="V18" t="n">
-        <v>7.3</v>
+        <v>5.4</v>
       </c>
       <c r="W18" t="n">
         <v>1.07</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y18" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG18" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH18" t="n">
-        <v>2</v>
+        <v>1.32</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45992.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.29</v>
+        <v>1.65</v>
       </c>
       <c r="M19" t="n">
-        <v>6.25</v>
+        <v>3.75</v>
       </c>
       <c r="N19" t="n">
-        <v>8.5</v>
+        <v>4.8</v>
       </c>
       <c r="O19" t="n">
-        <v>1.62</v>
+        <v>2.45</v>
       </c>
       <c r="P19" t="n">
-        <v>2.75</v>
+        <v>2.04</v>
       </c>
       <c r="Q19" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="S19" t="n">
-        <v>3.75</v>
+        <v>2.62</v>
       </c>
       <c r="T19" t="n">
-        <v>2.04</v>
+        <v>2.9</v>
       </c>
       <c r="U19" t="n">
-        <v>1.73</v>
+        <v>1.35</v>
       </c>
       <c r="V19" t="n">
-        <v>4.4</v>
+        <v>7.3</v>
       </c>
       <c r="W19" t="n">
-        <v>1.18</v>
+        <v>1.03</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="Z19" t="n">
-        <v>6.5</v>
+        <v>3.2</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.38</v>
+        <v>1.9</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.95</v>
+        <v>1.8</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.99</v>
+        <v>3.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.78</v>
+        <v>1.25</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AF19" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.33</v>
+        <v>1.95</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45992.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.05</v>
+        <v>1.21</v>
       </c>
       <c r="M20" t="n">
-        <v>3.39</v>
+        <v>5.6</v>
       </c>
       <c r="N20" t="n">
-        <v>2.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>7</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="V20" t="n">
+        <v>4</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AH20" t="n">
         <v>3.5</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V20" t="n">
-        <v>6</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.27</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45992.625</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.6</v>
+        <v>1.97</v>
       </c>
       <c r="M23" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="N23" t="n">
-        <v>2.07</v>
+        <v>3.75</v>
       </c>
       <c r="O23" t="n">
-        <v>4.03</v>
+        <v>2.72</v>
       </c>
       <c r="P23" t="n">
-        <v>1.92</v>
+        <v>2.09</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.93</v>
+        <v>4.04</v>
       </c>
       <c r="R23" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="S23" t="n">
-        <v>2.24</v>
+        <v>2.5</v>
       </c>
       <c r="T23" t="n">
-        <v>3.58</v>
+        <v>2.9</v>
       </c>
       <c r="U23" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="V23" t="n">
-        <v>8.5</v>
+        <v>7.9</v>
       </c>
       <c r="W23" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X23" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.43</v>
+        <v>2.98</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AC23" t="n">
-        <v>4</v>
+        <v>3.74</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.53</v>
+        <v>1.27</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.24</v>
+        <v>1.63</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45992.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="M24" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N24" t="n">
-        <v>2.4</v>
+        <v>2.07</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="Z24" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AA24" t="n">
         <v>2.35</v>
       </c>
-      <c r="AA24" t="n">
-        <v>2.62</v>
-      </c>
       <c r="AB24" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45992.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.95</v>
+        <v>2.8</v>
       </c>
       <c r="M25" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N25" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="O25" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.32</v>
+        <v>1.52</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.88</v>
+        <v>2.35</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.07</v>
+        <v>2.62</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.66</v>
+        <v>1.44</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45992.6875</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="M27" t="n">
-        <v>3.32</v>
+        <v>3.65</v>
       </c>
       <c r="N27" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="O27" t="n">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="P27" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.6</v>
+        <v>5.53</v>
       </c>
       <c r="R27" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="S27" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T27" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="U27" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W27" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X27" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.1</v>
+        <v>3.26</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>45992.70833333334</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="M28" t="n">
-        <v>3.5</v>
+        <v>3.32</v>
       </c>
       <c r="N28" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="O28" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="P28" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="Q28" t="n">
-        <v>5.53</v>
+        <v>4.6</v>
       </c>
       <c r="R28" t="n">
         <v>1.4</v>
       </c>
       <c r="S28" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="T28" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="U28" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W28" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X28" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.54</v>
+        <v>3.56</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AF28" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH28" t="n">
         <v>1.85</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>2.04</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45992.70833333334</v>
@@ -3881,10 +3881,10 @@
         <v>1.6</v>
       </c>
       <c r="O29" t="n">
-        <v>5.5</v>
+        <v>6.05</v>
       </c>
       <c r="P29" t="n">
-        <v>2.4</v>
+        <v>2.21</v>
       </c>
       <c r="Q29" t="n">
         <v>2.1</v>
@@ -3893,13 +3893,13 @@
         <v>1.35</v>
       </c>
       <c r="S29" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="T29" t="n">
-        <v>2.65</v>
+        <v>2.48</v>
       </c>
       <c r="U29" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="V29" t="n">
         <v>6.5</v>
@@ -3908,7 +3908,7 @@
         <v>1.05</v>
       </c>
       <c r="X29" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y29" t="n">
         <v>1.23</v>
@@ -3929,10 +3929,10 @@
         <v>1.33</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AG29" t="n">
         <v>1.25</v>

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.61</v>
+        <v>3.1</v>
       </c>
       <c r="M5" t="n">
-        <v>3.41</v>
+        <v>3.25</v>
       </c>
       <c r="N5" t="n">
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="O5" t="n">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="P5" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.37</v>
+        <v>2.8</v>
       </c>
       <c r="R5" t="n">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="S5" t="n">
-        <v>2.47</v>
+        <v>2.7</v>
       </c>
       <c r="T5" t="n">
-        <v>3.28</v>
+        <v>2.9</v>
       </c>
       <c r="U5" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="V5" t="n">
-        <v>9</v>
+        <v>7.7</v>
       </c>
       <c r="W5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X5" t="n">
         <v>1</v>
       </c>
-      <c r="X5" t="n">
-        <v>1.08</v>
-      </c>
       <c r="Y5" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.2</v>
+        <v>3.47</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.16</v>
+        <v>1.75</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AG5" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AH5" t="n">
         <v>1.3</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>2.16</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45992.45833333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.1</v>
+        <v>1.61</v>
       </c>
       <c r="M7" t="n">
-        <v>3.25</v>
+        <v>3.41</v>
       </c>
       <c r="N7" t="n">
-        <v>2.2</v>
+        <v>4.8</v>
       </c>
       <c r="O7" t="n">
-        <v>3.5</v>
+        <v>2.25</v>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="Q7" t="n">
+        <v>6.37</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V7" t="n">
+        <v>9</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z7" t="n">
         <v>2.8</v>
       </c>
-      <c r="R7" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V7" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3.1</v>
-      </c>
       <c r="AA7" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.47</v>
+        <v>4.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.75</v>
+        <v>2.16</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.3</v>
+        <v>2.16</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45992.45833333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.79</v>
+        <v>2.2</v>
       </c>
       <c r="M11" t="n">
-        <v>3.23</v>
+        <v>3.65</v>
       </c>
       <c r="N11" t="n">
-        <v>2.21</v>
+        <v>2.78</v>
       </c>
       <c r="O11" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="P11" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.89</v>
+        <v>3.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="S11" t="n">
-        <v>2.62</v>
+        <v>3.04</v>
       </c>
       <c r="T11" t="n">
-        <v>2.9</v>
+        <v>2.35</v>
       </c>
       <c r="U11" t="n">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="V11" t="n">
-        <v>6.9</v>
+        <v>5.4</v>
       </c>
       <c r="W11" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X11" t="n">
         <v>1.04</v>
       </c>
-      <c r="X11" t="n">
-        <v>1.02</v>
-      </c>
       <c r="Y11" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.93</v>
+        <v>1.68</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.34</v>
+        <v>2.48</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.75</v>
+        <v>1.52</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.94</v>
+        <v>2.3</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.34</v>
+        <v>1.66</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45992.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M13" t="n">
         <v>5.8</v>
       </c>
-      <c r="M13" t="n">
-        <v>4.2</v>
-      </c>
       <c r="N13" t="n">
-        <v>1.49</v>
+        <v>14</v>
       </c>
       <c r="O13" t="n">
-        <v>5.4</v>
+        <v>1.62</v>
       </c>
       <c r="P13" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.91</v>
+        <v>8.5</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="T13" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="U13" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.88</v>
+        <v>1.7</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.08</v>
+        <v>3.9</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.21</v>
+        <v>5.8</v>
       </c>
       <c r="M14" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="N14" t="n">
-        <v>3.28</v>
+        <v>1.49</v>
       </c>
       <c r="O14" t="n">
-        <v>2.75</v>
+        <v>5.4</v>
       </c>
       <c r="P14" t="n">
-        <v>2.24</v>
+        <v>2.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.62</v>
+        <v>1.91</v>
       </c>
       <c r="R14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.44</v>
+        <v>2.23</v>
       </c>
       <c r="U14" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="V14" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.51</v>
+        <v>2.63</v>
       </c>
       <c r="AD14" t="n">
         <v>1.42</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.54</v>
+        <v>1.73</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.28</v>
+        <v>1.88</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.58</v>
+        <v>1.08</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V15" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AD15" t="n">
         <v>1.25</v>
       </c>
-      <c r="M15" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="N15" t="n">
-        <v>14</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="V15" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AE15" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.7</v>
+        <v>1.94</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AH15" t="n">
-        <v>3.9</v>
+        <v>1.34</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2328,7 +2328,7 @@
         <v>1.84</v>
       </c>
       <c r="M16" t="n">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="N16" t="n">
         <v>4</v>
@@ -2340,10 +2340,10 @@
         <v>2.33</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.45</v>
+        <v>4.6</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S16" t="n">
         <v>2.77</v>
@@ -2355,40 +2355,40 @@
         <v>1.38</v>
       </c>
       <c r="V16" t="n">
-        <v>7</v>
+        <v>5.75</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X16" t="n">
         <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z16" t="n">
         <v>3.3</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AC16" t="n">
         <v>3.18</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.99</v>
+        <v>1.89</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH16" t="n">
         <v>1.91</v>
@@ -2447,16 +2447,16 @@
         <v>6.5</v>
       </c>
       <c r="M17" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="N17" t="n">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="O17" t="n">
-        <v>6.25</v>
+        <v>6.1</v>
       </c>
       <c r="P17" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q17" t="n">
         <v>1.85</v>
@@ -2465,52 +2465,52 @@
         <v>1.32</v>
       </c>
       <c r="S17" t="n">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="T17" t="n">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="U17" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="V17" t="n">
-        <v>5.7</v>
+        <v>5.55</v>
       </c>
       <c r="W17" t="n">
         <v>1.08</v>
       </c>
       <c r="X17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
         <v>1.2</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AC17" t="n">
         <v>2.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AF17" t="n">
         <v>1.85</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.05</v>
+        <v>1.65</v>
       </c>
       <c r="M18" t="n">
-        <v>3.39</v>
+        <v>3.75</v>
       </c>
       <c r="N18" t="n">
-        <v>2.01</v>
+        <v>4.8</v>
       </c>
       <c r="O18" t="n">
-        <v>3.78</v>
+        <v>2.45</v>
       </c>
       <c r="P18" t="n">
-        <v>2.38</v>
+        <v>2.04</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.48</v>
+        <v>4.5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="S18" t="n">
-        <v>3.05</v>
+        <v>2.62</v>
       </c>
       <c r="T18" t="n">
-        <v>2.35</v>
+        <v>2.9</v>
       </c>
       <c r="U18" t="n">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="V18" t="n">
-        <v>5.4</v>
+        <v>7.3</v>
       </c>
       <c r="W18" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="Z18" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AG18" t="n">
         <v>1.3</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.32</v>
+        <v>1.95</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45992.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="M19" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="N19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="O19" t="n">
         <v>1.65</v>
       </c>
-      <c r="M19" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O19" t="n">
-        <v>2.45</v>
-      </c>
       <c r="P19" t="n">
-        <v>2.04</v>
+        <v>2.75</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="R19" t="n">
-        <v>1.42</v>
+        <v>1.19</v>
       </c>
       <c r="S19" t="n">
-        <v>2.62</v>
+        <v>3.94</v>
       </c>
       <c r="T19" t="n">
-        <v>2.9</v>
+        <v>2.02</v>
       </c>
       <c r="U19" t="n">
-        <v>1.35</v>
+        <v>1.74</v>
       </c>
       <c r="V19" t="n">
-        <v>7.3</v>
+        <v>4</v>
       </c>
       <c r="W19" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="X19" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.28</v>
+        <v>1.08</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.2</v>
+        <v>5.7</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.8</v>
+        <v>2.75</v>
       </c>
       <c r="AC19" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AH19" t="n">
         <v>3.5</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.95</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45992.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.21</v>
+        <v>3.05</v>
       </c>
       <c r="M20" t="n">
-        <v>5.6</v>
+        <v>3.39</v>
       </c>
       <c r="N20" t="n">
-        <v>8.800000000000001</v>
+        <v>2.01</v>
       </c>
       <c r="O20" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V20" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA20" t="n">
         <v>1.65</v>
       </c>
-      <c r="P20" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>7</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="V20" t="n">
-        <v>4</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AA20" t="n">
+      <c r="AB20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD20" t="n">
         <v>1.4</v>
       </c>
-      <c r="AB20" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.79</v>
-      </c>
       <c r="AE20" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AH20" t="n">
-        <v>3.5</v>
+        <v>1.32</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45992.625</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="M21" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="N21" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="O21" t="n">
-        <v>3.1</v>
+        <v>3.38</v>
       </c>
       <c r="P21" t="n">
-        <v>2.25</v>
+        <v>2.51</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="R21" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="S21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="V21" t="n">
         <v>3.7</v>
       </c>
-      <c r="T21" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V21" t="n">
-        <v>5</v>
-      </c>
       <c r="W21" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.97</v>
+        <v>7.3</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.56</v>
+        <v>1.34</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.43</v>
+        <v>3.22</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.29</v>
+        <v>1.88</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.56</v>
+        <v>1.98</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.5</v>
+        <v>3.34</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45992.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M22" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="N22" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="O22" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P22" t="n">
-        <v>2.51</v>
+        <v>2.25</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="R22" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>4.75</v>
+        <v>3.4</v>
       </c>
       <c r="T22" t="n">
-        <v>1.85</v>
+        <v>2.23</v>
       </c>
       <c r="U22" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="V22" t="n">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="W22" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="X22" t="n">
         <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="Z22" t="n">
-        <v>6.38</v>
+        <v>4.87</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.31</v>
+        <v>1.58</v>
       </c>
       <c r="AB22" t="n">
-        <v>3.37</v>
+        <v>2.33</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.78</v>
+        <v>2.31</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.05</v>
+        <v>1.58</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AF22" t="n">
-        <v>3.3</v>
+        <v>2.61</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45992.66666666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="M24" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N24" t="n">
-        <v>2.07</v>
+        <v>2.4</v>
       </c>
       <c r="O24" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.35</v>
+        <v>2.62</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AC24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45992.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="M25" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N25" t="n">
-        <v>2.4</v>
+        <v>2.07</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="Z25" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AA25" t="n">
         <v>2.35</v>
       </c>
-      <c r="AA25" t="n">
-        <v>2.62</v>
-      </c>
       <c r="AB25" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45992.6875</v>
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="M26" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="N26" t="n">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="O26" t="n">
         <v>1.91</v>
@@ -3533,13 +3533,13 @@
         <v>7</v>
       </c>
       <c r="R26" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="S26" t="n">
         <v>2.79</v>
       </c>
       <c r="T26" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="U26" t="n">
         <v>1.38</v>
@@ -3551,7 +3551,7 @@
         <v>1.05</v>
       </c>
       <c r="X26" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
         <v>1.3</v>
@@ -3560,16 +3560,16 @@
         <v>3.16</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.97</v>
+        <v>2.03</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AC26" t="n">
         <v>3.55</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE26" t="n">
         <v>2.2</v>
@@ -3578,7 +3578,7 @@
         <v>1.62</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AH26" t="n">
         <v>2.63</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="M27" t="n">
-        <v>3.65</v>
+        <v>3.32</v>
       </c>
       <c r="N27" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="O27" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="P27" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="Q27" t="n">
-        <v>5.53</v>
+        <v>4.25</v>
       </c>
       <c r="R27" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="S27" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="T27" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="U27" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V27" t="n">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="W27" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.26</v>
+        <v>3.1</v>
       </c>
       <c r="AA27" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE27" t="n">
         <v>1.85</v>
       </c>
-      <c r="AB27" t="n">
+      <c r="AF27" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH27" t="n">
         <v>1.85</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>2.04</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>45992.70833333334</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="M28" t="n">
-        <v>3.32</v>
+        <v>3.65</v>
       </c>
       <c r="N28" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="O28" t="n">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="P28" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.6</v>
+        <v>5.53</v>
       </c>
       <c r="R28" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="S28" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T28" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="U28" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W28" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X28" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.1</v>
+        <v>3.26</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45992.70833333334</v>

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -936,10 +936,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -975,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,76 +1016,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.1</v>
+        <v>2.15</v>
       </c>
       <c r="M5" t="n">
-        <v>3.25</v>
+        <v>2.86</v>
       </c>
       <c r="N5" t="n">
-        <v>2.2</v>
+        <v>3.49</v>
       </c>
       <c r="O5" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.31</v>
+        <v>1.57</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.1</v>
+        <v>2.23</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
-        <v>45992.45833333334</v>
+        <v>45992.41666666666</v>
       </c>
     </row>
     <row r="6">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>6.37</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45992.45833333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.61</v>
+        <v>3.1</v>
       </c>
       <c r="M7" t="n">
-        <v>3.41</v>
+        <v>3.25</v>
       </c>
       <c r="N7" t="n">
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="O7" t="n">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="P7" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.37</v>
+        <v>2.8</v>
       </c>
       <c r="R7" t="n">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="S7" t="n">
-        <v>2.47</v>
+        <v>2.7</v>
       </c>
       <c r="T7" t="n">
-        <v>3.28</v>
+        <v>2.9</v>
       </c>
       <c r="U7" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="V7" t="n">
-        <v>9</v>
+        <v>7.7</v>
       </c>
       <c r="W7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X7" t="n">
         <v>1</v>
       </c>
-      <c r="X7" t="n">
-        <v>1.08</v>
-      </c>
       <c r="Y7" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.2</v>
+        <v>3.47</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.16</v>
+        <v>1.75</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AG7" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AH7" t="n">
         <v>1.3</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>2.16</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45992.45833333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.2</v>
+        <v>5.8</v>
       </c>
       <c r="M11" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="N11" t="n">
-        <v>2.78</v>
+        <v>1.49</v>
       </c>
       <c r="O11" t="n">
-        <v>2.75</v>
+        <v>5.4</v>
       </c>
       <c r="P11" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.5</v>
+        <v>1.91</v>
       </c>
       <c r="R11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="U11" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="V11" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.48</v>
+        <v>2.63</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.52</v>
+        <v>1.73</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.3</v>
+        <v>1.88</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.66</v>
+        <v>1.08</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45992.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>8</v>
+        <v>2.2</v>
       </c>
       <c r="M12" t="n">
-        <v>4.6</v>
+        <v>3.65</v>
       </c>
       <c r="N12" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V12" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AD12" t="n">
         <v>1.4</v>
       </c>
-      <c r="O12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V12" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AE12" t="n">
-        <v>2.2</v>
+        <v>1.52</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.06</v>
+        <v>1.66</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>5.8</v>
+        <v>1.84</v>
       </c>
       <c r="M14" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="N14" t="n">
-        <v>1.49</v>
+        <v>4</v>
       </c>
       <c r="O14" t="n">
-        <v>5.4</v>
+        <v>2.35</v>
       </c>
       <c r="P14" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="Q14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V14" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH14" t="n">
         <v>1.91</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.08</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.79</v>
+        <v>6.5</v>
       </c>
       <c r="M15" t="n">
-        <v>3.23</v>
+        <v>4.5</v>
       </c>
       <c r="N15" t="n">
-        <v>2.21</v>
+        <v>1.47</v>
       </c>
       <c r="O15" t="n">
-        <v>3.4</v>
+        <v>6.1</v>
       </c>
       <c r="P15" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.89</v>
+        <v>1.85</v>
       </c>
       <c r="R15" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="S15" t="n">
-        <v>2.62</v>
+        <v>3.16</v>
       </c>
       <c r="T15" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="U15" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="V15" t="n">
-        <v>6.9</v>
+        <v>5.55</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.2</v>
+        <v>3.95</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.93</v>
+        <v>1.69</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.77</v>
+        <v>2.11</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.34</v>
+        <v>2.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.34</v>
+        <v>1.08</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,40 +2325,40 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.84</v>
+        <v>2.79</v>
       </c>
       <c r="M16" t="n">
-        <v>3.5</v>
+        <v>3.23</v>
       </c>
       <c r="N16" t="n">
-        <v>4</v>
+        <v>2.21</v>
       </c>
       <c r="O16" t="n">
-        <v>2.35</v>
+        <v>3.4</v>
       </c>
       <c r="P16" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.6</v>
+        <v>2.89</v>
       </c>
       <c r="R16" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="S16" t="n">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="T16" t="n">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="U16" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="V16" t="n">
-        <v>5.75</v>
+        <v>6.9</v>
       </c>
       <c r="W16" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
         <v>1.02</v>
@@ -2367,31 +2367,31 @@
         <v>1.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.18</v>
+        <v>3.34</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="AG16" t="n">
         <v>1.3</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.91</v>
+        <v>1.34</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
+        <v>8</v>
+      </c>
+      <c r="M17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="O17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V17" t="n">
         <v>6.5</v>
       </c>
-      <c r="M17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="O17" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V17" t="n">
-        <v>5.55</v>
-      </c>
       <c r="W17" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG17" t="n">
         <v>1.2</v>
       </c>
-      <c r="Z17" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AH17" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.21</v>
+        <v>3.05</v>
       </c>
       <c r="M19" t="n">
-        <v>5.6</v>
+        <v>3.39</v>
       </c>
       <c r="N19" t="n">
-        <v>8.800000000000001</v>
+        <v>2.01</v>
       </c>
       <c r="O19" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V19" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA19" t="n">
         <v>1.65</v>
       </c>
-      <c r="P19" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>7</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="V19" t="n">
-        <v>4</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AA19" t="n">
+      <c r="AB19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD19" t="n">
         <v>1.4</v>
       </c>
-      <c r="AB19" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.79</v>
-      </c>
       <c r="AE19" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.5</v>
+        <v>1.32</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45992.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.05</v>
+        <v>1.21</v>
       </c>
       <c r="M20" t="n">
-        <v>3.39</v>
+        <v>5.6</v>
       </c>
       <c r="N20" t="n">
-        <v>2.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>3.78</v>
+        <v>1.65</v>
       </c>
       <c r="P20" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.48</v>
+        <v>7</v>
       </c>
       <c r="R20" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="S20" t="n">
-        <v>3.05</v>
+        <v>3.94</v>
       </c>
       <c r="T20" t="n">
-        <v>2.35</v>
+        <v>2.02</v>
       </c>
       <c r="U20" t="n">
-        <v>1.47</v>
+        <v>1.74</v>
       </c>
       <c r="V20" t="n">
-        <v>5.4</v>
+        <v>4</v>
       </c>
       <c r="W20" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="X20" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="Z20" t="n">
-        <v>4</v>
+        <v>5.7</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.7</v>
+        <v>1.91</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.4</v>
+        <v>1.79</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.32</v>
+        <v>3.5</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45992.625</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M21" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="N21" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="O21" t="n">
-        <v>3.38</v>
+        <v>3.1</v>
       </c>
       <c r="P21" t="n">
-        <v>2.51</v>
+        <v>2.25</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="R21" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="S21" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="T21" t="n">
-        <v>1.86</v>
+        <v>2.23</v>
       </c>
       <c r="U21" t="n">
-        <v>1.96</v>
+        <v>1.6</v>
       </c>
       <c r="V21" t="n">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="W21" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="Z21" t="n">
-        <v>7.3</v>
+        <v>4.87</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.34</v>
+        <v>1.58</v>
       </c>
       <c r="AB21" t="n">
-        <v>3.22</v>
+        <v>2.33</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.88</v>
+        <v>2.31</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.98</v>
+        <v>1.58</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.28</v>
+        <v>1.48</v>
       </c>
       <c r="AF21" t="n">
-        <v>3.34</v>
+        <v>2.61</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45992.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="M22" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="N22" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="O22" t="n">
-        <v>3.1</v>
+        <v>3.38</v>
       </c>
       <c r="P22" t="n">
-        <v>2.25</v>
+        <v>2.51</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="R22" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="S22" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="T22" t="n">
-        <v>2.23</v>
+        <v>1.86</v>
       </c>
       <c r="U22" t="n">
-        <v>1.6</v>
+        <v>1.96</v>
       </c>
       <c r="V22" t="n">
-        <v>4.8</v>
+        <v>3.7</v>
       </c>
       <c r="W22" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="X22" t="n">
         <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.87</v>
+        <v>7.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.58</v>
+        <v>1.34</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.33</v>
+        <v>3.22</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.31</v>
+        <v>1.88</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.58</v>
+        <v>1.98</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.61</v>
+        <v>3.34</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45992.66666666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="M24" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N24" t="n">
-        <v>2.4</v>
+        <v>2.07</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="Z24" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AA24" t="n">
         <v>2.35</v>
       </c>
-      <c r="AA24" t="n">
-        <v>2.62</v>
-      </c>
       <c r="AB24" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45992.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="M25" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N25" t="n">
-        <v>2.07</v>
+        <v>2.4</v>
       </c>
       <c r="O25" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.35</v>
+        <v>2.62</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AC25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45992.6875</v>

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -936,10 +936,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1055,10 +1055,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.61</v>
+        <v>3.1</v>
       </c>
       <c r="M6" t="n">
-        <v>3.41</v>
+        <v>3.25</v>
       </c>
       <c r="N6" t="n">
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="O6" t="n">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="P6" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.37</v>
+        <v>2.8</v>
       </c>
       <c r="R6" t="n">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="S6" t="n">
-        <v>2.47</v>
+        <v>2.7</v>
       </c>
       <c r="T6" t="n">
-        <v>3.28</v>
+        <v>2.9</v>
       </c>
       <c r="U6" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="V6" t="n">
-        <v>9</v>
+        <v>7.7</v>
       </c>
       <c r="W6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X6" t="n">
         <v>1</v>
       </c>
-      <c r="X6" t="n">
-        <v>1.08</v>
-      </c>
       <c r="Y6" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.2</v>
+        <v>3.47</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.16</v>
+        <v>1.75</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AG6" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AH6" t="n">
         <v>1.3</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>2.16</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45992.45833333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.1</v>
+        <v>1.61</v>
       </c>
       <c r="M7" t="n">
-        <v>3.25</v>
+        <v>3.41</v>
       </c>
       <c r="N7" t="n">
-        <v>2.2</v>
+        <v>4.8</v>
       </c>
       <c r="O7" t="n">
-        <v>3.5</v>
+        <v>2.25</v>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="Q7" t="n">
+        <v>6.37</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V7" t="n">
+        <v>9</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z7" t="n">
         <v>2.8</v>
       </c>
-      <c r="R7" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V7" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3.1</v>
-      </c>
       <c r="AA7" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.47</v>
+        <v>4.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.75</v>
+        <v>2.16</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.3</v>
+        <v>2.16</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45992.45833333334</v>
@@ -1492,22 +1492,22 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>3.65</v>
+        <v>3.38</v>
       </c>
       <c r="N9" t="n">
-        <v>4.9</v>
+        <v>4.85</v>
       </c>
       <c r="O9" t="n">
         <v>2.12</v>
       </c>
       <c r="P9" t="n">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.22</v>
+        <v>6.2</v>
       </c>
       <c r="R9" t="n">
         <v>1.42</v>
@@ -1516,10 +1516,10 @@
         <v>2.62</v>
       </c>
       <c r="T9" t="n">
-        <v>3.19</v>
+        <v>3.05</v>
       </c>
       <c r="U9" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V9" t="n">
         <v>7.8</v>
@@ -1531,22 +1531,22 @@
         <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z9" t="n">
         <v>2.88</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.97</v>
+        <v>2.15</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AC9" t="n">
         <v>3.72</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AE9" t="n">
         <v>2.1</v>
@@ -1558,7 +1558,7 @@
         <v>1.26</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.13</v>
+        <v>2.32</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45992.54166666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.2</v>
+        <v>1.84</v>
       </c>
       <c r="M12" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="N12" t="n">
-        <v>2.78</v>
+        <v>4</v>
       </c>
       <c r="O12" t="n">
-        <v>2.75</v>
+        <v>2.35</v>
       </c>
       <c r="P12" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="R12" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="S12" t="n">
-        <v>3.04</v>
+        <v>2.77</v>
       </c>
       <c r="T12" t="n">
-        <v>2.35</v>
+        <v>2.81</v>
       </c>
       <c r="U12" t="n">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="V12" t="n">
-        <v>5.4</v>
+        <v>5.75</v>
       </c>
       <c r="W12" t="n">
         <v>1.09</v>
       </c>
       <c r="X12" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.48</v>
+        <v>3.18</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.52</v>
+        <v>1.79</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.3</v>
+        <v>1.89</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.66</v>
+        <v>1.91</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.84</v>
+        <v>8</v>
       </c>
       <c r="M14" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="N14" t="n">
-        <v>4</v>
+        <v>1.4</v>
       </c>
       <c r="O14" t="n">
-        <v>2.35</v>
+        <v>8.6</v>
       </c>
       <c r="P14" t="n">
-        <v>2.33</v>
+        <v>2.24</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.6</v>
+        <v>1.73</v>
       </c>
       <c r="R14" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="S14" t="n">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="T14" t="n">
-        <v>2.81</v>
+        <v>2.69</v>
       </c>
       <c r="U14" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="V14" t="n">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.18</v>
+        <v>3.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.79</v>
+        <v>2.2</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.89</v>
+        <v>1.62</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.91</v>
+        <v>1.06</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>8</v>
+        <v>2.2</v>
       </c>
       <c r="M17" t="n">
-        <v>4.6</v>
+        <v>3.65</v>
       </c>
       <c r="N17" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V17" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AD17" t="n">
         <v>1.4</v>
       </c>
-      <c r="O17" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AE17" t="n">
-        <v>2.2</v>
+        <v>1.52</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.06</v>
+        <v>1.66</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V18" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA18" t="n">
         <v>1.65</v>
       </c>
-      <c r="M18" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N18" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O18" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V18" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AB18" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="AG18" t="n">
         <v>1.3</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.95</v>
+        <v>1.32</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45992.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.05</v>
+        <v>1.21</v>
       </c>
       <c r="M19" t="n">
-        <v>3.39</v>
+        <v>5.6</v>
       </c>
       <c r="N19" t="n">
-        <v>2.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>3.78</v>
+        <v>1.65</v>
       </c>
       <c r="P19" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.48</v>
+        <v>7</v>
       </c>
       <c r="R19" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="S19" t="n">
-        <v>3.05</v>
+        <v>3.94</v>
       </c>
       <c r="T19" t="n">
-        <v>2.35</v>
+        <v>2.02</v>
       </c>
       <c r="U19" t="n">
-        <v>1.47</v>
+        <v>1.74</v>
       </c>
       <c r="V19" t="n">
-        <v>5.4</v>
+        <v>4</v>
       </c>
       <c r="W19" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="X19" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="Z19" t="n">
-        <v>4</v>
+        <v>5.7</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.7</v>
+        <v>1.91</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.4</v>
+        <v>1.79</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.32</v>
+        <v>3.5</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45992.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.21</v>
+        <v>1.65</v>
       </c>
       <c r="M20" t="n">
-        <v>5.6</v>
+        <v>3.75</v>
       </c>
       <c r="N20" t="n">
-        <v>8.800000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="O20" t="n">
-        <v>1.65</v>
+        <v>2.45</v>
       </c>
       <c r="P20" t="n">
-        <v>2.75</v>
+        <v>2.04</v>
       </c>
       <c r="Q20" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="R20" t="n">
-        <v>1.19</v>
+        <v>1.42</v>
       </c>
       <c r="S20" t="n">
-        <v>3.94</v>
+        <v>2.62</v>
       </c>
       <c r="T20" t="n">
-        <v>2.02</v>
+        <v>2.9</v>
       </c>
       <c r="U20" t="n">
-        <v>1.74</v>
+        <v>1.35</v>
       </c>
       <c r="V20" t="n">
-        <v>4</v>
+        <v>7.3</v>
       </c>
       <c r="W20" t="n">
-        <v>1.18</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.7</v>
+        <v>3.2</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.91</v>
+        <v>3.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.79</v>
+        <v>1.25</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AH20" t="n">
-        <v>3.5</v>
+        <v>1.95</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45992.625</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="M21" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="N21" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="O21" t="n">
-        <v>3.1</v>
+        <v>3.38</v>
       </c>
       <c r="P21" t="n">
-        <v>2.25</v>
+        <v>2.51</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="R21" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="S21" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="T21" t="n">
-        <v>2.23</v>
+        <v>1.86</v>
       </c>
       <c r="U21" t="n">
-        <v>1.6</v>
+        <v>1.96</v>
       </c>
       <c r="V21" t="n">
-        <v>4.8</v>
+        <v>3.7</v>
       </c>
       <c r="W21" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.87</v>
+        <v>7.3</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.58</v>
+        <v>1.34</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.33</v>
+        <v>3.22</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.31</v>
+        <v>1.88</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.58</v>
+        <v>1.98</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.61</v>
+        <v>3.34</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45992.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M22" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="N22" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="O22" t="n">
-        <v>3.38</v>
+        <v>3.1</v>
       </c>
       <c r="P22" t="n">
-        <v>2.51</v>
+        <v>2.25</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="R22" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="T22" t="n">
-        <v>1.86</v>
+        <v>2.23</v>
       </c>
       <c r="U22" t="n">
-        <v>1.96</v>
+        <v>1.6</v>
       </c>
       <c r="V22" t="n">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="W22" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="X22" t="n">
         <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="Z22" t="n">
-        <v>7.3</v>
+        <v>4.87</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.34</v>
+        <v>1.58</v>
       </c>
       <c r="AB22" t="n">
-        <v>3.22</v>
+        <v>2.33</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.88</v>
+        <v>2.31</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.98</v>
+        <v>1.58</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.28</v>
+        <v>1.48</v>
       </c>
       <c r="AF22" t="n">
-        <v>3.34</v>
+        <v>2.61</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45992.66666666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.97</v>
+        <v>3.6</v>
       </c>
       <c r="M23" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="N23" t="n">
-        <v>3.75</v>
+        <v>2.07</v>
       </c>
       <c r="O23" t="n">
-        <v>2.72</v>
+        <v>3.85</v>
       </c>
       <c r="P23" t="n">
-        <v>2.09</v>
+        <v>1.88</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.04</v>
+        <v>3.02</v>
       </c>
       <c r="R23" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="S23" t="n">
-        <v>2.5</v>
+        <v>2.24</v>
       </c>
       <c r="T23" t="n">
-        <v>2.9</v>
+        <v>3.58</v>
       </c>
       <c r="U23" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="V23" t="n">
-        <v>7.9</v>
+        <v>11</v>
       </c>
       <c r="W23" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.98</v>
+        <v>2.34</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.74</v>
+        <v>4</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.78</v>
+        <v>1.62</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.27</v>
+        <v>1.53</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45992.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.6</v>
+        <v>1.97</v>
       </c>
       <c r="M24" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="N24" t="n">
-        <v>2.07</v>
+        <v>3.75</v>
       </c>
       <c r="O24" t="n">
-        <v>3.85</v>
+        <v>2.72</v>
       </c>
       <c r="P24" t="n">
-        <v>1.88</v>
+        <v>2.09</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.02</v>
+        <v>4.04</v>
       </c>
       <c r="R24" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="S24" t="n">
-        <v>2.24</v>
+        <v>2.5</v>
       </c>
       <c r="T24" t="n">
-        <v>3.58</v>
+        <v>2.9</v>
       </c>
       <c r="U24" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="V24" t="n">
-        <v>11</v>
+        <v>7.9</v>
       </c>
       <c r="W24" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X24" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.34</v>
+        <v>2.98</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AC24" t="n">
-        <v>4</v>
+        <v>3.74</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.08</v>
+        <v>1.97</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.53</v>
+        <v>1.27</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.25</v>
+        <v>1.63</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45992.6875</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="M27" t="n">
-        <v>3.32</v>
+        <v>3.65</v>
       </c>
       <c r="N27" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="O27" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="P27" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.25</v>
+        <v>5.53</v>
       </c>
       <c r="R27" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="S27" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T27" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="U27" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V27" t="n">
-        <v>7.7</v>
+        <v>7</v>
       </c>
       <c r="W27" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.1</v>
+        <v>3.26</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>45992.70833333334</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="M28" t="n">
-        <v>3.65</v>
+        <v>3.32</v>
       </c>
       <c r="N28" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="O28" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="P28" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="Q28" t="n">
-        <v>5.53</v>
+        <v>4.25</v>
       </c>
       <c r="R28" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="S28" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="T28" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="U28" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V28" t="n">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="W28" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.26</v>
+        <v>3.1</v>
       </c>
       <c r="AA28" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE28" t="n">
         <v>1.85</v>
       </c>
-      <c r="AB28" t="n">
+      <c r="AF28" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH28" t="n">
         <v>1.85</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>2.04</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45992.70833333334</v>

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -936,10 +936,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1055,10 +1055,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.1</v>
+        <v>1.74</v>
       </c>
       <c r="M6" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="N6" t="n">
-        <v>2.2</v>
+        <v>4.8</v>
       </c>
       <c r="O6" t="n">
-        <v>3.5</v>
+        <v>2.38</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="R6" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="S6" t="n">
-        <v>2.7</v>
+        <v>2.41</v>
       </c>
       <c r="T6" t="n">
-        <v>2.9</v>
+        <v>3.19</v>
       </c>
       <c r="U6" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="V6" t="n">
-        <v>7.7</v>
+        <v>9</v>
       </c>
       <c r="W6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X6" t="n">
         <v>1.03</v>
       </c>
-      <c r="X6" t="n">
-        <v>1</v>
-      </c>
       <c r="Y6" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.1</v>
+        <v>2.66</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.95</v>
+        <v>2.31</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.47</v>
+        <v>4.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.75</v>
+        <v>2.27</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.3</v>
+        <v>2.05</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45992.45833333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.61</v>
+        <v>3.1</v>
       </c>
       <c r="M7" t="n">
-        <v>3.41</v>
+        <v>3.25</v>
       </c>
       <c r="N7" t="n">
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="O7" t="n">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="P7" t="n">
-        <v>1.99</v>
+        <v>2.15</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.37</v>
+        <v>2.8</v>
       </c>
       <c r="R7" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="S7" t="n">
-        <v>2.47</v>
+        <v>2.9</v>
       </c>
       <c r="T7" t="n">
-        <v>3.28</v>
+        <v>2.95</v>
       </c>
       <c r="U7" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="V7" t="n">
-        <v>9</v>
+        <v>7.7</v>
       </c>
       <c r="W7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X7" t="n">
         <v>1</v>
       </c>
-      <c r="X7" t="n">
-        <v>1.08</v>
-      </c>
       <c r="Y7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH7" t="n">
         <v>1.36</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>2.16</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45992.45833333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.36</v>
+        <v>1.65</v>
       </c>
       <c r="M8" t="n">
         <v>3.65</v>
       </c>
       <c r="N8" t="n">
-        <v>2.37</v>
+        <v>4.9</v>
       </c>
       <c r="O8" t="n">
-        <v>2.8</v>
+        <v>2.12</v>
       </c>
       <c r="P8" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.8</v>
+        <v>6.2</v>
       </c>
       <c r="R8" t="n">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="S8" t="n">
-        <v>3.7</v>
+        <v>2.62</v>
       </c>
       <c r="T8" t="n">
-        <v>2.09</v>
+        <v>3.05</v>
       </c>
       <c r="U8" t="n">
-        <v>1.7</v>
+        <v>1.32</v>
       </c>
       <c r="V8" t="n">
-        <v>4.2</v>
+        <v>7.8</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
         <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.12</v>
+        <v>1.36</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.67</v>
+        <v>2.88</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.43</v>
+        <v>1.97</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.63</v>
+        <v>1.73</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.94</v>
+        <v>3.72</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.76</v>
+        <v>1.23</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.8</v>
+        <v>1.66</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.5</v>
+        <v>2.32</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45992.54166666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>2.36</v>
       </c>
       <c r="M9" t="n">
-        <v>3.38</v>
+        <v>3.65</v>
       </c>
       <c r="N9" t="n">
-        <v>4.85</v>
+        <v>2.37</v>
       </c>
       <c r="O9" t="n">
-        <v>2.12</v>
+        <v>2.8</v>
       </c>
       <c r="P9" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.2</v>
+        <v>2.8</v>
       </c>
       <c r="R9" t="n">
-        <v>1.42</v>
+        <v>1.22</v>
       </c>
       <c r="S9" t="n">
-        <v>2.62</v>
+        <v>3.7</v>
       </c>
       <c r="T9" t="n">
-        <v>3.05</v>
+        <v>2.09</v>
       </c>
       <c r="U9" t="n">
-        <v>1.32</v>
+        <v>1.7</v>
       </c>
       <c r="V9" t="n">
-        <v>7.8</v>
+        <v>4.2</v>
       </c>
       <c r="W9" t="n">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="X9" t="n">
         <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.36</v>
+        <v>1.12</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.88</v>
+        <v>5.67</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.15</v>
+        <v>1.43</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.68</v>
+        <v>2.63</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.72</v>
+        <v>1.94</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.23</v>
+        <v>1.76</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.66</v>
+        <v>2.8</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.32</v>
+        <v>1.5</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45992.54166666666</v>
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.5</v>
+        <v>2.96</v>
       </c>
       <c r="M10" t="n">
-        <v>3.05</v>
+        <v>2.84</v>
       </c>
       <c r="N10" t="n">
-        <v>3.05</v>
+        <v>2.59</v>
       </c>
       <c r="O10" t="n">
         <v>3.92</v>
@@ -1626,13 +1626,13 @@
         <v>1.86</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R10" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="S10" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="T10" t="n">
         <v>3.88</v>
@@ -1647,37 +1647,37 @@
         <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="AC10" t="n">
         <v>5.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="AF10" t="n">
         <v>1.63</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45992.5625</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>5.8</v>
+        <v>2.24</v>
       </c>
       <c r="M11" t="n">
-        <v>4.2</v>
+        <v>3.37</v>
       </c>
       <c r="N11" t="n">
-        <v>1.49</v>
+        <v>3.17</v>
       </c>
       <c r="O11" t="n">
-        <v>5.4</v>
+        <v>2.75</v>
       </c>
       <c r="P11" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.91</v>
+        <v>3.35</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T11" t="n">
-        <v>2.23</v>
+        <v>2.46</v>
       </c>
       <c r="U11" t="n">
         <v>1.5</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.63</v>
+        <v>2.48</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.88</v>
+        <v>2.38</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.08</v>
+        <v>1.62</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45992.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.84</v>
+        <v>1.25</v>
       </c>
       <c r="M12" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="N12" t="n">
+        <v>14</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S12" t="n">
         <v>3.5</v>
       </c>
-      <c r="N12" t="n">
-        <v>4</v>
-      </c>
-      <c r="O12" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.77</v>
-      </c>
       <c r="T12" t="n">
-        <v>2.81</v>
+        <v>2.23</v>
       </c>
       <c r="U12" t="n">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="V12" t="n">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.09</v>
+        <v>1.19</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.95</v>
+        <v>1.63</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.18</v>
+        <v>2.38</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.29</v>
+        <v>1.53</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.79</v>
+        <v>2.05</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.91</v>
+        <v>4.2</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45992.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.25</v>
+        <v>5.8</v>
       </c>
       <c r="M13" t="n">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="N13" t="n">
-        <v>14</v>
+        <v>1.49</v>
       </c>
       <c r="O13" t="n">
-        <v>1.62</v>
+        <v>5.4</v>
       </c>
       <c r="P13" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>8.5</v>
+        <v>1.91</v>
       </c>
       <c r="R13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="U13" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="V13" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
         <v>1.19</v>
       </c>
-      <c r="X13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.17</v>
-      </c>
       <c r="Z13" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.7</v>
+        <v>1.88</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.9</v>
+        <v>1.08</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>8</v>
+        <v>1.86</v>
       </c>
       <c r="M14" t="n">
-        <v>4.6</v>
+        <v>3.58</v>
       </c>
       <c r="N14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="R14" t="n">
         <v>1.4</v>
       </c>
-      <c r="O14" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.34</v>
-      </c>
       <c r="S14" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="T14" t="n">
-        <v>2.69</v>
+        <v>2.81</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="V14" t="n">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.6</v>
+        <v>3.38</v>
       </c>
       <c r="AA14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB14" t="n">
         <v>1.8</v>
       </c>
-      <c r="AB14" t="n">
+      <c r="AC14" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH14" t="n">
         <v>2</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.06</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>6.5</v>
+        <v>3.16</v>
       </c>
       <c r="M15" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>1.47</v>
+        <v>2.26</v>
       </c>
       <c r="O15" t="n">
-        <v>6.1</v>
+        <v>3.45</v>
       </c>
       <c r="P15" t="n">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.85</v>
+        <v>2.93</v>
       </c>
       <c r="R15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V15" t="n">
+        <v>7</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y15" t="n">
         <v>1.32</v>
       </c>
-      <c r="S15" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V15" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.2</v>
-      </c>
       <c r="Z15" t="n">
-        <v>3.95</v>
+        <v>3.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.69</v>
+        <v>2.09</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.11</v>
+        <v>1.72</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.14</v>
+        <v>1.57</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.08</v>
+        <v>1.36</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.79</v>
+        <v>8</v>
       </c>
       <c r="M16" t="n">
-        <v>3.23</v>
+        <v>4.6</v>
       </c>
       <c r="N16" t="n">
-        <v>2.21</v>
+        <v>1.4</v>
       </c>
       <c r="O16" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V16" t="n">
+        <v>6</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC16" t="n">
         <v>3.4</v>
       </c>
-      <c r="P16" t="n">
+      <c r="AD16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE16" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q16" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V16" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AF16" t="n">
-        <v>1.94</v>
+        <v>1.58</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.2</v>
+        <v>6.8</v>
       </c>
       <c r="M17" t="n">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="N17" t="n">
-        <v>2.78</v>
+        <v>1.47</v>
       </c>
       <c r="O17" t="n">
-        <v>2.75</v>
+        <v>6.1</v>
       </c>
       <c r="P17" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.5</v>
+        <v>1.85</v>
       </c>
       <c r="R17" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S17" t="n">
-        <v>3.04</v>
+        <v>3.26</v>
       </c>
       <c r="T17" t="n">
-        <v>2.35</v>
+        <v>2.44</v>
       </c>
       <c r="U17" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="V17" t="n">
-        <v>5.4</v>
+        <v>5.55</v>
       </c>
       <c r="W17" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
         <v>1.2</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AB17" t="n">
         <v>2.1</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.52</v>
+        <v>1.85</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.36</v>
+        <v>2.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.66</v>
+        <v>1.08</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.05</v>
+        <v>1.86</v>
       </c>
       <c r="M18" t="n">
-        <v>3.39</v>
+        <v>3.6</v>
       </c>
       <c r="N18" t="n">
-        <v>2.01</v>
+        <v>4.1</v>
       </c>
       <c r="O18" t="n">
-        <v>3.78</v>
+        <v>2.45</v>
       </c>
       <c r="P18" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.48</v>
+        <v>4.9</v>
       </c>
       <c r="R18" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="S18" t="n">
-        <v>3.05</v>
+        <v>2.66</v>
       </c>
       <c r="T18" t="n">
-        <v>2.35</v>
+        <v>2.8</v>
       </c>
       <c r="U18" t="n">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="V18" t="n">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="W18" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X18" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="Z18" t="n">
-        <v>4</v>
+        <v>3.26</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.65</v>
+        <v>2.04</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AG18" t="n">
         <v>1.3</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.32</v>
+        <v>1.91</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45992.625</v>
@@ -2703,13 +2703,13 @@
         <v>1.19</v>
       </c>
       <c r="S19" t="n">
-        <v>3.94</v>
+        <v>3.8</v>
       </c>
       <c r="T19" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="V19" t="n">
         <v>4</v>
@@ -2742,13 +2742,13 @@
         <v>1.67</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45992.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.65</v>
+        <v>2.9</v>
       </c>
       <c r="M20" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="N20" t="n">
-        <v>4.8</v>
+        <v>2.18</v>
       </c>
       <c r="O20" t="n">
-        <v>2.45</v>
+        <v>3.35</v>
       </c>
       <c r="P20" t="n">
-        <v>2.04</v>
+        <v>2.38</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.5</v>
+        <v>2.48</v>
       </c>
       <c r="R20" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="S20" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V20" t="n">
+        <v>6</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AC20" t="n">
         <v>2.62</v>
       </c>
-      <c r="T20" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V20" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AD20" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG20" t="n">
         <v>1.25</v>
       </c>
-      <c r="AE20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH20" t="n">
-        <v>1.95</v>
+        <v>1.33</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45992.625</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="M23" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="N23" t="n">
-        <v>2.07</v>
+        <v>2.27</v>
       </c>
       <c r="O23" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.35</v>
+        <v>2.62</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AC23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45992.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.97</v>
+        <v>3.29</v>
       </c>
       <c r="M24" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="N24" t="n">
-        <v>3.75</v>
+        <v>2.21</v>
       </c>
       <c r="O24" t="n">
-        <v>2.72</v>
+        <v>4.12</v>
       </c>
       <c r="P24" t="n">
-        <v>2.09</v>
+        <v>1.84</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.04</v>
+        <v>3.1</v>
       </c>
       <c r="R24" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="S24" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V24" t="n">
+        <v>10</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z24" t="n">
         <v>2.5</v>
       </c>
-      <c r="T24" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V24" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.98</v>
-      </c>
       <c r="AA24" t="n">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.74</v>
+        <v>4.9</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.97</v>
+        <v>2.23</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AG24" t="n">
         <v>1.27</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.63</v>
+        <v>1.27</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45992.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.8</v>
+        <v>1.95</v>
       </c>
       <c r="M25" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N25" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.35</v>
+        <v>2.83</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.62</v>
+        <v>2.1</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45992.6875</v>
@@ -3527,19 +3527,19 @@
         <v>1.91</v>
       </c>
       <c r="P26" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="Q26" t="n">
         <v>7</v>
       </c>
       <c r="R26" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S26" t="n">
-        <v>2.79</v>
+        <v>2.83</v>
       </c>
       <c r="T26" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="U26" t="n">
         <v>1.38</v>
@@ -3548,40 +3548,40 @@
         <v>7.5</v>
       </c>
       <c r="W26" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X26" t="n">
         <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.16</v>
+        <v>3.3</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.03</v>
+        <v>2.09</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AC26" t="n">
         <v>3.55</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.63</v>
+        <v>2.77</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>45992.69791666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="M27" t="n">
-        <v>3.65</v>
+        <v>3.34</v>
       </c>
       <c r="N27" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O27" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q27" t="n">
         <v>4.3</v>
       </c>
-      <c r="O27" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="P27" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>5.53</v>
-      </c>
       <c r="R27" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="S27" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="T27" t="n">
         <v>3</v>
       </c>
       <c r="U27" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V27" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y27" t="n">
         <v>1.33</v>
       </c>
-      <c r="V27" t="n">
-        <v>7</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.29</v>
-      </c>
       <c r="Z27" t="n">
-        <v>3.26</v>
+        <v>3.15</v>
       </c>
       <c r="AA27" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH27" t="n">
         <v>1.85</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>2.04</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>45992.70833333334</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="M28" t="n">
-        <v>3.32</v>
+        <v>3.5</v>
       </c>
       <c r="N28" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="O28" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="P28" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.25</v>
+        <v>5.53</v>
       </c>
       <c r="R28" t="n">
         <v>1.4</v>
       </c>
       <c r="S28" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T28" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="U28" t="n">
         <v>1.36</v>
       </c>
       <c r="V28" t="n">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="W28" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="AD28" t="n">
         <v>1.25</v>
       </c>
       <c r="AE28" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AF28" t="n">
         <v>1.85</v>
       </c>
-      <c r="AF28" t="n">
-        <v>1.88</v>
-      </c>
       <c r="AG28" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45992.70833333334</v>
@@ -3881,10 +3881,10 @@
         <v>1.6</v>
       </c>
       <c r="O29" t="n">
-        <v>6.05</v>
+        <v>5.5</v>
       </c>
       <c r="P29" t="n">
-        <v>2.21</v>
+        <v>2.4</v>
       </c>
       <c r="Q29" t="n">
         <v>2.1</v>
@@ -3896,19 +3896,19 @@
         <v>2.94</v>
       </c>
       <c r="T29" t="n">
-        <v>2.48</v>
+        <v>2.65</v>
       </c>
       <c r="U29" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="V29" t="n">
         <v>6.5</v>
       </c>
       <c r="W29" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X29" t="n">
         <v>1.05</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1</v>
       </c>
       <c r="Y29" t="n">
         <v>1.23</v>
@@ -3926,7 +3926,7 @@
         <v>2.98</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE29" t="n">
         <v>1.85</v>

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="M5" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="N5" t="n">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.74</v>
+        <v>3.1</v>
       </c>
       <c r="M6" t="n">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="N6" t="n">
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="O6" t="n">
-        <v>2.38</v>
+        <v>3.5</v>
       </c>
       <c r="P6" t="n">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="Q6" t="n">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S6" t="n">
-        <v>2.41</v>
+        <v>2.9</v>
       </c>
       <c r="T6" t="n">
-        <v>3.19</v>
+        <v>2.95</v>
       </c>
       <c r="U6" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="V6" t="n">
-        <v>9</v>
+        <v>7.7</v>
       </c>
       <c r="W6" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.66</v>
+        <v>3.14</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.31</v>
+        <v>2</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.2</v>
+        <v>3.47</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.27</v>
+        <v>1.77</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.05</v>
+        <v>1.36</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45992.45833333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.1</v>
+        <v>1.74</v>
       </c>
       <c r="M7" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="N7" t="n">
-        <v>2.2</v>
+        <v>4.8</v>
       </c>
       <c r="O7" t="n">
-        <v>3.5</v>
+        <v>2.38</v>
       </c>
       <c r="P7" t="n">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S7" t="n">
-        <v>2.9</v>
+        <v>2.41</v>
       </c>
       <c r="T7" t="n">
-        <v>2.95</v>
+        <v>3.19</v>
       </c>
       <c r="U7" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="V7" t="n">
-        <v>7.7</v>
+        <v>9</v>
       </c>
       <c r="W7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X7" t="n">
         <v>1.03</v>
       </c>
-      <c r="X7" t="n">
-        <v>1</v>
-      </c>
       <c r="Y7" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.14</v>
+        <v>2.66</v>
       </c>
       <c r="AA7" t="n">
-        <v>2</v>
+        <v>2.31</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.47</v>
+        <v>4.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.77</v>
+        <v>2.27</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.36</v>
+        <v>2.05</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45992.45833333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.65</v>
+        <v>2.27</v>
       </c>
       <c r="M8" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="N8" t="n">
-        <v>4.9</v>
+        <v>2.5</v>
       </c>
       <c r="O8" t="n">
-        <v>2.12</v>
+        <v>2.8</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.2</v>
+        <v>3.03</v>
       </c>
       <c r="R8" t="n">
-        <v>1.42</v>
+        <v>1.22</v>
       </c>
       <c r="S8" t="n">
-        <v>2.62</v>
+        <v>4</v>
       </c>
       <c r="T8" t="n">
-        <v>3.05</v>
+        <v>2.09</v>
       </c>
       <c r="U8" t="n">
-        <v>1.32</v>
+        <v>1.7</v>
       </c>
       <c r="V8" t="n">
-        <v>7.8</v>
+        <v>4.33</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>1.19</v>
       </c>
       <c r="X8" t="n">
         <v>1.02</v>
       </c>
       <c r="Y8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE8" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z8" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AF8" t="n">
-        <v>1.66</v>
+        <v>2.9</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.32</v>
+        <v>1.5</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45992.54166666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.36</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>3.65</v>
+        <v>3.38</v>
       </c>
       <c r="N9" t="n">
-        <v>2.37</v>
+        <v>4.85</v>
       </c>
       <c r="O9" t="n">
-        <v>2.8</v>
+        <v>2.06</v>
       </c>
       <c r="P9" t="n">
-        <v>2.36</v>
+        <v>2.03</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.8</v>
+        <v>5.22</v>
       </c>
       <c r="R9" t="n">
-        <v>1.22</v>
+        <v>1.43</v>
       </c>
       <c r="S9" t="n">
-        <v>3.7</v>
+        <v>2.62</v>
       </c>
       <c r="T9" t="n">
-        <v>2.09</v>
+        <v>3.05</v>
       </c>
       <c r="U9" t="n">
-        <v>1.7</v>
+        <v>1.32</v>
       </c>
       <c r="V9" t="n">
-        <v>4.2</v>
+        <v>7.8</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2</v>
+        <v>1.02</v>
       </c>
       <c r="X9" t="n">
         <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.12</v>
+        <v>1.36</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.67</v>
+        <v>2.88</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.43</v>
+        <v>2.15</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.63</v>
+        <v>1.71</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.94</v>
+        <v>3.72</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.76</v>
+        <v>1.2</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.8</v>
+        <v>1.66</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.5</v>
+        <v>2.13</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45992.54166666666</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.24</v>
+        <v>3.16</v>
       </c>
       <c r="M11" t="n">
-        <v>3.37</v>
+        <v>3.2</v>
       </c>
       <c r="N11" t="n">
-        <v>3.17</v>
+        <v>2.26</v>
       </c>
       <c r="O11" t="n">
-        <v>2.75</v>
+        <v>3.45</v>
       </c>
       <c r="P11" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.35</v>
+        <v>2.93</v>
       </c>
       <c r="R11" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="S11" t="n">
-        <v>3.04</v>
+        <v>2.62</v>
       </c>
       <c r="T11" t="n">
-        <v>2.46</v>
+        <v>2.9</v>
       </c>
       <c r="U11" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="V11" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="W11" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="Z11" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.68</v>
+        <v>2.09</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.15</v>
+        <v>1.72</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.48</v>
+        <v>3.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45992.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.25</v>
+        <v>5.8</v>
       </c>
       <c r="M12" t="n">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="N12" t="n">
-        <v>14</v>
+        <v>1.49</v>
       </c>
       <c r="O12" t="n">
-        <v>1.62</v>
+        <v>5.4</v>
       </c>
       <c r="P12" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>9.4</v>
+        <v>1.91</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
         <v>2.23</v>
       </c>
       <c r="U12" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="V12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
         <v>1.19</v>
       </c>
-      <c r="X12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.17</v>
-      </c>
       <c r="Z12" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.7</v>
+        <v>1.88</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AH12" t="n">
-        <v>4.2</v>
+        <v>1.08</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45992.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>5.8</v>
+        <v>2.24</v>
       </c>
       <c r="M13" t="n">
-        <v>4.2</v>
+        <v>3.37</v>
       </c>
       <c r="N13" t="n">
-        <v>1.49</v>
+        <v>3.17</v>
       </c>
       <c r="O13" t="n">
-        <v>5.4</v>
+        <v>2.75</v>
       </c>
       <c r="P13" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.91</v>
+        <v>3.35</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T13" t="n">
-        <v>2.23</v>
+        <v>2.46</v>
       </c>
       <c r="U13" t="n">
         <v>1.5</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.63</v>
+        <v>2.48</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.88</v>
+        <v>2.38</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.08</v>
+        <v>1.62</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.86</v>
+        <v>6.8</v>
       </c>
       <c r="M14" t="n">
-        <v>3.58</v>
+        <v>4.5</v>
       </c>
       <c r="N14" t="n">
-        <v>4.2</v>
+        <v>1.47</v>
       </c>
       <c r="O14" t="n">
-        <v>2.35</v>
+        <v>6.1</v>
       </c>
       <c r="P14" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.17</v>
+        <v>1.85</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="S14" t="n">
-        <v>2.77</v>
+        <v>3.26</v>
       </c>
       <c r="T14" t="n">
-        <v>2.81</v>
+        <v>2.44</v>
       </c>
       <c r="U14" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="V14" t="n">
-        <v>5.75</v>
+        <v>5.55</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.38</v>
+        <v>4.15</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.18</v>
+        <v>2.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="AE14" t="n">
         <v>1.85</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>2</v>
+        <v>1.08</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.16</v>
+        <v>9</v>
       </c>
       <c r="M15" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="N15" t="n">
-        <v>2.26</v>
+        <v>1.36</v>
       </c>
       <c r="O15" t="n">
-        <v>3.45</v>
+        <v>8.6</v>
       </c>
       <c r="P15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V15" t="n">
+        <v>6</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE15" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q15" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V15" t="n">
-        <v>7</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AF15" t="n">
-        <v>2</v>
+        <v>1.58</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.57</v>
+        <v>1.2</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.36</v>
+        <v>1.06</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>8</v>
+        <v>1.15</v>
       </c>
       <c r="M16" t="n">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="N16" t="n">
-        <v>1.4</v>
+        <v>10</v>
       </c>
       <c r="O16" t="n">
-        <v>8.6</v>
+        <v>1.62</v>
       </c>
       <c r="P16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V16" t="n">
+        <v>5</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB16" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q16" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V16" t="n">
-        <v>6</v>
-      </c>
-      <c r="W16" t="n">
+      <c r="AC16" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AG16" t="n">
         <v>1.11</v>
       </c>
-      <c r="X16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AH16" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>6.8</v>
+        <v>1.86</v>
       </c>
       <c r="M17" t="n">
-        <v>4.5</v>
+        <v>3.58</v>
       </c>
       <c r="N17" t="n">
-        <v>1.47</v>
+        <v>4.2</v>
       </c>
       <c r="O17" t="n">
-        <v>6.1</v>
+        <v>2.35</v>
       </c>
       <c r="P17" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.85</v>
+        <v>4.17</v>
       </c>
       <c r="R17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V17" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y17" t="n">
         <v>1.3</v>
       </c>
-      <c r="S17" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V17" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.2</v>
-      </c>
       <c r="Z17" t="n">
-        <v>4.15</v>
+        <v>3.38</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.6</v>
+        <v>3.18</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="AE17" t="n">
         <v>1.85</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.08</v>
+        <v>2</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="O19" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V19" t="n">
+        <v>6</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y19" t="n">
         <v>1.21</v>
       </c>
-      <c r="M19" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="N19" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>7</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V19" t="n">
-        <v>4</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.08</v>
-      </c>
       <c r="Z19" t="n">
-        <v>5.7</v>
+        <v>4.05</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.75</v>
+        <v>2.09</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.91</v>
+        <v>2.62</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.79</v>
+        <v>1.38</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.03</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.8</v>
+        <v>1.33</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45992.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.9</v>
+        <v>1.21</v>
       </c>
       <c r="M20" t="n">
-        <v>3.6</v>
+        <v>5.6</v>
       </c>
       <c r="N20" t="n">
-        <v>2.18</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>3.35</v>
+        <v>1.65</v>
       </c>
       <c r="P20" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.48</v>
+        <v>7</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="S20" t="n">
-        <v>3.05</v>
+        <v>3.8</v>
       </c>
       <c r="T20" t="n">
-        <v>2.49</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="V20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="W20" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="X20" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.05</v>
+        <v>5.7</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.09</v>
+        <v>2.75</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.62</v>
+        <v>1.91</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.38</v>
+        <v>1.79</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>1.03</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.33</v>
+        <v>3.8</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45992.625</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="M21" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="N21" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="O21" t="n">
-        <v>3.38</v>
+        <v>3.1</v>
       </c>
       <c r="P21" t="n">
-        <v>2.51</v>
+        <v>2.25</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.45</v>
+        <v>2.73</v>
       </c>
       <c r="R21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="W21" t="n">
         <v>1.15</v>
-      </c>
-      <c r="S21" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="V21" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.22</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="Z21" t="n">
-        <v>7.3</v>
+        <v>4.65</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.34</v>
+        <v>1.58</v>
       </c>
       <c r="AB21" t="n">
-        <v>3.22</v>
+        <v>2.4</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.88</v>
+        <v>2.31</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.98</v>
+        <v>1.58</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="AF21" t="n">
-        <v>3.34</v>
+        <v>2.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45992.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.76</v>
+        <v>2.99</v>
       </c>
       <c r="M22" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="N22" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="O22" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P22" t="n">
-        <v>2.25</v>
+        <v>2.51</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="R22" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="S22" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="T22" t="n">
-        <v>2.23</v>
+        <v>1.88</v>
       </c>
       <c r="U22" t="n">
-        <v>1.6</v>
+        <v>1.96</v>
       </c>
       <c r="V22" t="n">
-        <v>4.8</v>
+        <v>3.7</v>
       </c>
       <c r="W22" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="X22" t="n">
         <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.87</v>
+        <v>7</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.58</v>
+        <v>1.3</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.33</v>
+        <v>3.37</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.31</v>
+        <v>1.78</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.58</v>
+        <v>1.98</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.61</v>
+        <v>3.34</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45992.66666666666</v>
@@ -3640,28 +3640,28 @@
         <v>3.34</v>
       </c>
       <c r="N27" t="n">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="O27" t="n">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="P27" t="n">
         <v>2.14</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="S27" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="T27" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="U27" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V27" t="n">
         <v>7.5</v>
@@ -3676,10 +3676,10 @@
         <v>1.33</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="AB27" t="n">
         <v>1.83</v>
@@ -3697,7 +3697,7 @@
         <v>1.88</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AH27" t="n">
         <v>1.85</v>
@@ -3771,7 +3771,7 @@
         <v>5.53</v>
       </c>
       <c r="R28" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S28" t="n">
         <v>2.62</v>
@@ -3780,13 +3780,13 @@
         <v>3</v>
       </c>
       <c r="U28" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V28" t="n">
         <v>7.5</v>
       </c>
       <c r="W28" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X28" t="n">
         <v>1.01</v>
@@ -3801,7 +3801,7 @@
         <v>2.05</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AC28" t="n">
         <v>3.54</v>
@@ -3872,16 +3872,16 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>5.4</v>
+        <v>6.16</v>
       </c>
       <c r="M29" t="n">
-        <v>4.1</v>
+        <v>4.22</v>
       </c>
       <c r="N29" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="O29" t="n">
-        <v>5.5</v>
+        <v>6.47</v>
       </c>
       <c r="P29" t="n">
         <v>2.4</v>
@@ -3899,13 +3899,13 @@
         <v>2.65</v>
       </c>
       <c r="U29" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="V29" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="W29" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X29" t="n">
         <v>1.05</v>
@@ -3917,16 +3917,16 @@
         <v>3.7</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AC29" t="n">
         <v>2.98</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AE29" t="n">
         <v>1.85</v>

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI29"/>
+  <dimension ref="A1:AI30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -936,10 +936,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1055,10 +1055,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.27</v>
+        <v>2</v>
       </c>
       <c r="M8" t="n">
-        <v>3.7</v>
+        <v>3.38</v>
       </c>
       <c r="N8" t="n">
-        <v>2.5</v>
+        <v>4.85</v>
       </c>
       <c r="O8" t="n">
-        <v>2.8</v>
+        <v>2.06</v>
       </c>
       <c r="P8" t="n">
-        <v>2.5</v>
+        <v>2.03</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.03</v>
+        <v>5.22</v>
       </c>
       <c r="R8" t="n">
-        <v>1.22</v>
+        <v>1.43</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>2.62</v>
       </c>
       <c r="T8" t="n">
-        <v>2.09</v>
+        <v>3.05</v>
       </c>
       <c r="U8" t="n">
-        <v>1.7</v>
+        <v>1.32</v>
       </c>
       <c r="V8" t="n">
-        <v>4.33</v>
+        <v>7.8</v>
       </c>
       <c r="W8" t="n">
-        <v>1.19</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
         <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.12</v>
+        <v>1.36</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.75</v>
+        <v>2.88</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.43</v>
+        <v>2.15</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.68</v>
+        <v>1.71</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.05</v>
+        <v>3.72</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.36</v>
+        <v>2.1</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.9</v>
+        <v>1.66</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.5</v>
+        <v>2.13</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45992.54166666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>2.27</v>
       </c>
       <c r="M9" t="n">
-        <v>3.38</v>
+        <v>3.7</v>
       </c>
       <c r="N9" t="n">
-        <v>4.85</v>
+        <v>2.5</v>
       </c>
       <c r="O9" t="n">
-        <v>2.06</v>
+        <v>2.8</v>
       </c>
       <c r="P9" t="n">
-        <v>2.03</v>
+        <v>2.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.22</v>
+        <v>3.03</v>
       </c>
       <c r="R9" t="n">
-        <v>1.43</v>
+        <v>1.22</v>
       </c>
       <c r="S9" t="n">
-        <v>2.62</v>
+        <v>4</v>
       </c>
       <c r="T9" t="n">
-        <v>3.05</v>
+        <v>2.09</v>
       </c>
       <c r="U9" t="n">
-        <v>1.32</v>
+        <v>1.7</v>
       </c>
       <c r="V9" t="n">
-        <v>7.8</v>
+        <v>4.33</v>
       </c>
       <c r="W9" t="n">
-        <v>1.02</v>
+        <v>1.19</v>
       </c>
       <c r="X9" t="n">
         <v>1.02</v>
       </c>
       <c r="Y9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE9" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AF9" t="n">
-        <v>1.66</v>
+        <v>2.9</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.13</v>
+        <v>1.5</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45992.54166666666</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.16</v>
+        <v>6.8</v>
       </c>
       <c r="M11" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="N11" t="n">
-        <v>2.26</v>
+        <v>1.47</v>
       </c>
       <c r="O11" t="n">
-        <v>3.45</v>
+        <v>6.1</v>
       </c>
       <c r="P11" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.93</v>
+        <v>1.85</v>
       </c>
       <c r="R11" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>2.62</v>
+        <v>3.26</v>
       </c>
       <c r="T11" t="n">
-        <v>2.9</v>
+        <v>2.44</v>
       </c>
       <c r="U11" t="n">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="V11" t="n">
-        <v>7</v>
+        <v>5.55</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X11" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.2</v>
+        <v>4.15</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.09</v>
+        <v>1.69</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.72</v>
+        <v>2.1</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AF11" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.57</v>
+        <v>2.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.36</v>
+        <v>1.08</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45992.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>5.8</v>
+        <v>9</v>
       </c>
       <c r="M12" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="N12" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="O12" t="n">
-        <v>5.4</v>
+        <v>8.6</v>
       </c>
       <c r="P12" t="n">
         <v>2.5</v>
       </c>
       <c r="Q12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V12" t="n">
+        <v>6</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB12" t="n">
         <v>1.91</v>
       </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.08</v>
-      </c>
       <c r="AC12" t="n">
-        <v>2.63</v>
+        <v>3.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.88</v>
+        <v>1.58</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45992.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.24</v>
+        <v>3.16</v>
       </c>
       <c r="M13" t="n">
-        <v>3.37</v>
+        <v>3.2</v>
       </c>
       <c r="N13" t="n">
-        <v>3.17</v>
+        <v>2.26</v>
       </c>
       <c r="O13" t="n">
-        <v>2.75</v>
+        <v>3.45</v>
       </c>
       <c r="P13" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.35</v>
+        <v>2.93</v>
       </c>
       <c r="R13" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="S13" t="n">
-        <v>3.04</v>
+        <v>2.62</v>
       </c>
       <c r="T13" t="n">
-        <v>2.46</v>
+        <v>2.9</v>
       </c>
       <c r="U13" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="V13" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="W13" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="Z13" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.68</v>
+        <v>2.09</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.15</v>
+        <v>1.72</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.48</v>
+        <v>3.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>6.8</v>
+        <v>1.15</v>
       </c>
       <c r="M14" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="N14" t="n">
-        <v>1.47</v>
+        <v>10</v>
       </c>
       <c r="O14" t="n">
-        <v>6.1</v>
+        <v>1.62</v>
       </c>
       <c r="P14" t="n">
-        <v>2.34</v>
+        <v>2.7</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.85</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="S14" t="n">
-        <v>3.26</v>
+        <v>3.5</v>
       </c>
       <c r="T14" t="n">
-        <v>2.44</v>
+        <v>2.23</v>
       </c>
       <c r="U14" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="V14" t="n">
-        <v>5.55</v>
+        <v>5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.15</v>
+        <v>4.55</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="AB14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE14" t="n">
         <v>2.1</v>
       </c>
-      <c r="AC14" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AF14" t="n">
-        <v>1.9</v>
+        <v>1.66</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.5</v>
+        <v>1.11</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.08</v>
+        <v>4.2</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>9</v>
+        <v>2.24</v>
       </c>
       <c r="M15" t="n">
-        <v>4.6</v>
+        <v>3.37</v>
       </c>
       <c r="N15" t="n">
-        <v>1.36</v>
+        <v>3.17</v>
       </c>
       <c r="O15" t="n">
-        <v>8.6</v>
+        <v>2.75</v>
       </c>
       <c r="P15" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.73</v>
+        <v>3.35</v>
       </c>
       <c r="R15" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S15" t="n">
-        <v>2.77</v>
+        <v>3.04</v>
       </c>
       <c r="T15" t="n">
-        <v>2.69</v>
+        <v>2.46</v>
       </c>
       <c r="U15" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V15" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="W15" t="n">
         <v>1.11</v>
       </c>
       <c r="X15" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AG15" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AH15" t="n">
-        <v>1.06</v>
+        <v>1.62</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.15</v>
+        <v>1.86</v>
       </c>
       <c r="M16" t="n">
-        <v>5.8</v>
+        <v>3.58</v>
       </c>
       <c r="N16" t="n">
-        <v>10</v>
+        <v>4.2</v>
       </c>
       <c r="O16" t="n">
-        <v>1.62</v>
+        <v>2.35</v>
       </c>
       <c r="P16" t="n">
-        <v>2.7</v>
+        <v>2.33</v>
       </c>
       <c r="Q16" t="n">
-        <v>9.199999999999999</v>
+        <v>4.17</v>
       </c>
       <c r="R16" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="S16" t="n">
-        <v>3.5</v>
+        <v>2.77</v>
       </c>
       <c r="T16" t="n">
-        <v>2.23</v>
+        <v>2.81</v>
       </c>
       <c r="U16" t="n">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="V16" t="n">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="W16" t="n">
-        <v>1.19</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.55</v>
+        <v>3.38</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.38</v>
+        <v>3.18</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.53</v>
+        <v>1.27</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.66</v>
+        <v>1.93</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AH16" t="n">
-        <v>4.2</v>
+        <v>2</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.86</v>
+        <v>5.8</v>
       </c>
       <c r="M17" t="n">
-        <v>3.58</v>
+        <v>4.2</v>
       </c>
       <c r="N17" t="n">
-        <v>4.2</v>
+        <v>1.49</v>
       </c>
       <c r="O17" t="n">
-        <v>2.35</v>
+        <v>5.4</v>
       </c>
       <c r="P17" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.17</v>
+        <v>1.91</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.81</v>
+        <v>2.23</v>
       </c>
       <c r="U17" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="V17" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.38</v>
+        <v>4.1</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.8</v>
+        <v>2.08</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.18</v>
+        <v>2.63</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AH17" t="n">
-        <v>2</v>
+        <v>1.08</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N19" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>7</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="V19" t="n">
+        <v>4</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AB19" t="n">
         <v>2.9</v>
       </c>
-      <c r="M19" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N19" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="O19" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V19" t="n">
-        <v>6</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.09</v>
-      </c>
       <c r="AC19" t="n">
-        <v>2.62</v>
+        <v>1.98</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.38</v>
+        <v>1.78</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.56</v>
+        <v>1.76</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.33</v>
+        <v>4.12</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45992.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V20" t="n">
+        <v>6</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y20" t="n">
         <v>1.21</v>
       </c>
-      <c r="M20" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="N20" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>7</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V20" t="n">
+      <c r="Z20" t="n">
         <v>4</v>
       </c>
-      <c r="W20" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>5.7</v>
-      </c>
       <c r="AA20" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.75</v>
+        <v>2.09</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.91</v>
+        <v>2.62</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.79</v>
+        <v>1.46</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.03</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>3.8</v>
+        <v>1.37</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45992.625</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.45</v>
+        <v>1.95</v>
       </c>
       <c r="M23" t="n">
-        <v>2.62</v>
+        <v>3.25</v>
       </c>
       <c r="N23" t="n">
-        <v>2.27</v>
+        <v>3.4</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.35</v>
+        <v>2.83</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.62</v>
+        <v>2.1</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45992.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.95</v>
+        <v>3.45</v>
       </c>
       <c r="M25" t="n">
-        <v>3.25</v>
+        <v>2.62</v>
       </c>
       <c r="N25" t="n">
-        <v>3.4</v>
+        <v>2.27</v>
       </c>
       <c r="O25" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AB25" t="n">
         <v>1.44</v>
       </c>
-      <c r="S25" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="T25" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V25" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AC25" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45992.6875</v>
@@ -3759,7 +3759,7 @@
         <v>3.5</v>
       </c>
       <c r="N28" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="O28" t="n">
         <v>2.34</v>
@@ -3771,7 +3771,7 @@
         <v>5.53</v>
       </c>
       <c r="R28" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="S28" t="n">
         <v>2.62</v>
@@ -3780,16 +3780,16 @@
         <v>3</v>
       </c>
       <c r="U28" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V28" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="W28" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X28" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y28" t="n">
         <v>1.34</v>
@@ -3801,19 +3801,19 @@
         <v>2.05</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AC28" t="n">
         <v>3.54</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE28" t="n">
         <v>1.98</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG28" t="n">
         <v>1.28</v>
@@ -3942,6 +3942,125 @@
       </c>
       <c r="AI29" s="3" t="n">
         <v>45992.71875</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Audax Italiano</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Ñublense</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="M30" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="O30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V30" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AI30" s="3" t="n">
+        <v>45992.83333333334</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.1</v>
+        <v>1.74</v>
       </c>
       <c r="M6" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="N6" t="n">
-        <v>2.2</v>
+        <v>4.8</v>
       </c>
       <c r="O6" t="n">
-        <v>3.5</v>
+        <v>2.38</v>
       </c>
       <c r="P6" t="n">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="R6" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S6" t="n">
-        <v>2.9</v>
+        <v>2.41</v>
       </c>
       <c r="T6" t="n">
-        <v>2.95</v>
+        <v>3.19</v>
       </c>
       <c r="U6" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="V6" t="n">
-        <v>7.7</v>
+        <v>9</v>
       </c>
       <c r="W6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X6" t="n">
         <v>1.03</v>
       </c>
-      <c r="X6" t="n">
-        <v>1</v>
-      </c>
       <c r="Y6" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.14</v>
+        <v>2.66</v>
       </c>
       <c r="AA6" t="n">
-        <v>2</v>
+        <v>2.31</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.47</v>
+        <v>4.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.77</v>
+        <v>2.27</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.36</v>
+        <v>2.05</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45992.45833333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.74</v>
+        <v>3.1</v>
       </c>
       <c r="M7" t="n">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="N7" t="n">
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="O7" t="n">
-        <v>2.38</v>
+        <v>3.5</v>
       </c>
       <c r="P7" t="n">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="Q7" t="n">
-        <v>6</v>
+        <v>2.92</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S7" t="n">
-        <v>2.41</v>
+        <v>2.66</v>
       </c>
       <c r="T7" t="n">
-        <v>3.19</v>
+        <v>2.95</v>
       </c>
       <c r="U7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V7" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y7" t="n">
         <v>1.3</v>
       </c>
-      <c r="V7" t="n">
-        <v>9</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.37</v>
-      </c>
       <c r="Z7" t="n">
-        <v>2.66</v>
+        <v>3.14</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.31</v>
+        <v>1.95</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.2</v>
+        <v>3.47</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.27</v>
+        <v>1.77</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AG7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH7" t="n">
         <v>1.3</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>2.05</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45992.45833333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>2.27</v>
       </c>
       <c r="M8" t="n">
-        <v>3.38</v>
+        <v>3.7</v>
       </c>
       <c r="N8" t="n">
-        <v>4.85</v>
+        <v>2.5</v>
       </c>
       <c r="O8" t="n">
-        <v>2.06</v>
+        <v>2.8</v>
       </c>
       <c r="P8" t="n">
-        <v>2.03</v>
+        <v>2.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.22</v>
+        <v>3.03</v>
       </c>
       <c r="R8" t="n">
-        <v>1.43</v>
+        <v>1.22</v>
       </c>
       <c r="S8" t="n">
-        <v>2.62</v>
+        <v>4</v>
       </c>
       <c r="T8" t="n">
-        <v>3.05</v>
+        <v>2.09</v>
       </c>
       <c r="U8" t="n">
-        <v>1.32</v>
+        <v>1.7</v>
       </c>
       <c r="V8" t="n">
-        <v>7.8</v>
+        <v>4.33</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>1.19</v>
       </c>
       <c r="X8" t="n">
         <v>1.02</v>
       </c>
       <c r="Y8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE8" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z8" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AF8" t="n">
-        <v>1.66</v>
+        <v>2.9</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.13</v>
+        <v>1.5</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45992.54166666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.27</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>3.7</v>
+        <v>3.38</v>
       </c>
       <c r="N9" t="n">
-        <v>2.5</v>
+        <v>4.85</v>
       </c>
       <c r="O9" t="n">
-        <v>2.8</v>
+        <v>2.06</v>
       </c>
       <c r="P9" t="n">
-        <v>2.5</v>
+        <v>2.03</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.03</v>
+        <v>5.22</v>
       </c>
       <c r="R9" t="n">
-        <v>1.22</v>
+        <v>1.43</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>2.62</v>
       </c>
       <c r="T9" t="n">
-        <v>2.09</v>
+        <v>3.05</v>
       </c>
       <c r="U9" t="n">
-        <v>1.7</v>
+        <v>1.32</v>
       </c>
       <c r="V9" t="n">
-        <v>4.33</v>
+        <v>7.8</v>
       </c>
       <c r="W9" t="n">
-        <v>1.19</v>
+        <v>1.02</v>
       </c>
       <c r="X9" t="n">
         <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.12</v>
+        <v>1.36</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.75</v>
+        <v>2.88</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.43</v>
+        <v>2.15</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.68</v>
+        <v>1.71</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.05</v>
+        <v>3.72</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.36</v>
+        <v>2.1</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.9</v>
+        <v>1.66</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.5</v>
+        <v>2.13</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45992.54166666666</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>6.8</v>
+        <v>3.16</v>
       </c>
       <c r="M11" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="N11" t="n">
-        <v>1.47</v>
+        <v>2.26</v>
       </c>
       <c r="O11" t="n">
-        <v>6.1</v>
+        <v>3.45</v>
       </c>
       <c r="P11" t="n">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.85</v>
+        <v>2.93</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="S11" t="n">
-        <v>3.26</v>
+        <v>2.62</v>
       </c>
       <c r="T11" t="n">
-        <v>2.44</v>
+        <v>2.9</v>
       </c>
       <c r="U11" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="V11" t="n">
-        <v>5.55</v>
+        <v>7</v>
       </c>
       <c r="W11" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.15</v>
+        <v>3.2</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.69</v>
+        <v>2.09</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.1</v>
+        <v>1.72</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.5</v>
+        <v>1.57</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.08</v>
+        <v>1.36</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45992.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>9</v>
+        <v>5.8</v>
       </c>
       <c r="M12" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="N12" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="O12" t="n">
-        <v>8.6</v>
+        <v>5.4</v>
       </c>
       <c r="P12" t="n">
         <v>2.5</v>
       </c>
       <c r="Q12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE12" t="n">
         <v>1.73</v>
       </c>
-      <c r="R12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V12" t="n">
-        <v>6</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AF12" t="n">
-        <v>1.58</v>
+        <v>1.88</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45992.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.16</v>
+        <v>1.15</v>
       </c>
       <c r="M13" t="n">
-        <v>3.2</v>
+        <v>5.8</v>
       </c>
       <c r="N13" t="n">
-        <v>2.26</v>
+        <v>10</v>
       </c>
       <c r="O13" t="n">
-        <v>3.45</v>
+        <v>1.62</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.93</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="R13" t="n">
-        <v>1.41</v>
+        <v>1.2</v>
       </c>
       <c r="S13" t="n">
-        <v>2.62</v>
+        <v>3.5</v>
       </c>
       <c r="T13" t="n">
-        <v>2.9</v>
+        <v>2.23</v>
       </c>
       <c r="U13" t="n">
-        <v>1.35</v>
+        <v>1.6</v>
       </c>
       <c r="V13" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>1.19</v>
       </c>
       <c r="X13" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.2</v>
+        <v>4.55</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.09</v>
+        <v>1.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.72</v>
+        <v>2.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.7</v>
+        <v>2.38</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AF13" t="n">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.57</v>
+        <v>1.11</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.36</v>
+        <v>4.2</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.15</v>
+        <v>2.24</v>
       </c>
       <c r="M14" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V14" t="n">
         <v>5.8</v>
       </c>
-      <c r="N14" t="n">
-        <v>10</v>
-      </c>
-      <c r="O14" t="n">
+      <c r="W14" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH14" t="n">
         <v>1.62</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V14" t="n">
-        <v>5</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>4.2</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.24</v>
+        <v>1.86</v>
       </c>
       <c r="M15" t="n">
-        <v>3.37</v>
+        <v>3.58</v>
       </c>
       <c r="N15" t="n">
-        <v>3.17</v>
+        <v>4.2</v>
       </c>
       <c r="O15" t="n">
-        <v>2.75</v>
+        <v>2.35</v>
       </c>
       <c r="P15" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.35</v>
+        <v>4.17</v>
       </c>
       <c r="R15" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>3.04</v>
+        <v>2.77</v>
       </c>
       <c r="T15" t="n">
-        <v>2.46</v>
+        <v>2.81</v>
       </c>
       <c r="U15" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="V15" t="n">
-        <v>5.8</v>
+        <v>5.75</v>
       </c>
       <c r="W15" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>4</v>
+        <v>3.38</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.48</v>
+        <v>3.18</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.38</v>
+        <v>1.93</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.86</v>
+        <v>6.8</v>
       </c>
       <c r="M16" t="n">
-        <v>3.58</v>
+        <v>4.5</v>
       </c>
       <c r="N16" t="n">
-        <v>4.2</v>
+        <v>1.47</v>
       </c>
       <c r="O16" t="n">
-        <v>2.35</v>
+        <v>6.1</v>
       </c>
       <c r="P16" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.17</v>
+        <v>1.85</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="S16" t="n">
-        <v>2.77</v>
+        <v>3.26</v>
       </c>
       <c r="T16" t="n">
-        <v>2.81</v>
+        <v>2.44</v>
       </c>
       <c r="U16" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="V16" t="n">
-        <v>5.75</v>
+        <v>5.55</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.38</v>
+        <v>4.15</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.18</v>
+        <v>2.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="AE16" t="n">
         <v>1.85</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>2</v>
+        <v>1.08</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>5.8</v>
+        <v>9</v>
       </c>
       <c r="M17" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="N17" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="O17" t="n">
-        <v>5.4</v>
+        <v>8.6</v>
       </c>
       <c r="P17" t="n">
         <v>2.5</v>
       </c>
       <c r="Q17" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V17" t="n">
+        <v>6</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB17" t="n">
         <v>1.91</v>
       </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.08</v>
-      </c>
       <c r="AC17" t="n">
-        <v>2.63</v>
+        <v>3.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.88</v>
+        <v>1.58</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.86</v>
+        <v>2.8</v>
       </c>
       <c r="M18" t="n">
         <v>3.6</v>
       </c>
       <c r="N18" t="n">
-        <v>4.1</v>
+        <v>2.17</v>
       </c>
       <c r="O18" t="n">
-        <v>2.45</v>
+        <v>3.35</v>
       </c>
       <c r="P18" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.9</v>
+        <v>2.48</v>
       </c>
       <c r="R18" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="S18" t="n">
-        <v>2.66</v>
+        <v>3.05</v>
       </c>
       <c r="T18" t="n">
-        <v>2.8</v>
+        <v>2.48</v>
       </c>
       <c r="U18" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="V18" t="n">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="W18" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.26</v>
+        <v>4</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.04</v>
+        <v>1.7</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.75</v>
+        <v>2.09</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.4</v>
+        <v>2.62</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.24</v>
+        <v>1.46</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.8</v>
+        <v>1.56</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.91</v>
+        <v>1.37</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45992.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.25</v>
+        <v>1.65</v>
       </c>
       <c r="M19" t="n">
-        <v>5.5</v>
+        <v>3.75</v>
       </c>
       <c r="N19" t="n">
-        <v>9.449999999999999</v>
+        <v>4.8</v>
       </c>
       <c r="O19" t="n">
-        <v>1.65</v>
+        <v>2.32</v>
       </c>
       <c r="P19" t="n">
-        <v>2.75</v>
+        <v>2.04</v>
       </c>
       <c r="Q19" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.19</v>
+        <v>1.41</v>
       </c>
       <c r="S19" t="n">
-        <v>3.94</v>
+        <v>2.66</v>
       </c>
       <c r="T19" t="n">
-        <v>2.02</v>
+        <v>2.7</v>
       </c>
       <c r="U19" t="n">
-        <v>1.74</v>
+        <v>1.35</v>
       </c>
       <c r="V19" t="n">
-        <v>4</v>
+        <v>7.2</v>
       </c>
       <c r="W19" t="n">
-        <v>1.18</v>
+        <v>1.03</v>
       </c>
       <c r="X19" t="n">
         <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.65</v>
+        <v>3.08</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.37</v>
+        <v>1.9</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.98</v>
+        <v>3.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.78</v>
+        <v>1.24</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AF19" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="AH19" t="n">
-        <v>4.12</v>
+        <v>1.95</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45992.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.8</v>
+        <v>1.25</v>
       </c>
       <c r="M20" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="N20" t="n">
-        <v>2.17</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>3.35</v>
+        <v>1.65</v>
       </c>
       <c r="P20" t="n">
-        <v>2.28</v>
+        <v>2.75</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.48</v>
+        <v>7</v>
       </c>
       <c r="R20" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="S20" t="n">
-        <v>3.05</v>
+        <v>3.94</v>
       </c>
       <c r="T20" t="n">
-        <v>2.48</v>
+        <v>2.02</v>
       </c>
       <c r="U20" t="n">
-        <v>1.46</v>
+        <v>1.74</v>
       </c>
       <c r="V20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="W20" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="X20" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="Z20" t="n">
-        <v>4</v>
+        <v>5.65</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.7</v>
+        <v>1.37</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.09</v>
+        <v>2.9</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.62</v>
+        <v>1.98</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.46</v>
+        <v>1.78</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.56</v>
+        <v>1.76</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.37</v>
+        <v>4.12</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45992.625</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.95</v>
+        <v>3.32</v>
       </c>
       <c r="M23" t="n">
-        <v>3.25</v>
+        <v>2.79</v>
       </c>
       <c r="N23" t="n">
-        <v>3.4</v>
+        <v>2.27</v>
       </c>
       <c r="O23" t="n">
-        <v>2.69</v>
+        <v>4.12</v>
       </c>
       <c r="P23" t="n">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.24</v>
+        <v>3.1</v>
       </c>
       <c r="R23" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="S23" t="n">
-        <v>2.47</v>
+        <v>2.26</v>
       </c>
       <c r="T23" t="n">
-        <v>3.04</v>
+        <v>3.45</v>
       </c>
       <c r="U23" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="V23" t="n">
-        <v>7.9</v>
+        <v>10</v>
       </c>
       <c r="W23" t="n">
         <v>1.02</v>
       </c>
       <c r="X23" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.83</v>
+        <v>2.35</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.1</v>
+        <v>2.68</v>
       </c>
       <c r="AB23" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF23" t="n">
         <v>1.67</v>
       </c>
-      <c r="AC23" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AG23" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH23" t="n">
         <v>1.27</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.63</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45992.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.29</v>
+        <v>3.35</v>
       </c>
       <c r="M24" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="N24" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="O24" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AA24" t="n">
         <v>2.62</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45992.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.45</v>
+        <v>2.04</v>
       </c>
       <c r="M25" t="n">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="N25" t="n">
-        <v>2.27</v>
+        <v>3.5</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.35</v>
+        <v>2.98</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45992.6875</v>
@@ -3527,16 +3527,16 @@
         <v>1.91</v>
       </c>
       <c r="P26" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="Q26" t="n">
         <v>7</v>
       </c>
       <c r="R26" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S26" t="n">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="T26" t="n">
         <v>2.75</v>
@@ -3548,7 +3548,7 @@
         <v>7.5</v>
       </c>
       <c r="W26" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X26" t="n">
         <v>1.01</v>
@@ -3572,13 +3572,13 @@
         <v>1.29</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AH26" t="n">
         <v>2.77</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="M27" t="n">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="N27" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="O27" t="n">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="P27" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="Q27" t="n">
-        <v>4</v>
+        <v>5.53</v>
       </c>
       <c r="R27" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="S27" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="T27" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="U27" t="n">
         <v>1.36</v>
       </c>
       <c r="V27" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="W27" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X27" t="n">
         <v>1.06</v>
       </c>
-      <c r="X27" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Y27" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.7</v>
+        <v>3.54</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>45992.70833333334</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="M28" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N28" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O28" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="P28" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="Q28" t="n">
-        <v>5.53</v>
+        <v>4</v>
       </c>
       <c r="R28" t="n">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="S28" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="T28" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U28" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="V28" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="W28" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X28" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.54</v>
+        <v>3.7</v>
       </c>
       <c r="AD28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AG28" t="n">
         <v>1.22</v>
       </c>
-      <c r="AE28" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AH28" t="n">
-        <v>2.04</v>
+        <v>1.85</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45992.70833333334</v>
@@ -3872,37 +3872,37 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>6.16</v>
+        <v>6</v>
       </c>
       <c r="M29" t="n">
-        <v>4.22</v>
+        <v>4.2</v>
       </c>
       <c r="N29" t="n">
         <v>1.53</v>
       </c>
       <c r="O29" t="n">
-        <v>6.47</v>
+        <v>5.5</v>
       </c>
       <c r="P29" t="n">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="Q29" t="n">
         <v>2.1</v>
       </c>
       <c r="R29" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S29" t="n">
-        <v>2.94</v>
+        <v>3.19</v>
       </c>
       <c r="T29" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="U29" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="V29" t="n">
-        <v>6.6</v>
+        <v>6.65</v>
       </c>
       <c r="W29" t="n">
         <v>1.05</v>
@@ -3917,13 +3917,13 @@
         <v>3.7</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AB29" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.98</v>
+        <v>3.01</v>
       </c>
       <c r="AD29" t="n">
         <v>1.33</v>
@@ -3935,10 +3935,10 @@
         <v>1.85</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.25</v>
+        <v>2.4</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>45992.71875</v>

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -936,10 +936,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1055,10 +1055,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.16</v>
+        <v>8</v>
       </c>
       <c r="M11" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="N11" t="n">
-        <v>2.26</v>
+        <v>1.4</v>
       </c>
       <c r="O11" t="n">
-        <v>3.45</v>
+        <v>8.6</v>
       </c>
       <c r="P11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V11" t="n">
+        <v>6</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE11" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q11" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V11" t="n">
-        <v>7</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AF11" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.57</v>
+        <v>1.2</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.36</v>
+        <v>1.06</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45992.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>5.8</v>
+        <v>1.86</v>
       </c>
       <c r="M12" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="N12" t="n">
         <v>4.2</v>
       </c>
-      <c r="N12" t="n">
-        <v>1.49</v>
-      </c>
       <c r="O12" t="n">
-        <v>5.4</v>
+        <v>2.35</v>
       </c>
       <c r="P12" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.91</v>
+        <v>4.17</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T12" t="n">
-        <v>2.23</v>
+        <v>2.81</v>
       </c>
       <c r="U12" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.1</v>
+        <v>3.38</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.08</v>
+        <v>1.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.63</v>
+        <v>3.18</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.08</v>
+        <v>2</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45992.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.15</v>
+        <v>6.8</v>
       </c>
       <c r="M13" t="n">
-        <v>5.8</v>
+        <v>4.5</v>
       </c>
       <c r="N13" t="n">
-        <v>10</v>
+        <v>1.47</v>
       </c>
       <c r="O13" t="n">
-        <v>1.62</v>
+        <v>6.1</v>
       </c>
       <c r="P13" t="n">
-        <v>2.7</v>
+        <v>2.34</v>
       </c>
       <c r="Q13" t="n">
-        <v>9.199999999999999</v>
+        <v>1.85</v>
       </c>
       <c r="R13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V13" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y13" t="n">
         <v>1.2</v>
       </c>
-      <c r="S13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V13" t="n">
-        <v>5</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.17</v>
-      </c>
       <c r="Z13" t="n">
-        <v>4.55</v>
+        <v>4.15</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="AB13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG13" t="n">
         <v>2.5</v>
       </c>
-      <c r="AC13" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AH13" t="n">
-        <v>4.2</v>
+        <v>1.08</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.24</v>
+        <v>1.25</v>
       </c>
       <c r="M14" t="n">
-        <v>3.37</v>
+        <v>5.8</v>
       </c>
       <c r="N14" t="n">
-        <v>3.17</v>
+        <v>14</v>
       </c>
       <c r="O14" t="n">
-        <v>2.75</v>
+        <v>1.62</v>
       </c>
       <c r="P14" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.35</v>
+        <v>9.5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="S14" t="n">
-        <v>3.04</v>
+        <v>4.2</v>
       </c>
       <c r="T14" t="n">
-        <v>2.46</v>
+        <v>2.25</v>
       </c>
       <c r="U14" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="V14" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="W14" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG14" t="n">
         <v>1.11</v>
       </c>
-      <c r="X14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH14" t="n">
-        <v>1.62</v>
+        <v>4.2</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.86</v>
+        <v>5.8</v>
       </c>
       <c r="M15" t="n">
-        <v>3.58</v>
+        <v>4.2</v>
       </c>
       <c r="N15" t="n">
-        <v>4.2</v>
+        <v>1.49</v>
       </c>
       <c r="O15" t="n">
-        <v>2.35</v>
+        <v>5.4</v>
       </c>
       <c r="P15" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.17</v>
+        <v>1.91</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.81</v>
+        <v>2.23</v>
       </c>
       <c r="U15" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="V15" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.38</v>
+        <v>4.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.8</v>
+        <v>2.08</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.18</v>
+        <v>2.63</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AH15" t="n">
-        <v>2</v>
+        <v>1.08</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>6.8</v>
+        <v>2.24</v>
       </c>
       <c r="M16" t="n">
-        <v>4.5</v>
+        <v>3.37</v>
       </c>
       <c r="N16" t="n">
-        <v>1.47</v>
+        <v>3.17</v>
       </c>
       <c r="O16" t="n">
-        <v>6.1</v>
+        <v>2.75</v>
       </c>
       <c r="P16" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.85</v>
+        <v>3.35</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S16" t="n">
-        <v>3.26</v>
+        <v>3.04</v>
       </c>
       <c r="T16" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="U16" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="V16" t="n">
-        <v>5.55</v>
+        <v>5.8</v>
       </c>
       <c r="W16" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y16" t="n">
         <v>1.2</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.9</v>
+        <v>2.38</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.5</v>
+        <v>1.25</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.08</v>
+        <v>1.62</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>9</v>
+        <v>3.16</v>
       </c>
       <c r="M17" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="N17" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V17" t="n">
+        <v>7</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH17" t="n">
         <v>1.36</v>
-      </c>
-      <c r="O17" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V17" t="n">
-        <v>6</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.06</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N19" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="O19" t="n">
         <v>1.65</v>
       </c>
-      <c r="M19" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O19" t="n">
-        <v>2.32</v>
-      </c>
       <c r="P19" t="n">
-        <v>2.04</v>
+        <v>2.75</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="R19" t="n">
-        <v>1.41</v>
+        <v>1.19</v>
       </c>
       <c r="S19" t="n">
-        <v>2.66</v>
+        <v>3.94</v>
       </c>
       <c r="T19" t="n">
-        <v>2.7</v>
+        <v>2.02</v>
       </c>
       <c r="U19" t="n">
-        <v>1.35</v>
+        <v>1.74</v>
       </c>
       <c r="V19" t="n">
-        <v>7.2</v>
+        <v>4</v>
       </c>
       <c r="W19" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="X19" t="n">
         <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.08</v>
+        <v>5.65</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.9</v>
+        <v>1.37</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.4</v>
+        <v>1.98</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.24</v>
+        <v>1.78</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.95</v>
+        <v>4.12</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45992.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.25</v>
+        <v>1.65</v>
       </c>
       <c r="M20" t="n">
-        <v>5.5</v>
+        <v>3.75</v>
       </c>
       <c r="N20" t="n">
-        <v>9.449999999999999</v>
+        <v>4.8</v>
       </c>
       <c r="O20" t="n">
-        <v>1.65</v>
+        <v>2.32</v>
       </c>
       <c r="P20" t="n">
-        <v>2.75</v>
+        <v>2.04</v>
       </c>
       <c r="Q20" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="R20" t="n">
-        <v>1.19</v>
+        <v>1.41</v>
       </c>
       <c r="S20" t="n">
-        <v>3.94</v>
+        <v>2.66</v>
       </c>
       <c r="T20" t="n">
-        <v>2.02</v>
+        <v>2.7</v>
       </c>
       <c r="U20" t="n">
-        <v>1.74</v>
+        <v>1.35</v>
       </c>
       <c r="V20" t="n">
-        <v>4</v>
+        <v>7.2</v>
       </c>
       <c r="W20" t="n">
-        <v>1.18</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
         <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.65</v>
+        <v>3.08</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.37</v>
+        <v>1.9</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.98</v>
+        <v>3.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.78</v>
+        <v>1.24</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AF20" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="AH20" t="n">
-        <v>4.12</v>
+        <v>1.95</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45992.625</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="M27" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N27" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O27" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="P27" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="Q27" t="n">
-        <v>5.53</v>
+        <v>4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="S27" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="T27" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U27" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="V27" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="W27" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X27" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.54</v>
+        <v>3.7</v>
       </c>
       <c r="AD27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AG27" t="n">
         <v>1.22</v>
       </c>
-      <c r="AE27" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AH27" t="n">
-        <v>2.04</v>
+        <v>1.85</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>45992.70833333334</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.95</v>
+        <v>1.76</v>
       </c>
       <c r="M28" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N28" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O28" t="n">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="P28" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="Q28" t="n">
-        <v>4</v>
+        <v>5.53</v>
       </c>
       <c r="R28" t="n">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="S28" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T28" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U28" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="V28" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="W28" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X28" t="n">
         <v>1.06</v>
       </c>
-      <c r="X28" t="n">
-        <v>1.03</v>
-      </c>
       <c r="Y28" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.7</v>
+        <v>3.54</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45992.70833333334</v>

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45992.41666666666</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1055,10 +1055,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="M6" t="n">
-        <v>3.28</v>
+        <v>3.41</v>
       </c>
       <c r="N6" t="n">
         <v>4.8</v>
       </c>
       <c r="O6" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="P6" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="Q6" t="n">
-        <v>6</v>
+        <v>6.01</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="S6" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="T6" t="n">
         <v>3.19</v>
       </c>
       <c r="U6" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="V6" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="X6" t="n">
         <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.31</v>
+        <v>1.93</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.6</v>
+        <v>1.77</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.27</v>
+        <v>2.1</v>
       </c>
       <c r="AF6" t="n">
         <v>1.67</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45992.45833333334</v>
@@ -1269,19 +1269,19 @@
         <v>2.15</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="R7" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="S7" t="n">
         <v>2.66</v>
       </c>
       <c r="T7" t="n">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="U7" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="V7" t="n">
         <v>7.7</v>
@@ -1293,7 +1293,7 @@
         <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z7" t="n">
         <v>3.14</v>
@@ -1305,22 +1305,22 @@
         <v>1.75</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.47</v>
+        <v>3.44</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AF7" t="n">
         <v>1.86</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45992.45833333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.27</v>
+        <v>1.65</v>
       </c>
       <c r="M8" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="N8" t="n">
-        <v>2.5</v>
+        <v>4.9</v>
       </c>
       <c r="O8" t="n">
-        <v>2.8</v>
+        <v>2.12</v>
       </c>
       <c r="P8" t="n">
-        <v>2.5</v>
+        <v>2.09</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.03</v>
+        <v>6.2</v>
       </c>
       <c r="R8" t="n">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>2.62</v>
       </c>
       <c r="T8" t="n">
-        <v>2.09</v>
+        <v>3.19</v>
       </c>
       <c r="U8" t="n">
-        <v>1.7</v>
+        <v>1.32</v>
       </c>
       <c r="V8" t="n">
-        <v>4.33</v>
+        <v>7.8</v>
       </c>
       <c r="W8" t="n">
-        <v>1.19</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
         <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.12</v>
+        <v>1.36</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.75</v>
+        <v>2.88</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.43</v>
+        <v>1.97</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.68</v>
+        <v>1.73</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.05</v>
+        <v>3.72</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.36</v>
+        <v>2.1</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.9</v>
+        <v>1.66</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.5</v>
+        <v>2.32</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45992.54166666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>2.36</v>
       </c>
       <c r="M9" t="n">
-        <v>3.38</v>
+        <v>3.65</v>
       </c>
       <c r="N9" t="n">
-        <v>4.85</v>
+        <v>2.37</v>
       </c>
       <c r="O9" t="n">
-        <v>2.06</v>
+        <v>2.8</v>
       </c>
       <c r="P9" t="n">
-        <v>2.03</v>
+        <v>2.36</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.22</v>
+        <v>3.03</v>
       </c>
       <c r="R9" t="n">
-        <v>1.43</v>
+        <v>1.22</v>
       </c>
       <c r="S9" t="n">
-        <v>2.62</v>
+        <v>4</v>
       </c>
       <c r="T9" t="n">
-        <v>3.05</v>
+        <v>2.09</v>
       </c>
       <c r="U9" t="n">
-        <v>1.32</v>
+        <v>1.7</v>
       </c>
       <c r="V9" t="n">
-        <v>7.8</v>
+        <v>4.33</v>
       </c>
       <c r="W9" t="n">
-        <v>1.02</v>
+        <v>1.19</v>
       </c>
       <c r="X9" t="n">
         <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.36</v>
+        <v>1.08</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.88</v>
+        <v>5.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.15</v>
+        <v>1.42</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.71</v>
+        <v>2.65</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.72</v>
+        <v>1.94</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.2</v>
+        <v>1.76</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.1</v>
+        <v>1.35</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.66</v>
+        <v>2.8</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.13</v>
+        <v>1.5</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45992.54166666666</v>
@@ -1611,28 +1611,28 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.96</v>
+        <v>2.5</v>
       </c>
       <c r="M10" t="n">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="N10" t="n">
-        <v>2.59</v>
+        <v>3.05</v>
       </c>
       <c r="O10" t="n">
-        <v>3.92</v>
+        <v>3.46</v>
       </c>
       <c r="P10" t="n">
         <v>1.86</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R10" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="S10" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="T10" t="n">
         <v>3.88</v>
@@ -1647,34 +1647,34 @@
         <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="AC10" t="n">
-        <v>5.3</v>
+        <v>5.52</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
       <c r="AF10" t="n">
         <v>1.63</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.53</v>
+        <v>1.34</v>
       </c>
       <c r="AH10" t="n">
         <v>1.33</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>8</v>
+        <v>1.86</v>
       </c>
       <c r="M11" t="n">
-        <v>4.6</v>
+        <v>3.58</v>
       </c>
       <c r="N11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="R11" t="n">
         <v>1.4</v>
-      </c>
-      <c r="O11" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.36</v>
       </c>
       <c r="S11" t="n">
         <v>2.77</v>
       </c>
       <c r="T11" t="n">
-        <v>2.69</v>
+        <v>2.81</v>
       </c>
       <c r="U11" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="V11" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="W11" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.34</v>
+        <v>3.38</v>
       </c>
       <c r="AA11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB11" t="n">
         <v>1.8</v>
       </c>
-      <c r="AB11" t="n">
+      <c r="AC11" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH11" t="n">
         <v>2</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.06</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45992.58333333334</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.86</v>
+        <v>2.24</v>
       </c>
       <c r="M12" t="n">
-        <v>3.58</v>
+        <v>3.37</v>
       </c>
       <c r="N12" t="n">
-        <v>4.2</v>
+        <v>3.17</v>
       </c>
       <c r="O12" t="n">
-        <v>2.35</v>
+        <v>2.75</v>
       </c>
       <c r="P12" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.17</v>
+        <v>3.35</v>
       </c>
       <c r="R12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V12" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AD12" t="n">
         <v>1.4</v>
       </c>
-      <c r="S12" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V12" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AE12" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.93</v>
+        <v>2.38</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45992.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="M13" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="N13" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="O13" t="n">
-        <v>6.1</v>
+        <v>8.6</v>
       </c>
       <c r="P13" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="S13" t="n">
-        <v>3.26</v>
+        <v>2.77</v>
       </c>
       <c r="T13" t="n">
-        <v>2.44</v>
+        <v>2.69</v>
       </c>
       <c r="U13" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="V13" t="n">
-        <v>5.55</v>
+        <v>6</v>
       </c>
       <c r="W13" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.15</v>
+        <v>3.6</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.9</v>
+        <v>1.62</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.25</v>
+        <v>6.8</v>
       </c>
       <c r="M14" t="n">
-        <v>5.8</v>
+        <v>4.5</v>
       </c>
       <c r="N14" t="n">
-        <v>14</v>
+        <v>1.47</v>
       </c>
       <c r="O14" t="n">
-        <v>1.62</v>
+        <v>6.1</v>
       </c>
       <c r="P14" t="n">
-        <v>2.7</v>
+        <v>2.34</v>
       </c>
       <c r="Q14" t="n">
-        <v>9.5</v>
+        <v>1.85</v>
       </c>
       <c r="R14" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S14" t="n">
-        <v>4.2</v>
+        <v>3.26</v>
       </c>
       <c r="T14" t="n">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="U14" t="n">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="V14" t="n">
-        <v>5</v>
+        <v>5.55</v>
       </c>
       <c r="W14" t="n">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.07</v>
+        <v>4.15</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.11</v>
+        <v>2.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>4.2</v>
+        <v>1.08</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5.8</v>
+        <v>2.79</v>
       </c>
       <c r="M15" t="n">
-        <v>4.2</v>
+        <v>3.23</v>
       </c>
       <c r="N15" t="n">
-        <v>1.49</v>
+        <v>2.21</v>
       </c>
       <c r="O15" t="n">
-        <v>5.4</v>
+        <v>3.74</v>
       </c>
       <c r="P15" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.91</v>
+        <v>2.87</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T15" t="n">
-        <v>2.23</v>
+        <v>2.9</v>
       </c>
       <c r="U15" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.64</v>
+        <v>1.93</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.08</v>
+        <v>1.77</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.63</v>
+        <v>3.34</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.08</v>
+        <v>1.36</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.24</v>
+        <v>1.25</v>
       </c>
       <c r="M16" t="n">
-        <v>3.37</v>
+        <v>5.8</v>
       </c>
       <c r="N16" t="n">
-        <v>3.17</v>
+        <v>14</v>
       </c>
       <c r="O16" t="n">
-        <v>2.75</v>
+        <v>1.62</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.35</v>
+        <v>8.5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="S16" t="n">
-        <v>3.04</v>
+        <v>4.2</v>
       </c>
       <c r="T16" t="n">
-        <v>2.46</v>
+        <v>2.23</v>
       </c>
       <c r="U16" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="V16" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="W16" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG16" t="n">
         <v>1.11</v>
       </c>
-      <c r="X16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH16" t="n">
-        <v>1.62</v>
+        <v>4.2</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.16</v>
+        <v>5.8</v>
       </c>
       <c r="M17" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="N17" t="n">
-        <v>2.26</v>
+        <v>1.49</v>
       </c>
       <c r="O17" t="n">
-        <v>3.45</v>
+        <v>5.4</v>
       </c>
       <c r="P17" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.93</v>
+        <v>1.91</v>
       </c>
       <c r="R17" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.9</v>
+        <v>2.23</v>
       </c>
       <c r="U17" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="V17" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.09</v>
+        <v>1.64</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.72</v>
+        <v>2.08</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.7</v>
+        <v>2.63</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AF17" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.57</v>
+        <v>1.15</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.36</v>
+        <v>1.08</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.8</v>
+        <v>1.65</v>
       </c>
       <c r="M18" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="N18" t="n">
-        <v>2.17</v>
+        <v>4.8</v>
       </c>
       <c r="O18" t="n">
-        <v>3.35</v>
+        <v>2.32</v>
       </c>
       <c r="P18" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.48</v>
+        <v>5.19</v>
       </c>
       <c r="R18" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S18" t="n">
-        <v>3.05</v>
+        <v>2.66</v>
       </c>
       <c r="T18" t="n">
-        <v>2.48</v>
+        <v>2.9</v>
       </c>
       <c r="U18" t="n">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="V18" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="W18" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X18" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z18" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.09</v>
+        <v>1.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.62</v>
+        <v>3.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.56</v>
+        <v>1.8</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.3</v>
+        <v>1.81</v>
       </c>
       <c r="AG18" t="n">
         <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.37</v>
+        <v>1.95</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45992.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.25</v>
+        <v>3.05</v>
       </c>
       <c r="M19" t="n">
-        <v>5.5</v>
+        <v>3.39</v>
       </c>
       <c r="N19" t="n">
-        <v>9.449999999999999</v>
+        <v>2.01</v>
       </c>
       <c r="O19" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V19" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA19" t="n">
         <v>1.65</v>
       </c>
-      <c r="P19" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>7</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="V19" t="n">
-        <v>4</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.37</v>
-      </c>
       <c r="AB19" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.98</v>
+        <v>2.59</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.78</v>
+        <v>1.4</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.76</v>
+        <v>1.53</v>
       </c>
       <c r="AF19" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.12</v>
+        <v>1.67</v>
       </c>
       <c r="AH19" t="n">
-        <v>4.12</v>
+        <v>1.33</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45992.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.65</v>
+        <v>1.21</v>
       </c>
       <c r="M20" t="n">
-        <v>3.75</v>
+        <v>5.6</v>
       </c>
       <c r="N20" t="n">
-        <v>4.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>2.32</v>
+        <v>1.7</v>
       </c>
       <c r="P20" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>7</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T20" t="n">
         <v>2.04</v>
       </c>
-      <c r="Q20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.7</v>
-      </c>
       <c r="U20" t="n">
-        <v>1.35</v>
+        <v>1.73</v>
       </c>
       <c r="V20" t="n">
-        <v>7.2</v>
+        <v>4.2</v>
       </c>
       <c r="W20" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="X20" t="n">
         <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.08</v>
+        <v>5.75</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.9</v>
+        <v>1.36</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.8</v>
+        <v>2.99</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.4</v>
+        <v>1.91</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.24</v>
+        <v>1.79</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.3</v>
+        <v>1.06</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.95</v>
+        <v>3.6</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45992.625</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.76</v>
+        <v>2.99</v>
       </c>
       <c r="M21" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="N21" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="O21" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P21" t="n">
-        <v>2.25</v>
+        <v>2.51</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.73</v>
+        <v>2.45</v>
       </c>
       <c r="R21" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="S21" t="n">
-        <v>3.36</v>
+        <v>4.4</v>
       </c>
       <c r="T21" t="n">
-        <v>2.25</v>
+        <v>1.88</v>
       </c>
       <c r="U21" t="n">
-        <v>1.6</v>
+        <v>1.96</v>
       </c>
       <c r="V21" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="W21" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.65</v>
+        <v>7</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.58</v>
+        <v>1.3</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.4</v>
+        <v>3.37</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.31</v>
+        <v>1.78</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.58</v>
+        <v>1.98</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.5</v>
+        <v>3.34</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.5</v>
+        <v>1.21</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45992.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.99</v>
+        <v>2.76</v>
       </c>
       <c r="M22" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="N22" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="O22" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P22" t="n">
-        <v>2.51</v>
+        <v>2.25</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.45</v>
+        <v>2.73</v>
       </c>
       <c r="R22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V22" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="W22" t="n">
         <v>1.15</v>
-      </c>
-      <c r="S22" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="V22" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.21</v>
       </c>
       <c r="X22" t="n">
         <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="Z22" t="n">
-        <v>7</v>
+        <v>4.65</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.3</v>
+        <v>1.58</v>
       </c>
       <c r="AB22" t="n">
-        <v>3.37</v>
+        <v>2.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.78</v>
+        <v>2.31</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.98</v>
+        <v>1.58</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="AF22" t="n">
-        <v>3.34</v>
+        <v>2.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45992.66666666666</v>
@@ -3167,22 +3167,22 @@
         <v>2.27</v>
       </c>
       <c r="O23" t="n">
-        <v>4.12</v>
+        <v>4.1</v>
       </c>
       <c r="P23" t="n">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="Q23" t="n">
         <v>3.1</v>
       </c>
       <c r="R23" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S23" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="T23" t="n">
-        <v>3.45</v>
+        <v>3.58</v>
       </c>
       <c r="U23" t="n">
         <v>1.21</v>
@@ -3191,16 +3191,16 @@
         <v>10</v>
       </c>
       <c r="W23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X23" t="n">
         <v>1.05</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AA23" t="n">
         <v>2.68</v>
@@ -3212,16 +3212,16 @@
         <v>4</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AE23" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AH23" t="n">
         <v>1.27</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.35</v>
+        <v>2.04</v>
       </c>
       <c r="M24" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="N24" t="n">
-        <v>2.22</v>
+        <v>3.5</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.35</v>
+        <v>2.83</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45992.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.04</v>
+        <v>3.35</v>
       </c>
       <c r="M25" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="N25" t="n">
-        <v>3.5</v>
+        <v>2.22</v>
       </c>
       <c r="O25" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.35</v>
+        <v>1.52</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.98</v>
+        <v>2.35</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.2</v>
+        <v>2.69</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.6</v>
+        <v>1.41</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45992.6875</v>
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="M26" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="N26" t="n">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="O26" t="n">
         <v>1.91</v>
@@ -3533,10 +3533,10 @@
         <v>7</v>
       </c>
       <c r="R26" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="S26" t="n">
-        <v>2.9</v>
+        <v>2.79</v>
       </c>
       <c r="T26" t="n">
         <v>2.75</v>
@@ -3557,19 +3557,19 @@
         <v>1.35</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.3</v>
+        <v>3.16</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.09</v>
+        <v>1.97</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AC26" t="n">
         <v>3.55</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE26" t="n">
         <v>2.2</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="M27" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="N27" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O27" t="n">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="P27" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="Q27" t="n">
-        <v>4</v>
+        <v>5.69</v>
       </c>
       <c r="R27" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="S27" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T27" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U27" t="n">
         <v>1.37</v>
       </c>
       <c r="V27" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="W27" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X27" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.14</v>
+        <v>1.85</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.7</v>
+        <v>3.54</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>45992.70833333334</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="M28" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N28" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O28" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="P28" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="Q28" t="n">
-        <v>5.53</v>
+        <v>4</v>
       </c>
       <c r="R28" t="n">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="S28" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="T28" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U28" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="V28" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="W28" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X28" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.54</v>
+        <v>3.7</v>
       </c>
       <c r="AD28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AG28" t="n">
         <v>1.22</v>
       </c>
-      <c r="AE28" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AH28" t="n">
-        <v>2.04</v>
+        <v>1.85</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45992.70833333334</v>
@@ -3872,19 +3872,19 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="M29" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="N29" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="O29" t="n">
         <v>5.5</v>
       </c>
       <c r="P29" t="n">
-        <v>2.43</v>
+        <v>2.2</v>
       </c>
       <c r="Q29" t="n">
         <v>2.1</v>
@@ -3893,22 +3893,22 @@
         <v>1.36</v>
       </c>
       <c r="S29" t="n">
-        <v>3.19</v>
+        <v>2.89</v>
       </c>
       <c r="T29" t="n">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="U29" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="V29" t="n">
-        <v>6.65</v>
+        <v>6.25</v>
       </c>
       <c r="W29" t="n">
         <v>1.05</v>
       </c>
       <c r="X29" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y29" t="n">
         <v>1.23</v>
@@ -3917,16 +3917,16 @@
         <v>3.7</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.84</v>
+        <v>1.63</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE29" t="n">
         <v>1.85</v>
@@ -3938,7 +3938,7 @@
         <v>2.4</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>45992.71875</v>

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45992.41666666666</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45992.41666666666</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.86</v>
+        <v>6</v>
       </c>
       <c r="M11" t="n">
-        <v>3.58</v>
+        <v>4.3</v>
       </c>
       <c r="N11" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="O11" t="n">
-        <v>2.35</v>
+        <v>5.4</v>
       </c>
       <c r="P11" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.17</v>
+        <v>1.91</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.81</v>
+        <v>2.23</v>
       </c>
       <c r="U11" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="V11" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.38</v>
+        <v>4.1</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.8</v>
+        <v>2.08</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.18</v>
+        <v>2.63</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.3</v>
+        <v>2.28</v>
       </c>
       <c r="AH11" t="n">
-        <v>2</v>
+        <v>1.08</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45992.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.24</v>
+        <v>2.79</v>
       </c>
       <c r="M12" t="n">
-        <v>3.37</v>
+        <v>3.23</v>
       </c>
       <c r="N12" t="n">
-        <v>3.17</v>
+        <v>2.21</v>
       </c>
       <c r="O12" t="n">
-        <v>2.75</v>
+        <v>3.74</v>
       </c>
       <c r="P12" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.35</v>
+        <v>2.87</v>
       </c>
       <c r="R12" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="S12" t="n">
-        <v>3.04</v>
+        <v>2.59</v>
       </c>
       <c r="T12" t="n">
-        <v>2.46</v>
+        <v>2.9</v>
       </c>
       <c r="U12" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="V12" t="n">
-        <v>5.8</v>
+        <v>6.95</v>
       </c>
       <c r="W12" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="X12" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.68</v>
+        <v>1.93</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.15</v>
+        <v>1.77</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.48</v>
+        <v>3.34</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45992.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>8</v>
+        <v>1.86</v>
       </c>
       <c r="M13" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="N13" t="n">
-        <v>1.4</v>
+        <v>4.3</v>
       </c>
       <c r="O13" t="n">
-        <v>8.6</v>
+        <v>2.35</v>
       </c>
       <c r="P13" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.73</v>
+        <v>4.5</v>
       </c>
       <c r="R13" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U13" t="n">
         <v>1.38</v>
       </c>
-      <c r="S13" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.4</v>
-      </c>
       <c r="V13" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="W13" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.6</v>
+        <v>3.52</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB13" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.2</v>
+        <v>1.88</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.62</v>
+        <v>2.02</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.32</v>
+        <v>1.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.06</v>
+        <v>1.91</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>6.8</v>
+        <v>1.25</v>
       </c>
       <c r="M14" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="N14" t="n">
-        <v>1.47</v>
+        <v>14</v>
       </c>
       <c r="O14" t="n">
-        <v>6.1</v>
+        <v>1.62</v>
       </c>
       <c r="P14" t="n">
-        <v>2.34</v>
+        <v>2.7</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.85</v>
+        <v>8.5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="S14" t="n">
-        <v>3.26</v>
+        <v>4.2</v>
       </c>
       <c r="T14" t="n">
-        <v>2.44</v>
+        <v>2.23</v>
       </c>
       <c r="U14" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="V14" t="n">
-        <v>5.55</v>
+        <v>5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="X14" t="n">
         <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.15</v>
+        <v>4.8</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.5</v>
+        <v>1.11</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.08</v>
+        <v>4.2</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.79</v>
+        <v>6.8</v>
       </c>
       <c r="M15" t="n">
-        <v>3.23</v>
+        <v>4.5</v>
       </c>
       <c r="N15" t="n">
-        <v>2.21</v>
+        <v>1.47</v>
       </c>
       <c r="O15" t="n">
-        <v>3.74</v>
+        <v>6.1</v>
       </c>
       <c r="P15" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.87</v>
+        <v>1.85</v>
       </c>
       <c r="R15" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="S15" t="n">
-        <v>2.59</v>
+        <v>3.26</v>
       </c>
       <c r="T15" t="n">
-        <v>2.9</v>
+        <v>2.44</v>
       </c>
       <c r="U15" t="n">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="V15" t="n">
-        <v>6.95</v>
+        <v>5.55</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.2</v>
+        <v>4.15</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.93</v>
+        <v>1.69</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.34</v>
+        <v>2.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AF15" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.36</v>
+        <v>1.08</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.25</v>
+        <v>2.19</v>
       </c>
       <c r="M16" t="n">
-        <v>5.8</v>
+        <v>3.4</v>
       </c>
       <c r="N16" t="n">
-        <v>14</v>
+        <v>3.25</v>
       </c>
       <c r="O16" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V16" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH16" t="n">
         <v>1.62</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V16" t="n">
-        <v>5</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>4.2</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>5.8</v>
+        <v>8</v>
       </c>
       <c r="M17" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="N17" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="O17" t="n">
-        <v>5.4</v>
+        <v>8.6</v>
       </c>
       <c r="P17" t="n">
         <v>2.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T17" t="n">
-        <v>2.23</v>
+        <v>2.69</v>
       </c>
       <c r="U17" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.63</v>
+        <v>3.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.88</v>
+        <v>1.62</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.15</v>
+        <v>2.32</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.65</v>
+        <v>3.05</v>
       </c>
       <c r="M18" t="n">
-        <v>3.75</v>
+        <v>3.39</v>
       </c>
       <c r="N18" t="n">
-        <v>4.8</v>
+        <v>2.01</v>
       </c>
       <c r="O18" t="n">
-        <v>2.32</v>
+        <v>3.7</v>
       </c>
       <c r="P18" t="n">
-        <v>2.24</v>
+        <v>2.13</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.19</v>
+        <v>2.48</v>
       </c>
       <c r="R18" t="n">
         <v>1.33</v>
       </c>
       <c r="S18" t="n">
-        <v>2.66</v>
+        <v>3.05</v>
       </c>
       <c r="T18" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="U18" t="n">
-        <v>1.35</v>
+        <v>1.51</v>
       </c>
       <c r="V18" t="n">
-        <v>7.2</v>
+        <v>5.95</v>
       </c>
       <c r="W18" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.5</v>
+        <v>2.59</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.81</v>
+        <v>2.3</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.95</v>
+        <v>1.33</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45992.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.05</v>
+        <v>1.21</v>
       </c>
       <c r="M19" t="n">
-        <v>3.39</v>
+        <v>5.6</v>
       </c>
       <c r="N19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>7</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AF19" t="n">
         <v>2.01</v>
       </c>
-      <c r="O19" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="V19" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AG19" t="n">
-        <v>1.67</v>
+        <v>1.06</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.33</v>
+        <v>3.6</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45992.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.21</v>
+        <v>1.65</v>
       </c>
       <c r="M20" t="n">
-        <v>5.6</v>
+        <v>3.75</v>
       </c>
       <c r="N20" t="n">
-        <v>8.800000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="O20" t="n">
-        <v>1.7</v>
+        <v>2.32</v>
       </c>
       <c r="P20" t="n">
-        <v>2.75</v>
+        <v>2.24</v>
       </c>
       <c r="Q20" t="n">
-        <v>7</v>
+        <v>5.19</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="S20" t="n">
-        <v>4.2</v>
+        <v>2.66</v>
       </c>
       <c r="T20" t="n">
-        <v>2.04</v>
+        <v>2.9</v>
       </c>
       <c r="U20" t="n">
-        <v>1.73</v>
+        <v>1.35</v>
       </c>
       <c r="V20" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="W20" t="n">
-        <v>1.18</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
         <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.75</v>
+        <v>3.2</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.36</v>
+        <v>1.9</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.99</v>
+        <v>1.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.91</v>
+        <v>3.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.79</v>
+        <v>1.25</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.01</v>
+        <v>1.81</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>3.6</v>
+        <v>1.95</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45992.625</v>
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.99</v>
+        <v>3.15</v>
       </c>
       <c r="M21" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="N21" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="O21" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="P21" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="R21" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="S21" t="n">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="T21" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="U21" t="n">
-        <v>1.96</v>
+        <v>1.83</v>
       </c>
       <c r="V21" t="n">
-        <v>3.7</v>
+        <v>3.84</v>
       </c>
       <c r="W21" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Z21" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="AA21" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE21" t="n">
         <v>1.3</v>
       </c>
-      <c r="AB21" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AF21" t="n">
-        <v>3.34</v>
+        <v>3.14</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.21</v>
+        <v>1.76</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45992.66666666666</v>
@@ -3054,7 +3054,7 @@
         <v>2.25</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="R22" t="n">
         <v>1.25</v>
@@ -3063,16 +3063,16 @@
         <v>3.36</v>
       </c>
       <c r="T22" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="U22" t="n">
         <v>1.6</v>
       </c>
       <c r="V22" t="n">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="W22" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X22" t="n">
         <v>1.01</v>
@@ -3081,7 +3081,7 @@
         <v>1.13</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.65</v>
+        <v>5.3</v>
       </c>
       <c r="AA22" t="n">
         <v>1.58</v>
@@ -3090,22 +3090,22 @@
         <v>2.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AF22" t="n">
         <v>2.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45992.66666666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.32</v>
+        <v>2.04</v>
       </c>
       <c r="M23" t="n">
-        <v>2.79</v>
+        <v>3.1</v>
       </c>
       <c r="N23" t="n">
-        <v>2.27</v>
+        <v>3.5</v>
       </c>
       <c r="O23" t="n">
-        <v>4.1</v>
+        <v>2.71</v>
       </c>
       <c r="P23" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.1</v>
+        <v>4.45</v>
       </c>
       <c r="R23" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="S23" t="n">
-        <v>2.24</v>
+        <v>2.47</v>
       </c>
       <c r="T23" t="n">
-        <v>3.58</v>
+        <v>3.06</v>
       </c>
       <c r="U23" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="V23" t="n">
-        <v>10</v>
+        <v>7.9</v>
       </c>
       <c r="W23" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X23" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.38</v>
+        <v>2.83</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.68</v>
+        <v>2.2</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.41</v>
+        <v>1.6</v>
       </c>
       <c r="AC23" t="n">
-        <v>4</v>
+        <v>3.72</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.06</v>
+        <v>1.85</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AG23" t="n">
         <v>1.27</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.27</v>
+        <v>1.63</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45992.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.04</v>
+        <v>3.32</v>
       </c>
       <c r="M24" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="O24" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q24" t="n">
         <v>3.1</v>
       </c>
-      <c r="N24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O24" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>4.45</v>
-      </c>
       <c r="R24" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="S24" t="n">
-        <v>2.47</v>
+        <v>2.24</v>
       </c>
       <c r="T24" t="n">
-        <v>3.06</v>
+        <v>3.58</v>
       </c>
       <c r="U24" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="V24" t="n">
-        <v>7.9</v>
+        <v>10</v>
       </c>
       <c r="W24" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X24" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.83</v>
+        <v>2.38</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.2</v>
+        <v>2.68</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.6</v>
+        <v>1.41</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.72</v>
+        <v>4</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.85</v>
+        <v>2.06</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AG24" t="n">
         <v>1.27</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.63</v>
+        <v>1.27</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45992.6875</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="M27" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="N27" t="n">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="O27" t="n">
-        <v>2.31</v>
+        <v>2.5</v>
       </c>
       <c r="P27" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="Q27" t="n">
-        <v>5.69</v>
+        <v>4.85</v>
       </c>
       <c r="R27" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="S27" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="T27" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="U27" t="n">
         <v>1.37</v>
       </c>
       <c r="V27" t="n">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="W27" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X27" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="AA27" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH27" t="n">
         <v>1.85</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>2.07</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>45992.70833333334</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="M28" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="N28" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O28" t="n">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="P28" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="Q28" t="n">
-        <v>4</v>
+        <v>5.69</v>
       </c>
       <c r="R28" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="S28" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T28" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U28" t="n">
         <v>1.37</v>
       </c>
       <c r="V28" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="W28" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X28" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.14</v>
+        <v>1.85</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.7</v>
+        <v>3.54</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45992.70833333334</v>

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45992.41666666666</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45992.41666666666</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.61</v>
+        <v>3.1</v>
       </c>
       <c r="M6" t="n">
-        <v>3.41</v>
+        <v>3.25</v>
       </c>
       <c r="N6" t="n">
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="O6" t="n">
-        <v>2.39</v>
+        <v>3.5</v>
       </c>
       <c r="P6" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.01</v>
+        <v>2.8</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="S6" t="n">
-        <v>2.39</v>
+        <v>2.66</v>
       </c>
       <c r="T6" t="n">
-        <v>3.19</v>
+        <v>2.8</v>
       </c>
       <c r="U6" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="V6" t="n">
-        <v>9.5</v>
+        <v>7.7</v>
       </c>
       <c r="W6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X6" t="n">
         <v>1</v>
       </c>
-      <c r="X6" t="n">
-        <v>1.03</v>
-      </c>
       <c r="Y6" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.7</v>
+        <v>3.14</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.3</v>
+        <v>3.44</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AG6" t="n">
         <v>1.33</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.95</v>
+        <v>1.31</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45992.45833333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.1</v>
+        <v>1.61</v>
       </c>
       <c r="M7" t="n">
-        <v>3.25</v>
+        <v>3.41</v>
       </c>
       <c r="N7" t="n">
-        <v>2.2</v>
+        <v>4.8</v>
       </c>
       <c r="O7" t="n">
-        <v>3.5</v>
+        <v>2.39</v>
       </c>
       <c r="P7" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.8</v>
+        <v>6.01</v>
       </c>
       <c r="R7" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="S7" t="n">
-        <v>2.66</v>
+        <v>2.39</v>
       </c>
       <c r="T7" t="n">
-        <v>2.8</v>
+        <v>3.19</v>
       </c>
       <c r="U7" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V7" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y7" t="n">
         <v>1.4</v>
       </c>
-      <c r="V7" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.33</v>
-      </c>
       <c r="Z7" t="n">
-        <v>3.14</v>
+        <v>2.7</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.44</v>
+        <v>4.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="AG7" t="n">
         <v>1.33</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.31</v>
+        <v>1.95</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45992.45833333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>6</v>
+        <v>6.81</v>
       </c>
       <c r="M11" t="n">
-        <v>4.3</v>
+        <v>4.41</v>
       </c>
       <c r="N11" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="O11" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="P11" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="T11" t="n">
-        <v>2.23</v>
+        <v>2.47</v>
       </c>
       <c r="U11" t="n">
         <v>1.5</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.1</v>
+        <v>3.98</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.28</v>
+        <v>2.64</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45992.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.79</v>
+        <v>2.19</v>
       </c>
       <c r="M12" t="n">
-        <v>3.23</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>2.21</v>
+        <v>3.25</v>
       </c>
       <c r="O12" t="n">
-        <v>3.74</v>
+        <v>2.74</v>
       </c>
       <c r="P12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V12" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB12" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q12" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V12" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.77</v>
-      </c>
       <c r="AC12" t="n">
-        <v>3.34</v>
+        <v>2.51</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AF12" t="n">
-        <v>2</v>
+        <v>2.39</v>
       </c>
       <c r="AG12" t="n">
         <v>1.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45992.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.86</v>
+        <v>6</v>
       </c>
       <c r="M13" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="N13" t="n">
-        <v>4.3</v>
+        <v>1.5</v>
       </c>
       <c r="O13" t="n">
-        <v>2.35</v>
+        <v>5.4</v>
       </c>
       <c r="P13" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.5</v>
+        <v>1.91</v>
       </c>
       <c r="R13" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.81</v>
+        <v>2.23</v>
       </c>
       <c r="U13" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="V13" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.52</v>
+        <v>4.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.86</v>
+        <v>2.08</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.18</v>
+        <v>2.63</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AE13" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF13" t="n">
         <v>1.88</v>
       </c>
-      <c r="AF13" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AG13" t="n">
-        <v>1.3</v>
+        <v>2.28</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.91</v>
+        <v>1.08</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
+        <v>8</v>
+      </c>
+      <c r="M14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="O14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V14" t="n">
+        <v>6</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y14" t="n">
         <v>1.25</v>
       </c>
-      <c r="M14" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="N14" t="n">
-        <v>14</v>
-      </c>
-      <c r="O14" t="n">
+      <c r="Z14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF14" t="n">
         <v>1.62</v>
       </c>
-      <c r="P14" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V14" t="n">
-        <v>5</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AG14" t="n">
-        <v>1.11</v>
+        <v>2.32</v>
       </c>
       <c r="AH14" t="n">
-        <v>4.2</v>
+        <v>1.06</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>6.8</v>
+        <v>1.25</v>
       </c>
       <c r="M15" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="N15" t="n">
-        <v>1.47</v>
+        <v>14</v>
       </c>
       <c r="O15" t="n">
-        <v>6.1</v>
+        <v>1.62</v>
       </c>
       <c r="P15" t="n">
-        <v>2.34</v>
+        <v>2.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.85</v>
+        <v>8.5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="S15" t="n">
-        <v>3.26</v>
+        <v>4.2</v>
       </c>
       <c r="T15" t="n">
-        <v>2.44</v>
+        <v>2.23</v>
       </c>
       <c r="U15" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="V15" t="n">
-        <v>5.55</v>
+        <v>5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="X15" t="n">
         <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.15</v>
+        <v>4.8</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.5</v>
+        <v>1.11</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.08</v>
+        <v>4.2</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.19</v>
+        <v>1.86</v>
       </c>
       <c r="M16" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N16" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="O16" t="n">
-        <v>2.74</v>
+        <v>2.35</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="S16" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="T16" t="n">
-        <v>2.33</v>
+        <v>2.81</v>
       </c>
       <c r="U16" t="n">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="V16" t="n">
-        <v>5.3</v>
+        <v>5.75</v>
       </c>
       <c r="W16" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.98</v>
+        <v>3.52</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.2</v>
+        <v>1.86</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.51</v>
+        <v>3.18</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.56</v>
+        <v>1.88</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.39</v>
+        <v>2.02</v>
       </c>
       <c r="AG16" t="n">
         <v>1.3</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>8</v>
+        <v>2.79</v>
       </c>
       <c r="M17" t="n">
-        <v>4.6</v>
+        <v>3.23</v>
       </c>
       <c r="N17" t="n">
-        <v>1.4</v>
+        <v>2.21</v>
       </c>
       <c r="O17" t="n">
-        <v>8.6</v>
+        <v>3.74</v>
       </c>
       <c r="P17" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.73</v>
+        <v>2.87</v>
       </c>
       <c r="R17" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="S17" t="n">
-        <v>2.77</v>
+        <v>2.59</v>
       </c>
       <c r="T17" t="n">
-        <v>2.69</v>
+        <v>2.9</v>
       </c>
       <c r="U17" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="V17" t="n">
-        <v>6</v>
+        <v>6.95</v>
       </c>
       <c r="W17" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="X17" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AD17" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z17" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB17" t="n">
+      <c r="AE17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF17" t="n">
         <v>2</v>
       </c>
-      <c r="AC17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AG17" t="n">
-        <v>2.32</v>
+        <v>1.3</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.06</v>
+        <v>1.36</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.05</v>
+        <v>1.65</v>
       </c>
       <c r="M18" t="n">
-        <v>3.39</v>
+        <v>3.75</v>
       </c>
       <c r="N18" t="n">
-        <v>2.01</v>
+        <v>4.8</v>
       </c>
       <c r="O18" t="n">
-        <v>3.7</v>
+        <v>2.32</v>
       </c>
       <c r="P18" t="n">
-        <v>2.13</v>
+        <v>2.24</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.48</v>
+        <v>5.19</v>
       </c>
       <c r="R18" t="n">
         <v>1.33</v>
       </c>
       <c r="S18" t="n">
-        <v>3.05</v>
+        <v>2.66</v>
       </c>
       <c r="T18" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="U18" t="n">
-        <v>1.51</v>
+        <v>1.35</v>
       </c>
       <c r="V18" t="n">
-        <v>5.95</v>
+        <v>7.2</v>
       </c>
       <c r="W18" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="X18" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Z18" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.59</v>
+        <v>3.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.3</v>
+        <v>1.81</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.33</v>
+        <v>1.95</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45992.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.65</v>
+        <v>3.05</v>
       </c>
       <c r="M20" t="n">
-        <v>3.75</v>
+        <v>3.39</v>
       </c>
       <c r="N20" t="n">
-        <v>4.8</v>
+        <v>2.01</v>
       </c>
       <c r="O20" t="n">
-        <v>2.32</v>
+        <v>3.7</v>
       </c>
       <c r="P20" t="n">
-        <v>2.24</v>
+        <v>2.13</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.19</v>
+        <v>2.48</v>
       </c>
       <c r="R20" t="n">
         <v>1.33</v>
       </c>
       <c r="S20" t="n">
-        <v>2.66</v>
+        <v>3.05</v>
       </c>
       <c r="T20" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="U20" t="n">
-        <v>1.35</v>
+        <v>1.51</v>
       </c>
       <c r="V20" t="n">
-        <v>7.2</v>
+        <v>5.95</v>
       </c>
       <c r="W20" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.5</v>
+        <v>2.59</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.81</v>
+        <v>2.3</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.95</v>
+        <v>1.33</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45992.625</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.15</v>
+        <v>2.76</v>
       </c>
       <c r="M21" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="N21" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="O21" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="P21" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="R21" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="S21" t="n">
-        <v>4.33</v>
+        <v>3.36</v>
       </c>
       <c r="T21" t="n">
-        <v>1.92</v>
+        <v>2.23</v>
       </c>
       <c r="U21" t="n">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="V21" t="n">
-        <v>3.84</v>
+        <v>4.75</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="Z21" t="n">
-        <v>7.1</v>
+        <v>5.3</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.27</v>
+        <v>1.58</v>
       </c>
       <c r="AB21" t="n">
-        <v>3.05</v>
+        <v>2.4</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.82</v>
+        <v>2.29</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.85</v>
+        <v>1.59</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AF21" t="n">
-        <v>3.14</v>
+        <v>2.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.76</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45992.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.76</v>
+        <v>3.15</v>
       </c>
       <c r="M22" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="N22" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="O22" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="P22" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="R22" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="S22" t="n">
-        <v>3.36</v>
+        <v>4.33</v>
       </c>
       <c r="T22" t="n">
-        <v>2.23</v>
+        <v>1.92</v>
       </c>
       <c r="U22" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="V22" t="n">
-        <v>4.75</v>
+        <v>3.84</v>
       </c>
       <c r="W22" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="X22" t="n">
         <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="Z22" t="n">
-        <v>5.3</v>
+        <v>7.1</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.58</v>
+        <v>1.27</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.4</v>
+        <v>3.05</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.29</v>
+        <v>1.82</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.59</v>
+        <v>1.85</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.5</v>
+        <v>3.14</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.25</v>
+        <v>1.76</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45992.66666666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.04</v>
+        <v>3.35</v>
       </c>
       <c r="M23" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="N23" t="n">
-        <v>3.5</v>
+        <v>2.22</v>
       </c>
       <c r="O23" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.83</v>
+        <v>2.35</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.2</v>
+        <v>2.69</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.6</v>
+        <v>1.41</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45992.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.32</v>
+        <v>2.04</v>
       </c>
       <c r="M24" t="n">
-        <v>2.79</v>
+        <v>3.1</v>
       </c>
       <c r="N24" t="n">
-        <v>2.27</v>
+        <v>3.5</v>
       </c>
       <c r="O24" t="n">
-        <v>4.1</v>
+        <v>2.71</v>
       </c>
       <c r="P24" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.1</v>
+        <v>4.45</v>
       </c>
       <c r="R24" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="S24" t="n">
-        <v>2.24</v>
+        <v>2.47</v>
       </c>
       <c r="T24" t="n">
-        <v>3.58</v>
+        <v>3.06</v>
       </c>
       <c r="U24" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="V24" t="n">
-        <v>10</v>
+        <v>7.9</v>
       </c>
       <c r="W24" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X24" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.38</v>
+        <v>2.83</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.68</v>
+        <v>2.2</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.41</v>
+        <v>1.6</v>
       </c>
       <c r="AC24" t="n">
-        <v>4</v>
+        <v>3.72</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.06</v>
+        <v>1.85</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AG24" t="n">
         <v>1.27</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.27</v>
+        <v>1.63</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45992.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="M25" t="n">
-        <v>2.85</v>
+        <v>2.79</v>
       </c>
       <c r="N25" t="n">
-        <v>2.22</v>
+        <v>2.27</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="AB25" t="n">
         <v>1.41</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45992.6875</v>
@@ -4006,22 +4006,22 @@
         <v>2.2</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.75</v>
+        <v>4.13</v>
       </c>
       <c r="R30" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S30" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="T30" t="n">
         <v>2.65</v>
       </c>
       <c r="U30" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="V30" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="W30" t="n">
         <v>1.04</v>
@@ -4030,16 +4030,16 @@
         <v>1.05</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z30" t="n">
         <v>3.5</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AC30" t="n">
         <v>3</v>
@@ -4054,7 +4054,7 @@
         <v>2.05</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH30" t="n">
         <v>1.73</v>

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45992.41666666666</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45992.41666666666</v>
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="M6" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="N6" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="O6" t="n">
         <v>3.5</v>
@@ -1165,28 +1165,28 @@
         <v>1.4</v>
       </c>
       <c r="V6" t="n">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="W6" t="n">
         <v>1.03</v>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AB6" t="n">
         <v>1.75</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.44</v>
+        <v>3.45</v>
       </c>
       <c r="AD6" t="n">
         <v>1.3</v>
@@ -1198,10 +1198,10 @@
         <v>1.86</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45992.45833333334</v>
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="M8" t="n">
-        <v>3.65</v>
+        <v>3.38</v>
       </c>
       <c r="N8" t="n">
-        <v>4.9</v>
+        <v>4.85</v>
       </c>
       <c r="O8" t="n">
         <v>2.12</v>
@@ -1394,13 +1394,13 @@
         <v>1.42</v>
       </c>
       <c r="S8" t="n">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="T8" t="n">
         <v>3.19</v>
       </c>
       <c r="U8" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V8" t="n">
         <v>7.8</v>
@@ -1418,10 +1418,10 @@
         <v>2.88</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.97</v>
+        <v>2.16</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AC8" t="n">
         <v>3.72</v>
@@ -1436,7 +1436,7 @@
         <v>1.66</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="AH8" t="n">
         <v>2.32</v>
@@ -1611,16 +1611,16 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.5</v>
+        <v>2.96</v>
       </c>
       <c r="M10" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>3.05</v>
+        <v>2.6</v>
       </c>
       <c r="O10" t="n">
-        <v>3.46</v>
+        <v>3.92</v>
       </c>
       <c r="P10" t="n">
         <v>1.86</v>
@@ -1650,16 +1650,16 @@
         <v>1.09</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="AC10" t="n">
         <v>5.52</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>6.81</v>
+        <v>1.25</v>
       </c>
       <c r="M11" t="n">
-        <v>4.41</v>
+        <v>5.8</v>
       </c>
       <c r="N11" t="n">
-        <v>1.37</v>
+        <v>14</v>
       </c>
       <c r="O11" t="n">
-        <v>6.2</v>
+        <v>1.62</v>
       </c>
       <c r="P11" t="n">
-        <v>2.33</v>
+        <v>2.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.85</v>
+        <v>8.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="S11" t="n">
-        <v>3.26</v>
+        <v>4.2</v>
       </c>
       <c r="T11" t="n">
-        <v>2.47</v>
+        <v>2.23</v>
       </c>
       <c r="U11" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="V11" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="X11" t="n">
         <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.98</v>
+        <v>4.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.64</v>
+        <v>1.11</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.1</v>
+        <v>4.2</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45992.58333333334</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.19</v>
+        <v>1.86</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N12" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="O12" t="n">
-        <v>2.74</v>
+        <v>2.35</v>
       </c>
       <c r="P12" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="S12" t="n">
-        <v>3.04</v>
+        <v>2.77</v>
       </c>
       <c r="T12" t="n">
-        <v>2.33</v>
+        <v>2.81</v>
       </c>
       <c r="U12" t="n">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="V12" t="n">
-        <v>5.3</v>
+        <v>5.75</v>
       </c>
       <c r="W12" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="X12" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.98</v>
+        <v>3.38</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.51</v>
+        <v>3.18</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.56</v>
+        <v>1.88</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.39</v>
+        <v>2.02</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.62</v>
+        <v>1.81</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45992.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M13" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="N13" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="O13" t="n">
-        <v>5.4</v>
+        <v>8.6</v>
       </c>
       <c r="P13" t="n">
         <v>2.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T13" t="n">
-        <v>2.23</v>
+        <v>2.69</v>
       </c>
       <c r="U13" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.63</v>
+        <v>3.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.88</v>
+        <v>1.62</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>8</v>
+        <v>2.19</v>
       </c>
       <c r="M14" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="N14" t="n">
-        <v>1.4</v>
+        <v>3.25</v>
       </c>
       <c r="O14" t="n">
-        <v>8.6</v>
+        <v>2.49</v>
       </c>
       <c r="P14" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.73</v>
+        <v>3.5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S14" t="n">
-        <v>2.77</v>
+        <v>3.04</v>
       </c>
       <c r="T14" t="n">
-        <v>2.69</v>
+        <v>2.33</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V14" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="W14" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X14" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.6</v>
+        <v>4.63</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AB14" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.2</v>
+        <v>2.48</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.2</v>
+        <v>1.53</v>
       </c>
       <c r="AF14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH14" t="n">
         <v>1.62</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.06</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V15" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AD15" t="n">
         <v>1.25</v>
       </c>
-      <c r="M15" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="N15" t="n">
-        <v>14</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V15" t="n">
-        <v>5</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AE15" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AH15" t="n">
-        <v>4.2</v>
+        <v>1.36</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.86</v>
+        <v>6.81</v>
       </c>
       <c r="M16" t="n">
-        <v>3.6</v>
+        <v>4.41</v>
       </c>
       <c r="N16" t="n">
-        <v>4.3</v>
+        <v>1.37</v>
       </c>
       <c r="O16" t="n">
-        <v>2.35</v>
+        <v>6.2</v>
       </c>
       <c r="P16" t="n">
         <v>2.33</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.5</v>
+        <v>1.85</v>
       </c>
       <c r="R16" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>3.26</v>
       </c>
       <c r="T16" t="n">
-        <v>2.81</v>
+        <v>2.47</v>
       </c>
       <c r="U16" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="V16" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.52</v>
+        <v>3.98</v>
       </c>
       <c r="AA16" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE16" t="n">
         <v>1.75</v>
       </c>
-      <c r="AB16" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.88</v>
-      </c>
       <c r="AF16" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.3</v>
+        <v>2.64</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.91</v>
+        <v>1.1</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.79</v>
+        <v>6</v>
       </c>
       <c r="M17" t="n">
-        <v>3.23</v>
+        <v>4.3</v>
       </c>
       <c r="N17" t="n">
-        <v>2.21</v>
+        <v>1.5</v>
       </c>
       <c r="O17" t="n">
-        <v>3.74</v>
+        <v>5.4</v>
       </c>
       <c r="P17" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.87</v>
+        <v>1.91</v>
       </c>
       <c r="R17" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.9</v>
+        <v>2.23</v>
       </c>
       <c r="U17" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="V17" t="n">
-        <v>6.95</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.93</v>
+        <v>1.64</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.77</v>
+        <v>2.08</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.34</v>
+        <v>2.63</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AF17" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.3</v>
+        <v>2.28</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.36</v>
+        <v>1.08</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.65</v>
+        <v>1.21</v>
       </c>
       <c r="M18" t="n">
-        <v>3.75</v>
+        <v>5.6</v>
       </c>
       <c r="N18" t="n">
-        <v>4.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>2.32</v>
+        <v>1.7</v>
       </c>
       <c r="P18" t="n">
-        <v>2.24</v>
+        <v>2.75</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.19</v>
+        <v>7</v>
       </c>
       <c r="R18" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="S18" t="n">
-        <v>2.66</v>
+        <v>4.2</v>
       </c>
       <c r="T18" t="n">
-        <v>2.9</v>
+        <v>2.04</v>
       </c>
       <c r="U18" t="n">
-        <v>1.35</v>
+        <v>1.73</v>
       </c>
       <c r="V18" t="n">
-        <v>7.2</v>
+        <v>4.2</v>
       </c>
       <c r="W18" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.2</v>
+        <v>5.75</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.9</v>
+        <v>1.36</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.8</v>
+        <v>2.99</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.5</v>
+        <v>1.91</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.25</v>
+        <v>1.79</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.81</v>
+        <v>2.01</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.95</v>
+        <v>3.6</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45992.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.21</v>
+        <v>1.75</v>
       </c>
       <c r="M19" t="n">
-        <v>5.6</v>
+        <v>3.4</v>
       </c>
       <c r="N19" t="n">
-        <v>8.800000000000001</v>
+        <v>3.85</v>
       </c>
       <c r="O19" t="n">
-        <v>1.7</v>
+        <v>2.32</v>
       </c>
       <c r="P19" t="n">
-        <v>2.75</v>
+        <v>2.23</v>
       </c>
       <c r="Q19" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.2</v>
+        <v>1.39</v>
       </c>
       <c r="S19" t="n">
-        <v>4.2</v>
+        <v>2.66</v>
       </c>
       <c r="T19" t="n">
-        <v>2.04</v>
+        <v>2.9</v>
       </c>
       <c r="U19" t="n">
-        <v>1.73</v>
+        <v>1.35</v>
       </c>
       <c r="V19" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="W19" t="n">
-        <v>1.18</v>
+        <v>1.03</v>
       </c>
       <c r="X19" t="n">
         <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.75</v>
+        <v>3.2</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.36</v>
+        <v>2.05</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.99</v>
+        <v>1.8</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.91</v>
+        <v>3.34</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.79</v>
+        <v>1.24</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.01</v>
+        <v>1.81</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.6</v>
+        <v>1.95</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45992.625</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="M21" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="N21" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="O21" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="P21" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.7</v>
+        <v>2.42</v>
       </c>
       <c r="R21" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="S21" t="n">
-        <v>3.36</v>
+        <v>4.33</v>
       </c>
       <c r="T21" t="n">
-        <v>2.23</v>
+        <v>1.91</v>
       </c>
       <c r="U21" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="V21" t="n">
-        <v>4.75</v>
+        <v>3.84</v>
       </c>
       <c r="W21" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="Z21" t="n">
-        <v>5.3</v>
+        <v>7.1</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.58</v>
+        <v>1.27</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.4</v>
+        <v>3.14</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.29</v>
+        <v>1.82</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.59</v>
+        <v>1.94</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.5</v>
+        <v>3.21</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45992.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.15</v>
+        <v>2.78</v>
       </c>
       <c r="M22" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="N22" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="O22" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="P22" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="R22" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="S22" t="n">
-        <v>4.33</v>
+        <v>3.36</v>
       </c>
       <c r="T22" t="n">
-        <v>1.92</v>
+        <v>2.23</v>
       </c>
       <c r="U22" t="n">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="V22" t="n">
-        <v>3.84</v>
+        <v>4.8</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="X22" t="n">
         <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="Z22" t="n">
-        <v>7.1</v>
+        <v>5.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.27</v>
+        <v>1.58</v>
       </c>
       <c r="AB22" t="n">
-        <v>3.05</v>
+        <v>2.33</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.82</v>
+        <v>2.31</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AF22" t="n">
-        <v>3.14</v>
+        <v>2.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.76</v>
+        <v>1.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45992.66666666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.35</v>
+        <v>2.04</v>
       </c>
       <c r="M23" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="N23" t="n">
-        <v>2.22</v>
+        <v>3.5</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.35</v>
+        <v>2.83</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.69</v>
+        <v>2.2</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.41</v>
+        <v>1.6</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45992.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.04</v>
+        <v>3.22</v>
       </c>
       <c r="M24" t="n">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="N24" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="O24" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T24" t="n">
         <v>3.5</v>
       </c>
-      <c r="O24" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="R24" t="n">
+      <c r="U24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V24" t="n">
+        <v>10</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y24" t="n">
         <v>1.44</v>
       </c>
-      <c r="S24" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="T24" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V24" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.4</v>
-      </c>
       <c r="Z24" t="n">
-        <v>2.83</v>
+        <v>2.54</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.72</v>
+        <v>4</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.85</v>
+        <v>2.23</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.78</v>
+        <v>1.61</v>
       </c>
       <c r="AG24" t="n">
         <v>1.27</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.63</v>
+        <v>1.26</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45992.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="M25" t="n">
-        <v>2.79</v>
+        <v>2.85</v>
       </c>
       <c r="N25" t="n">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="O25" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="AB25" t="n">
         <v>1.41</v>
       </c>
       <c r="AC25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45992.6875</v>

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45992.41666666666</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="M5" t="n">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="N5" t="n">
-        <v>3.49</v>
+        <v>3.7</v>
       </c>
       <c r="O5" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45992.41666666666</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3</v>
+        <v>1.61</v>
       </c>
       <c r="M6" t="n">
-        <v>3.28</v>
+        <v>3.41</v>
       </c>
       <c r="N6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V6" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE6" t="n">
         <v>2.1</v>
       </c>
-      <c r="O6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V6" t="n">
-        <v>8</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AF6" t="n">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.3</v>
+        <v>1.95</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45992.45833333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.61</v>
+        <v>3.1</v>
       </c>
       <c r="M7" t="n">
-        <v>3.41</v>
+        <v>3.25</v>
       </c>
       <c r="N7" t="n">
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="O7" t="n">
-        <v>2.39</v>
+        <v>3.5</v>
       </c>
       <c r="P7" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.01</v>
+        <v>2.8</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="S7" t="n">
-        <v>2.39</v>
+        <v>2.66</v>
       </c>
       <c r="T7" t="n">
-        <v>3.19</v>
+        <v>2.8</v>
       </c>
       <c r="U7" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="V7" t="n">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.3</v>
+        <v>3.45</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.95</v>
+        <v>1.3</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45992.45833333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.54</v>
+        <v>2.36</v>
       </c>
       <c r="M8" t="n">
-        <v>3.38</v>
+        <v>3.65</v>
       </c>
       <c r="N8" t="n">
-        <v>4.85</v>
+        <v>2.37</v>
       </c>
       <c r="O8" t="n">
-        <v>2.12</v>
+        <v>2.8</v>
       </c>
       <c r="P8" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T8" t="n">
         <v>2.09</v>
       </c>
-      <c r="Q8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.19</v>
-      </c>
       <c r="U8" t="n">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="V8" t="n">
-        <v>7.8</v>
+        <v>4.2</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="X8" t="n">
         <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.36</v>
+        <v>1.08</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.88</v>
+        <v>5.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.16</v>
+        <v>1.42</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.68</v>
+        <v>2.65</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.72</v>
+        <v>1.94</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.2</v>
+        <v>1.76</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.1</v>
+        <v>1.35</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.66</v>
+        <v>2.75</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.32</v>
+        <v>1.5</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45992.54166666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.36</v>
+        <v>1.65</v>
       </c>
       <c r="M9" t="n">
         <v>3.65</v>
       </c>
       <c r="N9" t="n">
-        <v>2.37</v>
+        <v>4.9</v>
       </c>
       <c r="O9" t="n">
-        <v>2.8</v>
+        <v>2.12</v>
       </c>
       <c r="P9" t="n">
-        <v>2.36</v>
+        <v>2.09</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.03</v>
+        <v>6.2</v>
       </c>
       <c r="R9" t="n">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>2.72</v>
       </c>
       <c r="T9" t="n">
-        <v>2.09</v>
+        <v>3.19</v>
       </c>
       <c r="U9" t="n">
-        <v>1.7</v>
+        <v>1.33</v>
       </c>
       <c r="V9" t="n">
-        <v>4.33</v>
+        <v>7.8</v>
       </c>
       <c r="W9" t="n">
-        <v>1.19</v>
+        <v>1.02</v>
       </c>
       <c r="X9" t="n">
         <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.08</v>
+        <v>1.36</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.5</v>
+        <v>2.88</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.42</v>
+        <v>1.97</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.65</v>
+        <v>1.73</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.94</v>
+        <v>3.72</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.76</v>
+        <v>1.2</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.35</v>
+        <v>2.1</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.8</v>
+        <v>1.66</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.5</v>
+        <v>2.32</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45992.54166666666</v>
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.96</v>
+        <v>2.5</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="N10" t="n">
-        <v>2.6</v>
+        <v>3.05</v>
       </c>
       <c r="O10" t="n">
         <v>3.92</v>
@@ -1650,16 +1650,16 @@
         <v>1.09</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="AC10" t="n">
         <v>5.52</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.25</v>
+        <v>5.75</v>
       </c>
       <c r="M11" t="n">
-        <v>5.8</v>
+        <v>4.5</v>
       </c>
       <c r="N11" t="n">
-        <v>14</v>
+        <v>1.48</v>
       </c>
       <c r="O11" t="n">
-        <v>1.62</v>
+        <v>6</v>
       </c>
       <c r="P11" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>8.5</v>
+        <v>1.93</v>
       </c>
       <c r="R11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y11" t="n">
         <v>1.2</v>
       </c>
-      <c r="S11" t="n">
+      <c r="Z11" t="n">
         <v>4.2</v>
       </c>
-      <c r="T11" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V11" t="n">
-        <v>5</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>4.8</v>
-      </c>
       <c r="AA11" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.05</v>
+        <v>1.84</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.7</v>
+        <v>1.92</v>
       </c>
       <c r="AG11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH11" t="n">
         <v>1.11</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>4.2</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45992.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M13" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="N13" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="O13" t="n">
-        <v>8.6</v>
+        <v>5.4</v>
       </c>
       <c r="P13" t="n">
         <v>2.5</v>
       </c>
       <c r="Q13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE13" t="n">
         <v>1.73</v>
       </c>
-      <c r="R13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V13" t="n">
-        <v>6</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AF13" t="n">
-        <v>1.62</v>
+        <v>1.88</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.19</v>
+        <v>8</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="N14" t="n">
-        <v>3.25</v>
+        <v>1.4</v>
       </c>
       <c r="O14" t="n">
-        <v>2.49</v>
+        <v>8.6</v>
       </c>
       <c r="P14" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.5</v>
+        <v>1.73</v>
       </c>
       <c r="R14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V14" t="n">
+        <v>6</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD14" t="n">
         <v>1.33</v>
       </c>
-      <c r="S14" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V14" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y14" t="n">
+      <c r="AE14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG14" t="n">
         <v>1.2</v>
       </c>
-      <c r="Z14" t="n">
-        <v>4.63</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH14" t="n">
-        <v>1.62</v>
+        <v>1.06</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2215,7 +2215,7 @@
         <v>2.21</v>
       </c>
       <c r="O15" t="n">
-        <v>3.74</v>
+        <v>3.83</v>
       </c>
       <c r="P15" t="n">
         <v>2.2</v>
@@ -2224,7 +2224,7 @@
         <v>2.87</v>
       </c>
       <c r="R15" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="S15" t="n">
         <v>2.59</v>
@@ -2236,13 +2236,13 @@
         <v>1.35</v>
       </c>
       <c r="V15" t="n">
-        <v>6.95</v>
+        <v>7</v>
       </c>
       <c r="W15" t="n">
         <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
         <v>1.3</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>6.81</v>
+        <v>2.19</v>
       </c>
       <c r="M16" t="n">
-        <v>4.41</v>
+        <v>3.4</v>
       </c>
       <c r="N16" t="n">
-        <v>1.37</v>
+        <v>3.25</v>
       </c>
       <c r="O16" t="n">
-        <v>6.2</v>
+        <v>2.49</v>
       </c>
       <c r="P16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="T16" t="n">
         <v>2.33</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.47</v>
       </c>
       <c r="U16" t="n">
         <v>1.5</v>
       </c>
       <c r="V16" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="W16" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y16" t="n">
         <v>1.2</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.98</v>
+        <v>4.63</v>
       </c>
       <c r="AA16" t="n">
         <v>1.68</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.64</v>
+        <v>1.3</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.1</v>
+        <v>1.62</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>6</v>
+        <v>1.25</v>
       </c>
       <c r="M17" t="n">
-        <v>4.3</v>
+        <v>5.8</v>
       </c>
       <c r="N17" t="n">
-        <v>1.5</v>
+        <v>14</v>
       </c>
       <c r="O17" t="n">
-        <v>5.4</v>
+        <v>1.62</v>
       </c>
       <c r="P17" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.91</v>
+        <v>7.24</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T17" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="U17" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.88</v>
+        <v>1.7</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.28</v>
+        <v>1.1</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.08</v>
+        <v>4.75</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.21</v>
+        <v>1.65</v>
       </c>
       <c r="M18" t="n">
-        <v>5.6</v>
+        <v>3.75</v>
       </c>
       <c r="N18" t="n">
-        <v>8.800000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="O18" t="n">
-        <v>1.7</v>
+        <v>2.32</v>
       </c>
       <c r="P18" t="n">
-        <v>2.75</v>
+        <v>2.23</v>
       </c>
       <c r="Q18" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.2</v>
+        <v>1.39</v>
       </c>
       <c r="S18" t="n">
-        <v>4.2</v>
+        <v>2.66</v>
       </c>
       <c r="T18" t="n">
-        <v>2.04</v>
+        <v>2.9</v>
       </c>
       <c r="U18" t="n">
-        <v>1.73</v>
+        <v>1.35</v>
       </c>
       <c r="V18" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="W18" t="n">
-        <v>1.18</v>
+        <v>1.03</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.75</v>
+        <v>3.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.36</v>
+        <v>1.9</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.99</v>
+        <v>1.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.91</v>
+        <v>3.34</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.79</v>
+        <v>1.24</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.01</v>
+        <v>1.81</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.6</v>
+        <v>1.95</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45992.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.75</v>
+        <v>1.21</v>
       </c>
       <c r="M19" t="n">
-        <v>3.4</v>
+        <v>5.6</v>
       </c>
       <c r="N19" t="n">
-        <v>3.85</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>2.32</v>
+        <v>1.7</v>
       </c>
       <c r="P19" t="n">
-        <v>2.23</v>
+        <v>2.75</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="R19" t="n">
-        <v>1.39</v>
+        <v>1.2</v>
       </c>
       <c r="S19" t="n">
-        <v>2.66</v>
+        <v>4.2</v>
       </c>
       <c r="T19" t="n">
-        <v>2.9</v>
+        <v>2.05</v>
       </c>
       <c r="U19" t="n">
-        <v>1.35</v>
+        <v>1.72</v>
       </c>
       <c r="V19" t="n">
-        <v>7.2</v>
+        <v>4.2</v>
       </c>
       <c r="W19" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="X19" t="n">
         <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.2</v>
+        <v>5.75</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.05</v>
+        <v>1.36</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.8</v>
+        <v>2.99</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.34</v>
+        <v>1.91</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.24</v>
+        <v>1.79</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.95</v>
+        <v>3.5</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45992.625</v>
@@ -2810,10 +2810,10 @@
         <v>2.01</v>
       </c>
       <c r="O20" t="n">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="P20" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="Q20" t="n">
         <v>2.48</v>
@@ -2822,25 +2822,25 @@
         <v>1.33</v>
       </c>
       <c r="S20" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T20" t="n">
         <v>2.5</v>
       </c>
       <c r="U20" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="V20" t="n">
         <v>5.95</v>
       </c>
       <c r="W20" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X20" t="n">
         <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z20" t="n">
         <v>4</v>
@@ -2852,16 +2852,16 @@
         <v>2.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="AD20" t="n">
         <v>1.4</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="AG20" t="n">
         <v>1.67</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.04</v>
+        <v>3.32</v>
       </c>
       <c r="M23" t="n">
-        <v>3.1</v>
+        <v>2.79</v>
       </c>
       <c r="N23" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="O23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T23" t="n">
         <v>3.5</v>
       </c>
-      <c r="O23" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="R23" t="n">
+      <c r="U23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V23" t="n">
+        <v>10</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y23" t="n">
         <v>1.44</v>
       </c>
-      <c r="S23" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V23" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.4</v>
-      </c>
       <c r="Z23" t="n">
-        <v>2.83</v>
+        <v>2.54</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.2</v>
+        <v>2.68</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.6</v>
+        <v>1.41</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.72</v>
+        <v>4</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.85</v>
+        <v>2.23</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.78</v>
+        <v>1.61</v>
       </c>
       <c r="AG23" t="n">
         <v>1.27</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.63</v>
+        <v>1.26</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45992.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.22</v>
+        <v>2.04</v>
       </c>
       <c r="M24" t="n">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="N24" t="n">
-        <v>2.14</v>
+        <v>3.5</v>
       </c>
       <c r="O24" t="n">
-        <v>4.1</v>
+        <v>2.69</v>
       </c>
       <c r="P24" t="n">
-        <v>1.82</v>
+        <v>1.94</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.02</v>
+        <v>4.25</v>
       </c>
       <c r="R24" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="S24" t="n">
-        <v>2.36</v>
+        <v>2.47</v>
       </c>
       <c r="T24" t="n">
-        <v>3.5</v>
+        <v>3.04</v>
       </c>
       <c r="U24" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="V24" t="n">
-        <v>10</v>
+        <v>7.9</v>
       </c>
       <c r="W24" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X24" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.54</v>
+        <v>2.98</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.46</v>
+        <v>1.6</v>
       </c>
       <c r="AC24" t="n">
-        <v>4</v>
+        <v>3.72</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.23</v>
+        <v>1.85</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.61</v>
+        <v>1.78</v>
       </c>
       <c r="AG24" t="n">
         <v>1.27</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.26</v>
+        <v>1.63</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45992.6875</v>
@@ -3405,13 +3405,13 @@
         <v>2.22</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3453,10 +3453,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -3569,19 +3569,19 @@
         <v>3.55</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE26" t="n">
         <v>2.2</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AG26" t="n">
         <v>1.22</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.77</v>
+        <v>2.63</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>45992.69791666666</v>
@@ -3640,7 +3640,7 @@
         <v>3.3</v>
       </c>
       <c r="N27" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="O27" t="n">
         <v>2.5</v>
@@ -3661,7 +3661,7 @@
         <v>2.75</v>
       </c>
       <c r="U27" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="V27" t="n">
         <v>7.7</v>
@@ -3676,10 +3676,10 @@
         <v>1.36</v>
       </c>
       <c r="Z27" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AB27" t="n">
         <v>1.75</v>
@@ -3762,13 +3762,13 @@
         <v>4.3</v>
       </c>
       <c r="O28" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="P28" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="Q28" t="n">
-        <v>5.69</v>
+        <v>5.74</v>
       </c>
       <c r="R28" t="n">
         <v>1.4</v>
@@ -3780,13 +3780,13 @@
         <v>3</v>
       </c>
       <c r="U28" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="V28" t="n">
         <v>7</v>
       </c>
       <c r="W28" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X28" t="n">
         <v>1.04</v>
@@ -3810,16 +3810,16 @@
         <v>1.28</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45992.70833333334</v>
@@ -3884,34 +3884,34 @@
         <v>5.5</v>
       </c>
       <c r="P29" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="R29" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S29" t="n">
-        <v>2.89</v>
+        <v>3.2</v>
       </c>
       <c r="T29" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="U29" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="V29" t="n">
         <v>6.25</v>
       </c>
       <c r="W29" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X29" t="n">
         <v>1.05</v>
       </c>
-      <c r="X29" t="n">
-        <v>1</v>
-      </c>
       <c r="Y29" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z29" t="n">
         <v>3.7</v>
@@ -3926,7 +3926,7 @@
         <v>3</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE29" t="n">
         <v>1.85</v>

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.99</v>
+        <v>4.3</v>
       </c>
       <c r="M2" t="n">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="N2" t="n">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -897,55 +897,55 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.15</v>
+        <v>1.97</v>
       </c>
       <c r="M4" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="N4" t="n">
-        <v>3.49</v>
+        <v>3.6</v>
       </c>
       <c r="O4" t="n">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="P4" t="n">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.2</v>
+        <v>4.79</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="S4" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="T4" t="n">
-        <v>3.85</v>
+        <v>3.76</v>
       </c>
       <c r="U4" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="V4" t="n">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X4" t="n">
         <v>1.08</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.23</v>
+        <v>2.39</v>
       </c>
       <c r="AA4" t="n">
         <v>2.8</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AC4" t="n">
         <v>5.4</v>
@@ -954,16 +954,16 @@
         <v>1.08</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45992.41666666666</v>
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="M5" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="N5" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1135,37 +1135,37 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
       <c r="M6" t="n">
-        <v>3.41</v>
+        <v>3.38</v>
       </c>
       <c r="N6" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="O6" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="P6" t="n">
         <v>2.03</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.01</v>
+        <v>6</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S6" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="T6" t="n">
-        <v>3.19</v>
+        <v>3.15</v>
       </c>
       <c r="U6" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="V6" t="n">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W6" t="n">
         <v>1</v>
@@ -1180,13 +1180,13 @@
         <v>2.7</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.93</v>
+        <v>2.33</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.77</v>
+        <v>1.53</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="AD6" t="n">
         <v>1.15</v>
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.1</v>
+        <v>3.56</v>
       </c>
       <c r="M7" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="N7" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="O7" t="n">
         <v>3.5</v>
@@ -1272,22 +1272,22 @@
         <v>2.8</v>
       </c>
       <c r="R7" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S7" t="n">
-        <v>2.66</v>
+        <v>2.59</v>
       </c>
       <c r="T7" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="U7" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="V7" t="n">
         <v>8</v>
       </c>
       <c r="W7" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
         <v>1.06</v>
@@ -1296,31 +1296,31 @@
         <v>1.28</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.45</v>
+        <v>3.88</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="AF7" t="n">
         <v>1.86</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45992.45833333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.36</v>
+        <v>1.56</v>
       </c>
       <c r="M8" t="n">
-        <v>3.65</v>
+        <v>3.84</v>
       </c>
       <c r="N8" t="n">
-        <v>2.37</v>
+        <v>4.85</v>
       </c>
       <c r="O8" t="n">
-        <v>2.8</v>
+        <v>2.12</v>
       </c>
       <c r="P8" t="n">
-        <v>2.36</v>
+        <v>2.09</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.03</v>
+        <v>5.22</v>
       </c>
       <c r="R8" t="n">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="S8" t="n">
-        <v>3.7</v>
+        <v>2.62</v>
       </c>
       <c r="T8" t="n">
-        <v>2.09</v>
+        <v>3.19</v>
       </c>
       <c r="U8" t="n">
-        <v>1.7</v>
+        <v>1.32</v>
       </c>
       <c r="V8" t="n">
-        <v>4.2</v>
+        <v>7.8</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
         <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.08</v>
+        <v>1.36</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.5</v>
+        <v>2.88</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.42</v>
+        <v>2.16</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.65</v>
+        <v>1.71</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.94</v>
+        <v>3.72</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.76</v>
+        <v>1.2</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.35</v>
+        <v>2.1</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.75</v>
+        <v>1.66</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.5</v>
+        <v>2.13</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45992.54166666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.65</v>
+        <v>2.41</v>
       </c>
       <c r="M9" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="N9" t="n">
-        <v>4.9</v>
+        <v>2.5</v>
       </c>
       <c r="O9" t="n">
-        <v>2.12</v>
+        <v>2.8</v>
       </c>
       <c r="P9" t="n">
-        <v>2.09</v>
+        <v>2.36</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.2</v>
+        <v>3.03</v>
       </c>
       <c r="R9" t="n">
-        <v>1.42</v>
+        <v>1.22</v>
       </c>
       <c r="S9" t="n">
-        <v>2.72</v>
+        <v>3.7</v>
       </c>
       <c r="T9" t="n">
-        <v>3.19</v>
+        <v>2.1</v>
       </c>
       <c r="U9" t="n">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="V9" t="n">
-        <v>7.8</v>
+        <v>4.2</v>
       </c>
       <c r="W9" t="n">
-        <v>1.02</v>
+        <v>1.19</v>
       </c>
       <c r="X9" t="n">
         <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.36</v>
+        <v>1.08</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.88</v>
+        <v>5.73</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.97</v>
+        <v>1.43</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.73</v>
+        <v>2.63</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.72</v>
+        <v>2.05</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.2</v>
+        <v>1.71</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.1</v>
+        <v>1.38</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.66</v>
+        <v>2.95</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.13</v>
+        <v>1.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.32</v>
+        <v>1.5</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45992.54166666666</v>
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.5</v>
+        <v>2.99</v>
       </c>
       <c r="M10" t="n">
-        <v>3.05</v>
+        <v>2.99</v>
       </c>
       <c r="N10" t="n">
-        <v>3.05</v>
+        <v>2.59</v>
       </c>
       <c r="O10" t="n">
         <v>3.92</v>
@@ -1650,19 +1650,19 @@
         <v>1.09</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="AC10" t="n">
-        <v>5.52</v>
+        <v>5.59</v>
       </c>
       <c r="AD10" t="n">
         <v>1.09</v>
@@ -1674,10 +1674,10 @@
         <v>1.63</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45992.5625</v>
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>5.75</v>
+        <v>6.05</v>
       </c>
       <c r="M11" t="n">
-        <v>4.5</v>
+        <v>4.21</v>
       </c>
       <c r="N11" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="O11" t="n">
         <v>6</v>
@@ -1748,7 +1748,7 @@
         <v>1.93</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S11" t="n">
         <v>3.26</v>
@@ -1757,16 +1757,16 @@
         <v>2.53</v>
       </c>
       <c r="U11" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="V11" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="W11" t="n">
         <v>1.08</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
         <v>1.2</v>
@@ -1787,10 +1787,10 @@
         <v>1.4</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.92</v>
+        <v>1.81</v>
       </c>
       <c r="AG11" t="n">
         <v>1.22</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.86</v>
+        <v>2.23</v>
       </c>
       <c r="M12" t="n">
-        <v>3.6</v>
+        <v>3.36</v>
       </c>
       <c r="N12" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="O12" t="n">
-        <v>2.35</v>
+        <v>2.49</v>
       </c>
       <c r="P12" t="n">
-        <v>2.33</v>
+        <v>2.18</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.5</v>
+        <v>3.64</v>
       </c>
       <c r="R12" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="S12" t="n">
-        <v>2.77</v>
+        <v>3.04</v>
       </c>
       <c r="T12" t="n">
-        <v>2.81</v>
+        <v>2.41</v>
       </c>
       <c r="U12" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="V12" t="n">
-        <v>5.75</v>
+        <v>5.3</v>
       </c>
       <c r="W12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X12" t="n">
         <v>1.04</v>
       </c>
-      <c r="X12" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y12" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.38</v>
+        <v>4.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.18</v>
+        <v>2.48</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.88</v>
+        <v>1.53</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.02</v>
+        <v>2.34</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.81</v>
+        <v>1.6</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45992.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M13" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="N13" t="n">
-        <v>1.5</v>
+        <v>1.26</v>
       </c>
       <c r="O13" t="n">
-        <v>5.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="P13" t="n">
         <v>2.5</v>
       </c>
       <c r="Q13" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB13" t="n">
         <v>1.91</v>
       </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.08</v>
-      </c>
       <c r="AC13" t="n">
-        <v>2.63</v>
+        <v>3.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.73</v>
+        <v>2.38</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.88</v>
+        <v>1.62</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.28</v>
+        <v>1.11</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>8</v>
+        <v>1.2</v>
       </c>
       <c r="M14" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="N14" t="n">
-        <v>1.4</v>
+        <v>11.64</v>
       </c>
       <c r="O14" t="n">
-        <v>8.6</v>
+        <v>1.62</v>
       </c>
       <c r="P14" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.73</v>
+        <v>8.5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="S14" t="n">
-        <v>2.77</v>
+        <v>3.55</v>
       </c>
       <c r="T14" t="n">
-        <v>2.69</v>
+        <v>2.18</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="V14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="X14" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.2</v>
+        <v>2.38</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.06</v>
+        <v>4.2</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.79</v>
+        <v>8</v>
       </c>
       <c r="M15" t="n">
-        <v>3.23</v>
+        <v>6</v>
       </c>
       <c r="N15" t="n">
-        <v>2.21</v>
+        <v>1.26</v>
       </c>
       <c r="O15" t="n">
-        <v>3.83</v>
+        <v>7.97</v>
       </c>
       <c r="P15" t="n">
-        <v>2.2</v>
+        <v>2.84</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.87</v>
+        <v>1.61</v>
       </c>
       <c r="R15" t="n">
-        <v>1.38</v>
+        <v>1.16</v>
       </c>
       <c r="S15" t="n">
-        <v>2.59</v>
+        <v>4.15</v>
       </c>
       <c r="T15" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="U15" t="n">
-        <v>1.35</v>
+        <v>1.8</v>
       </c>
       <c r="V15" t="n">
-        <v>7</v>
+        <v>3.75</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.19</v>
       </c>
       <c r="X15" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>1.05</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.2</v>
+        <v>6.6</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.93</v>
+        <v>1.28</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.77</v>
+        <v>3.44</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.34</v>
+        <v>1.84</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.25</v>
+        <v>1.9</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AF15" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.3</v>
+        <v>1.07</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.19</v>
+        <v>2.87</v>
       </c>
       <c r="M16" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>3.25</v>
+        <v>2.26</v>
       </c>
       <c r="O16" t="n">
-        <v>2.49</v>
+        <v>3.88</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.5</v>
+        <v>2.92</v>
       </c>
       <c r="R16" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V16" t="n">
+        <v>7</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH16" t="n">
         <v>1.33</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V16" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>4.63</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.62</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.25</v>
+        <v>1.86</v>
       </c>
       <c r="M17" t="n">
-        <v>5.8</v>
+        <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="O17" t="n">
-        <v>1.62</v>
+        <v>2.35</v>
       </c>
       <c r="P17" t="n">
-        <v>2.7</v>
+        <v>2.33</v>
       </c>
       <c r="Q17" t="n">
-        <v>7.24</v>
+        <v>4.5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>2.77</v>
       </c>
       <c r="T17" t="n">
-        <v>2.21</v>
+        <v>2.81</v>
       </c>
       <c r="U17" t="n">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="V17" t="n">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="W17" t="n">
-        <v>1.19</v>
+        <v>1.09</v>
       </c>
       <c r="X17" t="n">
         <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.25</v>
+        <v>3.18</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.53</v>
+        <v>1.27</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.1</v>
+        <v>1.32</v>
       </c>
       <c r="AH17" t="n">
-        <v>4.75</v>
+        <v>1.95</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.65</v>
+        <v>2.9</v>
       </c>
       <c r="M18" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="N18" t="n">
-        <v>4.8</v>
+        <v>2.22</v>
       </c>
       <c r="O18" t="n">
-        <v>2.32</v>
+        <v>3.34</v>
       </c>
       <c r="P18" t="n">
-        <v>2.23</v>
+        <v>2.12</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.5</v>
+        <v>2.48</v>
       </c>
       <c r="R18" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="S18" t="n">
-        <v>2.66</v>
+        <v>3.2</v>
       </c>
       <c r="T18" t="n">
-        <v>2.9</v>
+        <v>2.68</v>
       </c>
       <c r="U18" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="V18" t="n">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="W18" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y18" t="n">
         <v>1.25</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.8</v>
+        <v>2.04</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.34</v>
+        <v>2.74</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.81</v>
+        <v>2.2</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.95</v>
+        <v>1.33</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45992.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.21</v>
+        <v>1.75</v>
       </c>
       <c r="M19" t="n">
-        <v>5.6</v>
+        <v>3.4</v>
       </c>
       <c r="N19" t="n">
-        <v>8.800000000000001</v>
+        <v>4.15</v>
       </c>
       <c r="O19" t="n">
-        <v>1.7</v>
+        <v>2.32</v>
       </c>
       <c r="P19" t="n">
-        <v>2.75</v>
+        <v>2.23</v>
       </c>
       <c r="Q19" t="n">
-        <v>7</v>
+        <v>5.14</v>
       </c>
       <c r="R19" t="n">
-        <v>1.2</v>
+        <v>1.41</v>
       </c>
       <c r="S19" t="n">
-        <v>4.2</v>
+        <v>2.66</v>
       </c>
       <c r="T19" t="n">
-        <v>2.05</v>
+        <v>2.9</v>
       </c>
       <c r="U19" t="n">
-        <v>1.72</v>
+        <v>1.35</v>
       </c>
       <c r="V19" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="W19" t="n">
-        <v>1.17</v>
+        <v>1.03</v>
       </c>
       <c r="X19" t="n">
         <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.75</v>
+        <v>3.3</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.36</v>
+        <v>2.06</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.99</v>
+        <v>1.77</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.91</v>
+        <v>3.34</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.79</v>
+        <v>1.24</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AF19" t="n">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.5</v>
+        <v>1.98</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45992.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.05</v>
+        <v>1.3</v>
       </c>
       <c r="M20" t="n">
-        <v>3.39</v>
+        <v>5.5</v>
       </c>
       <c r="N20" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>7</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="V20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AC20" t="n">
         <v>2.01</v>
       </c>
-      <c r="O20" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V20" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.62</v>
-      </c>
       <c r="AD20" t="n">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.41</v>
+        <v>2.02</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.67</v>
+        <v>1.14</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.33</v>
+        <v>3.5</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45992.625</v>
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="M21" t="n">
-        <v>3.75</v>
+        <v>4.05</v>
       </c>
       <c r="N21" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="O21" t="n">
         <v>3.35</v>
@@ -2935,7 +2935,7 @@
         <v>2.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="R21" t="n">
         <v>1.16</v>
@@ -2944,16 +2944,16 @@
         <v>4.33</v>
       </c>
       <c r="T21" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="U21" t="n">
-        <v>1.82</v>
+        <v>1.96</v>
       </c>
       <c r="V21" t="n">
         <v>3.84</v>
       </c>
       <c r="W21" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
@@ -2965,7 +2965,7 @@
         <v>7.1</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AB21" t="n">
         <v>3.14</v>
@@ -3063,16 +3063,16 @@
         <v>3.36</v>
       </c>
       <c r="T22" t="n">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
       <c r="U22" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="V22" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="W22" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X22" t="n">
         <v>1.01</v>
@@ -3081,7 +3081,7 @@
         <v>1.13</v>
       </c>
       <c r="Z22" t="n">
-        <v>5.3</v>
+        <v>4.65</v>
       </c>
       <c r="AA22" t="n">
         <v>1.58</v>
@@ -3096,16 +3096,16 @@
         <v>1.58</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AF22" t="n">
         <v>2.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.25</v>
+        <v>1.56</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45992.66666666666</v>
@@ -3158,31 +3158,31 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.32</v>
+        <v>3.22</v>
       </c>
       <c r="M23" t="n">
-        <v>2.79</v>
+        <v>2.84</v>
       </c>
       <c r="N23" t="n">
-        <v>2.27</v>
+        <v>2.14</v>
       </c>
       <c r="O23" t="n">
-        <v>4.1</v>
+        <v>4.34</v>
       </c>
       <c r="P23" t="n">
         <v>1.82</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="R23" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="S23" t="n">
         <v>2.36</v>
       </c>
       <c r="T23" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U23" t="n">
         <v>1.22</v>
@@ -3191,28 +3191,28 @@
         <v>10</v>
       </c>
       <c r="W23" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X23" t="n">
         <v>1.05</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.68</v>
+        <v>2.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="AC23" t="n">
         <v>4</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AE23" t="n">
         <v>2.23</v>
@@ -3221,7 +3221,7 @@
         <v>1.61</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AH23" t="n">
         <v>1.26</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.04</v>
+        <v>3.25</v>
       </c>
       <c r="M24" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="N24" t="n">
-        <v>3.5</v>
+        <v>2.15</v>
       </c>
       <c r="O24" t="n">
-        <v>2.69</v>
+        <v>4.33</v>
       </c>
       <c r="P24" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.25</v>
+        <v>3</v>
       </c>
       <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AB24" t="n">
         <v>1.44</v>
       </c>
-      <c r="S24" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="T24" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V24" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AC24" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.85</v>
+        <v>2.37</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.78</v>
+        <v>1.53</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45992.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.35</v>
+        <v>2</v>
       </c>
       <c r="M25" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="N25" t="n">
-        <v>2.22</v>
+        <v>3.3</v>
       </c>
       <c r="O25" t="n">
-        <v>4.33</v>
+        <v>2.6</v>
       </c>
       <c r="P25" t="n">
-        <v>1.83</v>
+        <v>2.12</v>
       </c>
       <c r="Q25" t="n">
-        <v>3</v>
+        <v>4.24</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.35</v>
+        <v>2.98</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.69</v>
+        <v>2.1</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.41</v>
+        <v>1.64</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.37</v>
+        <v>1.85</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.53</v>
+        <v>1.78</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45992.6875</v>
@@ -3515,19 +3515,19 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="M26" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="N26" t="n">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="O26" t="n">
         <v>1.91</v>
       </c>
       <c r="P26" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="Q26" t="n">
         <v>7</v>
@@ -3536,34 +3536,34 @@
         <v>1.4</v>
       </c>
       <c r="S26" t="n">
-        <v>2.79</v>
+        <v>2.89</v>
       </c>
       <c r="T26" t="n">
         <v>2.75</v>
       </c>
       <c r="U26" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="V26" t="n">
         <v>7.5</v>
       </c>
       <c r="W26" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X26" t="n">
         <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AC26" t="n">
         <v>3.55</v>
@@ -3575,7 +3575,7 @@
         <v>2.2</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AG26" t="n">
         <v>1.22</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="M27" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N27" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="O27" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="P27" t="n">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.85</v>
+        <v>5.74</v>
       </c>
       <c r="R27" t="n">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="S27" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T27" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="U27" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="V27" t="n">
-        <v>7.7</v>
+        <v>7</v>
       </c>
       <c r="W27" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X27" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.7</v>
+        <v>3.54</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.85</v>
+        <v>2.09</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>45992.70833333334</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.78</v>
+        <v>2.01</v>
       </c>
       <c r="M28" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="N28" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="O28" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="P28" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="Q28" t="n">
-        <v>5.74</v>
+        <v>4.85</v>
       </c>
       <c r="R28" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="S28" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="T28" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="U28" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V28" t="n">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="W28" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X28" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AA28" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH28" t="n">
         <v>1.85</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>2.09</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45992.70833333334</v>
@@ -3872,19 +3872,19 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="M29" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="N29" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="O29" t="n">
-        <v>5.5</v>
+        <v>4.65</v>
       </c>
       <c r="P29" t="n">
-        <v>2.4</v>
+        <v>2.16</v>
       </c>
       <c r="Q29" t="n">
         <v>2.02</v>
@@ -3893,19 +3893,19 @@
         <v>1.35</v>
       </c>
       <c r="S29" t="n">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="T29" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="U29" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="V29" t="n">
         <v>6.25</v>
       </c>
       <c r="W29" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X29" t="n">
         <v>1.05</v>
@@ -3917,28 +3917,28 @@
         <v>3.7</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.25</v>
+        <v>2.03</v>
       </c>
       <c r="AC29" t="n">
-        <v>3</v>
+        <v>3.03</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AF29" t="n">
         <v>1.85</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.4</v>
+        <v>1.19</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>45992.71875</v>
@@ -4000,28 +4000,28 @@
         <v>3.64</v>
       </c>
       <c r="O30" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="P30" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.13</v>
+        <v>3.75</v>
       </c>
       <c r="R30" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S30" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="T30" t="n">
-        <v>2.65</v>
+        <v>2.79</v>
       </c>
       <c r="U30" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="V30" t="n">
-        <v>6.8</v>
+        <v>6.75</v>
       </c>
       <c r="W30" t="n">
         <v>1.04</v>
@@ -4033,13 +4033,13 @@
         <v>1.25</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AC30" t="n">
         <v>3</v>
@@ -4051,13 +4051,13 @@
         <v>1.67</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>45992.83333333334</v>

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="M2" t="n">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="N2" t="n">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -698,16 +698,16 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="M4" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="N4" t="n">
-        <v>3.6</v>
+        <v>3.96</v>
       </c>
       <c r="O4" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.79</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.39</v>
+        <v>2.17</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.8</v>
+        <v>2.15</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45992.41666666666</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="M5" t="n">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="N5" t="n">
-        <v>3.75</v>
+        <v>3.61</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45992.41666666666</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.76</v>
+        <v>3.56</v>
       </c>
       <c r="M6" t="n">
-        <v>3.38</v>
+        <v>3</v>
       </c>
       <c r="N6" t="n">
-        <v>4.6</v>
+        <v>2</v>
       </c>
       <c r="O6" t="n">
-        <v>2.38</v>
+        <v>3.5</v>
       </c>
       <c r="P6" t="n">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="Q6" t="n">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="R6" t="n">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="S6" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="T6" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="U6" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V6" t="n">
+        <v>8</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH6" t="n">
         <v>1.27</v>
-      </c>
-      <c r="V6" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.95</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45992.45833333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.56</v>
+        <v>1.76</v>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
+        <v>3.38</v>
       </c>
       <c r="N7" t="n">
-        <v>2</v>
+        <v>4.6</v>
       </c>
       <c r="O7" t="n">
-        <v>3.5</v>
+        <v>2.38</v>
       </c>
       <c r="P7" t="n">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="S7" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="T7" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="U7" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="V7" t="n">
-        <v>8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="Z7" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.08</v>
+        <v>2.33</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.88</v>
+        <v>4.25</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.27</v>
+        <v>1.95</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45992.45833333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>6.05</v>
+        <v>2.87</v>
       </c>
       <c r="M11" t="n">
-        <v>4.21</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>1.43</v>
+        <v>2.26</v>
       </c>
       <c r="O11" t="n">
-        <v>6</v>
+        <v>3.88</v>
       </c>
       <c r="P11" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.93</v>
+        <v>2.92</v>
       </c>
       <c r="R11" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="S11" t="n">
-        <v>3.26</v>
+        <v>2.59</v>
       </c>
       <c r="T11" t="n">
-        <v>2.53</v>
+        <v>2.9</v>
       </c>
       <c r="U11" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="V11" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="W11" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.7</v>
+        <v>1.99</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.1</v>
+        <v>1.81</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.6</v>
+        <v>3.34</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.22</v>
+        <v>1.6</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="M14" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="O14" t="n">
+        <v>6</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V14" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y14" t="n">
         <v>1.2</v>
       </c>
-      <c r="M14" t="n">
-        <v>6</v>
-      </c>
-      <c r="N14" t="n">
-        <v>11.64</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="R14" t="n">
+      <c r="Z14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AG14" t="n">
         <v>1.22</v>
       </c>
-      <c r="S14" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V14" t="n">
-        <v>5</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AH14" t="n">
-        <v>4.2</v>
+        <v>1.11</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.87</v>
+        <v>1.2</v>
       </c>
       <c r="M16" t="n">
-        <v>3.25</v>
+        <v>6</v>
       </c>
       <c r="N16" t="n">
-        <v>2.26</v>
+        <v>11.64</v>
       </c>
       <c r="O16" t="n">
-        <v>3.88</v>
+        <v>1.62</v>
       </c>
       <c r="P16" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.92</v>
+        <v>8.5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="S16" t="n">
-        <v>2.59</v>
+        <v>3.55</v>
       </c>
       <c r="T16" t="n">
-        <v>2.9</v>
+        <v>2.18</v>
       </c>
       <c r="U16" t="n">
-        <v>1.35</v>
+        <v>1.6</v>
       </c>
       <c r="V16" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.06</v>
+        <v>1.19</v>
       </c>
       <c r="X16" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.2</v>
+        <v>4.8</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.99</v>
+        <v>1.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.81</v>
+        <v>2.4</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.34</v>
+        <v>2.38</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AF16" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.6</v>
+        <v>1.13</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.33</v>
+        <v>4.2</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.75</v>
+        <v>1.3</v>
       </c>
       <c r="M19" t="n">
-        <v>3.4</v>
+        <v>5.5</v>
       </c>
       <c r="N19" t="n">
-        <v>4.15</v>
+        <v>8.6</v>
       </c>
       <c r="O19" t="n">
-        <v>2.32</v>
+        <v>1.7</v>
       </c>
       <c r="P19" t="n">
-        <v>2.23</v>
+        <v>2.75</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.14</v>
+        <v>7</v>
       </c>
       <c r="R19" t="n">
-        <v>1.41</v>
+        <v>1.19</v>
       </c>
       <c r="S19" t="n">
-        <v>2.66</v>
+        <v>3.85</v>
       </c>
       <c r="T19" t="n">
-        <v>2.9</v>
+        <v>2.05</v>
       </c>
       <c r="U19" t="n">
-        <v>1.35</v>
+        <v>1.72</v>
       </c>
       <c r="V19" t="n">
-        <v>7.2</v>
+        <v>4.2</v>
       </c>
       <c r="W19" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="X19" t="n">
         <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.3</v>
+        <v>5.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.06</v>
+        <v>1.39</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.77</v>
+        <v>2.9</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.34</v>
+        <v>2.01</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.24</v>
+        <v>1.75</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.81</v>
+        <v>2.02</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.98</v>
+        <v>3.5</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45992.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.3</v>
+        <v>1.75</v>
       </c>
       <c r="M20" t="n">
-        <v>5.5</v>
+        <v>3.4</v>
       </c>
       <c r="N20" t="n">
-        <v>8.6</v>
+        <v>4.15</v>
       </c>
       <c r="O20" t="n">
-        <v>1.7</v>
+        <v>2.32</v>
       </c>
       <c r="P20" t="n">
-        <v>2.75</v>
+        <v>2.23</v>
       </c>
       <c r="Q20" t="n">
-        <v>7</v>
+        <v>5.14</v>
       </c>
       <c r="R20" t="n">
-        <v>1.19</v>
+        <v>1.41</v>
       </c>
       <c r="S20" t="n">
-        <v>3.85</v>
+        <v>2.66</v>
       </c>
       <c r="T20" t="n">
-        <v>2.05</v>
+        <v>2.9</v>
       </c>
       <c r="U20" t="n">
-        <v>1.72</v>
+        <v>1.35</v>
       </c>
       <c r="V20" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="W20" t="n">
-        <v>1.17</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
         <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.5</v>
+        <v>3.3</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.39</v>
+        <v>2.06</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.9</v>
+        <v>1.77</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.01</v>
+        <v>3.34</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.75</v>
+        <v>1.24</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.02</v>
+        <v>1.81</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>3.5</v>
+        <v>1.98</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45992.625</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="M23" t="n">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="N23" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="O23" t="n">
-        <v>4.34</v>
+        <v>4.33</v>
       </c>
       <c r="P23" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="R23" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.46</v>
+        <v>2.35</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AC23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.23</v>
+        <v>2.37</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45992.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="M24" t="n">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="N24" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="O24" t="n">
-        <v>4.33</v>
+        <v>4.34</v>
       </c>
       <c r="P24" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="Q24" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.52</v>
+        <v>1.43</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.35</v>
+        <v>2.46</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.37</v>
+        <v>2.23</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45992.6875</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.72</v>
+        <v>2.01</v>
       </c>
       <c r="M27" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N27" t="n">
-        <v>4.8</v>
+        <v>3.95</v>
       </c>
       <c r="O27" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="P27" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="Q27" t="n">
-        <v>5.74</v>
+        <v>4.85</v>
       </c>
       <c r="R27" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="S27" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="T27" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="U27" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="V27" t="n">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="W27" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X27" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.54</v>
+        <v>3.7</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.77</v>
+        <v>1.88</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.09</v>
+        <v>1.85</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>45992.70833333334</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.01</v>
+        <v>1.72</v>
       </c>
       <c r="M28" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N28" t="n">
-        <v>3.95</v>
+        <v>4.8</v>
       </c>
       <c r="O28" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="P28" t="n">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.85</v>
+        <v>5.74</v>
       </c>
       <c r="R28" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="S28" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="T28" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="U28" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="V28" t="n">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="W28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X28" t="n">
         <v>1.04</v>
       </c>
-      <c r="X28" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y28" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.7</v>
+        <v>3.54</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.85</v>
+        <v>2.09</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45992.70833333334</v>

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.04</v>
+        <v>2.13</v>
       </c>
       <c r="M4" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="N4" t="n">
-        <v>3.96</v>
+        <v>3.61</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.15</v>
+        <v>2.73</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.61</v>
+        <v>1.4</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45992.41666666666</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.13</v>
+        <v>2.04</v>
       </c>
       <c r="M5" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="N5" t="n">
-        <v>3.61</v>
+        <v>3.96</v>
       </c>
       <c r="O5" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.79</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.73</v>
+        <v>2.15</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.4</v>
+        <v>1.61</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45992.41666666666</v>
@@ -1135,22 +1135,22 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.56</v>
+        <v>3.1</v>
       </c>
       <c r="M6" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="N6" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="O6" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="P6" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="R6" t="n">
         <v>1.43</v>
@@ -1159,7 +1159,7 @@
         <v>2.59</v>
       </c>
       <c r="T6" t="n">
-        <v>3.05</v>
+        <v>2.99</v>
       </c>
       <c r="U6" t="n">
         <v>1.34</v>
@@ -1171,25 +1171,25 @@
         <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="Z6" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.88</v>
+        <v>3.92</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE6" t="n">
         <v>1.89</v>
@@ -1198,10 +1198,10 @@
         <v>1.86</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45992.45833333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.56</v>
+        <v>2.4</v>
       </c>
       <c r="M8" t="n">
-        <v>3.84</v>
+        <v>3.65</v>
       </c>
       <c r="N8" t="n">
-        <v>4.85</v>
+        <v>2.5</v>
       </c>
       <c r="O8" t="n">
-        <v>2.12</v>
+        <v>2.8</v>
       </c>
       <c r="P8" t="n">
-        <v>2.09</v>
+        <v>2.55</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.22</v>
+        <v>3.06</v>
       </c>
       <c r="R8" t="n">
-        <v>1.42</v>
+        <v>1.22</v>
       </c>
       <c r="S8" t="n">
-        <v>2.62</v>
+        <v>3.7</v>
       </c>
       <c r="T8" t="n">
-        <v>3.19</v>
+        <v>1.95</v>
       </c>
       <c r="U8" t="n">
-        <v>1.32</v>
+        <v>1.67</v>
       </c>
       <c r="V8" t="n">
-        <v>7.8</v>
+        <v>4.2</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>1.19</v>
       </c>
       <c r="X8" t="n">
         <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.36</v>
+        <v>1.08</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.88</v>
+        <v>5.3</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.16</v>
+        <v>1.43</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.71</v>
+        <v>2.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.72</v>
+        <v>2.05</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.2</v>
+        <v>1.67</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.1</v>
+        <v>1.39</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.66</v>
+        <v>2.96</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.13</v>
+        <v>1.55</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45992.54166666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.41</v>
+        <v>1.56</v>
       </c>
       <c r="M9" t="n">
-        <v>3.6</v>
+        <v>3.84</v>
       </c>
       <c r="N9" t="n">
-        <v>2.5</v>
+        <v>4.85</v>
       </c>
       <c r="O9" t="n">
-        <v>2.8</v>
+        <v>2.12</v>
       </c>
       <c r="P9" t="n">
-        <v>2.36</v>
+        <v>2.09</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.03</v>
+        <v>5.22</v>
       </c>
       <c r="R9" t="n">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="S9" t="n">
-        <v>3.7</v>
+        <v>2.62</v>
       </c>
       <c r="T9" t="n">
-        <v>2.1</v>
+        <v>3.19</v>
       </c>
       <c r="U9" t="n">
-        <v>1.7</v>
+        <v>1.32</v>
       </c>
       <c r="V9" t="n">
-        <v>4.2</v>
+        <v>7.8</v>
       </c>
       <c r="W9" t="n">
-        <v>1.19</v>
+        <v>1.02</v>
       </c>
       <c r="X9" t="n">
         <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.08</v>
+        <v>1.36</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.73</v>
+        <v>2.88</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.43</v>
+        <v>2.16</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.63</v>
+        <v>1.71</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.05</v>
+        <v>3.72</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.71</v>
+        <v>1.2</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.38</v>
+        <v>2.1</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.95</v>
+        <v>1.66</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.5</v>
+        <v>2.13</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45992.54166666666</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.87</v>
+        <v>1.86</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="N11" t="n">
-        <v>2.26</v>
+        <v>4</v>
       </c>
       <c r="O11" t="n">
-        <v>3.88</v>
+        <v>2.35</v>
       </c>
       <c r="P11" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.92</v>
+        <v>4.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="S11" t="n">
-        <v>2.59</v>
+        <v>2.77</v>
       </c>
       <c r="T11" t="n">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="U11" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="V11" t="n">
-        <v>7</v>
+        <v>5.75</v>
       </c>
       <c r="W11" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X11" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.99</v>
+        <v>1.75</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.81</v>
+        <v>1.92</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.34</v>
+        <v>3.18</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AF11" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.6</v>
+        <v>1.32</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.33</v>
+        <v>1.95</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45992.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.23</v>
+        <v>8</v>
       </c>
       <c r="M12" t="n">
-        <v>3.36</v>
+        <v>6</v>
       </c>
       <c r="N12" t="n">
-        <v>3.2</v>
+        <v>1.26</v>
       </c>
       <c r="O12" t="n">
-        <v>2.49</v>
+        <v>7.97</v>
       </c>
       <c r="P12" t="n">
-        <v>2.18</v>
+        <v>2.84</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.64</v>
+        <v>1.61</v>
       </c>
       <c r="R12" t="n">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="S12" t="n">
-        <v>3.04</v>
+        <v>4.15</v>
       </c>
       <c r="T12" t="n">
-        <v>2.41</v>
+        <v>1.9</v>
       </c>
       <c r="U12" t="n">
-        <v>1.56</v>
+        <v>1.8</v>
       </c>
       <c r="V12" t="n">
-        <v>5.3</v>
+        <v>3.75</v>
       </c>
       <c r="W12" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AH12" t="n">
         <v>1.11</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.6</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45992.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>8</v>
+        <v>2.87</v>
       </c>
       <c r="M13" t="n">
-        <v>4.4</v>
+        <v>3.25</v>
       </c>
       <c r="N13" t="n">
-        <v>1.26</v>
+        <v>2.26</v>
       </c>
       <c r="O13" t="n">
-        <v>8.800000000000001</v>
+        <v>3.88</v>
       </c>
       <c r="P13" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.73</v>
+        <v>2.92</v>
       </c>
       <c r="R13" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="S13" t="n">
-        <v>2.8</v>
+        <v>2.59</v>
       </c>
       <c r="T13" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="U13" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="V13" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="W13" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X13" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AD13" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD13" t="n">
+      <c r="AE13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH13" t="n">
         <v>1.33</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.01</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,43 +2087,43 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>6.05</v>
+        <v>2.23</v>
       </c>
       <c r="M14" t="n">
-        <v>4.21</v>
+        <v>3.36</v>
       </c>
       <c r="N14" t="n">
-        <v>1.43</v>
+        <v>3.2</v>
       </c>
       <c r="O14" t="n">
-        <v>6</v>
+        <v>2.49</v>
       </c>
       <c r="P14" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.93</v>
+        <v>3.64</v>
       </c>
       <c r="R14" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S14" t="n">
-        <v>3.26</v>
+        <v>3.04</v>
       </c>
       <c r="T14" t="n">
-        <v>2.53</v>
+        <v>2.41</v>
       </c>
       <c r="U14" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="V14" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="W14" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y14" t="n">
         <v>1.2</v>
@@ -2132,28 +2132,28 @@
         <v>4.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AB14" t="n">
         <v>2.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="AD14" t="n">
         <v>1.4</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.94</v>
+        <v>1.53</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.81</v>
+        <v>2.34</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.11</v>
+        <v>1.6</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,70 +2206,70 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>8</v>
+        <v>6.05</v>
       </c>
       <c r="M15" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="O15" t="n">
         <v>6</v>
       </c>
-      <c r="N15" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="O15" t="n">
-        <v>7.97</v>
-      </c>
       <c r="P15" t="n">
-        <v>2.84</v>
+        <v>2.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.61</v>
+        <v>1.93</v>
       </c>
       <c r="R15" t="n">
-        <v>1.16</v>
+        <v>1.31</v>
       </c>
       <c r="S15" t="n">
-        <v>4.15</v>
+        <v>3.26</v>
       </c>
       <c r="T15" t="n">
-        <v>1.9</v>
+        <v>2.53</v>
       </c>
       <c r="U15" t="n">
-        <v>1.8</v>
+        <v>1.48</v>
       </c>
       <c r="V15" t="n">
-        <v>3.75</v>
+        <v>5.8</v>
       </c>
       <c r="W15" t="n">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>6.6</v>
+        <v>4.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.28</v>
+        <v>1.7</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.44</v>
+        <v>2.1</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.84</v>
+        <v>2.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.63</v>
+        <v>1.94</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.12</v>
+        <v>1.81</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="AH15" t="n">
         <v>1.11</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.2</v>
+        <v>8</v>
       </c>
       <c r="M16" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="N16" t="n">
-        <v>11.64</v>
+        <v>1.26</v>
       </c>
       <c r="O16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AF16" t="n">
         <v>1.62</v>
       </c>
-      <c r="P16" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V16" t="n">
-        <v>5</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X16" t="n">
+      <c r="AG16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AH16" t="n">
         <v>1.01</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>4.2</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.86</v>
+        <v>1.2</v>
       </c>
       <c r="M17" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="N17" t="n">
-        <v>4</v>
+        <v>11.64</v>
       </c>
       <c r="O17" t="n">
-        <v>2.35</v>
+        <v>1.62</v>
       </c>
       <c r="P17" t="n">
-        <v>2.33</v>
+        <v>2.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.5</v>
+        <v>8.5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="S17" t="n">
-        <v>2.77</v>
+        <v>3.55</v>
       </c>
       <c r="T17" t="n">
-        <v>2.81</v>
+        <v>2.18</v>
       </c>
       <c r="U17" t="n">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="V17" t="n">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.09</v>
+        <v>1.19</v>
       </c>
       <c r="X17" t="n">
         <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.92</v>
+        <v>2.4</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.18</v>
+        <v>2.38</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.27</v>
+        <v>1.53</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.32</v>
+        <v>1.13</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.95</v>
+        <v>4.2</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>7</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="V18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AB18" t="n">
         <v>2.9</v>
       </c>
-      <c r="M18" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N18" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="O18" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V18" t="n">
-        <v>6</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA18" t="n">
+      <c r="AC18" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AD18" t="n">
         <v>1.75</v>
       </c>
-      <c r="AB18" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AE18" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.33</v>
+        <v>3.5</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45992.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="O19" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R19" t="n">
         <v>1.3</v>
       </c>
-      <c r="M19" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="N19" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>7</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.19</v>
-      </c>
       <c r="S19" t="n">
-        <v>3.85</v>
+        <v>3</v>
       </c>
       <c r="T19" t="n">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="U19" t="n">
-        <v>1.72</v>
+        <v>1.46</v>
       </c>
       <c r="V19" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="W19" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.5</v>
+        <v>3.8</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.39</v>
+        <v>1.75</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.9</v>
+        <v>2.04</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.01</v>
+        <v>2.7</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.75</v>
+        <v>1.36</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.14</v>
+        <v>1.31</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.5</v>
+        <v>1.33</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45992.625</v>
@@ -2801,55 +2801,55 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="M20" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="N20" t="n">
-        <v>4.15</v>
+        <v>4.8</v>
       </c>
       <c r="O20" t="n">
         <v>2.32</v>
       </c>
       <c r="P20" t="n">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.14</v>
+        <v>4.5</v>
       </c>
       <c r="R20" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="S20" t="n">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="T20" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="U20" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="V20" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="W20" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y20" t="n">
         <v>1.25</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AC20" t="n">
         <v>3.34</v>
@@ -2861,13 +2861,13 @@
         <v>1.8</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45992.625</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.12</v>
+        <v>2.78</v>
       </c>
       <c r="M21" t="n">
-        <v>4.05</v>
+        <v>3.5</v>
       </c>
       <c r="N21" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="O21" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="P21" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.32</v>
+        <v>2.7</v>
       </c>
       <c r="R21" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="S21" t="n">
-        <v>4.33</v>
+        <v>3.36</v>
       </c>
       <c r="T21" t="n">
-        <v>1.88</v>
+        <v>2.28</v>
       </c>
       <c r="U21" t="n">
-        <v>1.96</v>
+        <v>1.61</v>
       </c>
       <c r="V21" t="n">
-        <v>3.84</v>
+        <v>4.7</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="Z21" t="n">
-        <v>7.1</v>
+        <v>4.65</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.33</v>
+        <v>1.58</v>
       </c>
       <c r="AB21" t="n">
-        <v>3.14</v>
+        <v>2.33</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.82</v>
+        <v>2.31</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.94</v>
+        <v>1.58</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="AF21" t="n">
-        <v>3.21</v>
+        <v>2.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.21</v>
+        <v>1.56</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45992.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.78</v>
+        <v>3.12</v>
       </c>
       <c r="M22" t="n">
-        <v>3.5</v>
+        <v>4.05</v>
       </c>
       <c r="N22" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="O22" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="P22" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.7</v>
+        <v>2.32</v>
       </c>
       <c r="R22" t="n">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="S22" t="n">
-        <v>3.36</v>
+        <v>4.33</v>
       </c>
       <c r="T22" t="n">
-        <v>2.28</v>
+        <v>1.88</v>
       </c>
       <c r="U22" t="n">
-        <v>1.61</v>
+        <v>1.96</v>
       </c>
       <c r="V22" t="n">
-        <v>4.7</v>
+        <v>3.84</v>
       </c>
       <c r="W22" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="X22" t="n">
         <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.65</v>
+        <v>7.1</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.58</v>
+        <v>1.33</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.33</v>
+        <v>3.14</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.31</v>
+        <v>1.82</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.58</v>
+        <v>1.94</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.5</v>
+        <v>3.21</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.56</v>
+        <v>1.21</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45992.66666666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.22</v>
+        <v>1.95</v>
       </c>
       <c r="M24" t="n">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="N24" t="n">
-        <v>2.14</v>
+        <v>3.3</v>
       </c>
       <c r="O24" t="n">
-        <v>4.34</v>
+        <v>2.6</v>
       </c>
       <c r="P24" t="n">
-        <v>1.82</v>
+        <v>1.94</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.04</v>
+        <v>4.24</v>
       </c>
       <c r="R24" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="S24" t="n">
-        <v>2.36</v>
+        <v>2.47</v>
       </c>
       <c r="T24" t="n">
-        <v>3.4</v>
+        <v>3.06</v>
       </c>
       <c r="U24" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="V24" t="n">
-        <v>10</v>
+        <v>7.9</v>
       </c>
       <c r="W24" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X24" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.46</v>
+        <v>2.83</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.48</v>
+        <v>1.64</v>
       </c>
       <c r="AC24" t="n">
-        <v>4</v>
+        <v>3.72</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.23</v>
+        <v>1.97</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.61</v>
+        <v>1.78</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.26</v>
+        <v>1.63</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45992.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2</v>
+        <v>3.22</v>
       </c>
       <c r="M25" t="n">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="N25" t="n">
-        <v>3.3</v>
+        <v>2.14</v>
       </c>
       <c r="O25" t="n">
-        <v>2.6</v>
+        <v>4.34</v>
       </c>
       <c r="P25" t="n">
-        <v>2.12</v>
+        <v>1.82</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.24</v>
+        <v>3.04</v>
       </c>
       <c r="R25" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V25" t="n">
+        <v>10</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y25" t="n">
         <v>1.43</v>
       </c>
-      <c r="S25" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T25" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V25" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.4</v>
-      </c>
       <c r="Z25" t="n">
-        <v>2.98</v>
+        <v>2.46</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.64</v>
+        <v>1.48</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.72</v>
+        <v>4</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.85</v>
+        <v>2.23</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.78</v>
+        <v>1.61</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.63</v>
+        <v>1.26</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45992.6875</v>
@@ -3518,31 +3518,31 @@
         <v>1.36</v>
       </c>
       <c r="M26" t="n">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="N26" t="n">
         <v>7.5</v>
       </c>
       <c r="O26" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="P26" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="R26" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S26" t="n">
-        <v>2.89</v>
+        <v>2.72</v>
       </c>
       <c r="T26" t="n">
-        <v>2.75</v>
+        <v>3.12</v>
       </c>
       <c r="U26" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="V26" t="n">
         <v>7.5</v>
@@ -3554,22 +3554,22 @@
         <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE26" t="n">
         <v>2.2</v>
@@ -3634,46 +3634,46 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="M27" t="n">
-        <v>3.3</v>
+        <v>3.26</v>
       </c>
       <c r="N27" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="O27" t="n">
-        <v>2.5</v>
+        <v>2.72</v>
       </c>
       <c r="P27" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.85</v>
+        <v>4.63</v>
       </c>
       <c r="R27" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S27" t="n">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="T27" t="n">
-        <v>2.75</v>
+        <v>3.21</v>
       </c>
       <c r="U27" t="n">
         <v>1.35</v>
       </c>
       <c r="V27" t="n">
-        <v>7.3</v>
+        <v>8.5</v>
       </c>
       <c r="W27" t="n">
         <v>1.04</v>
       </c>
       <c r="X27" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z27" t="n">
         <v>3.1</v>
@@ -3682,25 +3682,25 @@
         <v>2.15</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AD27" t="n">
         <v>1.25</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>45992.70833333334</v>
@@ -3991,31 +3991,31 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.07</v>
+        <v>1.92</v>
       </c>
       <c r="M30" t="n">
-        <v>3.25</v>
+        <v>3.54</v>
       </c>
       <c r="N30" t="n">
-        <v>3.64</v>
+        <v>4.15</v>
       </c>
       <c r="O30" t="n">
-        <v>2.53</v>
+        <v>2.36</v>
       </c>
       <c r="P30" t="n">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="Q30" t="n">
         <v>3.75</v>
       </c>
       <c r="R30" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S30" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="T30" t="n">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
       <c r="U30" t="n">
         <v>1.42</v>
@@ -4030,28 +4030,28 @@
         <v>1.05</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AA30" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AB30" t="n">
         <v>1.91</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.98</v>
       </c>
       <c r="AC30" t="n">
         <v>3</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="AG30" t="n">
         <v>1.3</v>

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -778,22 +778,22 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -823,16 +823,16 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE3" t="n">
         <v>0</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.13</v>
+        <v>2.04</v>
       </c>
       <c r="M4" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="N4" t="n">
-        <v>3.61</v>
+        <v>3.96</v>
       </c>
       <c r="O4" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.79</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.73</v>
+        <v>2.15</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.4</v>
+        <v>1.61</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45992.41666666666</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.04</v>
+        <v>2.13</v>
       </c>
       <c r="M5" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="N5" t="n">
-        <v>3.96</v>
+        <v>3.61</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.15</v>
+        <v>2.73</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.61</v>
+        <v>1.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45992.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.4</v>
+        <v>1.65</v>
       </c>
       <c r="M8" t="n">
         <v>3.65</v>
       </c>
       <c r="N8" t="n">
-        <v>2.5</v>
+        <v>4.9</v>
       </c>
       <c r="O8" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="P8" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.06</v>
+        <v>5.22</v>
       </c>
       <c r="R8" t="n">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="S8" t="n">
-        <v>3.7</v>
+        <v>2.62</v>
       </c>
       <c r="T8" t="n">
-        <v>1.95</v>
+        <v>3.16</v>
       </c>
       <c r="U8" t="n">
-        <v>1.67</v>
+        <v>1.32</v>
       </c>
       <c r="V8" t="n">
-        <v>4.2</v>
+        <v>7.8</v>
       </c>
       <c r="W8" t="n">
-        <v>1.19</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
         <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.08</v>
+        <v>1.34</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.3</v>
+        <v>3.17</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.43</v>
+        <v>1.97</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.6</v>
+        <v>1.73</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.05</v>
+        <v>3.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.67</v>
+        <v>1.2</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.39</v>
+        <v>2.11</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.96</v>
+        <v>1.65</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.55</v>
+        <v>2.13</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45992.54166666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.56</v>
+        <v>2.4</v>
       </c>
       <c r="M9" t="n">
-        <v>3.84</v>
+        <v>3.65</v>
       </c>
       <c r="N9" t="n">
-        <v>4.85</v>
+        <v>2.5</v>
       </c>
       <c r="O9" t="n">
-        <v>2.12</v>
+        <v>2.8</v>
       </c>
       <c r="P9" t="n">
-        <v>2.09</v>
+        <v>2.55</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.22</v>
+        <v>3.06</v>
       </c>
       <c r="R9" t="n">
-        <v>1.42</v>
+        <v>1.22</v>
       </c>
       <c r="S9" t="n">
-        <v>2.62</v>
+        <v>3.7</v>
       </c>
       <c r="T9" t="n">
-        <v>3.19</v>
+        <v>1.95</v>
       </c>
       <c r="U9" t="n">
-        <v>1.32</v>
+        <v>1.67</v>
       </c>
       <c r="V9" t="n">
-        <v>7.8</v>
+        <v>4.2</v>
       </c>
       <c r="W9" t="n">
-        <v>1.02</v>
+        <v>1.19</v>
       </c>
       <c r="X9" t="n">
         <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.36</v>
+        <v>1.08</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.88</v>
+        <v>5.3</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.16</v>
+        <v>1.43</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.71</v>
+        <v>2.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.72</v>
+        <v>2.05</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.2</v>
+        <v>1.67</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.1</v>
+        <v>1.39</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.66</v>
+        <v>2.96</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.13</v>
+        <v>1.55</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45992.54166666666</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.86</v>
+        <v>1.25</v>
       </c>
       <c r="M11" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="N11" t="n">
+        <v>14</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S11" t="n">
         <v>3.5</v>
       </c>
-      <c r="N11" t="n">
-        <v>4</v>
-      </c>
-      <c r="O11" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.77</v>
-      </c>
       <c r="T11" t="n">
-        <v>2.81</v>
+        <v>2.08</v>
       </c>
       <c r="U11" t="n">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="V11" t="n">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.09</v>
+        <v>1.19</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.18</v>
+        <v>2.25</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.27</v>
+        <v>1.53</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.95</v>
+        <v>3.65</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45992.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>8</v>
+        <v>2.87</v>
       </c>
       <c r="M12" t="n">
-        <v>6</v>
+        <v>3.25</v>
       </c>
       <c r="N12" t="n">
-        <v>1.26</v>
+        <v>2.26</v>
       </c>
       <c r="O12" t="n">
-        <v>7.97</v>
+        <v>3.88</v>
       </c>
       <c r="P12" t="n">
-        <v>2.84</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.61</v>
+        <v>2.92</v>
       </c>
       <c r="R12" t="n">
-        <v>1.16</v>
+        <v>1.41</v>
       </c>
       <c r="S12" t="n">
-        <v>4.15</v>
+        <v>2.59</v>
       </c>
       <c r="T12" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="U12" t="n">
-        <v>1.8</v>
+        <v>1.35</v>
       </c>
       <c r="V12" t="n">
-        <v>3.75</v>
+        <v>7</v>
       </c>
       <c r="W12" t="n">
-        <v>1.19</v>
+        <v>1.06</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.05</v>
+        <v>1.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>6.6</v>
+        <v>3.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.28</v>
+        <v>1.99</v>
       </c>
       <c r="AB12" t="n">
-        <v>3.44</v>
+        <v>1.81</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.84</v>
+        <v>3.34</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.9</v>
+        <v>1.25</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.07</v>
+        <v>1.6</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45992.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.87</v>
+        <v>6.05</v>
       </c>
       <c r="M13" t="n">
-        <v>3.25</v>
+        <v>4.21</v>
       </c>
       <c r="N13" t="n">
-        <v>2.26</v>
+        <v>1.43</v>
       </c>
       <c r="O13" t="n">
-        <v>3.88</v>
+        <v>6</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.92</v>
+        <v>1.93</v>
       </c>
       <c r="R13" t="n">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="S13" t="n">
-        <v>2.59</v>
+        <v>3.26</v>
       </c>
       <c r="T13" t="n">
-        <v>2.9</v>
+        <v>2.53</v>
       </c>
       <c r="U13" t="n">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="V13" t="n">
-        <v>7</v>
+        <v>5.8</v>
       </c>
       <c r="W13" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X13" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.99</v>
+        <v>1.7</v>
       </c>
       <c r="AB13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AF13" t="n">
         <v>1.81</v>
       </c>
-      <c r="AC13" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2</v>
-      </c>
       <c r="AG13" t="n">
-        <v>1.6</v>
+        <v>1.22</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.33</v>
+        <v>1.11</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.23</v>
+        <v>8</v>
       </c>
       <c r="M14" t="n">
-        <v>3.36</v>
+        <v>4.6</v>
       </c>
       <c r="N14" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="O14" t="n">
-        <v>2.49</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.64</v>
+        <v>1.73</v>
       </c>
       <c r="R14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V14" t="n">
+        <v>7</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AD14" t="n">
         <v>1.33</v>
       </c>
-      <c r="S14" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="U14" t="n">
+      <c r="AE14" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AF14" t="n">
         <v>1.56</v>
       </c>
-      <c r="V14" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2.34</v>
-      </c>
       <c r="AG14" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.6</v>
+        <v>1.02</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>6.05</v>
+        <v>1.86</v>
       </c>
       <c r="M15" t="n">
-        <v>4.21</v>
+        <v>3.5</v>
       </c>
       <c r="N15" t="n">
-        <v>1.43</v>
+        <v>4</v>
       </c>
       <c r="O15" t="n">
-        <v>6</v>
+        <v>2.35</v>
       </c>
       <c r="P15" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.93</v>
+        <v>4.5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="S15" t="n">
-        <v>3.26</v>
+        <v>2.77</v>
       </c>
       <c r="T15" t="n">
-        <v>2.53</v>
+        <v>2.81</v>
       </c>
       <c r="U15" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="V15" t="n">
-        <v>5.8</v>
+        <v>5.75</v>
       </c>
       <c r="W15" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.6</v>
+        <v>3.18</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.11</v>
+        <v>1.95</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>8</v>
+        <v>2.23</v>
       </c>
       <c r="M16" t="n">
-        <v>4.4</v>
+        <v>3.36</v>
       </c>
       <c r="N16" t="n">
-        <v>1.26</v>
+        <v>3.2</v>
       </c>
       <c r="O16" t="n">
-        <v>8.800000000000001</v>
+        <v>2.49</v>
       </c>
       <c r="P16" t="n">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.73</v>
+        <v>3.64</v>
       </c>
       <c r="R16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V16" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AG16" t="n">
         <v>1.36</v>
       </c>
-      <c r="S16" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V16" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AH16" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,37 +2444,37 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.2</v>
+        <v>8</v>
       </c>
       <c r="M17" t="n">
         <v>6</v>
       </c>
       <c r="N17" t="n">
-        <v>11.64</v>
+        <v>1.26</v>
       </c>
       <c r="O17" t="n">
-        <v>1.62</v>
+        <v>7.97</v>
       </c>
       <c r="P17" t="n">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="Q17" t="n">
-        <v>8.5</v>
+        <v>1.61</v>
       </c>
       <c r="R17" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="S17" t="n">
-        <v>3.55</v>
+        <v>4.15</v>
       </c>
       <c r="T17" t="n">
-        <v>2.18</v>
+        <v>1.9</v>
       </c>
       <c r="U17" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="V17" t="n">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="W17" t="n">
         <v>1.19</v>
@@ -2483,34 +2483,34 @@
         <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.4</v>
+        <v>3.44</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.38</v>
+        <v>1.84</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.53</v>
+        <v>1.9</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.05</v>
+        <v>1.63</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.7</v>
+        <v>2.12</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AH17" t="n">
-        <v>4.2</v>
+        <v>1.11</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.9</v>
+        <v>1.65</v>
       </c>
       <c r="M19" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="N19" t="n">
-        <v>2.25</v>
+        <v>4.8</v>
       </c>
       <c r="O19" t="n">
-        <v>3.97</v>
+        <v>2.32</v>
       </c>
       <c r="P19" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.45</v>
+        <v>4.5</v>
       </c>
       <c r="R19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V19" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG19" t="n">
         <v>1.3</v>
       </c>
-      <c r="S19" t="n">
-        <v>3</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V19" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AH19" t="n">
-        <v>1.33</v>
+        <v>2.02</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45992.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.65</v>
+        <v>2.9</v>
       </c>
       <c r="M20" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="N20" t="n">
-        <v>4.8</v>
+        <v>2.25</v>
       </c>
       <c r="O20" t="n">
-        <v>2.32</v>
+        <v>3.97</v>
       </c>
       <c r="P20" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.5</v>
+        <v>2.45</v>
       </c>
       <c r="R20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V20" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH20" t="n">
         <v>1.33</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V20" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>2.02</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45992.625</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.78</v>
+        <v>3.12</v>
       </c>
       <c r="M21" t="n">
-        <v>3.5</v>
+        <v>4.05</v>
       </c>
       <c r="N21" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="O21" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="P21" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.7</v>
+        <v>2.32</v>
       </c>
       <c r="R21" t="n">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="S21" t="n">
-        <v>3.36</v>
+        <v>4.33</v>
       </c>
       <c r="T21" t="n">
-        <v>2.28</v>
+        <v>1.88</v>
       </c>
       <c r="U21" t="n">
-        <v>1.61</v>
+        <v>1.96</v>
       </c>
       <c r="V21" t="n">
-        <v>4.7</v>
+        <v>3.84</v>
       </c>
       <c r="W21" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.65</v>
+        <v>7.1</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.58</v>
+        <v>1.33</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.33</v>
+        <v>3.14</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.31</v>
+        <v>1.82</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.58</v>
+        <v>1.94</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.5</v>
+        <v>3.21</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.56</v>
+        <v>1.21</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45992.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.12</v>
+        <v>2.78</v>
       </c>
       <c r="M22" t="n">
-        <v>4.05</v>
+        <v>3.5</v>
       </c>
       <c r="N22" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="O22" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="P22" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.32</v>
+        <v>2.7</v>
       </c>
       <c r="R22" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="S22" t="n">
-        <v>4.33</v>
+        <v>3.36</v>
       </c>
       <c r="T22" t="n">
-        <v>1.88</v>
+        <v>2.28</v>
       </c>
       <c r="U22" t="n">
-        <v>1.96</v>
+        <v>1.61</v>
       </c>
       <c r="V22" t="n">
-        <v>3.84</v>
+        <v>4.7</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="X22" t="n">
         <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="Z22" t="n">
-        <v>7.1</v>
+        <v>4.65</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.33</v>
+        <v>1.58</v>
       </c>
       <c r="AB22" t="n">
-        <v>3.14</v>
+        <v>2.33</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.82</v>
+        <v>2.31</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.94</v>
+        <v>1.58</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="AF22" t="n">
-        <v>3.21</v>
+        <v>2.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.21</v>
+        <v>1.56</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45992.66666666666</v>
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="M23" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="N23" t="n">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="O23" t="n">
         <v>4.33</v>
@@ -3203,10 +3203,10 @@
         <v>2.35</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.95</v>
+        <v>3.32</v>
       </c>
       <c r="M24" t="n">
-        <v>3.1</v>
+        <v>2.79</v>
       </c>
       <c r="N24" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="O24" t="n">
+        <v>4</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="T24" t="n">
         <v>3.3</v>
       </c>
-      <c r="O24" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>4.24</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="T24" t="n">
-        <v>3.06</v>
-      </c>
       <c r="U24" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="V24" t="n">
-        <v>7.9</v>
+        <v>10</v>
       </c>
       <c r="W24" t="n">
         <v>1.02</v>
       </c>
       <c r="X24" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.83</v>
+        <v>2.56</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.1</v>
+        <v>2.68</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.64</v>
+        <v>1.41</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.72</v>
+        <v>4</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.63</v>
+        <v>1.23</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45992.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.22</v>
+        <v>2.04</v>
       </c>
       <c r="M25" t="n">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="N25" t="n">
-        <v>2.14</v>
+        <v>3.5</v>
       </c>
       <c r="O25" t="n">
-        <v>4.34</v>
+        <v>2.6</v>
       </c>
       <c r="P25" t="n">
-        <v>1.82</v>
+        <v>1.94</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.04</v>
+        <v>4.24</v>
       </c>
       <c r="R25" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="S25" t="n">
-        <v>2.36</v>
+        <v>2.47</v>
       </c>
       <c r="T25" t="n">
-        <v>3.4</v>
+        <v>3.06</v>
       </c>
       <c r="U25" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="V25" t="n">
-        <v>10</v>
+        <v>7.9</v>
       </c>
       <c r="W25" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X25" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.46</v>
+        <v>2.83</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="AC25" t="n">
-        <v>4</v>
+        <v>3.72</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.23</v>
+        <v>1.97</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.61</v>
+        <v>1.78</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.26</v>
+        <v>1.63</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45992.6875</v>
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="M29" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="N29" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="O29" t="n">
         <v>4.65</v>
@@ -3896,13 +3896,13 @@
         <v>2.94</v>
       </c>
       <c r="T29" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="U29" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="V29" t="n">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="W29" t="n">
         <v>1.05</v>
@@ -3917,28 +3917,28 @@
         <v>3.7</v>
       </c>
       <c r="AA29" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE29" t="n">
         <v>1.85</v>
       </c>
-      <c r="AB29" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.86</v>
-      </c>
       <c r="AF29" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>45992.71875</v>

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.1</v>
+        <v>1.61</v>
       </c>
       <c r="M6" t="n">
-        <v>3.25</v>
+        <v>3.41</v>
       </c>
       <c r="N6" t="n">
-        <v>2.2</v>
+        <v>4.8</v>
       </c>
       <c r="O6" t="n">
-        <v>3.8</v>
+        <v>2.39</v>
       </c>
       <c r="P6" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.7</v>
+        <v>6.01</v>
       </c>
       <c r="R6" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="S6" t="n">
-        <v>2.59</v>
+        <v>2.39</v>
       </c>
       <c r="T6" t="n">
-        <v>2.99</v>
+        <v>3.35</v>
       </c>
       <c r="U6" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="V6" t="n">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.14</v>
+        <v>2.63</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.92</v>
+        <v>4.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.89</v>
+        <v>2.15</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="AG6" t="n">
         <v>1.33</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.28</v>
+        <v>1.95</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45992.45833333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.76</v>
+        <v>3.1</v>
       </c>
       <c r="M7" t="n">
-        <v>3.38</v>
+        <v>3.25</v>
       </c>
       <c r="N7" t="n">
-        <v>4.6</v>
+        <v>2.2</v>
       </c>
       <c r="O7" t="n">
-        <v>2.38</v>
+        <v>3.8</v>
       </c>
       <c r="P7" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>6</v>
+        <v>2.7</v>
       </c>
       <c r="R7" t="n">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="S7" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="T7" t="n">
-        <v>3.15</v>
+        <v>2.99</v>
       </c>
       <c r="U7" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="V7" t="n">
-        <v>9.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.7</v>
+        <v>3.14</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.33</v>
+        <v>1.95</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.25</v>
+        <v>3.92</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AG7" t="n">
         <v>1.33</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.95</v>
+        <v>1.28</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45992.45833333334</v>
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="M9" t="n">
         <v>3.65</v>
       </c>
       <c r="N9" t="n">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="O9" t="n">
         <v>2.8</v>
@@ -1537,16 +1537,16 @@
         <v>5.3</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AE9" t="n">
         <v>1.39</v>
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.99</v>
+        <v>2.5</v>
       </c>
       <c r="M10" t="n">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="N10" t="n">
-        <v>2.59</v>
+        <v>3.05</v>
       </c>
       <c r="O10" t="n">
         <v>3.92</v>
@@ -1650,19 +1650,19 @@
         <v>1.09</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="AC10" t="n">
-        <v>5.59</v>
+        <v>5.67</v>
       </c>
       <c r="AD10" t="n">
         <v>1.09</v>
@@ -1674,10 +1674,10 @@
         <v>1.63</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45992.5625</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.25</v>
+        <v>1.86</v>
       </c>
       <c r="M11" t="n">
-        <v>5.8</v>
+        <v>3.5</v>
       </c>
       <c r="N11" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="O11" t="n">
-        <v>1.62</v>
+        <v>2.35</v>
       </c>
       <c r="P11" t="n">
-        <v>2.7</v>
+        <v>2.33</v>
       </c>
       <c r="Q11" t="n">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.21</v>
+        <v>1.39</v>
       </c>
       <c r="S11" t="n">
-        <v>3.5</v>
+        <v>2.77</v>
       </c>
       <c r="T11" t="n">
-        <v>2.08</v>
+        <v>2.81</v>
       </c>
       <c r="U11" t="n">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="V11" t="n">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="W11" t="n">
-        <v>1.19</v>
+        <v>1.09</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.25</v>
+        <v>3.18</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.53</v>
+        <v>1.27</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.65</v>
+        <v>1.89</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.07</v>
+        <v>1.32</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.65</v>
+        <v>1.95</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45992.58333333334</v>
@@ -1849,58 +1849,58 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.87</v>
+        <v>2.79</v>
       </c>
       <c r="M12" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="N12" t="n">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="O12" t="n">
-        <v>3.88</v>
+        <v>3.86</v>
       </c>
       <c r="P12" t="n">
         <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="R12" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="S12" t="n">
-        <v>2.59</v>
+        <v>2.8</v>
       </c>
       <c r="T12" t="n">
         <v>2.9</v>
       </c>
       <c r="U12" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="V12" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X12" t="n">
         <v>1.07</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z12" t="n">
         <v>3.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.34</v>
+        <v>3.76</v>
       </c>
       <c r="AD12" t="n">
         <v>1.25</v>
@@ -1909,13 +1909,13 @@
         <v>1.75</v>
       </c>
       <c r="AF12" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.6</v>
+        <v>1.35</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2090,70 +2090,70 @@
         <v>8</v>
       </c>
       <c r="M14" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="N14" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="O14" t="n">
-        <v>8.800000000000001</v>
+        <v>7.97</v>
       </c>
       <c r="P14" t="n">
-        <v>2.5</v>
+        <v>2.84</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="R14" t="n">
-        <v>1.36</v>
+        <v>1.16</v>
       </c>
       <c r="S14" t="n">
-        <v>2.88</v>
+        <v>4.15</v>
       </c>
       <c r="T14" t="n">
-        <v>2.65</v>
+        <v>1.9</v>
       </c>
       <c r="U14" t="n">
-        <v>1.42</v>
+        <v>1.8</v>
       </c>
       <c r="V14" t="n">
-        <v>7</v>
+        <v>3.75</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="X14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y14" t="n">
         <v>1.05</v>
       </c>
-      <c r="Y14" t="n">
-        <v>1.25</v>
-      </c>
       <c r="Z14" t="n">
-        <v>3.4</v>
+        <v>6.6</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.8</v>
+        <v>1.28</v>
       </c>
       <c r="AB14" t="n">
-        <v>2</v>
+        <v>3.44</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.1</v>
+        <v>1.84</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.33</v>
+        <v>1.9</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.39</v>
+        <v>1.63</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.56</v>
+        <v>2.12</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.86</v>
+        <v>1.25</v>
       </c>
       <c r="M15" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="N15" t="n">
+        <v>14</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S15" t="n">
         <v>3.5</v>
       </c>
-      <c r="N15" t="n">
-        <v>4</v>
-      </c>
-      <c r="O15" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.77</v>
-      </c>
       <c r="T15" t="n">
-        <v>2.81</v>
+        <v>2.08</v>
       </c>
       <c r="U15" t="n">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="V15" t="n">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.09</v>
+        <v>1.19</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.18</v>
+        <v>2.25</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.27</v>
+        <v>1.53</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.95</v>
+        <v>3.65</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2447,70 +2447,70 @@
         <v>8</v>
       </c>
       <c r="M17" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="N17" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="O17" t="n">
-        <v>7.97</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="P17" t="n">
-        <v>2.84</v>
+        <v>2.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="R17" t="n">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="S17" t="n">
-        <v>4.15</v>
+        <v>2.88</v>
       </c>
       <c r="T17" t="n">
-        <v>1.9</v>
+        <v>2.65</v>
       </c>
       <c r="U17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V17" t="n">
+        <v>7</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA17" t="n">
         <v>1.8</v>
       </c>
-      <c r="V17" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AB17" t="n">
-        <v>3.44</v>
+        <v>2</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.84</v>
+        <v>3.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.9</v>
+        <v>1.33</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.63</v>
+        <v>2.39</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.12</v>
+        <v>1.56</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V18" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG18" t="n">
         <v>1.3</v>
       </c>
-      <c r="M18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="N18" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>7</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="V18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF18" t="n">
+      <c r="AH18" t="n">
         <v>2.02</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>3.5</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45992.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="O19" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA19" t="n">
         <v>1.65</v>
       </c>
-      <c r="M19" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O19" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R19" t="n">
+      <c r="AB19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH19" t="n">
         <v>1.33</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V19" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>2.02</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45992.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N20" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>7</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="V20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AB20" t="n">
         <v>2.9</v>
       </c>
-      <c r="M20" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N20" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="O20" t="n">
-        <v>3.97</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V20" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA20" t="n">
+      <c r="AC20" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AD20" t="n">
         <v>1.75</v>
       </c>
-      <c r="AB20" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AE20" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.33</v>
+        <v>3.5</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45992.625</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.12</v>
+        <v>2.78</v>
       </c>
       <c r="M21" t="n">
-        <v>4.05</v>
+        <v>3.5</v>
       </c>
       <c r="N21" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="O21" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="P21" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.32</v>
+        <v>2.7</v>
       </c>
       <c r="R21" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="S21" t="n">
-        <v>4.33</v>
+        <v>3.36</v>
       </c>
       <c r="T21" t="n">
-        <v>1.88</v>
+        <v>2.28</v>
       </c>
       <c r="U21" t="n">
-        <v>1.96</v>
+        <v>1.61</v>
       </c>
       <c r="V21" t="n">
-        <v>3.84</v>
+        <v>4.7</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="Z21" t="n">
-        <v>7.1</v>
+        <v>4.65</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.33</v>
+        <v>1.58</v>
       </c>
       <c r="AB21" t="n">
-        <v>3.14</v>
+        <v>2.33</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.82</v>
+        <v>2.31</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.94</v>
+        <v>1.58</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="AF21" t="n">
-        <v>3.21</v>
+        <v>2.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.21</v>
+        <v>1.56</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45992.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.78</v>
+        <v>3.12</v>
       </c>
       <c r="M22" t="n">
-        <v>3.5</v>
+        <v>4.05</v>
       </c>
       <c r="N22" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="O22" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="P22" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.7</v>
+        <v>2.32</v>
       </c>
       <c r="R22" t="n">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="S22" t="n">
-        <v>3.36</v>
+        <v>4.33</v>
       </c>
       <c r="T22" t="n">
-        <v>2.28</v>
+        <v>1.88</v>
       </c>
       <c r="U22" t="n">
-        <v>1.61</v>
+        <v>1.96</v>
       </c>
       <c r="V22" t="n">
-        <v>4.7</v>
+        <v>3.84</v>
       </c>
       <c r="W22" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="X22" t="n">
         <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.65</v>
+        <v>7.1</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.58</v>
+        <v>1.33</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.33</v>
+        <v>3.14</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.31</v>
+        <v>1.82</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.58</v>
+        <v>1.94</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.5</v>
+        <v>3.21</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.56</v>
+        <v>1.21</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45992.66666666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.35</v>
+        <v>2.04</v>
       </c>
       <c r="M23" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="N23" t="n">
-        <v>2.22</v>
+        <v>3.5</v>
       </c>
       <c r="O23" t="n">
-        <v>4.33</v>
+        <v>2.6</v>
       </c>
       <c r="P23" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="Q23" t="n">
-        <v>3</v>
+        <v>4.24</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.35</v>
+        <v>2.83</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.69</v>
+        <v>2.2</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.41</v>
+        <v>1.6</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.37</v>
+        <v>1.97</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.53</v>
+        <v>1.78</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45992.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.04</v>
+        <v>3.35</v>
       </c>
       <c r="M25" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="N25" t="n">
-        <v>3.5</v>
+        <v>2.22</v>
       </c>
       <c r="O25" t="n">
-        <v>2.6</v>
+        <v>4.33</v>
       </c>
       <c r="P25" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.24</v>
+        <v>3</v>
       </c>
       <c r="R25" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.83</v>
+        <v>2.35</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.2</v>
+        <v>2.69</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.6</v>
+        <v>1.41</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.97</v>
+        <v>2.37</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.78</v>
+        <v>1.53</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45992.6875</v>
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="M26" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="N26" t="n">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="O26" t="n">
         <v>1.93</v>
@@ -3560,10 +3560,10 @@
         <v>3.25</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.11</v>
+        <v>1.97</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AC26" t="n">
         <v>3.6</v>
@@ -3753,34 +3753,34 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="M28" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="N28" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="O28" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="P28" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="Q28" t="n">
         <v>5.74</v>
       </c>
       <c r="R28" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S28" t="n">
-        <v>2.62</v>
+        <v>2.94</v>
       </c>
       <c r="T28" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="U28" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="V28" t="n">
         <v>7</v>
@@ -3792,34 +3792,34 @@
         <v>1.04</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.05</v>
+        <v>3.12</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.54</v>
+        <v>3.44</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AG28" t="n">
         <v>1.26</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45992.70833333334</v>

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -659,43 +659,43 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="M2" t="n">
-        <v>2.87</v>
+        <v>2.95</v>
       </c>
       <c r="N2" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>5.77</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y2" t="n">
         <v>1.53</v>
@@ -710,22 +710,22 @@
         <v>1.49</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45992.29166666666</v>
@@ -787,46 +787,46 @@
         <v>13</v>
       </c>
       <c r="O3" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="P3" t="n">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="Q3" t="n">
-        <v>12</v>
+        <v>10.4</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AB3" t="n">
-        <v>3</v>
+        <v>2.52</v>
       </c>
       <c r="AC3" t="n">
         <v>1.8</v>
@@ -835,16 +835,16 @@
         <v>1.85</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45992.375</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="M4" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="N4" t="n">
-        <v>3.96</v>
+        <v>3.55</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.15</v>
+        <v>2.73</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.61</v>
+        <v>1.4</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45992.41666666666</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="M5" t="n">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="N5" t="n">
-        <v>3.61</v>
+        <v>3.7</v>
       </c>
       <c r="O5" t="n">
         <v>2.8</v>
       </c>
       <c r="P5" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.79</v>
+        <v>5.06</v>
       </c>
       <c r="R5" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="S5" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="T5" t="n">
-        <v>3.76</v>
+        <v>3.92</v>
       </c>
       <c r="U5" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="V5" t="n">
-        <v>12</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
         <v>1.08</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.73</v>
+        <v>2.99</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.22</v>
+        <v>2.34</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AG5" t="n">
         <v>1.32</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45992.41666666666</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.61</v>
+        <v>3.1</v>
       </c>
       <c r="M6" t="n">
-        <v>3.41</v>
+        <v>3.25</v>
       </c>
       <c r="N6" t="n">
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="O6" t="n">
-        <v>2.39</v>
+        <v>3.8</v>
       </c>
       <c r="P6" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.01</v>
+        <v>2.7</v>
       </c>
       <c r="R6" t="n">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="S6" t="n">
-        <v>2.39</v>
+        <v>2.59</v>
       </c>
       <c r="T6" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="U6" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="V6" t="n">
-        <v>9.5</v>
+        <v>8.1</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.63</v>
+        <v>2.97</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.3</v>
+        <v>3.58</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AG6" t="n">
         <v>1.33</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.95</v>
+        <v>1.29</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45992.45833333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.1</v>
+        <v>1.61</v>
       </c>
       <c r="M7" t="n">
-        <v>3.25</v>
+        <v>3.41</v>
       </c>
       <c r="N7" t="n">
-        <v>2.2</v>
+        <v>4.8</v>
       </c>
       <c r="O7" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="P7" t="n">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.7</v>
+        <v>5</v>
       </c>
       <c r="R7" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="S7" t="n">
-        <v>2.59</v>
+        <v>2.41</v>
       </c>
       <c r="T7" t="n">
-        <v>2.99</v>
+        <v>3.19</v>
       </c>
       <c r="U7" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="V7" t="n">
-        <v>8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.14</v>
+        <v>2.63</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.92</v>
+        <v>4.25</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.89</v>
+        <v>2.26</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="AG7" t="n">
         <v>1.33</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.28</v>
+        <v>1.95</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45992.45833333334</v>
@@ -1388,7 +1388,7 @@
         <v>2.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.22</v>
+        <v>6.3</v>
       </c>
       <c r="R8" t="n">
         <v>1.42</v>
@@ -1397,7 +1397,7 @@
         <v>2.62</v>
       </c>
       <c r="T8" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="U8" t="n">
         <v>1.32</v>
@@ -1412,10 +1412,10 @@
         <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.17</v>
+        <v>2.88</v>
       </c>
       <c r="AA8" t="n">
         <v>1.97</v>
@@ -1439,7 +1439,7 @@
         <v>1.26</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.13</v>
+        <v>2.34</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45992.54166666666</v>
@@ -1501,16 +1501,16 @@
         <v>2.37</v>
       </c>
       <c r="O9" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="P9" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.06</v>
+        <v>2.9</v>
       </c>
       <c r="R9" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="S9" t="n">
         <v>3.7</v>
@@ -1531,7 +1531,7 @@
         <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Z9" t="n">
         <v>5.3</v>
@@ -1549,16 +1549,16 @@
         <v>1.76</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.96</v>
+        <v>2.99</v>
       </c>
       <c r="AG9" t="n">
         <v>1.27</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45992.54166666666</v>
@@ -1620,34 +1620,34 @@
         <v>3.05</v>
       </c>
       <c r="O10" t="n">
-        <v>3.92</v>
+        <v>3.95</v>
       </c>
       <c r="P10" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="R10" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="S10" t="n">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="T10" t="n">
-        <v>3.88</v>
+        <v>3.62</v>
       </c>
       <c r="U10" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="V10" t="n">
-        <v>12</v>
+        <v>9.9</v>
       </c>
       <c r="W10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="Y10" t="n">
         <v>1.58</v>
@@ -1662,22 +1662,22 @@
         <v>1.52</v>
       </c>
       <c r="AC10" t="n">
-        <v>5.67</v>
+        <v>5.19</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45992.5625</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.79</v>
+        <v>8</v>
       </c>
       <c r="M12" t="n">
-        <v>3.23</v>
+        <v>6</v>
       </c>
       <c r="N12" t="n">
-        <v>2.21</v>
+        <v>1.26</v>
       </c>
       <c r="O12" t="n">
-        <v>3.86</v>
+        <v>7.97</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2</v>
+        <v>2.84</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.93</v>
+        <v>1.61</v>
       </c>
       <c r="R12" t="n">
-        <v>1.38</v>
+        <v>1.16</v>
       </c>
       <c r="S12" t="n">
-        <v>2.8</v>
+        <v>4.15</v>
       </c>
       <c r="T12" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="U12" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="V12" t="n">
-        <v>7.5</v>
+        <v>3.75</v>
       </c>
       <c r="W12" t="n">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="X12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AG12" t="n">
         <v>1.07</v>
       </c>
-      <c r="Y12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AH12" t="n">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45992.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>6.05</v>
+        <v>8</v>
       </c>
       <c r="M13" t="n">
-        <v>4.21</v>
+        <v>4.6</v>
       </c>
       <c r="N13" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="O13" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P13" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="R13" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="S13" t="n">
-        <v>3.26</v>
+        <v>3</v>
       </c>
       <c r="T13" t="n">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="U13" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="V13" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="W13" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.2</v>
+        <v>3.54</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.6</v>
+        <v>2.92</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.94</v>
+        <v>2.08</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.81</v>
+        <v>1.53</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>8</v>
+        <v>1.25</v>
       </c>
       <c r="M14" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="N14" t="n">
-        <v>1.26</v>
+        <v>14</v>
       </c>
       <c r="O14" t="n">
-        <v>7.97</v>
+        <v>1.62</v>
       </c>
       <c r="P14" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.61</v>
+        <v>8.5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="S14" t="n">
-        <v>4.15</v>
+        <v>3.28</v>
       </c>
       <c r="T14" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="U14" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="V14" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="W14" t="n">
         <v>1.19</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="Z14" t="n">
-        <v>6.6</v>
+        <v>4.55</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.28</v>
+        <v>1.63</v>
       </c>
       <c r="AB14" t="n">
-        <v>3.44</v>
+        <v>2.25</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.84</v>
+        <v>2.25</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.9</v>
+        <v>1.53</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.63</v>
+        <v>2.02</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.12</v>
+        <v>1.64</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.11</v>
+        <v>3.65</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V15" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AD15" t="n">
         <v>1.25</v>
       </c>
-      <c r="M15" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="N15" t="n">
-        <v>14</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V15" t="n">
-        <v>5</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AE15" t="n">
-        <v>2.05</v>
+        <v>1.77</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="AH15" t="n">
-        <v>3.65</v>
+        <v>1.36</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>8</v>
+        <v>6.05</v>
       </c>
       <c r="M17" t="n">
-        <v>4.6</v>
+        <v>4.21</v>
       </c>
       <c r="N17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="O17" t="n">
+        <v>6</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V17" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD17" t="n">
         <v>1.4</v>
       </c>
-      <c r="O17" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V17" t="n">
-        <v>7</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AE17" t="n">
-        <v>2.39</v>
+        <v>1.94</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.56</v>
+        <v>1.81</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2572,22 +2572,22 @@
         <v>4.8</v>
       </c>
       <c r="O18" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="R18" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="S18" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="T18" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="U18" t="n">
         <v>1.4</v>
@@ -2602,10 +2602,10 @@
         <v>1.06</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="AA18" t="n">
         <v>1.9</v>
@@ -2614,22 +2614,22 @@
         <v>1.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45992.625</v>
@@ -2691,7 +2691,7 @@
         <v>2.01</v>
       </c>
       <c r="O19" t="n">
-        <v>3.97</v>
+        <v>3.6</v>
       </c>
       <c r="P19" t="n">
         <v>2.14</v>
@@ -2700,25 +2700,25 @@
         <v>2.45</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S19" t="n">
         <v>3</v>
       </c>
       <c r="T19" t="n">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
       <c r="U19" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="V19" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="W19" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X19" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y19" t="n">
         <v>1.18</v>
@@ -2733,7 +2733,7 @@
         <v>2.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AD19" t="n">
         <v>1.36</v>
@@ -2801,34 +2801,34 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="M20" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="N20" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="P20" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="Q20" t="n">
         <v>7</v>
       </c>
       <c r="R20" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S20" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="T20" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="U20" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="V20" t="n">
         <v>4.2</v>
@@ -2840,34 +2840,34 @@
         <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.9</v>
+        <v>2.99</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="AH20" t="n">
-        <v>3.5</v>
+        <v>3.96</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45992.625</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.04</v>
+        <v>3.35</v>
       </c>
       <c r="M23" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="N23" t="n">
-        <v>3.5</v>
+        <v>2.22</v>
       </c>
       <c r="O23" t="n">
-        <v>2.6</v>
+        <v>4.33</v>
       </c>
       <c r="P23" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.24</v>
+        <v>3</v>
       </c>
       <c r="R23" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.83</v>
+        <v>2.35</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.2</v>
+        <v>2.69</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.6</v>
+        <v>1.41</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.97</v>
+        <v>2.37</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.78</v>
+        <v>1.53</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45992.6875</v>
@@ -3286,40 +3286,40 @@
         <v>2.27</v>
       </c>
       <c r="O24" t="n">
-        <v>4</v>
+        <v>4.51</v>
       </c>
       <c r="P24" t="n">
         <v>1.86</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="R24" t="n">
         <v>1.5</v>
       </c>
       <c r="S24" t="n">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="T24" t="n">
         <v>3.3</v>
       </c>
       <c r="U24" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="V24" t="n">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="W24" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X24" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="Y24" t="n">
         <v>1.42</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.56</v>
+        <v>2.49</v>
       </c>
       <c r="AA24" t="n">
         <v>2.68</v>
@@ -3328,22 +3328,22 @@
         <v>1.41</v>
       </c>
       <c r="AC24" t="n">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45992.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.35</v>
+        <v>2.04</v>
       </c>
       <c r="M25" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="N25" t="n">
-        <v>2.22</v>
+        <v>3.5</v>
       </c>
       <c r="O25" t="n">
-        <v>4.33</v>
+        <v>2.71</v>
       </c>
       <c r="P25" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="Q25" t="n">
-        <v>3</v>
+        <v>4.45</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.35</v>
+        <v>2.98</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.69</v>
+        <v>2.2</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.41</v>
+        <v>1.6</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.37</v>
+        <v>1.85</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.53</v>
+        <v>1.82</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45992.6875</v>
@@ -3524,28 +3524,28 @@
         <v>7.2</v>
       </c>
       <c r="O26" t="n">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="P26" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="R26" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="S26" t="n">
         <v>2.72</v>
       </c>
       <c r="T26" t="n">
-        <v>3.12</v>
+        <v>2.75</v>
       </c>
       <c r="U26" t="n">
         <v>1.36</v>
       </c>
       <c r="V26" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="W26" t="n">
         <v>1.04</v>
@@ -3557,7 +3557,7 @@
         <v>1.31</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AA26" t="n">
         <v>1.97</v>
@@ -3569,19 +3569,19 @@
         <v>3.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>45992.69791666666</v>
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="M28" t="n">
-        <v>3.65</v>
+        <v>3.53</v>
       </c>
       <c r="N28" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O28" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="P28" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="Q28" t="n">
-        <v>5.74</v>
+        <v>5.44</v>
       </c>
       <c r="R28" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S28" t="n">
         <v>2.94</v>
       </c>
       <c r="T28" t="n">
-        <v>2.95</v>
+        <v>3.02</v>
       </c>
       <c r="U28" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="V28" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="W28" t="n">
         <v>1.02</v>
       </c>
       <c r="X28" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.12</v>
+        <v>3.37</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.44</v>
+        <v>3.38</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AE28" t="n">
         <v>1.93</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45992.70833333334</v>
@@ -3881,28 +3881,28 @@
         <v>1.6</v>
       </c>
       <c r="O29" t="n">
-        <v>4.65</v>
+        <v>6</v>
       </c>
       <c r="P29" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R29" t="n">
         <v>1.35</v>
       </c>
       <c r="S29" t="n">
-        <v>2.94</v>
+        <v>3.21</v>
       </c>
       <c r="T29" t="n">
-        <v>2.65</v>
+        <v>2.43</v>
       </c>
       <c r="U29" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="V29" t="n">
-        <v>6.5</v>
+        <v>6.55</v>
       </c>
       <c r="W29" t="n">
         <v>1.05</v>
@@ -3911,10 +3911,10 @@
         <v>1.05</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AA29" t="n">
         <v>1.63</v>
@@ -3923,22 +3923,22 @@
         <v>2.25</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.08</v>
+        <v>2.85</v>
       </c>
       <c r="AD29" t="n">
         <v>1.33</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>45992.71875</v>

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -900,70 +900,70 @@
         <v>2.08</v>
       </c>
       <c r="M4" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O4" t="n">
         <v>2.8</v>
-      </c>
-      <c r="N4" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O4" t="n">
-        <v>2.84</v>
       </c>
       <c r="P4" t="n">
         <v>1.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.9</v>
+        <v>5.06</v>
       </c>
       <c r="R4" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="S4" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="T4" t="n">
-        <v>3.7</v>
+        <v>3.92</v>
       </c>
       <c r="U4" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="V4" t="n">
-        <v>9.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
         <v>1.08</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.73</v>
+        <v>2.99</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.25</v>
+        <v>5.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AG4" t="n">
         <v>1.32</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45992.41666666666</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1019,70 +1019,70 @@
         <v>2.08</v>
       </c>
       <c r="M5" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="N5" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="O5" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="P5" t="n">
         <v>1.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.06</v>
+        <v>4.9</v>
       </c>
       <c r="R5" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="S5" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="T5" t="n">
-        <v>3.92</v>
+        <v>3.7</v>
       </c>
       <c r="U5" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="V5" t="n">
-        <v>9.699999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
         <v>1.08</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.99</v>
+        <v>2.73</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.9</v>
+        <v>5.25</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.34</v>
+        <v>2.18</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AG5" t="n">
         <v>1.32</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45992.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.65</v>
+        <v>2.36</v>
       </c>
       <c r="M8" t="n">
         <v>3.65</v>
       </c>
       <c r="N8" t="n">
-        <v>4.9</v>
+        <v>2.37</v>
       </c>
       <c r="O8" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="P8" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.3</v>
+        <v>2.9</v>
       </c>
       <c r="R8" t="n">
-        <v>1.42</v>
+        <v>1.2</v>
       </c>
       <c r="S8" t="n">
-        <v>2.62</v>
+        <v>3.7</v>
       </c>
       <c r="T8" t="n">
-        <v>3.18</v>
+        <v>1.95</v>
       </c>
       <c r="U8" t="n">
-        <v>1.32</v>
+        <v>1.67</v>
       </c>
       <c r="V8" t="n">
-        <v>7.8</v>
+        <v>4.2</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>1.19</v>
       </c>
       <c r="X8" t="n">
         <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.35</v>
+        <v>1.13</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.88</v>
+        <v>5.3</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.97</v>
+        <v>1.42</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.73</v>
+        <v>2.65</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.7</v>
+        <v>1.94</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.2</v>
+        <v>1.76</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.11</v>
+        <v>1.36</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.65</v>
+        <v>2.99</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.34</v>
+        <v>1.59</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45992.54166666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.36</v>
+        <v>1.65</v>
       </c>
       <c r="M9" t="n">
         <v>3.65</v>
       </c>
       <c r="N9" t="n">
-        <v>2.37</v>
+        <v>4.9</v>
       </c>
       <c r="O9" t="n">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="P9" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.9</v>
+        <v>6.3</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2</v>
+        <v>1.42</v>
       </c>
       <c r="S9" t="n">
-        <v>3.7</v>
+        <v>2.62</v>
       </c>
       <c r="T9" t="n">
-        <v>1.95</v>
+        <v>3.18</v>
       </c>
       <c r="U9" t="n">
-        <v>1.67</v>
+        <v>1.32</v>
       </c>
       <c r="V9" t="n">
-        <v>4.2</v>
+        <v>7.8</v>
       </c>
       <c r="W9" t="n">
-        <v>1.19</v>
+        <v>1.02</v>
       </c>
       <c r="X9" t="n">
         <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.13</v>
+        <v>1.35</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.3</v>
+        <v>2.88</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.42</v>
+        <v>1.97</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.65</v>
+        <v>1.73</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.94</v>
+        <v>3.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.76</v>
+        <v>1.2</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.36</v>
+        <v>2.11</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.99</v>
+        <v>1.65</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.59</v>
+        <v>2.34</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45992.54166666666</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.86</v>
+        <v>10</v>
       </c>
       <c r="M11" t="n">
-        <v>3.5</v>
+        <v>7.53</v>
       </c>
       <c r="N11" t="n">
-        <v>4</v>
+        <v>1.23</v>
       </c>
       <c r="O11" t="n">
-        <v>2.35</v>
+        <v>8.1</v>
       </c>
       <c r="P11" t="n">
-        <v>2.33</v>
+        <v>2.88</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.5</v>
+        <v>1.52</v>
       </c>
       <c r="R11" t="n">
-        <v>1.39</v>
+        <v>1.16</v>
       </c>
       <c r="S11" t="n">
-        <v>2.77</v>
+        <v>4.15</v>
       </c>
       <c r="T11" t="n">
-        <v>2.81</v>
+        <v>1.81</v>
       </c>
       <c r="U11" t="n">
-        <v>1.38</v>
+        <v>1.89</v>
       </c>
       <c r="V11" t="n">
-        <v>5.75</v>
+        <v>3.34</v>
       </c>
       <c r="W11" t="n">
-        <v>1.09</v>
+        <v>1.24</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA11" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z11" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AB11" t="n">
-        <v>1.92</v>
+        <v>3.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.18</v>
+        <v>1.63</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.27</v>
+        <v>2.14</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.32</v>
+        <v>1.1</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.95</v>
+        <v>1.04</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45992.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1852,70 +1852,70 @@
         <v>8</v>
       </c>
       <c r="M12" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="N12" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="O12" t="n">
-        <v>7.97</v>
+        <v>9</v>
       </c>
       <c r="P12" t="n">
-        <v>2.84</v>
+        <v>2.38</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="R12" t="n">
-        <v>1.16</v>
+        <v>1.38</v>
       </c>
       <c r="S12" t="n">
-        <v>4.15</v>
+        <v>3</v>
       </c>
       <c r="T12" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="U12" t="n">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="V12" t="n">
-        <v>3.75</v>
+        <v>7</v>
       </c>
       <c r="W12" t="n">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH12" t="n">
         <v>1.05</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.11</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45992.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>8</v>
+        <v>6.25</v>
       </c>
       <c r="M13" t="n">
-        <v>4.6</v>
+        <v>4.35</v>
       </c>
       <c r="N13" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="O13" t="n">
-        <v>9</v>
+        <v>6.15</v>
       </c>
       <c r="P13" t="n">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="R13" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V13" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AD13" t="n">
         <v>1.38</v>
       </c>
-      <c r="S13" t="n">
-        <v>3</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V13" t="n">
-        <v>7</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AE13" t="n">
-        <v>2.08</v>
+        <v>1.81</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.53</v>
+        <v>1.89</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.79</v>
+        <v>1.87</v>
       </c>
       <c r="M15" t="n">
-        <v>3.23</v>
+        <v>3.5</v>
       </c>
       <c r="N15" t="n">
-        <v>2.21</v>
+        <v>4.24</v>
       </c>
       <c r="O15" t="n">
-        <v>3.88</v>
+        <v>2.38</v>
       </c>
       <c r="P15" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.9</v>
+        <v>4.94</v>
       </c>
       <c r="R15" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="T15" t="n">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="U15" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="V15" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="W15" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="n">
         <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.77</v>
+        <v>1.91</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.76</v>
+        <v>3.18</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AF15" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.36</v>
+        <v>1.91</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2325,58 +2325,58 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.23</v>
+        <v>2.31</v>
       </c>
       <c r="M16" t="n">
-        <v>3.36</v>
+        <v>3.4</v>
       </c>
       <c r="N16" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O16" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="P16" t="n">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.64</v>
+        <v>3.5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S16" t="n">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="T16" t="n">
-        <v>2.41</v>
+        <v>2.47</v>
       </c>
       <c r="U16" t="n">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="V16" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X16" t="n">
         <v>1.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z16" t="n">
         <v>4.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AB16" t="n">
         <v>2.1</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="AD16" t="n">
         <v>1.4</v>
@@ -2385,13 +2385,13 @@
         <v>1.53</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="AG16" t="n">
         <v>1.36</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>6.05</v>
+        <v>2.79</v>
       </c>
       <c r="M17" t="n">
-        <v>4.21</v>
+        <v>3.23</v>
       </c>
       <c r="N17" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R17" t="n">
         <v>1.43</v>
       </c>
-      <c r="O17" t="n">
-        <v>6</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q17" t="n">
+      <c r="S17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V17" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AA17" t="n">
         <v>1.93</v>
       </c>
-      <c r="R17" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V17" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AB17" t="n">
-        <v>2.1</v>
+        <v>1.77</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.6</v>
+        <v>3.76</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.94</v>
+        <v>1.77</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V18" t="n">
+        <v>6</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA18" t="n">
         <v>1.65</v>
       </c>
-      <c r="M18" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N18" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O18" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T18" t="n">
+      <c r="AB18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC18" t="n">
         <v>2.9</v>
       </c>
-      <c r="U18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V18" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>3.35</v>
-      </c>
       <c r="AD18" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.92</v>
+        <v>1.62</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.81</v>
+        <v>2.2</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.93</v>
+        <v>1.33</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45992.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.05</v>
+        <v>1.65</v>
       </c>
       <c r="M19" t="n">
-        <v>3.39</v>
+        <v>3.75</v>
       </c>
       <c r="N19" t="n">
-        <v>2.01</v>
+        <v>4.8</v>
       </c>
       <c r="O19" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="P19" t="n">
-        <v>2.14</v>
+        <v>2.23</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.45</v>
+        <v>4.33</v>
       </c>
       <c r="R19" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="T19" t="n">
-        <v>2.56</v>
+        <v>2.9</v>
       </c>
       <c r="U19" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V19" t="n">
-        <v>6</v>
+        <v>7.3</v>
       </c>
       <c r="W19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X19" t="n">
         <v>1.06</v>
       </c>
-      <c r="X19" t="n">
-        <v>1.04</v>
-      </c>
       <c r="Y19" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.9</v>
+        <v>3.35</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.62</v>
+        <v>1.92</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.2</v>
+        <v>1.81</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.33</v>
+        <v>1.93</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45992.625</v>
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.78</v>
+        <v>2.85</v>
       </c>
       <c r="M21" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="N21" t="n">
         <v>2.2</v>
       </c>
       <c r="O21" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P21" t="n">
-        <v>2.25</v>
+        <v>2.48</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.7</v>
+        <v>2.61</v>
       </c>
       <c r="R21" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="S21" t="n">
         <v>3.36</v>
       </c>
       <c r="T21" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="U21" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="V21" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="W21" t="n">
         <v>1.15</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.65</v>
+        <v>5.2</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AC21" t="n">
         <v>2.31</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.56</v>
+        <v>1.28</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45992.66666666666</v>
@@ -3039,40 +3039,40 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.12</v>
+        <v>3.05</v>
       </c>
       <c r="M22" t="n">
-        <v>4.05</v>
+        <v>3.9</v>
       </c>
       <c r="N22" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="O22" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="P22" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="R22" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="S22" t="n">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="T22" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="U22" t="n">
         <v>1.96</v>
       </c>
       <c r="V22" t="n">
-        <v>3.84</v>
+        <v>3.6</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="X22" t="n">
         <v>1.01</v>
@@ -3081,31 +3081,31 @@
         <v>1.04</v>
       </c>
       <c r="Z22" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AB22" t="n">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AF22" t="n">
-        <v>3.21</v>
+        <v>3.12</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45992.66666666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.35</v>
+        <v>2.04</v>
       </c>
       <c r="M23" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="N23" t="n">
-        <v>2.22</v>
+        <v>3.5</v>
       </c>
       <c r="O23" t="n">
-        <v>4.33</v>
+        <v>2.71</v>
       </c>
       <c r="P23" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="Q23" t="n">
-        <v>3</v>
+        <v>4.45</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.35</v>
+        <v>2.98</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.69</v>
+        <v>2.2</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.41</v>
+        <v>1.6</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.37</v>
+        <v>1.85</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.53</v>
+        <v>1.82</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45992.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="M24" t="n">
-        <v>2.79</v>
+        <v>2.85</v>
       </c>
       <c r="N24" t="n">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="O24" t="n">
-        <v>4.51</v>
+        <v>4.33</v>
       </c>
       <c r="P24" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.49</v>
+        <v>2.35</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="AB24" t="n">
         <v>1.41</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.01</v>
+        <v>2.37</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45992.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.04</v>
+        <v>3.32</v>
       </c>
       <c r="M25" t="n">
-        <v>3.1</v>
+        <v>2.79</v>
       </c>
       <c r="N25" t="n">
-        <v>3.5</v>
+        <v>2.27</v>
       </c>
       <c r="O25" t="n">
-        <v>2.71</v>
+        <v>4.51</v>
       </c>
       <c r="P25" t="n">
-        <v>1.94</v>
+        <v>1.86</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.45</v>
+        <v>2.83</v>
       </c>
       <c r="R25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V25" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y25" t="n">
         <v>1.42</v>
       </c>
-      <c r="S25" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U25" t="n">
+      <c r="Z25" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG25" t="n">
         <v>1.36</v>
       </c>
-      <c r="V25" t="n">
-        <v>8</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AH25" t="n">
-        <v>1.63</v>
+        <v>1.26</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45992.6875</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="M27" t="n">
-        <v>3.26</v>
+        <v>3.53</v>
       </c>
       <c r="N27" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="O27" t="n">
-        <v>2.72</v>
+        <v>2.3</v>
       </c>
       <c r="P27" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.63</v>
+        <v>5.44</v>
       </c>
       <c r="R27" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="S27" t="n">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="T27" t="n">
-        <v>3.21</v>
+        <v>3.02</v>
       </c>
       <c r="U27" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="V27" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="W27" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X27" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.1</v>
+        <v>3.37</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.75</v>
+        <v>3.38</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.8</v>
+        <v>2.22</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>45992.70833333334</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.81</v>
+        <v>2.03</v>
       </c>
       <c r="M28" t="n">
-        <v>3.53</v>
+        <v>3.24</v>
       </c>
       <c r="N28" t="n">
-        <v>4.2</v>
+        <v>4.07</v>
       </c>
       <c r="O28" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="P28" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>5.44</v>
+        <v>4</v>
       </c>
       <c r="R28" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S28" t="n">
-        <v>2.94</v>
+        <v>2.79</v>
       </c>
       <c r="T28" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="U28" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="V28" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="W28" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X28" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.37</v>
+        <v>3.1</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.87</v>
+        <v>1.68</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.38</v>
+        <v>4</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.22</v>
+        <v>1.75</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45992.70833333334</v>

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -659,16 +659,16 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="M2" t="n">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="N2" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="O2" t="n">
-        <v>5.77</v>
+        <v>6.84</v>
       </c>
       <c r="P2" t="n">
         <v>1.85</v>
@@ -677,10 +677,10 @@
         <v>2.5</v>
       </c>
       <c r="R2" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S2" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="T2" t="n">
         <v>3.42</v>
@@ -698,34 +698,34 @@
         <v>1.06</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.25</v>
+        <v>2.42</v>
       </c>
       <c r="AA2" t="n">
         <v>2.44</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.75</v>
+        <v>4.55</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.18</v>
+        <v>2.27</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45992.29166666666</v>
@@ -897,34 +897,34 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.08</v>
+        <v>2.03</v>
       </c>
       <c r="M4" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="N4" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O4" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="P4" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.06</v>
+        <v>5.18</v>
       </c>
       <c r="R4" t="n">
         <v>1.65</v>
       </c>
       <c r="S4" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="T4" t="n">
-        <v>3.92</v>
+        <v>3.94</v>
       </c>
       <c r="U4" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="V4" t="n">
         <v>9.699999999999999</v>
@@ -933,22 +933,22 @@
         <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="AD4" t="n">
         <v>1.07</v>
@@ -957,13 +957,13 @@
         <v>2.34</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45992.41666666666</v>
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="M5" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="N5" t="n">
-        <v>3.55</v>
+        <v>3.69</v>
       </c>
       <c r="O5" t="n">
         <v>2.84</v>
@@ -1034,37 +1034,37 @@
         <v>4.9</v>
       </c>
       <c r="R5" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="S5" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="T5" t="n">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="U5" t="n">
         <v>1.2</v>
       </c>
       <c r="V5" t="n">
-        <v>9.1</v>
+        <v>11</v>
       </c>
       <c r="W5" t="n">
         <v>1.03</v>
       </c>
       <c r="X5" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AC5" t="n">
         <v>5.25</v>
@@ -1076,13 +1076,13 @@
         <v>2.18</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AG5" t="n">
         <v>1.32</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45992.41666666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.36</v>
+        <v>1.62</v>
       </c>
       <c r="M8" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="N8" t="n">
-        <v>2.37</v>
+        <v>5.5</v>
       </c>
       <c r="O8" t="n">
-        <v>2.75</v>
+        <v>2.13</v>
       </c>
       <c r="P8" t="n">
-        <v>2.5</v>
+        <v>2.08</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.9</v>
+        <v>6.2</v>
       </c>
       <c r="R8" t="n">
-        <v>1.2</v>
+        <v>1.43</v>
       </c>
       <c r="S8" t="n">
-        <v>3.7</v>
+        <v>2.59</v>
       </c>
       <c r="T8" t="n">
-        <v>1.95</v>
+        <v>3.28</v>
       </c>
       <c r="U8" t="n">
-        <v>1.67</v>
+        <v>1.31</v>
       </c>
       <c r="V8" t="n">
-        <v>4.2</v>
+        <v>7.9</v>
       </c>
       <c r="W8" t="n">
-        <v>1.19</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
         <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.3</v>
+        <v>2.83</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.42</v>
+        <v>2.16</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.65</v>
+        <v>1.7</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.94</v>
+        <v>3.78</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.76</v>
+        <v>1.19</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.36</v>
+        <v>2.11</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.99</v>
+        <v>1.68</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.59</v>
+        <v>2.3</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45992.54166666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.65</v>
+        <v>2.36</v>
       </c>
       <c r="M9" t="n">
         <v>3.65</v>
       </c>
       <c r="N9" t="n">
-        <v>4.9</v>
+        <v>2.37</v>
       </c>
       <c r="O9" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="P9" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.3</v>
+        <v>2.9</v>
       </c>
       <c r="R9" t="n">
-        <v>1.42</v>
+        <v>1.2</v>
       </c>
       <c r="S9" t="n">
-        <v>2.62</v>
+        <v>3.7</v>
       </c>
       <c r="T9" t="n">
-        <v>3.18</v>
+        <v>1.95</v>
       </c>
       <c r="U9" t="n">
-        <v>1.32</v>
+        <v>1.67</v>
       </c>
       <c r="V9" t="n">
-        <v>7.8</v>
+        <v>4.2</v>
       </c>
       <c r="W9" t="n">
-        <v>1.02</v>
+        <v>1.19</v>
       </c>
       <c r="X9" t="n">
         <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.35</v>
+        <v>1.13</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.88</v>
+        <v>5.3</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.97</v>
+        <v>1.42</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.73</v>
+        <v>2.65</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.7</v>
+        <v>1.94</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.2</v>
+        <v>1.76</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.11</v>
+        <v>1.36</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.65</v>
+        <v>2.99</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.34</v>
+        <v>1.59</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45992.54166666666</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>10</v>
+        <v>2.31</v>
       </c>
       <c r="M11" t="n">
-        <v>7.53</v>
+        <v>3.4</v>
       </c>
       <c r="N11" t="n">
-        <v>1.23</v>
+        <v>3.15</v>
       </c>
       <c r="O11" t="n">
-        <v>8.1</v>
+        <v>2.5</v>
       </c>
       <c r="P11" t="n">
-        <v>2.88</v>
+        <v>2.13</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.52</v>
+        <v>3.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.16</v>
+        <v>1.34</v>
       </c>
       <c r="S11" t="n">
-        <v>4.15</v>
+        <v>2.99</v>
       </c>
       <c r="T11" t="n">
-        <v>1.81</v>
+        <v>2.47</v>
       </c>
       <c r="U11" t="n">
-        <v>1.89</v>
+        <v>1.48</v>
       </c>
       <c r="V11" t="n">
-        <v>3.34</v>
+        <v>5.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="Z11" t="n">
-        <v>7.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.22</v>
+        <v>1.7</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.63</v>
+        <v>2.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.14</v>
+        <v>1.4</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.1</v>
+        <v>1.36</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.04</v>
+        <v>1.62</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45992.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>8</v>
+        <v>6.25</v>
       </c>
       <c r="M12" t="n">
-        <v>4.6</v>
+        <v>4.35</v>
       </c>
       <c r="N12" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="O12" t="n">
-        <v>9</v>
+        <v>6.15</v>
       </c>
       <c r="P12" t="n">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="R12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V12" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AD12" t="n">
         <v>1.38</v>
       </c>
-      <c r="S12" t="n">
-        <v>3</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V12" t="n">
-        <v>7</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AE12" t="n">
-        <v>2.08</v>
+        <v>1.81</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.53</v>
+        <v>1.89</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45992.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>6.25</v>
+        <v>8</v>
       </c>
       <c r="M13" t="n">
-        <v>4.35</v>
+        <v>4.6</v>
       </c>
       <c r="N13" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="O13" t="n">
-        <v>6.15</v>
+        <v>9</v>
       </c>
       <c r="P13" t="n">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="Q13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V13" t="n">
+        <v>7</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB13" t="n">
         <v>2</v>
       </c>
-      <c r="R13" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V13" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.24</v>
-      </c>
       <c r="AC13" t="n">
-        <v>2.56</v>
+        <v>2.92</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.81</v>
+        <v>2.08</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.89</v>
+        <v>1.53</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.25</v>
+        <v>1.87</v>
       </c>
       <c r="M14" t="n">
-        <v>5.8</v>
+        <v>3.5</v>
       </c>
       <c r="N14" t="n">
-        <v>14</v>
+        <v>4.24</v>
       </c>
       <c r="O14" t="n">
-        <v>1.62</v>
+        <v>2.38</v>
       </c>
       <c r="P14" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.5</v>
+        <v>4.94</v>
       </c>
       <c r="R14" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>3.28</v>
+        <v>2.77</v>
       </c>
       <c r="T14" t="n">
-        <v>2.25</v>
+        <v>2.81</v>
       </c>
       <c r="U14" t="n">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="V14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W14" t="n">
-        <v>1.19</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.55</v>
+        <v>3.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.63</v>
+        <v>1.96</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.25</v>
+        <v>3.18</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.53</v>
+        <v>1.27</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.02</v>
+        <v>1.83</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="AG14" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="AH14" t="n">
-        <v>3.65</v>
+        <v>1.91</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.87</v>
+        <v>2.79</v>
       </c>
       <c r="M15" t="n">
-        <v>3.5</v>
+        <v>3.23</v>
       </c>
       <c r="N15" t="n">
-        <v>4.24</v>
+        <v>2.21</v>
       </c>
       <c r="O15" t="n">
-        <v>2.38</v>
+        <v>3.88</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.94</v>
+        <v>2.9</v>
       </c>
       <c r="R15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U15" t="n">
         <v>1.4</v>
       </c>
-      <c r="S15" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.38</v>
-      </c>
       <c r="V15" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
         <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.91</v>
+        <v>1.77</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.18</v>
+        <v>3.76</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.91</v>
+        <v>1.36</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.31</v>
+        <v>10</v>
       </c>
       <c r="M16" t="n">
-        <v>3.4</v>
+        <v>7.53</v>
       </c>
       <c r="N16" t="n">
-        <v>3.15</v>
+        <v>1.23</v>
       </c>
       <c r="O16" t="n">
-        <v>2.5</v>
+        <v>8.1</v>
       </c>
       <c r="P16" t="n">
-        <v>2.13</v>
+        <v>2.88</v>
       </c>
       <c r="Q16" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="S16" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="V16" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AB16" t="n">
         <v>3.5</v>
       </c>
-      <c r="R16" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V16" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X16" t="n">
+      <c r="AC16" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AH16" t="n">
         <v>1.04</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.62</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.79</v>
+        <v>1.25</v>
       </c>
       <c r="M17" t="n">
-        <v>3.23</v>
+        <v>5.8</v>
       </c>
       <c r="N17" t="n">
-        <v>2.21</v>
+        <v>14</v>
       </c>
       <c r="O17" t="n">
-        <v>3.88</v>
+        <v>1.62</v>
       </c>
       <c r="P17" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.9</v>
+        <v>8.5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="S17" t="n">
-        <v>2.8</v>
+        <v>3.28</v>
       </c>
       <c r="T17" t="n">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="U17" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="V17" t="n">
-        <v>7.1</v>
+        <v>5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="X17" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.95</v>
+        <v>4.55</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.93</v>
+        <v>1.63</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.77</v>
+        <v>2.25</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.76</v>
+        <v>2.25</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.77</v>
+        <v>2.02</v>
       </c>
       <c r="AF17" t="n">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.36</v>
+        <v>3.65</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.05</v>
+        <v>1.65</v>
       </c>
       <c r="M18" t="n">
-        <v>3.39</v>
+        <v>3.75</v>
       </c>
       <c r="N18" t="n">
-        <v>2.01</v>
+        <v>4.8</v>
       </c>
       <c r="O18" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="P18" t="n">
-        <v>2.14</v>
+        <v>2.23</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.45</v>
+        <v>4.33</v>
       </c>
       <c r="R18" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="T18" t="n">
-        <v>2.56</v>
+        <v>2.9</v>
       </c>
       <c r="U18" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V18" t="n">
-        <v>6</v>
+        <v>7.3</v>
       </c>
       <c r="W18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X18" t="n">
         <v>1.06</v>
       </c>
-      <c r="X18" t="n">
-        <v>1.04</v>
-      </c>
       <c r="Y18" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.9</v>
+        <v>3.35</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.62</v>
+        <v>1.92</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.2</v>
+        <v>1.81</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.33</v>
+        <v>1.93</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45992.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.65</v>
+        <v>1.21</v>
       </c>
       <c r="M19" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="N19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>7</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S19" t="n">
         <v>3.75</v>
       </c>
-      <c r="N19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O19" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.62</v>
-      </c>
       <c r="T19" t="n">
-        <v>2.9</v>
+        <v>2.09</v>
       </c>
       <c r="U19" t="n">
-        <v>1.4</v>
+        <v>1.71</v>
       </c>
       <c r="V19" t="n">
-        <v>7.3</v>
+        <v>4.2</v>
       </c>
       <c r="W19" t="n">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="X19" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.3</v>
+        <v>6</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.9</v>
+        <v>1.36</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.8</v>
+        <v>2.99</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.35</v>
+        <v>1.91</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.28</v>
+        <v>1.79</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.92</v>
+        <v>1.81</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.81</v>
+        <v>1.98</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.22</v>
+        <v>1.03</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.93</v>
+        <v>3.96</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45992.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.21</v>
+        <v>3.1</v>
       </c>
       <c r="M20" t="n">
-        <v>5.6</v>
+        <v>3.35</v>
       </c>
       <c r="N20" t="n">
-        <v>8.800000000000001</v>
+        <v>2.2</v>
       </c>
       <c r="O20" t="n">
-        <v>1.67</v>
+        <v>3.6</v>
       </c>
       <c r="P20" t="n">
-        <v>2.65</v>
+        <v>2.19</v>
       </c>
       <c r="Q20" t="n">
-        <v>7</v>
+        <v>2.74</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="S20" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="T20" t="n">
-        <v>2.09</v>
+        <v>2.53</v>
       </c>
       <c r="U20" t="n">
-        <v>1.71</v>
+        <v>1.45</v>
       </c>
       <c r="V20" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="W20" t="n">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z20" t="n">
-        <v>6</v>
+        <v>3.92</v>
       </c>
       <c r="AA20" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD20" t="n">
         <v>1.36</v>
       </c>
-      <c r="AB20" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.79</v>
-      </c>
       <c r="AE20" t="n">
-        <v>1.81</v>
+        <v>1.58</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.03</v>
+        <v>1.3</v>
       </c>
       <c r="AH20" t="n">
-        <v>3.96</v>
+        <v>1.33</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45992.625</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.04</v>
+        <v>3.32</v>
       </c>
       <c r="M23" t="n">
-        <v>3.1</v>
+        <v>2.79</v>
       </c>
       <c r="N23" t="n">
-        <v>3.5</v>
+        <v>2.27</v>
       </c>
       <c r="O23" t="n">
-        <v>2.71</v>
+        <v>4.51</v>
       </c>
       <c r="P23" t="n">
-        <v>1.94</v>
+        <v>1.86</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.45</v>
+        <v>2.83</v>
       </c>
       <c r="R23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V23" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y23" t="n">
         <v>1.42</v>
       </c>
-      <c r="S23" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U23" t="n">
+      <c r="Z23" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG23" t="n">
         <v>1.36</v>
       </c>
-      <c r="V23" t="n">
-        <v>8</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AH23" t="n">
-        <v>1.63</v>
+        <v>1.26</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45992.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.35</v>
+        <v>2.04</v>
       </c>
       <c r="M24" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="N24" t="n">
-        <v>2.22</v>
+        <v>3.5</v>
       </c>
       <c r="O24" t="n">
-        <v>4.33</v>
+        <v>2.71</v>
       </c>
       <c r="P24" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="Q24" t="n">
-        <v>3</v>
+        <v>4.45</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.35</v>
+        <v>2.98</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.69</v>
+        <v>2.2</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.41</v>
+        <v>1.6</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.37</v>
+        <v>1.85</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.53</v>
+        <v>1.82</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45992.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="M25" t="n">
-        <v>2.79</v>
+        <v>2.85</v>
       </c>
       <c r="N25" t="n">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="O25" t="n">
-        <v>4.51</v>
+        <v>4.33</v>
       </c>
       <c r="P25" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="R25" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.49</v>
+        <v>2.35</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="AB25" t="n">
         <v>1.41</v>
       </c>
       <c r="AC25" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.01</v>
+        <v>2.37</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45992.6875</v>
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="M30" t="n">
-        <v>3.54</v>
+        <v>3.95</v>
       </c>
       <c r="N30" t="n">
-        <v>4.15</v>
+        <v>3.95</v>
       </c>
       <c r="O30" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="P30" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.75</v>
+        <v>4.53</v>
       </c>
       <c r="R30" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S30" t="n">
-        <v>2.9</v>
+        <v>3.22</v>
       </c>
       <c r="T30" t="n">
-        <v>2.76</v>
+        <v>2.69</v>
       </c>
       <c r="U30" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="V30" t="n">
-        <v>6.75</v>
+        <v>6.65</v>
       </c>
       <c r="W30" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X30" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.5</v>
+        <v>3.88</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="AC30" t="n">
         <v>3</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>45992.83333333334</v>

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -642,20 +642,20 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="M3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N3" t="n">
-        <v>13</v>
+        <v>8.75</v>
       </c>
       <c r="O3" t="n">
-        <v>1.51</v>
+        <v>1.87</v>
       </c>
       <c r="P3" t="n">
-        <v>2.84</v>
+        <v>2.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>10.4</v>
+        <v>7.08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.17</v>
+        <v>1.35</v>
       </c>
       <c r="S3" t="n">
-        <v>4.5</v>
+        <v>2.79</v>
       </c>
       <c r="T3" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="U3" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="V3" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="W3" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X3" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.5</v>
+        <v>4.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.52</v>
+        <v>2.04</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.8</v>
+        <v>2.54</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.85</v>
+        <v>1.45</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.6</v>
+        <v>2.24</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AH3" t="n">
-        <v>4.65</v>
+        <v>3.3</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45992.375</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="M4" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="N4" t="n">
-        <v>3.75</v>
+        <v>3.69</v>
       </c>
       <c r="O4" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="P4" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.18</v>
+        <v>4.9</v>
       </c>
       <c r="R4" t="n">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="S4" t="n">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="T4" t="n">
-        <v>3.94</v>
+        <v>3.68</v>
       </c>
       <c r="U4" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="V4" t="n">
-        <v>9.699999999999999</v>
+        <v>11</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X4" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Y4" t="n">
         <v>1.57</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AA4" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.4</v>
+        <v>5.25</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.34</v>
+        <v>2.18</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45992.41666666666</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="M5" t="n">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="N5" t="n">
-        <v>3.69</v>
+        <v>3.75</v>
       </c>
       <c r="O5" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.9</v>
+        <v>5.18</v>
       </c>
       <c r="R5" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="S5" t="n">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="T5" t="n">
-        <v>3.68</v>
+        <v>3.94</v>
       </c>
       <c r="U5" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="V5" t="n">
-        <v>11</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Y5" t="n">
         <v>1.57</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.25</v>
+        <v>5.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45992.41666666666</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.1</v>
+        <v>1.61</v>
       </c>
       <c r="M6" t="n">
-        <v>3.25</v>
+        <v>3.41</v>
       </c>
       <c r="N6" t="n">
-        <v>2.2</v>
+        <v>4.8</v>
       </c>
       <c r="O6" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="P6" t="n">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.7</v>
+        <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="S6" t="n">
-        <v>2.59</v>
+        <v>2.41</v>
       </c>
       <c r="T6" t="n">
-        <v>3.05</v>
+        <v>3.19</v>
       </c>
       <c r="U6" t="n">
         <v>1.32</v>
       </c>
       <c r="V6" t="n">
-        <v>8.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.97</v>
+        <v>2.63</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.58</v>
+        <v>4.25</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.92</v>
+        <v>2.26</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AG6" t="n">
         <v>1.33</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.29</v>
+        <v>1.95</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45992.45833333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.61</v>
+        <v>3.6</v>
       </c>
       <c r="M7" t="n">
-        <v>3.41</v>
+        <v>3.15</v>
       </c>
       <c r="N7" t="n">
-        <v>4.8</v>
+        <v>2.05</v>
       </c>
       <c r="O7" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="P7" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>5</v>
+        <v>2.7</v>
       </c>
       <c r="R7" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="S7" t="n">
-        <v>2.41</v>
+        <v>2.79</v>
       </c>
       <c r="T7" t="n">
-        <v>3.19</v>
+        <v>3.05</v>
       </c>
       <c r="U7" t="n">
         <v>1.32</v>
       </c>
       <c r="V7" t="n">
-        <v>9.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.63</v>
+        <v>2.97</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.93</v>
+        <v>2.13</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.25</v>
+        <v>3.9</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.26</v>
+        <v>1.92</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AG7" t="n">
         <v>1.33</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.95</v>
+        <v>1.25</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45992.45833333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.62</v>
+        <v>2.25</v>
       </c>
       <c r="M8" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="N8" t="n">
-        <v>5.5</v>
+        <v>2.65</v>
       </c>
       <c r="O8" t="n">
-        <v>2.13</v>
+        <v>2.75</v>
       </c>
       <c r="P8" t="n">
-        <v>2.08</v>
+        <v>2.36</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.2</v>
+        <v>2.87</v>
       </c>
       <c r="R8" t="n">
-        <v>1.43</v>
+        <v>1.2</v>
       </c>
       <c r="S8" t="n">
-        <v>2.59</v>
+        <v>3.7</v>
       </c>
       <c r="T8" t="n">
-        <v>3.28</v>
+        <v>2.05</v>
       </c>
       <c r="U8" t="n">
-        <v>1.31</v>
+        <v>1.7</v>
       </c>
       <c r="V8" t="n">
-        <v>7.9</v>
+        <v>4.1</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>1.19</v>
       </c>
       <c r="X8" t="n">
         <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.83</v>
+        <v>5.75</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.16</v>
+        <v>1.44</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.7</v>
+        <v>2.76</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.78</v>
+        <v>2.08</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.19</v>
+        <v>1.76</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.11</v>
+        <v>1.36</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.68</v>
+        <v>3.01</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.3</v>
+        <v>1.52</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45992.54166666666</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.36</v>
+        <v>1.62</v>
       </c>
       <c r="M9" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="N9" t="n">
-        <v>2.37</v>
+        <v>5.5</v>
       </c>
       <c r="O9" t="n">
-        <v>2.75</v>
+        <v>2.13</v>
       </c>
       <c r="P9" t="n">
-        <v>2.5</v>
+        <v>2.08</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.9</v>
+        <v>6.2</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2</v>
+        <v>1.43</v>
       </c>
       <c r="S9" t="n">
-        <v>3.7</v>
+        <v>2.59</v>
       </c>
       <c r="T9" t="n">
-        <v>1.95</v>
+        <v>3.28</v>
       </c>
       <c r="U9" t="n">
-        <v>1.67</v>
+        <v>1.31</v>
       </c>
       <c r="V9" t="n">
-        <v>4.2</v>
+        <v>7.9</v>
       </c>
       <c r="W9" t="n">
-        <v>1.19</v>
+        <v>1.02</v>
       </c>
       <c r="X9" t="n">
         <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.3</v>
+        <v>2.83</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.42</v>
+        <v>2.16</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.65</v>
+        <v>1.7</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.94</v>
+        <v>3.78</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.76</v>
+        <v>1.19</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.36</v>
+        <v>2.11</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.99</v>
+        <v>1.68</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.59</v>
+        <v>2.3</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45992.54166666666</v>
@@ -1611,22 +1611,22 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.5</v>
+        <v>2.96</v>
       </c>
       <c r="M10" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>3.05</v>
+        <v>2.26</v>
       </c>
       <c r="O10" t="n">
-        <v>3.95</v>
+        <v>3.99</v>
       </c>
       <c r="P10" t="n">
         <v>1.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.34</v>
+        <v>3.32</v>
       </c>
       <c r="R10" t="n">
         <v>1.58</v>
@@ -1641,28 +1641,28 @@
         <v>1.25</v>
       </c>
       <c r="V10" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X10" t="n">
         <v>1.12</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.4</v>
+        <v>2.64</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.35</v>
+        <v>2.62</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="AC10" t="n">
-        <v>5.19</v>
+        <v>4.8</v>
       </c>
       <c r="AD10" t="n">
         <v>1.12</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.31</v>
+        <v>2.79</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4</v>
+        <v>3.23</v>
       </c>
       <c r="N11" t="n">
-        <v>3.15</v>
+        <v>2.21</v>
       </c>
       <c r="O11" t="n">
-        <v>2.5</v>
+        <v>3.88</v>
       </c>
       <c r="P11" t="n">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="R11" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="S11" t="n">
-        <v>2.99</v>
+        <v>2.8</v>
       </c>
       <c r="T11" t="n">
-        <v>2.47</v>
+        <v>2.9</v>
       </c>
       <c r="U11" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="V11" t="n">
-        <v>5.5</v>
+        <v>7.1</v>
       </c>
       <c r="W11" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.2</v>
+        <v>2.95</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.7</v>
+        <v>1.93</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.1</v>
+        <v>1.77</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.6</v>
+        <v>3.76</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AG11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH11" t="n">
         <v>1.36</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.62</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45992.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>6.25</v>
+        <v>1.87</v>
       </c>
       <c r="M12" t="n">
-        <v>4.35</v>
+        <v>3.5</v>
       </c>
       <c r="N12" t="n">
-        <v>1.47</v>
+        <v>4.24</v>
       </c>
       <c r="O12" t="n">
-        <v>6.15</v>
+        <v>2.38</v>
       </c>
       <c r="P12" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>2</v>
+        <v>4.94</v>
       </c>
       <c r="R12" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>3.26</v>
+        <v>2.77</v>
       </c>
       <c r="T12" t="n">
-        <v>2.4</v>
+        <v>2.81</v>
       </c>
       <c r="U12" t="n">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="V12" t="n">
-        <v>5.45</v>
+        <v>7</v>
       </c>
       <c r="W12" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.67</v>
+        <v>1.96</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.24</v>
+        <v>1.91</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.56</v>
+        <v>3.18</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.06</v>
+        <v>1.91</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45992.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>8</v>
+        <v>2.31</v>
       </c>
       <c r="M13" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="N13" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD13" t="n">
         <v>1.4</v>
       </c>
-      <c r="O13" t="n">
-        <v>9</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V13" t="n">
-        <v>7</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AE13" t="n">
-        <v>2.08</v>
+        <v>1.53</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.53</v>
+        <v>2.3</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.05</v>
+        <v>1.62</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.87</v>
+        <v>6.25</v>
       </c>
       <c r="M14" t="n">
-        <v>3.5</v>
+        <v>4.35</v>
       </c>
       <c r="N14" t="n">
-        <v>4.24</v>
+        <v>1.47</v>
       </c>
       <c r="O14" t="n">
-        <v>2.38</v>
+        <v>6.15</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.94</v>
+        <v>2</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="S14" t="n">
-        <v>2.77</v>
+        <v>3.26</v>
       </c>
       <c r="T14" t="n">
-        <v>2.81</v>
+        <v>2.4</v>
       </c>
       <c r="U14" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V14" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AD14" t="n">
         <v>1.38</v>
       </c>
-      <c r="V14" t="n">
-        <v>7</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AE14" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.91</v>
+        <v>1.06</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.79</v>
+        <v>7.7</v>
       </c>
       <c r="M15" t="n">
-        <v>3.23</v>
+        <v>7.59</v>
       </c>
       <c r="N15" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O15" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="U15" t="n">
         <v>2.21</v>
       </c>
-      <c r="O15" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.4</v>
-      </c>
       <c r="V15" t="n">
-        <v>7.1</v>
+        <v>3.28</v>
       </c>
       <c r="W15" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="X15" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>1.02</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.95</v>
+        <v>7.8</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.93</v>
+        <v>1.21</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.77</v>
+        <v>3.58</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.76</v>
+        <v>1.61</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.25</v>
+        <v>2.17</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.77</v>
+        <v>1.59</v>
       </c>
       <c r="AF15" t="n">
-        <v>2</v>
+        <v>2.19</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.36</v>
+        <v>1</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>10</v>
+        <v>1.25</v>
       </c>
       <c r="M16" t="n">
-        <v>7.53</v>
+        <v>5.8</v>
       </c>
       <c r="N16" t="n">
-        <v>1.23</v>
+        <v>14</v>
       </c>
       <c r="O16" t="n">
-        <v>8.1</v>
+        <v>1.62</v>
       </c>
       <c r="P16" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.52</v>
+        <v>8.5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="S16" t="n">
-        <v>4.15</v>
+        <v>3.28</v>
       </c>
       <c r="T16" t="n">
-        <v>1.81</v>
+        <v>2.25</v>
       </c>
       <c r="U16" t="n">
-        <v>1.89</v>
+        <v>1.62</v>
       </c>
       <c r="V16" t="n">
-        <v>3.34</v>
+        <v>5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="Z16" t="n">
-        <v>7.5</v>
+        <v>4.55</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.22</v>
+        <v>1.63</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.5</v>
+        <v>2.25</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.63</v>
+        <v>2.25</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.14</v>
+        <v>1.53</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.65</v>
+        <v>2.02</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.05</v>
+        <v>1.64</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.25</v>
+        <v>8</v>
       </c>
       <c r="M17" t="n">
-        <v>5.8</v>
+        <v>4.6</v>
       </c>
       <c r="N17" t="n">
-        <v>14</v>
+        <v>1.4</v>
       </c>
       <c r="O17" t="n">
-        <v>1.62</v>
+        <v>9</v>
       </c>
       <c r="P17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S17" t="n">
         <v>3</v>
       </c>
-      <c r="Q17" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.28</v>
-      </c>
       <c r="T17" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="U17" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="V17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W17" t="n">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.55</v>
+        <v>3.54</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.25</v>
+        <v>2.92</v>
       </c>
       <c r="AD17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AF17" t="n">
         <v>1.53</v>
       </c>
-      <c r="AE17" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.64</v>
-      </c>
       <c r="AG17" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AH17" t="n">
-        <v>3.65</v>
+        <v>1.05</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.65</v>
+        <v>1.82</v>
       </c>
       <c r="M18" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="N18" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="O18" t="n">
         <v>2.4</v>
@@ -2581,10 +2581,10 @@
         <v>4.33</v>
       </c>
       <c r="R18" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S18" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="T18" t="n">
         <v>2.9</v>
@@ -2593,7 +2593,7 @@
         <v>1.4</v>
       </c>
       <c r="V18" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="W18" t="n">
         <v>1.07</v>
@@ -2602,16 +2602,16 @@
         <v>1.06</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z18" t="n">
         <v>3.3</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC18" t="n">
         <v>3.35</v>
@@ -2629,7 +2629,7 @@
         <v>1.22</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45992.625</v>
@@ -2920,22 +2920,22 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="M21" t="n">
         <v>3.55</v>
       </c>
       <c r="N21" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="O21" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P21" t="n">
         <v>2.48</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.61</v>
+        <v>2.7</v>
       </c>
       <c r="R21" t="n">
         <v>1.25</v>
@@ -2944,10 +2944,10 @@
         <v>3.36</v>
       </c>
       <c r="T21" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="U21" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="V21" t="n">
         <v>4.8</v>
@@ -2962,19 +2962,19 @@
         <v>1.17</v>
       </c>
       <c r="Z21" t="n">
-        <v>5.2</v>
+        <v>4.65</v>
       </c>
       <c r="AA21" t="n">
         <v>1.48</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.35</v>
+        <v>2.48</v>
       </c>
       <c r="AC21" t="n">
         <v>2.31</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="AE21" t="n">
         <v>1.45</v>
@@ -2983,10 +2983,10 @@
         <v>2.63</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45992.66666666666</v>
@@ -3039,31 +3039,31 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="M22" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="N22" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="O22" t="n">
         <v>3</v>
       </c>
       <c r="P22" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="R22" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="S22" t="n">
         <v>4.75</v>
       </c>
       <c r="T22" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="U22" t="n">
         <v>1.96</v>
@@ -3072,7 +3072,7 @@
         <v>3.6</v>
       </c>
       <c r="W22" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="X22" t="n">
         <v>1.01</v>
@@ -3081,25 +3081,25 @@
         <v>1.04</v>
       </c>
       <c r="Z22" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AB22" t="n">
         <v>3.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AF22" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="AG22" t="n">
         <v>1.24</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.32</v>
+        <v>2.04</v>
       </c>
       <c r="M23" t="n">
-        <v>2.79</v>
+        <v>3.1</v>
       </c>
       <c r="N23" t="n">
-        <v>2.27</v>
+        <v>3.5</v>
       </c>
       <c r="O23" t="n">
-        <v>4.51</v>
+        <v>2.71</v>
       </c>
       <c r="P23" t="n">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.83</v>
+        <v>4.45</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="S23" t="n">
-        <v>2.4</v>
+        <v>2.65</v>
       </c>
       <c r="T23" t="n">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="U23" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="V23" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="W23" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X23" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.49</v>
+        <v>2.98</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.68</v>
+        <v>2.2</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.41</v>
+        <v>1.6</v>
       </c>
       <c r="AC23" t="n">
-        <v>4.75</v>
+        <v>3.72</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.01</v>
+        <v>1.85</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.26</v>
+        <v>1.63</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45992.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.04</v>
+        <v>3.5</v>
       </c>
       <c r="M24" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="N24" t="n">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="O24" t="n">
-        <v>2.71</v>
+        <v>4.56</v>
       </c>
       <c r="P24" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.45</v>
+        <v>2.83</v>
       </c>
       <c r="R24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V24" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y24" t="n">
         <v>1.42</v>
       </c>
-      <c r="S24" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V24" t="n">
-        <v>8</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.4</v>
-      </c>
       <c r="Z24" t="n">
-        <v>2.98</v>
+        <v>2.49</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.72</v>
+        <v>4.75</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.85</v>
+        <v>2.03</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.63</v>
+        <v>1.26</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45992.6875</v>
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="M26" t="n">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="N26" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="O26" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="P26" t="n">
         <v>2.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="R26" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V26" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH26" t="n">
         <v>2.72</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V26" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>2.8</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>45992.69791666666</v>

--- a/jogos_2025-12-01.xlsx
+++ b/jogos_2025-12-01.xlsx
@@ -761,20 +761,20 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -871,99 +871,99 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="M4" t="n">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="N4" t="n">
-        <v>3.69</v>
+        <v>3.75</v>
       </c>
       <c r="O4" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="P4" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.9</v>
+        <v>5.18</v>
       </c>
       <c r="R4" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="S4" t="n">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="T4" t="n">
-        <v>3.68</v>
+        <v>3.94</v>
       </c>
       <c r="U4" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="V4" t="n">
-        <v>11</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Y4" t="n">
         <v>1.57</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.25</v>
+        <v>5.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45992.41666666666</v>
@@ -990,99 +990,99 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="M5" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="N5" t="n">
-        <v>3.75</v>
+        <v>3.69</v>
       </c>
       <c r="O5" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="P5" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.18</v>
+        <v>4.9</v>
       </c>
       <c r="R5" t="n">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="S5" t="n">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="T5" t="n">
-        <v>3.94</v>
+        <v>3.68</v>
       </c>
       <c r="U5" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="V5" t="n">
-        <v>9.699999999999999</v>
+        <v>11</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Y5" t="n">
         <v>1.57</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AA5" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.4</v>
+        <v>5.25</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.34</v>
+        <v>2.18</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45992.41666666666</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.61</v>
+        <v>3.1</v>
       </c>
       <c r="M6" t="n">
-        <v>3.41</v>
+        <v>3.25</v>
       </c>
       <c r="N6" t="n">
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="O6" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="P6" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>5</v>
+        <v>2.7</v>
       </c>
       <c r="R6" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="S6" t="n">
-        <v>2.41</v>
+        <v>2.79</v>
       </c>
       <c r="T6" t="n">
-        <v>3.19</v>
+        <v>3.05</v>
       </c>
       <c r="U6" t="n">
         <v>1.32</v>
       </c>
       <c r="V6" t="n">
-        <v>9.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.63</v>
+        <v>2.97</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.25</v>
+        <v>3.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.26</v>
+        <v>1.92</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AG6" t="n">
         <v>1.33</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.95</v>
+        <v>1.25</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45992.45833333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.6</v>
+        <v>1.61</v>
       </c>
       <c r="M7" t="n">
-        <v>3.15</v>
+        <v>3.41</v>
       </c>
       <c r="N7" t="n">
-        <v>2.05</v>
+        <v>4.8</v>
       </c>
       <c r="O7" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="P7" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.7</v>
+        <v>5</v>
       </c>
       <c r="R7" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S7" t="n">
-        <v>2.79</v>
+        <v>2.39</v>
       </c>
       <c r="T7" t="n">
-        <v>3.05</v>
+        <v>3.19</v>
       </c>
       <c r="U7" t="n">
         <v>1.32</v>
       </c>
       <c r="V7" t="n">
-        <v>8.199999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.97</v>
+        <v>2.63</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.13</v>
+        <v>1.93</v>
       </c>
       <c r="AB7" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AF7" t="n">
         <v>1.67</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.83</v>
       </c>
       <c r="AG7" t="n">
         <v>1.33</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.25</v>
+        <v>2.01</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45992.45833333334</v>
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="M8" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="N8" t="n">
-        <v>2.65</v>
+        <v>2.37</v>
       </c>
       <c r="O8" t="n">
         <v>2.75</v>
@@ -1418,13 +1418,13 @@
         <v>5.75</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.76</v>
+        <v>2.65</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="AD8" t="n">
         <v>1.76</v>
@@ -1492,37 +1492,37 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.62</v>
+        <v>1.84</v>
       </c>
       <c r="M9" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="N9" t="n">
         <v>3.8</v>
       </c>
-      <c r="N9" t="n">
-        <v>5.5</v>
-      </c>
       <c r="O9" t="n">
-        <v>2.13</v>
+        <v>2.53</v>
       </c>
       <c r="P9" t="n">
-        <v>2.08</v>
+        <v>1.99</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
       <c r="R9" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="S9" t="n">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="T9" t="n">
-        <v>3.28</v>
+        <v>3.31</v>
       </c>
       <c r="U9" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="V9" t="n">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="W9" t="n">
         <v>1.02</v>
@@ -1531,34 +1531,34 @@
         <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.83</v>
+        <v>2.78</v>
       </c>
       <c r="AA9" t="n">
         <v>2.16</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.78</v>
+        <v>3.85</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.11</v>
+        <v>1.94</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.3</v>
+        <v>1.86</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45992.54166666666</v>
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="N10" t="n">
-        <v>2.26</v>
+        <v>2.58</v>
       </c>
       <c r="O10" t="n">
         <v>3.99</v>
@@ -1650,16 +1650,16 @@
         <v>1.12</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.64</v>
+        <v>2.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.62</v>
+        <v>2.35</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="AC10" t="n">
         <v>4.8</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.79</v>
+        <v>7.7</v>
       </c>
       <c r="M11" t="n">
-        <v>3.23</v>
+        <v>7.59</v>
       </c>
       <c r="N11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O11" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="U11" t="n">
         <v>2.21</v>
       </c>
-      <c r="O11" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.4</v>
-      </c>
       <c r="V11" t="n">
-        <v>7.1</v>
+        <v>3.28</v>
       </c>
       <c r="W11" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="X11" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.3</v>
+        <v>1.02</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.95</v>
+        <v>7.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.93</v>
+        <v>1.21</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.77</v>
+        <v>3.58</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.76</v>
+        <v>1.61</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.25</v>
+        <v>2.17</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.77</v>
+        <v>1.59</v>
       </c>
       <c r="AF11" t="n">
-        <v>2</v>
+        <v>2.19</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.36</v>
+        <v>1</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45992.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.87</v>
+        <v>3</v>
       </c>
       <c r="M12" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="N12" t="n">
-        <v>4.24</v>
+        <v>2.14</v>
       </c>
       <c r="O12" t="n">
-        <v>2.38</v>
+        <v>3.97</v>
       </c>
       <c r="P12" t="n">
         <v>2.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.94</v>
+        <v>2.95</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="S12" t="n">
-        <v>2.77</v>
+        <v>2.47</v>
       </c>
       <c r="T12" t="n">
-        <v>2.81</v>
+        <v>3.05</v>
       </c>
       <c r="U12" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="V12" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.3</v>
+        <v>2.78</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.18</v>
+        <v>3.92</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AF12" t="n">
         <v>1.85</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.91</v>
+        <v>1.36</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45992.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.31</v>
+        <v>6.5</v>
       </c>
       <c r="M13" t="n">
-        <v>3.4</v>
+        <v>4.65</v>
       </c>
       <c r="N13" t="n">
-        <v>3.15</v>
+        <v>1.32</v>
       </c>
       <c r="O13" t="n">
-        <v>2.5</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.5</v>
+        <v>1.9</v>
       </c>
       <c r="R13" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>2.99</v>
+        <v>2.69</v>
       </c>
       <c r="T13" t="n">
-        <v>2.47</v>
+        <v>2.8</v>
       </c>
       <c r="U13" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="V13" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="W13" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH13" t="n">
         <v>1.08</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.62</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,31 +2087,31 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>6.25</v>
+        <v>2.25</v>
       </c>
       <c r="M14" t="n">
-        <v>4.35</v>
+        <v>3.49</v>
       </c>
       <c r="N14" t="n">
-        <v>1.47</v>
+        <v>2.7</v>
       </c>
       <c r="O14" t="n">
-        <v>6.15</v>
+        <v>2.5</v>
       </c>
       <c r="P14" t="n">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S14" t="n">
-        <v>3.26</v>
+        <v>3.02</v>
       </c>
       <c r="T14" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="U14" t="n">
         <v>1.49</v>
@@ -2120,40 +2120,40 @@
         <v>5.45</v>
       </c>
       <c r="W14" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z14" t="n">
         <v>4.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.81</v>
+        <v>1.53</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.89</v>
+        <v>2.35</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.06</v>
+        <v>1.62</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>7.7</v>
+        <v>6.4</v>
       </c>
       <c r="M15" t="n">
-        <v>7.59</v>
+        <v>4.35</v>
       </c>
       <c r="N15" t="n">
-        <v>1.24</v>
+        <v>1.46</v>
       </c>
       <c r="O15" t="n">
-        <v>7.37</v>
+        <v>5.8</v>
       </c>
       <c r="P15" t="n">
-        <v>2.94</v>
+        <v>2.55</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.55</v>
+        <v>2.02</v>
       </c>
       <c r="R15" t="n">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="S15" t="n">
-        <v>4.45</v>
+        <v>3.26</v>
       </c>
       <c r="T15" t="n">
-        <v>1.65</v>
+        <v>2.3</v>
       </c>
       <c r="U15" t="n">
-        <v>2.21</v>
+        <v>1.52</v>
       </c>
       <c r="V15" t="n">
-        <v>3.28</v>
+        <v>5.3</v>
       </c>
       <c r="W15" t="n">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>7.8</v>
+        <v>4.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.21</v>
+        <v>1.64</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.58</v>
+        <v>2.27</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.61</v>
+        <v>2.46</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.17</v>
+        <v>1.43</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.59</v>
+        <v>1.76</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.19</v>
+        <v>1.89</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AH15" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.25</v>
+        <v>1.85</v>
       </c>
       <c r="M16" t="n">
-        <v>5.8</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="O16" t="n">
-        <v>1.62</v>
+        <v>2.38</v>
       </c>
       <c r="P16" t="n">
-        <v>3</v>
+        <v>2.15</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.5</v>
+        <v>4.6</v>
       </c>
       <c r="R16" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="S16" t="n">
-        <v>3.28</v>
+        <v>3.11</v>
       </c>
       <c r="T16" t="n">
-        <v>2.25</v>
+        <v>2.77</v>
       </c>
       <c r="U16" t="n">
-        <v>1.62</v>
+        <v>1.39</v>
       </c>
       <c r="V16" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W16" t="n">
-        <v>1.19</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.55</v>
+        <v>3.44</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.63</v>
+        <v>1.94</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.25</v>
+        <v>2.99</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.02</v>
+        <v>1.81</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.64</v>
+        <v>2.05</v>
       </c>
       <c r="AG16" t="n">
-        <v>1</v>
+        <v>1.34</v>
       </c>
       <c r="AH16" t="n">
-        <v>3.65</v>
+        <v>1.96</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>8</v>
+        <v>1.18</v>
       </c>
       <c r="M17" t="n">
-        <v>4.6</v>
+        <v>6.1</v>
       </c>
       <c r="N17" t="n">
-        <v>1.4</v>
+        <v>14</v>
       </c>
       <c r="O17" t="n">
-        <v>9</v>
+        <v>1.62</v>
       </c>
       <c r="P17" t="n">
-        <v>2.38</v>
+        <v>2.94</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.8</v>
+        <v>10</v>
       </c>
       <c r="R17" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>3.28</v>
       </c>
       <c r="T17" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="U17" t="n">
-        <v>1.44</v>
+        <v>1.59</v>
       </c>
       <c r="V17" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X17" t="n">
         <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.54</v>
+        <v>4.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AB17" t="n">
-        <v>2</v>
+        <v>2.24</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.92</v>
+        <v>2.38</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.05</v>
+        <v>4.2</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45992.58333333334</v>
@@ -2572,55 +2572,55 @@
         <v>4.2</v>
       </c>
       <c r="O18" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="P18" t="n">
-        <v>2.23</v>
+        <v>2.12</v>
       </c>
       <c r="Q18" t="n">
         <v>4.33</v>
       </c>
       <c r="R18" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S18" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="T18" t="n">
         <v>2.9</v>
       </c>
       <c r="U18" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="V18" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="W18" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X18" t="n">
         <v>1.06</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AF18" t="n">
         <v>1.81</v>
@@ -2629,7 +2629,7 @@
         <v>1.22</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45992.625</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.21</v>
+        <v>3.05</v>
       </c>
       <c r="M19" t="n">
-        <v>5.6</v>
+        <v>3.39</v>
       </c>
       <c r="N19" t="n">
-        <v>8.800000000000001</v>
+        <v>2.01</v>
       </c>
       <c r="O19" t="n">
-        <v>1.67</v>
+        <v>3.6</v>
       </c>
       <c r="P19" t="n">
-        <v>2.65</v>
+        <v>2.19</v>
       </c>
       <c r="Q19" t="n">
-        <v>7</v>
+        <v>2.74</v>
       </c>
       <c r="R19" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="S19" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="T19" t="n">
-        <v>2.09</v>
+        <v>2.53</v>
       </c>
       <c r="U19" t="n">
-        <v>1.71</v>
+        <v>1.45</v>
       </c>
       <c r="V19" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="W19" t="n">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z19" t="n">
-        <v>6</v>
+        <v>3.92</v>
       </c>
       <c r="AA19" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD19" t="n">
         <v>1.36</v>
       </c>
-      <c r="AB19" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.79</v>
-      </c>
       <c r="AE19" t="n">
-        <v>1.81</v>
+        <v>1.58</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.03</v>
+        <v>1.3</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.96</v>
+        <v>1.33</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45992.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.1</v>
+        <v>1.29</v>
       </c>
       <c r="M20" t="n">
-        <v>3.35</v>
+        <v>6</v>
       </c>
       <c r="N20" t="n">
-        <v>2.2</v>
+        <v>9.59</v>
       </c>
       <c r="O20" t="n">
-        <v>3.6</v>
+        <v>1.67</v>
       </c>
       <c r="P20" t="n">
-        <v>2.19</v>
+        <v>2.75</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.74</v>
+        <v>7</v>
       </c>
       <c r="R20" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="T20" t="n">
-        <v>2.53</v>
+        <v>2.08</v>
       </c>
       <c r="U20" t="n">
-        <v>1.45</v>
+        <v>1.7</v>
       </c>
       <c r="V20" t="n">
-        <v>6</v>
+        <v>4.33</v>
       </c>
       <c r="W20" t="n">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="X20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.92</v>
+        <v>6.2</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.05</v>
+        <v>2.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.9</v>
+        <v>2.07</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.36</v>
+        <v>1.84</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.58</v>
+        <v>1.79</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.3</v>
+        <v>1.04</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.33</v>
+        <v>3.91</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45992.625</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.88</v>
+        <v>3.51</v>
       </c>
       <c r="M21" t="n">
-        <v>3.55</v>
+        <v>4.49</v>
       </c>
       <c r="N21" t="n">
-        <v>2.08</v>
+        <v>1.84</v>
       </c>
       <c r="O21" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P21" t="n">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="R21" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="V21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="W21" t="n">
         <v>1.25</v>
       </c>
-      <c r="S21" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V21" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.15</v>
-      </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.65</v>
+        <v>7.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.48</v>
+        <v>1.26</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.48</v>
+        <v>3.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.31</v>
+        <v>1.74</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.64</v>
+        <v>2.13</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.63</v>
+        <v>3.26</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45992.66666666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="M22" t="n">
         <v>3.85</v>
       </c>
       <c r="N22" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="O22" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="P22" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="Q22" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V22" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AB22" t="n">
         <v>2.35</v>
       </c>
-      <c r="R22" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="S22" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="V22" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="AA22" t="n">
+      <c r="AC22" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AG22" t="n">
         <v>1.27</v>
       </c>
-      <c r="AB22" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AH22" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45992.66666666666</v>
@@ -3167,13 +3167,13 @@
         <v>3.5</v>
       </c>
       <c r="O23" t="n">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="P23" t="n">
         <v>1.94</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="R23" t="n">
         <v>1.42</v>
@@ -3197,10 +3197,10 @@
         <v>1.03</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="AA23" t="n">
         <v>2.2</v>
@@ -3209,7 +3209,7 @@
         <v>1.6</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.72</v>
+        <v>3.75</v>
       </c>
       <c r="AD23" t="n">
         <v>1.22</v>
@@ -3221,10 +3221,10 @@
         <v>1.82</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.63</v>
+        <v>1.74</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45992.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="M24" t="n">
-        <v>2.96</v>
+        <v>2.85</v>
       </c>
       <c r="N24" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="O24" t="n">
-        <v>4.56</v>
+        <v>4.33</v>
       </c>
       <c r="P24" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="R24" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.49</v>
+        <v>2.35</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.5</v>
+        <v>2.69</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.03</v>
+        <v>2.37</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45992.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="M25" t="n">
-        <v>2.85</v>
+        <v>2.79</v>
       </c>
       <c r="N25" t="n">
-        <v>2.22</v>
+        <v>2.27</v>
       </c>
       <c r="O25" t="n">
-        <v>4.33</v>
+        <v>4.56</v>
       </c>
       <c r="P25" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="Q25" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.35</v>
+        <v>2.49</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="AB25" t="n">
         <v>1.41</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.37</v>
+        <v>2.03</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45992.6875</v>
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.35</v>
+        <v>1.51</v>
       </c>
       <c r="M26" t="n">
-        <v>4.15</v>
+        <v>4.4</v>
       </c>
       <c r="N26" t="n">
-        <v>7.3</v>
+        <v>7.13</v>
       </c>
       <c r="O26" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="P26" t="n">
         <v>2.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>7</v>
+        <v>6.3</v>
       </c>
       <c r="R26" t="n">
         <v>1.35</v>
       </c>
       <c r="S26" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="T26" t="n">
         <v>2.7</v>
       </c>
       <c r="U26" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="V26" t="n">
-        <v>6.95</v>
+        <v>6.75</v>
       </c>
       <c r="W26" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X26" t="n">
         <v>1.05</v>
       </c>
-      <c r="X26" t="n">
-        <v>1.03</v>
-      </c>
       <c r="Y26" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="AD26" t="n">
         <v>1.33</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>45992.69791666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="M27" t="n">
-        <v>3.53</v>
+        <v>3.25</v>
       </c>
       <c r="N27" t="n">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="O27" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="P27" t="n">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="Q27" t="n">
-        <v>5.44</v>
+        <v>4.65</v>
       </c>
       <c r="R27" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="S27" t="n">
-        <v>2.94</v>
+        <v>2.5</v>
       </c>
       <c r="T27" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="U27" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="V27" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="W27" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.37</v>
+        <v>2.9</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.38</v>
+        <v>4.1</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.22</v>
+        <v>1.79</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>45992.70833333334</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="M28" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="N28" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O28" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P28" t="n">
         <v>2.03</v>
       </c>
-      <c r="M28" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="N28" t="n">
-        <v>4.07</v>
-      </c>
-      <c r="O28" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P28" t="n">
-        <v>2</v>
-      </c>
       <c r="Q28" t="n">
-        <v>4</v>
+        <v>4.42</v>
       </c>
       <c r="R28" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="S28" t="n">
-        <v>2.79</v>
+        <v>2.92</v>
       </c>
       <c r="T28" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="U28" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V28" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="W28" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X28" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.68</v>
+        <v>1.87</v>
       </c>
       <c r="AC28" t="n">
-        <v>4</v>
+        <v>3.38</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.75</v>
+        <v>2.14</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45992.70833333334</v>
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="M29" t="n">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="N29" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="O29" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="P29" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="Q29" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="R29" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S29" t="n">
-        <v>3.21</v>
+        <v>3.04</v>
       </c>
       <c r="T29" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="U29" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="V29" t="n">
-        <v>6.55</v>
+        <v>6.15</v>
       </c>
       <c r="W29" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X29" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y29" t="n">
         <v>1.21</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.63</v>
+        <v>1.74</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.85</v>
+   